--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.4 → 50.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.4</t>
+  </si>
+  <si>
+    <t>50.0</t>
+  </si>
+  <si>
+    <t>56.5 → 48.8</t>
+  </si>
+  <si>
+    <t>56.5</t>
+  </si>
+  <si>
+    <t>48.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -368,14 +404,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -890,10 +927,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>620.65</v>
+        <v>615.2</v>
       </c>
       <c r="D2">
-        <v>0.02</v>
+        <v>-0.88</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +939,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-32.45</v>
+        <v>-33.04</v>
       </c>
       <c r="H2">
-        <v>18.93</v>
+        <v>17.89</v>
       </c>
       <c r="I2">
-        <v>-1.22</v>
+        <v>-1.13</v>
       </c>
       <c r="J2">
-        <v>-9.949999999999999</v>
+        <v>-10.41</v>
       </c>
       <c r="K2">
-        <v>-7.57</v>
+        <v>-7.96</v>
       </c>
       <c r="L2">
-        <v>-29.81</v>
+        <v>-28.7</v>
       </c>
       <c r="M2">
-        <v>-13.83</v>
+        <v>-13.62</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P2">
-        <v>620.0599999999999</v>
+        <v>618.65</v>
       </c>
       <c r="Q2">
-        <v>654.29</v>
+        <v>650.92</v>
       </c>
       <c r="R2">
-        <v>709.1799999999999</v>
+        <v>706.71</v>
       </c>
       <c r="S2">
-        <v>681.3</v>
+        <v>680.87</v>
       </c>
       <c r="T2">
-        <v>-8.9</v>
+        <v>-9.65</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,43 +993,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>33.14</v>
+        <v>31.73</v>
       </c>
       <c r="Z2">
-        <v>-24.43</v>
+        <v>-24.28</v>
       </c>
       <c r="AA2">
-        <v>-23.13</v>
+        <v>-23.36</v>
       </c>
       <c r="AB2">
-        <v>-1.3</v>
+        <v>-0.92</v>
       </c>
       <c r="AC2">
-        <v>48.2</v>
+        <v>45.19</v>
       </c>
       <c r="AD2">
-        <v>42.56</v>
+        <v>45.24</v>
       </c>
       <c r="AE2">
-        <v>25.51</v>
+        <v>25.35</v>
       </c>
       <c r="AF2">
-        <v>-79.12</v>
+        <v>10.01</v>
       </c>
       <c r="AG2">
-        <v>709.91</v>
+        <v>707.5</v>
       </c>
       <c r="AH2">
-        <v>598.67</v>
+        <v>594.35</v>
       </c>
       <c r="AI2">
-        <v>698.48</v>
+        <v>691.91</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>37.6</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1040,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>556.05</v>
+        <v>546.4</v>
       </c>
       <c r="D3">
-        <v>2.43</v>
+        <v>-1.74</v>
       </c>
       <c r="E3">
         <v>831.05</v>
@@ -1015,46 +1052,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-33.09</v>
+        <v>-34.25</v>
       </c>
       <c r="H3">
-        <v>8.390000000000001</v>
+        <v>6.51</v>
       </c>
       <c r="I3">
-        <v>-1.59</v>
+        <v>-2.99</v>
       </c>
       <c r="J3">
-        <v>-1.09</v>
+        <v>-3.36</v>
       </c>
       <c r="K3">
-        <v>-2.93</v>
+        <v>-2.99</v>
       </c>
       <c r="L3">
-        <v>-31.47</v>
+        <v>-32.59</v>
       </c>
       <c r="M3">
-        <v>-2.74</v>
+        <v>-2.09</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P3">
-        <v>554.83</v>
+        <v>551.46</v>
       </c>
       <c r="Q3">
-        <v>564.79</v>
+        <v>564.05</v>
       </c>
       <c r="R3">
-        <v>566.04</v>
+        <v>565.42</v>
       </c>
       <c r="S3">
-        <v>581.48</v>
+        <v>580.85</v>
       </c>
       <c r="T3">
-        <v>-4.37</v>
+        <v>-5.93</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1069,34 +1106,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>46.09</v>
+        <v>41.49</v>
       </c>
       <c r="Z3">
-        <v>-3.82</v>
+        <v>-4.53</v>
       </c>
       <c r="AA3">
-        <v>-1.99</v>
+        <v>-2.5</v>
       </c>
       <c r="AB3">
-        <v>-1.83</v>
+        <v>-2.03</v>
       </c>
       <c r="AC3">
-        <v>15.83</v>
+        <v>23.42</v>
       </c>
       <c r="AD3">
-        <v>21.31</v>
+        <v>19.08</v>
       </c>
       <c r="AE3">
-        <v>12.53</v>
+        <v>12.49</v>
       </c>
       <c r="AF3">
-        <v>100.91</v>
+        <v>-33.77</v>
       </c>
       <c r="AG3">
-        <v>584.1</v>
+        <v>585.01</v>
       </c>
       <c r="AH3">
-        <v>545.48</v>
+        <v>543.1</v>
       </c>
       <c r="AI3">
         <v>581</v>
@@ -1105,7 +1142,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>24.69</v>
+        <v>24.31</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1153,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>1033</v>
+        <v>1025</v>
       </c>
       <c r="D4">
-        <v>-1.62</v>
+        <v>-0.77</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1128,46 +1165,46 @@
         <v>979.9299999999999</v>
       </c>
       <c r="G4">
-        <v>-18.43</v>
+        <v>-19.06</v>
       </c>
       <c r="H4">
-        <v>5.42</v>
+        <v>4.6</v>
       </c>
       <c r="I4">
-        <v>-4.87</v>
+        <v>-3.14</v>
       </c>
       <c r="J4">
-        <v>-5.09</v>
+        <v>-4.09</v>
       </c>
       <c r="K4">
-        <v>0.27</v>
+        <v>-0.53</v>
       </c>
       <c r="L4">
-        <v>-15.83</v>
+        <v>-14.43</v>
       </c>
       <c r="M4">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="N4">
         <v>60</v>
       </c>
       <c r="O4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P4">
-        <v>1057.5</v>
+        <v>1050.86</v>
       </c>
       <c r="Q4">
-        <v>1064.14</v>
+        <v>1062.31</v>
       </c>
       <c r="R4">
-        <v>1045.89</v>
+        <v>1046.21</v>
       </c>
       <c r="S4">
-        <v>1103.2</v>
+        <v>1102.74</v>
       </c>
       <c r="T4">
-        <v>-6.36</v>
+        <v>-7.05</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1182,34 +1219,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>41.57</v>
+        <v>39.64</v>
       </c>
       <c r="Z4">
-        <v>0.83</v>
+        <v>-2.17</v>
       </c>
       <c r="AA4">
-        <v>5.03</v>
+        <v>3.59</v>
       </c>
       <c r="AB4">
-        <v>-4.2</v>
+        <v>-5.76</v>
       </c>
       <c r="AC4">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>27.29</v>
+        <v>16.93</v>
       </c>
       <c r="AE4">
-        <v>26.1</v>
+        <v>25.45</v>
       </c>
       <c r="AF4">
-        <v>147.51</v>
+        <v>36.79</v>
       </c>
       <c r="AG4">
-        <v>1087.72</v>
+        <v>1091.69</v>
       </c>
       <c r="AH4">
-        <v>1040.56</v>
+        <v>1032.93</v>
       </c>
       <c r="AI4">
         <v>1020.19</v>
@@ -1218,7 +1255,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>19.61</v>
+        <v>22.48</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1266,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1292.2</v>
+        <v>1289.8</v>
       </c>
       <c r="D5">
-        <v>-1.47</v>
+        <v>-0.19</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,46 +1278,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-8.85</v>
+        <v>-9.02</v>
       </c>
       <c r="H5">
-        <v>72.52</v>
+        <v>72.2</v>
       </c>
       <c r="I5">
-        <v>-3.36</v>
+        <v>-1.45</v>
       </c>
       <c r="J5">
-        <v>-8.85</v>
+        <v>-6.7</v>
       </c>
       <c r="K5">
-        <v>18.43</v>
+        <v>20.19</v>
       </c>
       <c r="L5">
-        <v>15.35</v>
+        <v>13.35</v>
       </c>
       <c r="M5">
-        <v>17.34</v>
+        <v>17.93</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="P5">
-        <v>1307.54</v>
+        <v>1303.74</v>
       </c>
       <c r="Q5">
-        <v>1330.27</v>
+        <v>1327.92</v>
       </c>
       <c r="R5">
-        <v>1212.7</v>
+        <v>1216.66</v>
       </c>
       <c r="S5">
-        <v>1055.94</v>
+        <v>1056.86</v>
       </c>
       <c r="T5">
-        <v>22.37</v>
+        <v>22.04</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1295,34 +1332,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>50.44</v>
+        <v>49.97</v>
       </c>
       <c r="Z5">
-        <v>20.48</v>
+        <v>17.14</v>
       </c>
       <c r="AA5">
-        <v>32.63</v>
+        <v>29.53</v>
       </c>
       <c r="AB5">
-        <v>-12.15</v>
+        <v>-12.39</v>
       </c>
       <c r="AC5">
         <v>2.36</v>
       </c>
       <c r="AD5">
-        <v>5.91</v>
+        <v>4.23</v>
       </c>
       <c r="AE5">
-        <v>42.08</v>
+        <v>41.2</v>
       </c>
       <c r="AF5">
-        <v>-85.7</v>
+        <v>-67.65000000000001</v>
       </c>
       <c r="AG5">
-        <v>1381.74</v>
+        <v>1382.35</v>
       </c>
       <c r="AH5">
-        <v>1278.79</v>
+        <v>1273.49</v>
       </c>
       <c r="AI5">
         <v>1225.87</v>
@@ -1331,7 +1368,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>18.21</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1379,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2108.4</v>
+        <v>2037.9</v>
       </c>
       <c r="D6">
-        <v>1.86</v>
+        <v>-3.34</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1391,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-9.130000000000001</v>
+        <v>-12.17</v>
       </c>
       <c r="H6">
-        <v>43.3</v>
+        <v>38.51</v>
       </c>
       <c r="I6">
-        <v>0.89</v>
+        <v>0.21</v>
       </c>
       <c r="J6">
-        <v>-1.15</v>
+        <v>-5.77</v>
       </c>
       <c r="K6">
-        <v>23.13</v>
+        <v>17.76</v>
       </c>
       <c r="L6">
-        <v>0.49</v>
+        <v>-3.64</v>
       </c>
       <c r="M6">
-        <v>6.37</v>
+        <v>5.68</v>
       </c>
       <c r="N6">
         <v>79</v>
       </c>
       <c r="O6">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="P6">
-        <v>2078.58</v>
+        <v>2079.44</v>
       </c>
       <c r="Q6">
-        <v>2095.43</v>
+        <v>2091.95</v>
       </c>
       <c r="R6">
-        <v>1939.43</v>
+        <v>1945.9</v>
       </c>
       <c r="S6">
-        <v>1887.92</v>
+        <v>1886.64</v>
       </c>
       <c r="T6">
-        <v>11.68</v>
+        <v>8.02</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1408,34 +1445,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>56.5</v>
+        <v>48.79</v>
       </c>
       <c r="Z6">
-        <v>33.94</v>
+        <v>27.46</v>
       </c>
       <c r="AA6">
-        <v>46.34</v>
+        <v>42.57</v>
       </c>
       <c r="AB6">
-        <v>-12.4</v>
+        <v>-15.1</v>
       </c>
       <c r="AC6">
-        <v>27.02</v>
+        <v>20.25</v>
       </c>
       <c r="AD6">
-        <v>21.54</v>
+        <v>22.81</v>
       </c>
       <c r="AE6">
-        <v>65.2</v>
+        <v>66.14</v>
       </c>
       <c r="AF6">
-        <v>-54.91</v>
+        <v>-25.46</v>
       </c>
       <c r="AG6">
-        <v>2166.59</v>
+        <v>2167.32</v>
       </c>
       <c r="AH6">
-        <v>2024.27</v>
+        <v>2016.59</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1444,7 +1481,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>19.64</v>
+        <v>19.88</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1622,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1605,719 +1642,774 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-9.949999999999999</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-10.41</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-3.41</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-1.09</v>
       </c>
-      <c r="E8" s="7">
-        <v>2.32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-3.36</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-3.44</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-5.09</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-4.09</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>7.57</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-8.85</v>
       </c>
-      <c r="E10" s="6">
-        <v>-16.42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-6.7</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>1.98</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-1.15</v>
       </c>
-      <c r="E11" s="6">
-        <v>-3.13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-5.77</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-4.62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-5.32</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-1.22</v>
       </c>
-      <c r="E12" s="7">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-1.13</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-2.51</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-1.59</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-2.99</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-1.91</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-4.87</v>
       </c>
-      <c r="E14" s="6">
-        <v>-2.96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-3.14</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-0.46</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-3.36</v>
       </c>
-      <c r="E15" s="6">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-1.45</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-1.7</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>0.89</v>
       </c>
-      <c r="E16" s="7">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>-29.45</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>-29.81</v>
       </c>
-      <c r="E17" s="6">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-28.7</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>-33.31</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>-31.47</v>
       </c>
-      <c r="E18" s="7">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-32.59</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-15.6</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-15.83</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-14.43</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>17.64</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>15.35</v>
       </c>
-      <c r="E20" s="6">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="6">
+        <v>13.35</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>0.49</v>
       </c>
-      <c r="E21" s="6">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>-3.64</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-4.13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>-10.62</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>-7.57</v>
       </c>
-      <c r="E22" s="7">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>-7.96</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>-6.83</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>-2.93</v>
       </c>
-      <c r="E23" s="7">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="6">
+        <v>-2.99</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5">
-        <v>4.38</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="6">
         <v>0.27</v>
       </c>
-      <c r="E24" s="6">
-        <v>-4.11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="6">
+        <v>-0.53</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>14.44</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="6">
         <v>18.43</v>
       </c>
-      <c r="E25" s="7">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="6">
+        <v>20.19</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>15.37</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="6">
         <v>23.13</v>
       </c>
-      <c r="E26" s="7">
-        <v>7.76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="6">
+        <v>17.76</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-5.37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5">
-        <v>-32.46</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="6">
         <v>-32.45</v>
       </c>
-      <c r="E27" s="7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D28" s="6">
+        <v>-33.04</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="5">
-        <v>-34.68</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C29" s="6">
         <v>-33.09</v>
       </c>
-      <c r="E28" s="7">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D29" s="6">
+        <v>-34.25</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="5">
-        <v>-17.09</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C30" s="6">
         <v>-18.43</v>
       </c>
-      <c r="E29" s="6">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-19.06</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="5">
-        <v>-7.49</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C31" s="6">
         <v>-8.85</v>
       </c>
-      <c r="E30" s="6">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="D31" s="6">
+        <v>-9.02</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="5">
-        <v>-10.79</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C32" s="6">
         <v>-9.130000000000001</v>
       </c>
-      <c r="E31" s="7">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="D32" s="6">
+        <v>-12.17</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="5">
-        <v>620.5</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C33" s="6">
         <v>620.65</v>
       </c>
-      <c r="E32" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="D33" s="6">
+        <v>615.2</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-5.45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="5">
-        <v>542.85</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C34" s="6">
         <v>556.05</v>
       </c>
-      <c r="E33" s="7">
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="D34" s="6">
+        <v>546.4</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-9.65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="5">
-        <v>1050</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C35" s="6">
         <v>1033</v>
       </c>
-      <c r="E34" s="6">
-        <v>-17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="D35" s="6">
+        <v>1025</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="5">
-        <v>1311.5</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C36" s="6">
         <v>1292.2</v>
       </c>
-      <c r="E35" s="6">
-        <v>-19.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="D36" s="6">
+        <v>1289.8</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="5">
-        <v>2070</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C37" s="6">
         <v>2108.4</v>
       </c>
-      <c r="E36" s="7">
-        <v>38.4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="D37" s="6">
+        <v>2037.9</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-70.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="5">
-        <v>33.07</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C38" s="6">
         <v>33.14</v>
       </c>
-      <c r="E37" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="D38" s="6">
+        <v>31.73</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="5">
-        <v>37.25</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="C39" s="6">
         <v>46.09</v>
       </c>
-      <c r="E38" s="7">
-        <v>8.84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="D39" s="6">
+        <v>41.49</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-4.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="5">
-        <v>46</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C40" s="6">
         <v>41.57</v>
       </c>
-      <c r="E39" s="6">
-        <v>-4.43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="D40" s="6">
+        <v>39.64</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="5">
-        <v>54.24</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="C41" s="6">
         <v>50.44</v>
       </c>
-      <c r="E40" s="6">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="D41" s="6">
+        <v>49.97</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="5">
-        <v>52.72</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C42" s="6">
         <v>56.5</v>
       </c>
-      <c r="E41" s="7">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="D42" s="6">
+        <v>48.79</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-7.71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>-74.97</v>
-      </c>
-      <c r="D42" s="5">
+      <c r="C43" s="6">
         <v>-79.12</v>
       </c>
-      <c r="E42" s="6">
-        <v>-4.15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="D43" s="6">
+        <v>10.01</v>
+      </c>
+      <c r="E43" s="8">
+        <v>89.13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="5">
-        <v>-11.94</v>
-      </c>
-      <c r="D43" s="5">
+      <c r="C44" s="6">
         <v>100.91</v>
       </c>
-      <c r="E43" s="7">
-        <v>112.85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="D44" s="6">
+        <v>-33.77</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-134.68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="5">
-        <v>429.21</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C45" s="6">
         <v>147.51</v>
       </c>
-      <c r="E44" s="6">
-        <v>-281.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="D45" s="6">
+        <v>36.79</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-110.72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="5">
-        <v>-81.44</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="C46" s="6">
         <v>-85.7</v>
       </c>
-      <c r="E45" s="6">
-        <v>-4.26</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="D46" s="6">
+        <v>-67.65000000000001</v>
+      </c>
+      <c r="E46" s="8">
+        <v>18.05</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B47" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="5">
-        <v>-39.88</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C47" s="6">
         <v>-54.91</v>
       </c>
-      <c r="E46" s="6">
-        <v>-15.03</v>
+      <c r="D47" s="6">
+        <v>-25.46</v>
+      </c>
+      <c r="E47" s="8">
+        <v>29.45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2337,60 +2429,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
+      <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>49.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>45.5</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>42.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="10">
-        <v>-5.2</v>
-      </c>
-      <c r="G2" s="10">
-        <v>6.3</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-6.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -2492,37 +2584,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1734</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.06370000000000001</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.0188</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0274</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1383</v>
+      <c r="A2" s="14">
+        <v>0.1793</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0568</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0184</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0209</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1362</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,43 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.4 → 50.0</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>56.5 → 48.8</t>
-  </si>
-  <si>
-    <t>56.5</t>
-  </si>
-  <si>
-    <t>48.8</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -404,15 +368,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -927,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>615.2</v>
+        <v>607.85</v>
       </c>
       <c r="D2">
-        <v>-0.88</v>
+        <v>-1.19</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -939,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-33.04</v>
+        <v>-33.84</v>
       </c>
       <c r="H2">
-        <v>17.89</v>
+        <v>16.48</v>
       </c>
       <c r="I2">
-        <v>-1.13</v>
+        <v>-1.41</v>
       </c>
       <c r="J2">
-        <v>-10.41</v>
+        <v>-10.93</v>
       </c>
       <c r="K2">
-        <v>-7.96</v>
+        <v>-7.51</v>
       </c>
       <c r="L2">
-        <v>-28.7</v>
+        <v>-28.52</v>
       </c>
       <c r="M2">
-        <v>-13.62</v>
+        <v>-14.69</v>
       </c>
       <c r="N2">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="O2">
         <v>15</v>
       </c>
       <c r="P2">
-        <v>618.65</v>
+        <v>616.91</v>
       </c>
       <c r="Q2">
-        <v>650.92</v>
+        <v>647.1799999999999</v>
       </c>
       <c r="R2">
-        <v>706.71</v>
+        <v>703.11</v>
       </c>
       <c r="S2">
-        <v>680.87</v>
+        <v>680.47</v>
       </c>
       <c r="T2">
-        <v>-9.65</v>
+        <v>-10.67</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -993,43 +956,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>31.73</v>
+        <v>29.88</v>
       </c>
       <c r="Z2">
-        <v>-24.28</v>
+        <v>-24.48</v>
       </c>
       <c r="AA2">
-        <v>-23.36</v>
+        <v>-23.58</v>
       </c>
       <c r="AB2">
-        <v>-0.92</v>
+        <v>-0.89</v>
       </c>
       <c r="AC2">
-        <v>45.19</v>
+        <v>37.19</v>
       </c>
       <c r="AD2">
-        <v>45.24</v>
+        <v>43.53</v>
       </c>
       <c r="AE2">
-        <v>25.35</v>
+        <v>24.26</v>
       </c>
       <c r="AF2">
-        <v>10.01</v>
+        <v>-42.84</v>
       </c>
       <c r="AG2">
-        <v>707.5</v>
+        <v>704.8</v>
       </c>
       <c r="AH2">
-        <v>594.35</v>
+        <v>589.5599999999999</v>
       </c>
       <c r="AI2">
-        <v>691.91</v>
+        <v>683.8</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>39.83</v>
+        <v>41.76</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1040,58 +1003,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>546.4</v>
+        <v>552.25</v>
       </c>
       <c r="D3">
-        <v>-1.74</v>
+        <v>1.07</v>
       </c>
       <c r="E3">
-        <v>831.05</v>
+        <v>816.05</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-34.25</v>
+        <v>-32.33</v>
       </c>
       <c r="H3">
-        <v>6.51</v>
+        <v>7.65</v>
       </c>
       <c r="I3">
-        <v>-2.99</v>
+        <v>-2.51</v>
       </c>
       <c r="J3">
-        <v>-3.36</v>
+        <v>-1.58</v>
       </c>
       <c r="K3">
-        <v>-2.99</v>
+        <v>-2.13</v>
       </c>
       <c r="L3">
-        <v>-32.59</v>
+        <v>-33.55</v>
       </c>
       <c r="M3">
-        <v>-2.09</v>
+        <v>-2.37</v>
       </c>
       <c r="N3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P3">
-        <v>551.46</v>
+        <v>548.62</v>
       </c>
       <c r="Q3">
-        <v>564.05</v>
+        <v>562.85</v>
       </c>
       <c r="R3">
-        <v>565.42</v>
+        <v>564.8099999999999</v>
       </c>
       <c r="S3">
-        <v>580.85</v>
+        <v>580.3099999999999</v>
       </c>
       <c r="T3">
-        <v>-5.93</v>
+        <v>-4.83</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1106,34 +1069,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.49</v>
+        <v>45.07</v>
       </c>
       <c r="Z3">
-        <v>-4.53</v>
+        <v>-4.57</v>
       </c>
       <c r="AA3">
-        <v>-2.5</v>
+        <v>-2.91</v>
       </c>
       <c r="AB3">
-        <v>-2.03</v>
+        <v>-1.66</v>
       </c>
       <c r="AC3">
-        <v>23.42</v>
+        <v>37.43</v>
       </c>
       <c r="AD3">
-        <v>19.08</v>
+        <v>25.56</v>
       </c>
       <c r="AE3">
-        <v>12.49</v>
+        <v>12.22</v>
       </c>
       <c r="AF3">
-        <v>-33.77</v>
+        <v>-24.13</v>
       </c>
       <c r="AG3">
-        <v>585.01</v>
+        <v>583.59</v>
       </c>
       <c r="AH3">
-        <v>543.1</v>
+        <v>542.11</v>
       </c>
       <c r="AI3">
         <v>581</v>
@@ -1142,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>24.31</v>
+        <v>23.98</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,58 +1116,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>1025</v>
+        <v>910</v>
       </c>
       <c r="D4">
-        <v>-0.77</v>
+        <v>-11.22</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
       </c>
       <c r="F4">
-        <v>979.9299999999999</v>
+        <v>910</v>
       </c>
       <c r="G4">
-        <v>-19.06</v>
+        <v>-28.14</v>
       </c>
       <c r="H4">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-3.14</v>
+        <v>-14.87</v>
       </c>
       <c r="J4">
-        <v>-4.09</v>
+        <v>-14.28</v>
       </c>
       <c r="K4">
-        <v>-0.53</v>
+        <v>-11.93</v>
       </c>
       <c r="L4">
-        <v>-14.43</v>
+        <v>-22.97</v>
       </c>
       <c r="M4">
-        <v>1.84</v>
+        <v>-0.78</v>
       </c>
       <c r="N4">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="O4">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="P4">
-        <v>1050.86</v>
+        <v>1019.06</v>
       </c>
       <c r="Q4">
-        <v>1062.31</v>
+        <v>1055.18</v>
       </c>
       <c r="R4">
-        <v>1046.21</v>
+        <v>1044.42</v>
       </c>
       <c r="S4">
-        <v>1102.74</v>
+        <v>1101.7</v>
       </c>
       <c r="T4">
-        <v>-7.05</v>
+        <v>-17.4</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1219,43 +1182,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>39.64</v>
+        <v>23.06</v>
       </c>
       <c r="Z4">
-        <v>-2.17</v>
+        <v>-13.66</v>
       </c>
       <c r="AA4">
-        <v>3.59</v>
+        <v>0.14</v>
       </c>
       <c r="AB4">
-        <v>-5.76</v>
+        <v>-13.8</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>16.93</v>
+        <v>6.57</v>
       </c>
       <c r="AE4">
-        <v>25.45</v>
+        <v>32.01</v>
       </c>
       <c r="AF4">
-        <v>36.79</v>
+        <v>3144.57</v>
       </c>
       <c r="AG4">
-        <v>1091.69</v>
+        <v>1129.43</v>
       </c>
       <c r="AH4">
-        <v>1032.93</v>
+        <v>980.92</v>
       </c>
       <c r="AI4">
-        <v>1020.19</v>
+        <v>1025.82</v>
       </c>
       <c r="AJ4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK4">
-        <v>22.48</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1289.8</v>
+        <v>1235.2</v>
       </c>
       <c r="D5">
-        <v>-0.19</v>
+        <v>-4.23</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1278,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-9.02</v>
+        <v>-12.87</v>
       </c>
       <c r="H5">
-        <v>72.2</v>
+        <v>64.91</v>
       </c>
       <c r="I5">
-        <v>-1.45</v>
+        <v>-6.45</v>
       </c>
       <c r="J5">
-        <v>-6.7</v>
+        <v>-7.59</v>
       </c>
       <c r="K5">
-        <v>20.19</v>
+        <v>7.12</v>
       </c>
       <c r="L5">
-        <v>13.35</v>
+        <v>8.56</v>
       </c>
       <c r="M5">
-        <v>17.93</v>
+        <v>16.89</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>1303.74</v>
+        <v>1286.7</v>
       </c>
       <c r="Q5">
-        <v>1327.92</v>
+        <v>1320.71</v>
       </c>
       <c r="R5">
-        <v>1216.66</v>
+        <v>1220.17</v>
       </c>
       <c r="S5">
-        <v>1056.86</v>
+        <v>1057.56</v>
       </c>
       <c r="T5">
-        <v>22.04</v>
+        <v>16.8</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1332,34 +1295,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.97</v>
+        <v>40.71</v>
       </c>
       <c r="Z5">
-        <v>17.14</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="AA5">
-        <v>29.53</v>
+        <v>25.62</v>
       </c>
       <c r="AB5">
-        <v>-12.39</v>
+        <v>-15.65</v>
       </c>
       <c r="AC5">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>4.23</v>
+        <v>1.58</v>
       </c>
       <c r="AE5">
-        <v>41.2</v>
+        <v>44.39</v>
       </c>
       <c r="AF5">
-        <v>-67.65000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="AG5">
-        <v>1382.35</v>
+        <v>1383.92</v>
       </c>
       <c r="AH5">
-        <v>1273.49</v>
+        <v>1257.5</v>
       </c>
       <c r="AI5">
         <v>1225.87</v>
@@ -1368,7 +1331,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>18.51</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1379,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2037.9</v>
+        <v>2015</v>
       </c>
       <c r="D6">
-        <v>-3.34</v>
+        <v>-1.12</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1391,25 +1354,25 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-12.17</v>
+        <v>-13.16</v>
       </c>
       <c r="H6">
-        <v>38.51</v>
+        <v>36.95</v>
       </c>
       <c r="I6">
-        <v>0.21</v>
+        <v>-4</v>
       </c>
       <c r="J6">
-        <v>-5.77</v>
+        <v>-4.38</v>
       </c>
       <c r="K6">
-        <v>17.76</v>
+        <v>16.24</v>
       </c>
       <c r="L6">
-        <v>-3.64</v>
+        <v>-2.26</v>
       </c>
       <c r="M6">
-        <v>5.68</v>
+        <v>5.29</v>
       </c>
       <c r="N6">
         <v>79</v>
@@ -1418,19 +1381,19 @@
         <v>62</v>
       </c>
       <c r="P6">
-        <v>2079.44</v>
+        <v>2062.64</v>
       </c>
       <c r="Q6">
-        <v>2091.95</v>
+        <v>2087.48</v>
       </c>
       <c r="R6">
-        <v>1945.9</v>
+        <v>1951.79</v>
       </c>
       <c r="S6">
-        <v>1886.64</v>
+        <v>1885.32</v>
       </c>
       <c r="T6">
-        <v>8.02</v>
+        <v>6.88</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1445,34 +1408,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>48.79</v>
+        <v>46.56</v>
       </c>
       <c r="Z6">
-        <v>27.46</v>
+        <v>20.25</v>
       </c>
       <c r="AA6">
-        <v>42.57</v>
+        <v>38.1</v>
       </c>
       <c r="AB6">
-        <v>-15.1</v>
+        <v>-17.86</v>
       </c>
       <c r="AC6">
-        <v>20.25</v>
+        <v>15.56</v>
       </c>
       <c r="AD6">
-        <v>22.81</v>
+        <v>20.94</v>
       </c>
       <c r="AE6">
-        <v>66.14</v>
+        <v>65.55</v>
       </c>
       <c r="AF6">
-        <v>-25.46</v>
+        <v>-35.25</v>
       </c>
       <c r="AG6">
-        <v>2167.32</v>
+        <v>2170</v>
       </c>
       <c r="AH6">
-        <v>2016.59</v>
+        <v>2004.97</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1481,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>19.88</v>
+        <v>22.21</v>
       </c>
     </row>
   </sheetData>
@@ -1622,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1642,774 +1605,770 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-10.41</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-10.93</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-3.36</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-1.58</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-4.09</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-14.28</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-10.19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-6.7</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-7.59</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-5.77</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-4.38</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-10.41</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-1.13</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-1.41</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-1.09</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-3.36</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-2.99</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-2.51</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-5.09</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-4.09</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-3.14</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-14.87</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-11.73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-8.85</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-6.7</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-1.45</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-6.45</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-1.15</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-5.77</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-4.62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-4</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-4.21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-1.22</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-1.13</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-28.7</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-28.52</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-1.59</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-32.59</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-33.55</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-14.43</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-22.97</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-8.539999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>13.35</v>
+      </c>
+      <c r="D20" s="5">
+        <v>8.56</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-4.79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-3.64</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-2.26</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-7.96</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-7.51</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
         <v>-2.99</v>
       </c>
-      <c r="E14" s="7">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D23" s="5">
+        <v>-2.13</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-4.87</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-3.14</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-0.53</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-11.93</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-11.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-3.36</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.45</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>20.19</v>
+      </c>
+      <c r="D25" s="5">
+        <v>7.12</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-13.07</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.89</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.21</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>17.76</v>
+      </c>
+      <c r="D26" s="5">
+        <v>16.24</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-29.81</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-28.7</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-33.04</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-33.84</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-31.47</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-32.59</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-34.25</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-32.33</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-15.83</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-14.43</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-19.06</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-28.14</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-9.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>15.35</v>
-      </c>
-      <c r="D21" s="6">
-        <v>13.35</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-9.02</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-12.87</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.49</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-3.64</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-4.13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-12.17</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-13.16</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-7.57</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-7.96</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>615.2</v>
+      </c>
+      <c r="D32" s="5">
+        <v>607.85</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-7.35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-2.93</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-2.99</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>546.4</v>
+      </c>
+      <c r="D33" s="5">
+        <v>552.25</v>
+      </c>
+      <c r="E33" s="7">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.27</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-0.53</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1025</v>
+      </c>
+      <c r="D34" s="5">
+        <v>910</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>18.43</v>
-      </c>
-      <c r="D26" s="6">
-        <v>20.19</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1289.8</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1235.2</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-54.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>23.13</v>
-      </c>
-      <c r="D27" s="6">
-        <v>17.76</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-5.37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2037.9</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2015</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-22.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-32.45</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-33.04</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="5">
+        <v>21</v>
+      </c>
+      <c r="D37" s="5">
+        <v>40</v>
+      </c>
+      <c r="E37" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-33.09</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-34.25</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="5">
+        <v>40</v>
+      </c>
+      <c r="D38" s="5">
+        <v>60</v>
+      </c>
+      <c r="E38" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-18.43</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-19.06</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="5">
+        <v>60</v>
+      </c>
+      <c r="D39" s="5">
+        <v>21</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>31.73</v>
+      </c>
+      <c r="D40" s="5">
+        <v>29.88</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>41.49</v>
+      </c>
+      <c r="D41" s="5">
+        <v>45.07</v>
+      </c>
+      <c r="E41" s="7">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="5">
+        <v>39.64</v>
+      </c>
+      <c r="D42" s="5">
+        <v>23.06</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-16.58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-8.85</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-9.02</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>49.97</v>
+      </c>
+      <c r="D43" s="5">
+        <v>40.71</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-9.26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-9.130000000000001</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-12.17</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-3.04</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5">
+        <v>48.79</v>
+      </c>
+      <c r="D44" s="5">
+        <v>46.56</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>620.65</v>
-      </c>
-      <c r="D33" s="6">
-        <v>615.2</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-5.45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>10.01</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-42.84</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-52.85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>556.05</v>
-      </c>
-      <c r="D34" s="6">
-        <v>546.4</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-9.65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-33.77</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-24.13</v>
+      </c>
+      <c r="E46" s="7">
+        <v>9.640000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1033</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1025</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
+        <v>36.79</v>
+      </c>
+      <c r="D47" s="5">
+        <v>3144.57</v>
+      </c>
+      <c r="E47" s="7">
+        <v>3107.78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1292.2</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1289.8</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-67.65000000000001</v>
+      </c>
+      <c r="D48" s="5">
+        <v>9.73</v>
+      </c>
+      <c r="E48" s="7">
+        <v>77.38</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>2108.4</v>
-      </c>
-      <c r="D37" s="6">
-        <v>2037.9</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-70.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>33.14</v>
-      </c>
-      <c r="D38" s="6">
-        <v>31.73</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>46.09</v>
-      </c>
-      <c r="D39" s="6">
-        <v>41.49</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-4.6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>41.57</v>
-      </c>
-      <c r="D40" s="6">
-        <v>39.64</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>50.44</v>
-      </c>
-      <c r="D41" s="6">
-        <v>49.97</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>56.5</v>
-      </c>
-      <c r="D42" s="6">
-        <v>48.79</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-7.71</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="B49" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="6">
-        <v>-79.12</v>
-      </c>
-      <c r="D43" s="6">
-        <v>10.01</v>
-      </c>
-      <c r="E43" s="8">
-        <v>89.13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>100.91</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-33.77</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-134.68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>147.51</v>
-      </c>
-      <c r="D45" s="6">
-        <v>36.79</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-110.72</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-85.7</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-67.65000000000001</v>
-      </c>
-      <c r="E46" s="8">
-        <v>18.05</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-54.91</v>
-      </c>
-      <c r="D47" s="6">
+      <c r="C49" s="5">
         <v>-25.46</v>
       </c>
-      <c r="E47" s="8">
-        <v>29.45</v>
+      <c r="D49" s="5">
+        <v>-35.25</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-9.789999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2429,60 +2388,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>73</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>49.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>42.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>37.1</v>
+      </c>
+      <c r="E2" s="10">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>5.3</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-7.8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>40</v>
       </c>
     </row>
@@ -2584,37 +2543,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1793</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0568</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0184</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0209</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1362</v>
+      <c r="A2" s="13">
+        <v>0.1689</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0529</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0237</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1469</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,46 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>45.1 → 50.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>45.1</t>
+  </si>
+  <si>
+    <t>50.6</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>23.1 → 30.4</t>
+  </si>
+  <si>
+    <t>23.1</t>
+  </si>
+  <si>
+    <t>30.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,17 +407,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -890,10 +930,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>607.85</v>
+        <v>602.05</v>
       </c>
       <c r="D2">
-        <v>-1.19</v>
+        <v>-0.95</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +942,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-33.84</v>
+        <v>-34.47</v>
       </c>
       <c r="H2">
-        <v>16.48</v>
+        <v>15.37</v>
       </c>
       <c r="I2">
-        <v>-1.41</v>
+        <v>-2.95</v>
       </c>
       <c r="J2">
-        <v>-10.93</v>
+        <v>-11.81</v>
       </c>
       <c r="K2">
-        <v>-7.51</v>
+        <v>-10.91</v>
       </c>
       <c r="L2">
-        <v>-28.52</v>
+        <v>-27.51</v>
       </c>
       <c r="M2">
-        <v>-14.69</v>
+        <v>-14.48</v>
       </c>
       <c r="N2">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="O2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P2">
-        <v>616.91</v>
+        <v>613.25</v>
       </c>
       <c r="Q2">
-        <v>647.1799999999999</v>
+        <v>642.26</v>
       </c>
       <c r="R2">
-        <v>703.11</v>
+        <v>699.5</v>
       </c>
       <c r="S2">
-        <v>680.47</v>
+        <v>680.14</v>
       </c>
       <c r="T2">
-        <v>-10.67</v>
+        <v>-11.48</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,43 +996,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>29.88</v>
+        <v>28.46</v>
       </c>
       <c r="Z2">
-        <v>-24.48</v>
+        <v>-24.81</v>
       </c>
       <c r="AA2">
-        <v>-23.58</v>
+        <v>-23.83</v>
       </c>
       <c r="AB2">
-        <v>-0.89</v>
+        <v>-0.98</v>
       </c>
       <c r="AC2">
-        <v>37.19</v>
+        <v>25.45</v>
       </c>
       <c r="AD2">
-        <v>43.53</v>
+        <v>35.94</v>
       </c>
       <c r="AE2">
-        <v>24.26</v>
+        <v>24.48</v>
       </c>
       <c r="AF2">
-        <v>-42.84</v>
+        <v>32.28</v>
       </c>
       <c r="AG2">
-        <v>704.8</v>
+        <v>697.49</v>
       </c>
       <c r="AH2">
-        <v>589.5599999999999</v>
+        <v>587.04</v>
       </c>
       <c r="AI2">
-        <v>683.8</v>
+        <v>676.71</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>41.76</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1043,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>552.25</v>
+        <v>562.2</v>
       </c>
       <c r="D3">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="E3">
         <v>816.05</v>
@@ -1015,46 +1055,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-32.33</v>
+        <v>-31.11</v>
       </c>
       <c r="H3">
-        <v>7.65</v>
+        <v>9.59</v>
       </c>
       <c r="I3">
-        <v>-2.51</v>
+        <v>3.05</v>
       </c>
       <c r="J3">
-        <v>-1.58</v>
+        <v>-2.46</v>
       </c>
       <c r="K3">
-        <v>-2.13</v>
+        <v>-1.33</v>
       </c>
       <c r="L3">
-        <v>-33.55</v>
+        <v>-30.76</v>
       </c>
       <c r="M3">
-        <v>-2.37</v>
+        <v>-1.77</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P3">
-        <v>548.62</v>
+        <v>551.95</v>
       </c>
       <c r="Q3">
-        <v>562.85</v>
+        <v>562.37</v>
       </c>
       <c r="R3">
-        <v>564.8099999999999</v>
+        <v>564.52</v>
       </c>
       <c r="S3">
-        <v>580.3099999999999</v>
+        <v>579.79</v>
       </c>
       <c r="T3">
-        <v>-4.83</v>
+        <v>-3.03</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1069,34 +1109,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>45.07</v>
+        <v>50.6</v>
       </c>
       <c r="Z3">
-        <v>-4.57</v>
+        <v>-3.75</v>
       </c>
       <c r="AA3">
-        <v>-2.91</v>
+        <v>-3.08</v>
       </c>
       <c r="AB3">
-        <v>-1.66</v>
+        <v>-0.67</v>
       </c>
       <c r="AC3">
-        <v>37.43</v>
+        <v>45.52</v>
       </c>
       <c r="AD3">
-        <v>25.56</v>
+        <v>35.46</v>
       </c>
       <c r="AE3">
-        <v>12.22</v>
+        <v>12.84</v>
       </c>
       <c r="AF3">
-        <v>-24.13</v>
+        <v>121.77</v>
       </c>
       <c r="AG3">
-        <v>583.59</v>
+        <v>582.67</v>
       </c>
       <c r="AH3">
-        <v>542.11</v>
+        <v>542.0599999999999</v>
       </c>
       <c r="AI3">
         <v>581</v>
@@ -1105,7 +1145,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>23.98</v>
+        <v>23.03</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1156,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>910</v>
+        <v>936.9</v>
       </c>
       <c r="D4">
-        <v>-11.22</v>
+        <v>2.96</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1128,46 +1168,46 @@
         <v>910</v>
       </c>
       <c r="G4">
-        <v>-28.14</v>
+        <v>-26.02</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="I4">
-        <v>-14.87</v>
+        <v>-13.03</v>
       </c>
       <c r="J4">
-        <v>-14.28</v>
+        <v>-11</v>
       </c>
       <c r="K4">
-        <v>-11.93</v>
+        <v>-9.84</v>
       </c>
       <c r="L4">
-        <v>-22.97</v>
+        <v>-21.82</v>
       </c>
       <c r="M4">
-        <v>-0.78</v>
+        <v>-0.05</v>
       </c>
       <c r="N4">
+        <v>40</v>
+      </c>
+      <c r="O4">
         <v>21</v>
       </c>
-      <c r="O4">
-        <v>14</v>
-      </c>
       <c r="P4">
-        <v>1019.06</v>
+        <v>990.98</v>
       </c>
       <c r="Q4">
-        <v>1055.18</v>
+        <v>1049.14</v>
       </c>
       <c r="R4">
-        <v>1044.42</v>
+        <v>1043.43</v>
       </c>
       <c r="S4">
-        <v>1101.7</v>
+        <v>1100.81</v>
       </c>
       <c r="T4">
-        <v>-17.4</v>
+        <v>-14.89</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1182,43 +1222,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>23.06</v>
+        <v>30.39</v>
       </c>
       <c r="Z4">
-        <v>-13.66</v>
+        <v>-20.36</v>
       </c>
       <c r="AA4">
-        <v>0.14</v>
+        <v>-3.96</v>
       </c>
       <c r="AB4">
-        <v>-13.8</v>
+        <v>-16.4</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>6.83</v>
       </c>
       <c r="AD4">
-        <v>6.57</v>
+        <v>2.28</v>
       </c>
       <c r="AE4">
-        <v>32.01</v>
+        <v>32.06</v>
       </c>
       <c r="AF4">
-        <v>3144.57</v>
+        <v>292.76</v>
       </c>
       <c r="AG4">
-        <v>1129.43</v>
+        <v>1140.26</v>
       </c>
       <c r="AH4">
-        <v>980.92</v>
+        <v>958.01</v>
       </c>
       <c r="AI4">
-        <v>1025.82</v>
+        <v>1018.82</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>29.6</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1269,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1235.2</v>
+        <v>1255.6</v>
       </c>
       <c r="D5">
-        <v>-4.23</v>
+        <v>1.65</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,25 +1281,25 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-12.87</v>
+        <v>-11.43</v>
       </c>
       <c r="H5">
-        <v>64.91</v>
+        <v>67.64</v>
       </c>
       <c r="I5">
-        <v>-6.45</v>
+        <v>-3.77</v>
       </c>
       <c r="J5">
-        <v>-7.59</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="K5">
-        <v>7.12</v>
+        <v>10.62</v>
       </c>
       <c r="L5">
-        <v>8.56</v>
+        <v>13.26</v>
       </c>
       <c r="M5">
-        <v>16.89</v>
+        <v>17.43</v>
       </c>
       <c r="N5">
         <v>99</v>
@@ -1268,19 +1308,19 @@
         <v>64</v>
       </c>
       <c r="P5">
-        <v>1286.7</v>
+        <v>1276.86</v>
       </c>
       <c r="Q5">
-        <v>1320.71</v>
+        <v>1316.52</v>
       </c>
       <c r="R5">
-        <v>1220.17</v>
+        <v>1224.19</v>
       </c>
       <c r="S5">
-        <v>1057.56</v>
+        <v>1058.4</v>
       </c>
       <c r="T5">
-        <v>16.8</v>
+        <v>18.63</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1295,34 +1335,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>40.71</v>
+        <v>44.83</v>
       </c>
       <c r="Z5">
-        <v>9.970000000000001</v>
+        <v>5.87</v>
       </c>
       <c r="AA5">
-        <v>25.62</v>
+        <v>21.67</v>
       </c>
       <c r="AB5">
-        <v>-15.65</v>
+        <v>-15.8</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="AD5">
-        <v>1.58</v>
+        <v>3.08</v>
       </c>
       <c r="AE5">
-        <v>44.39</v>
+        <v>46.56</v>
       </c>
       <c r="AF5">
-        <v>9.73</v>
+        <v>369.95</v>
       </c>
       <c r="AG5">
-        <v>1383.92</v>
+        <v>1385.38</v>
       </c>
       <c r="AH5">
-        <v>1257.5</v>
+        <v>1247.67</v>
       </c>
       <c r="AI5">
         <v>1225.87</v>
@@ -1331,7 +1371,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>23.4</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1382,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2015</v>
+        <v>2028</v>
       </c>
       <c r="D6">
-        <v>-1.12</v>
+        <v>0.65</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1394,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-13.16</v>
+        <v>-12.6</v>
       </c>
       <c r="H6">
-        <v>36.95</v>
+        <v>37.84</v>
       </c>
       <c r="I6">
-        <v>-4</v>
+        <v>-2.59</v>
       </c>
       <c r="J6">
-        <v>-4.38</v>
+        <v>-3.63</v>
       </c>
       <c r="K6">
-        <v>16.24</v>
+        <v>18.31</v>
       </c>
       <c r="L6">
-        <v>-2.26</v>
+        <v>-0.77</v>
       </c>
       <c r="M6">
-        <v>5.29</v>
+        <v>5.57</v>
       </c>
       <c r="N6">
         <v>79</v>
       </c>
       <c r="O6">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="P6">
-        <v>2062.64</v>
+        <v>2051.86</v>
       </c>
       <c r="Q6">
-        <v>2087.48</v>
+        <v>2084.37</v>
       </c>
       <c r="R6">
-        <v>1951.79</v>
+        <v>1958.25</v>
       </c>
       <c r="S6">
-        <v>1885.32</v>
+        <v>1884.02</v>
       </c>
       <c r="T6">
-        <v>6.88</v>
+        <v>7.64</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1408,34 +1448,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>46.56</v>
+        <v>48.01</v>
       </c>
       <c r="Z6">
-        <v>20.25</v>
+        <v>15.4</v>
       </c>
       <c r="AA6">
-        <v>38.1</v>
+        <v>33.56</v>
       </c>
       <c r="AB6">
-        <v>-17.86</v>
+        <v>-18.16</v>
       </c>
       <c r="AC6">
-        <v>15.56</v>
+        <v>2.72</v>
       </c>
       <c r="AD6">
-        <v>20.94</v>
+        <v>12.85</v>
       </c>
       <c r="AE6">
-        <v>65.55</v>
+        <v>63.66</v>
       </c>
       <c r="AF6">
-        <v>-35.25</v>
+        <v>-55.54</v>
       </c>
       <c r="AG6">
-        <v>2170</v>
+        <v>2171.04</v>
       </c>
       <c r="AH6">
-        <v>2004.97</v>
+        <v>1997.7</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1444,7 +1484,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>22.21</v>
+        <v>24.22</v>
       </c>
     </row>
   </sheetData>
@@ -1605,770 +1645,808 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-10.41</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-10.93</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-11.81</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-3.36</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-1.58</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-2.46</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-4.09</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-14.28</v>
       </c>
-      <c r="E9" s="6">
-        <v>-10.19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-11</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-6.7</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-7.59</v>
       </c>
-      <c r="E10" s="6">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-5.77</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-4.38</v>
       </c>
-      <c r="E11" s="7">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-3.63</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-1.13</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-1.41</v>
       </c>
-      <c r="E12" s="6">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-2.95</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-2.99</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-2.51</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>3.05</v>
+      </c>
+      <c r="E14" s="8">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-3.14</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-14.87</v>
       </c>
-      <c r="E14" s="6">
-        <v>-11.73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-13.03</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-1.45</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-6.45</v>
       </c>
-      <c r="E15" s="6">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-3.77</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>0.21</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-4</v>
       </c>
-      <c r="E16" s="6">
-        <v>-4.21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-2.59</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>-28.7</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>-28.52</v>
       </c>
-      <c r="E17" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-27.51</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>-32.59</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>-33.55</v>
       </c>
-      <c r="E18" s="6">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-30.76</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-14.43</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-22.97</v>
       </c>
-      <c r="E19" s="6">
-        <v>-8.539999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-21.82</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>13.35</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>8.56</v>
       </c>
-      <c r="E20" s="6">
-        <v>-4.79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="6">
+        <v>13.26</v>
+      </c>
+      <c r="E21" s="8">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-3.64</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>-2.26</v>
       </c>
-      <c r="E21" s="7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>-0.77</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>-7.96</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>-7.51</v>
       </c>
-      <c r="E22" s="7">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>-10.91</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>-2.99</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>-2.13</v>
       </c>
-      <c r="E23" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="6">
+        <v>-1.33</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5">
-        <v>-0.53</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="6">
         <v>-11.93</v>
       </c>
-      <c r="E24" s="6">
-        <v>-11.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="6">
+        <v>-9.84</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>20.19</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="6">
         <v>7.12</v>
       </c>
-      <c r="E25" s="6">
-        <v>-13.07</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="6">
+        <v>10.62</v>
+      </c>
+      <c r="E26" s="8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>17.76</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="6">
         <v>16.24</v>
       </c>
-      <c r="E26" s="6">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="6">
+        <v>18.31</v>
+      </c>
+      <c r="E27" s="8">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5">
-        <v>-33.04</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="6">
         <v>-33.84</v>
       </c>
-      <c r="E27" s="6">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D28" s="6">
+        <v>-34.47</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="5">
-        <v>-34.25</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C29" s="6">
         <v>-32.33</v>
       </c>
-      <c r="E28" s="7">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D29" s="6">
+        <v>-31.11</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="5">
-        <v>-19.06</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C30" s="6">
         <v>-28.14</v>
       </c>
-      <c r="E29" s="6">
-        <v>-9.08</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-26.02</v>
+      </c>
+      <c r="E30" s="8">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="5">
-        <v>-9.02</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C31" s="6">
         <v>-12.87</v>
       </c>
-      <c r="E30" s="6">
-        <v>-3.85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="D31" s="6">
+        <v>-11.43</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="5">
-        <v>-12.17</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C32" s="6">
         <v>-13.16</v>
       </c>
-      <c r="E31" s="6">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="D32" s="6">
+        <v>-12.6</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="5">
-        <v>615.2</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C33" s="6">
         <v>607.85</v>
       </c>
-      <c r="E32" s="6">
-        <v>-7.35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="D33" s="6">
+        <v>602.05</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-5.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="5">
-        <v>546.4</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C34" s="6">
         <v>552.25</v>
       </c>
-      <c r="E33" s="7">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="D34" s="6">
+        <v>562.2</v>
+      </c>
+      <c r="E34" s="8">
+        <v>9.949999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="5">
-        <v>1025</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C35" s="6">
         <v>910</v>
       </c>
-      <c r="E34" s="6">
-        <v>-115</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="D35" s="6">
+        <v>936.9</v>
+      </c>
+      <c r="E35" s="8">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="5">
-        <v>1289.8</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C36" s="6">
         <v>1235.2</v>
       </c>
-      <c r="E35" s="6">
-        <v>-54.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="D36" s="6">
+        <v>1255.6</v>
+      </c>
+      <c r="E36" s="8">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="5">
-        <v>2037.9</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C37" s="6">
         <v>2015</v>
       </c>
-      <c r="E36" s="6">
-        <v>-22.9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="D37" s="6">
+        <v>2028</v>
+      </c>
+      <c r="E37" s="8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C38" s="6">
+        <v>40</v>
+      </c>
+      <c r="D38" s="6">
         <v>21</v>
       </c>
-      <c r="D37" s="5">
+      <c r="E38" s="7">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="6">
+        <v>21</v>
+      </c>
+      <c r="D39" s="6">
         <v>40</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E39" s="8">
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>29.88</v>
+      </c>
+      <c r="D40" s="6">
+        <v>28.46</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="5">
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>45.07</v>
+      </c>
+      <c r="D41" s="6">
+        <v>50.6</v>
+      </c>
+      <c r="E41" s="8">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>23.06</v>
+      </c>
+      <c r="D42" s="6">
+        <v>30.39</v>
+      </c>
+      <c r="E42" s="8">
+        <v>7.33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D38" s="5">
-        <v>60</v>
-      </c>
-      <c r="E38" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>40.71</v>
+      </c>
+      <c r="D43" s="6">
+        <v>44.83</v>
+      </c>
+      <c r="E43" s="8">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>46.56</v>
+      </c>
+      <c r="D44" s="6">
+        <v>48.01</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-42.84</v>
+      </c>
+      <c r="D45" s="6">
+        <v>32.28</v>
+      </c>
+      <c r="E45" s="8">
+        <v>75.12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-24.13</v>
+      </c>
+      <c r="D46" s="6">
+        <v>121.77</v>
+      </c>
+      <c r="E46" s="8">
+        <v>145.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="5">
-        <v>60</v>
-      </c>
-      <c r="D39" s="5">
-        <v>21</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>31.73</v>
-      </c>
-      <c r="D40" s="5">
-        <v>29.88</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>41.49</v>
-      </c>
-      <c r="D41" s="5">
-        <v>45.07</v>
-      </c>
-      <c r="E41" s="7">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="5">
-        <v>39.64</v>
-      </c>
-      <c r="D42" s="5">
-        <v>23.06</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-16.58</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>3144.57</v>
+      </c>
+      <c r="D47" s="6">
+        <v>292.76</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-2851.81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>49.97</v>
-      </c>
-      <c r="D43" s="5">
-        <v>40.71</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-9.26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="6">
+        <v>9.73</v>
+      </c>
+      <c r="D48" s="6">
+        <v>369.95</v>
+      </c>
+      <c r="E48" s="8">
+        <v>360.22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="5">
-        <v>48.79</v>
-      </c>
-      <c r="D44" s="5">
-        <v>46.56</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="3" t="s">
+      <c r="B49" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="5">
-        <v>10.01</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-42.84</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-52.85</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-33.77</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-24.13</v>
-      </c>
-      <c r="E46" s="7">
-        <v>9.640000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="5">
-        <v>36.79</v>
-      </c>
-      <c r="D47" s="5">
-        <v>3144.57</v>
-      </c>
-      <c r="E47" s="7">
-        <v>3107.78</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-67.65000000000001</v>
-      </c>
-      <c r="D48" s="5">
-        <v>9.73</v>
-      </c>
-      <c r="E48" s="7">
-        <v>77.38</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-25.46</v>
-      </c>
-      <c r="D49" s="5">
+      <c r="C49" s="6">
         <v>-35.25</v>
       </c>
-      <c r="E49" s="6">
-        <v>-9.789999999999999</v>
+      <c r="D49" s="6">
+        <v>-55.54</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-20.29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2388,60 +2466,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>49.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>37.1</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>40.5</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="10">
-        <v>-7.8</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-7.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -2543,37 +2621,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1689</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0529</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.007800000000000001</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0237</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1469</v>
+      <c r="A2" s="14">
+        <v>0.1743</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0557</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0005</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0177</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1448</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,46 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>45.1 → 50.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.1</t>
-  </si>
-  <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>23.1 → 30.4</t>
-  </si>
-  <si>
-    <t>23.1</t>
-  </si>
-  <si>
-    <t>30.4</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,18 +368,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>602.05</v>
+        <v>593.95</v>
       </c>
       <c r="D2">
-        <v>-0.95</v>
+        <v>-1.35</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -942,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-34.47</v>
+        <v>-35.35</v>
       </c>
       <c r="H2">
-        <v>15.37</v>
+        <v>13.82</v>
       </c>
       <c r="I2">
-        <v>-2.95</v>
+        <v>-4.28</v>
       </c>
       <c r="J2">
-        <v>-11.81</v>
+        <v>-15.2</v>
       </c>
       <c r="K2">
-        <v>-10.91</v>
+        <v>-21.31</v>
       </c>
       <c r="L2">
-        <v>-27.51</v>
+        <v>-26.09</v>
       </c>
       <c r="M2">
-        <v>-14.48</v>
+        <v>-14.11</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P2">
-        <v>613.25</v>
+        <v>607.9400000000001</v>
       </c>
       <c r="Q2">
-        <v>642.26</v>
+        <v>637.42</v>
       </c>
       <c r="R2">
-        <v>699.5</v>
+        <v>695.83</v>
       </c>
       <c r="S2">
-        <v>680.14</v>
+        <v>679.8099999999999</v>
       </c>
       <c r="T2">
-        <v>-11.48</v>
+        <v>-12.63</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -996,43 +956,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>28.46</v>
+        <v>26.58</v>
       </c>
       <c r="Z2">
-        <v>-24.81</v>
+        <v>-25.44</v>
       </c>
       <c r="AA2">
-        <v>-23.83</v>
+        <v>-24.15</v>
       </c>
       <c r="AB2">
-        <v>-0.98</v>
+        <v>-1.29</v>
       </c>
       <c r="AC2">
-        <v>25.45</v>
+        <v>12.69</v>
       </c>
       <c r="AD2">
-        <v>35.94</v>
+        <v>25.11</v>
       </c>
       <c r="AE2">
-        <v>24.48</v>
+        <v>24.15</v>
       </c>
       <c r="AF2">
-        <v>32.28</v>
+        <v>-33.08</v>
       </c>
       <c r="AG2">
-        <v>697.49</v>
+        <v>691.71</v>
       </c>
       <c r="AH2">
-        <v>587.04</v>
+        <v>583.13</v>
       </c>
       <c r="AI2">
-        <v>676.71</v>
+        <v>672.71</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>45.08</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,58 +1003,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>562.2</v>
+        <v>580.5</v>
       </c>
       <c r="D3">
-        <v>1.8</v>
+        <v>3.26</v>
       </c>
       <c r="E3">
-        <v>816.05</v>
+        <v>800.4</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-31.11</v>
+        <v>-27.47</v>
       </c>
       <c r="H3">
-        <v>9.59</v>
+        <v>13.16</v>
       </c>
       <c r="I3">
-        <v>3.05</v>
+        <v>6.94</v>
       </c>
       <c r="J3">
-        <v>-2.46</v>
+        <v>1.52</v>
       </c>
       <c r="K3">
-        <v>-1.33</v>
+        <v>3.16</v>
       </c>
       <c r="L3">
-        <v>-30.76</v>
+        <v>-28.86</v>
       </c>
       <c r="M3">
-        <v>-1.77</v>
+        <v>-0.96</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="P3">
-        <v>551.95</v>
+        <v>559.48</v>
       </c>
       <c r="Q3">
-        <v>562.37</v>
+        <v>563</v>
       </c>
       <c r="R3">
-        <v>564.52</v>
+        <v>564.6</v>
       </c>
       <c r="S3">
-        <v>579.79</v>
+        <v>579.35</v>
       </c>
       <c r="T3">
-        <v>-3.03</v>
+        <v>0.2</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1106,37 +1066,37 @@
         <v>43</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>50.6</v>
+        <v>58.82</v>
       </c>
       <c r="Z3">
-        <v>-3.75</v>
+        <v>-1.61</v>
       </c>
       <c r="AA3">
-        <v>-3.08</v>
+        <v>-2.79</v>
       </c>
       <c r="AB3">
-        <v>-0.67</v>
+        <v>1.18</v>
       </c>
       <c r="AC3">
-        <v>45.52</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="AD3">
-        <v>35.46</v>
+        <v>51.4</v>
       </c>
       <c r="AE3">
-        <v>12.84</v>
+        <v>13.94</v>
       </c>
       <c r="AF3">
-        <v>121.77</v>
+        <v>526.67</v>
       </c>
       <c r="AG3">
-        <v>582.67</v>
+        <v>584.77</v>
       </c>
       <c r="AH3">
-        <v>542.0599999999999</v>
+        <v>541.24</v>
       </c>
       <c r="AI3">
         <v>581</v>
@@ -1145,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>23.03</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1116,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>936.9</v>
+        <v>934.3</v>
       </c>
       <c r="D4">
-        <v>2.96</v>
+        <v>-0.28</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1168,46 +1128,46 @@
         <v>910</v>
       </c>
       <c r="G4">
-        <v>-26.02</v>
+        <v>-26.22</v>
       </c>
       <c r="H4">
-        <v>2.96</v>
+        <v>2.67</v>
       </c>
       <c r="I4">
-        <v>-13.03</v>
+        <v>-11.02</v>
       </c>
       <c r="J4">
-        <v>-11</v>
+        <v>-11.67</v>
       </c>
       <c r="K4">
-        <v>-9.84</v>
+        <v>-7.9</v>
       </c>
       <c r="L4">
-        <v>-21.82</v>
+        <v>-19.81</v>
       </c>
       <c r="M4">
-        <v>-0.05</v>
+        <v>-0.27</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P4">
-        <v>990.98</v>
+        <v>967.84</v>
       </c>
       <c r="Q4">
-        <v>1049.14</v>
+        <v>1042.26</v>
       </c>
       <c r="R4">
-        <v>1043.43</v>
+        <v>1042.21</v>
       </c>
       <c r="S4">
-        <v>1100.81</v>
+        <v>1099.93</v>
       </c>
       <c r="T4">
-        <v>-14.89</v>
+        <v>-15.06</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1222,34 +1182,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>30.39</v>
+        <v>30.09</v>
       </c>
       <c r="Z4">
-        <v>-20.36</v>
+        <v>-25.59</v>
       </c>
       <c r="AA4">
-        <v>-3.96</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="AB4">
-        <v>-16.4</v>
+        <v>-17.3</v>
       </c>
       <c r="AC4">
-        <v>6.83</v>
+        <v>13.39</v>
       </c>
       <c r="AD4">
-        <v>2.28</v>
+        <v>6.74</v>
       </c>
       <c r="AE4">
-        <v>32.06</v>
+        <v>30.67</v>
       </c>
       <c r="AF4">
-        <v>292.76</v>
+        <v>2.15</v>
       </c>
       <c r="AG4">
-        <v>1140.26</v>
+        <v>1146.04</v>
       </c>
       <c r="AH4">
-        <v>958.01</v>
+        <v>938.47</v>
       </c>
       <c r="AI4">
         <v>1018.82</v>
@@ -1258,7 +1218,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>35.8</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1255.6</v>
+        <v>1252.5</v>
       </c>
       <c r="D5">
-        <v>1.65</v>
+        <v>-0.25</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1281,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-11.43</v>
+        <v>-11.65</v>
       </c>
       <c r="H5">
-        <v>67.64</v>
+        <v>67.22</v>
       </c>
       <c r="I5">
-        <v>-3.77</v>
+        <v>-4.5</v>
       </c>
       <c r="J5">
-        <v>-8.970000000000001</v>
+        <v>-6.48</v>
       </c>
       <c r="K5">
-        <v>10.62</v>
+        <v>8.32</v>
       </c>
       <c r="L5">
-        <v>13.26</v>
+        <v>13.8</v>
       </c>
       <c r="M5">
-        <v>17.43</v>
+        <v>17.03</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>1276.86</v>
+        <v>1265.06</v>
       </c>
       <c r="Q5">
-        <v>1316.52</v>
+        <v>1312.42</v>
       </c>
       <c r="R5">
-        <v>1224.19</v>
+        <v>1228.3</v>
       </c>
       <c r="S5">
-        <v>1058.4</v>
+        <v>1059.19</v>
       </c>
       <c r="T5">
-        <v>18.63</v>
+        <v>18.25</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1335,34 +1295,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>44.83</v>
+        <v>44.32</v>
       </c>
       <c r="Z5">
-        <v>5.87</v>
+        <v>2.34</v>
       </c>
       <c r="AA5">
-        <v>21.67</v>
+        <v>17.8</v>
       </c>
       <c r="AB5">
-        <v>-15.8</v>
+        <v>-15.46</v>
       </c>
       <c r="AC5">
-        <v>6.89</v>
+        <v>13.17</v>
       </c>
       <c r="AD5">
-        <v>3.08</v>
+        <v>6.69</v>
       </c>
       <c r="AE5">
-        <v>46.56</v>
+        <v>46.24</v>
       </c>
       <c r="AF5">
-        <v>369.95</v>
+        <v>-44.95</v>
       </c>
       <c r="AG5">
-        <v>1385.38</v>
+        <v>1386.33</v>
       </c>
       <c r="AH5">
-        <v>1247.67</v>
+        <v>1238.5</v>
       </c>
       <c r="AI5">
         <v>1225.87</v>
@@ -1371,7 +1331,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>28.06</v>
+        <v>32.09</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2028</v>
+        <v>1990</v>
       </c>
       <c r="D6">
-        <v>0.65</v>
+        <v>-1.87</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1394,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-12.6</v>
+        <v>-14.24</v>
       </c>
       <c r="H6">
-        <v>37.84</v>
+        <v>35.25</v>
       </c>
       <c r="I6">
-        <v>-2.59</v>
+        <v>-3.86</v>
       </c>
       <c r="J6">
-        <v>-3.63</v>
+        <v>-4.8</v>
       </c>
       <c r="K6">
-        <v>18.31</v>
+        <v>18.01</v>
       </c>
       <c r="L6">
-        <v>-0.77</v>
+        <v>0.92</v>
       </c>
       <c r="M6">
-        <v>5.57</v>
+        <v>5.18</v>
       </c>
       <c r="N6">
         <v>79</v>
       </c>
       <c r="O6">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="P6">
-        <v>2051.86</v>
+        <v>2035.86</v>
       </c>
       <c r="Q6">
-        <v>2084.37</v>
+        <v>2078.76</v>
       </c>
       <c r="R6">
-        <v>1958.25</v>
+        <v>1964.17</v>
       </c>
       <c r="S6">
-        <v>1884.02</v>
+        <v>1882.37</v>
       </c>
       <c r="T6">
-        <v>7.64</v>
+        <v>5.72</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1448,34 +1408,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>48.01</v>
+        <v>44.24</v>
       </c>
       <c r="Z6">
-        <v>15.4</v>
+        <v>8.4</v>
       </c>
       <c r="AA6">
-        <v>33.56</v>
+        <v>28.53</v>
       </c>
       <c r="AB6">
-        <v>-18.16</v>
+        <v>-20.13</v>
       </c>
       <c r="AC6">
         <v>2.72</v>
       </c>
       <c r="AD6">
-        <v>12.85</v>
+        <v>7</v>
       </c>
       <c r="AE6">
-        <v>63.66</v>
+        <v>62.26</v>
       </c>
       <c r="AF6">
-        <v>-55.54</v>
+        <v>-34.62</v>
       </c>
       <c r="AG6">
-        <v>2171.04</v>
+        <v>2174.62</v>
       </c>
       <c r="AH6">
-        <v>1997.7</v>
+        <v>1982.91</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1484,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>24.22</v>
+        <v>25.64</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1645,808 +1605,719 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>66</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-11.81</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-15.2</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-3.39</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-2.46</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-11</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-11.67</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-6.48</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-3.63</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-4.8</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-10.93</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-11.81</v>
-      </c>
-      <c r="E8" s="7">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-2.95</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-4.28</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>3.05</v>
+      </c>
+      <c r="D13" s="5">
+        <v>6.94</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-13.03</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-11.02</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-3.77</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-4.5</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-2.59</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.86</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-27.51</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-26.09</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-30.76</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-28.86</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-21.82</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-19.81</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>13.26</v>
+      </c>
+      <c r="D20" s="5">
+        <v>13.8</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-0.77</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-10.91</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-21.31</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-10.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-1.33</v>
+      </c>
+      <c r="D23" s="5">
+        <v>3.16</v>
+      </c>
+      <c r="E23" s="7">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-9.84</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-7.9</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>10.62</v>
+      </c>
+      <c r="D25" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>18.31</v>
+      </c>
+      <c r="D26" s="5">
+        <v>18.01</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-34.47</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-35.35</v>
+      </c>
+      <c r="E27" s="6">
         <v>-0.88</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-1.58</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-2.46</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-31.11</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-27.47</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-14.28</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-11</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-26.02</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-26.22</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-7.59</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-8.970000000000001</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-11.43</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-11.65</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-4.38</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-3.63</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-12.6</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-14.24</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-1.41</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.95</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>602.05</v>
+      </c>
+      <c r="D32" s="5">
+        <v>593.95</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-8.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.51</v>
-      </c>
-      <c r="D14" s="6">
-        <v>3.05</v>
-      </c>
-      <c r="E14" s="8">
-        <v>5.56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>562.2</v>
+      </c>
+      <c r="D33" s="5">
+        <v>580.5</v>
+      </c>
+      <c r="E33" s="7">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-14.87</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-13.03</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>936.9</v>
+      </c>
+      <c r="D34" s="5">
+        <v>934.3</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-6.45</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1255.6</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1252.5</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2028</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1990</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>28.46</v>
+      </c>
+      <c r="D37" s="5">
+        <v>26.58</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>50.6</v>
+      </c>
+      <c r="D38" s="5">
+        <v>58.82</v>
+      </c>
+      <c r="E38" s="7">
+        <v>8.220000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>30.39</v>
+      </c>
+      <c r="D39" s="5">
+        <v>30.09</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>44.83</v>
+      </c>
+      <c r="D40" s="5">
+        <v>44.32</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>48.01</v>
+      </c>
+      <c r="D41" s="5">
+        <v>44.24</v>
+      </c>
+      <c r="E41" s="6">
         <v>-3.77</v>
       </c>
-      <c r="E16" s="8">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>32.28</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-33.08</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-65.36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>121.77</v>
+      </c>
+      <c r="D43" s="5">
+        <v>526.67</v>
+      </c>
+      <c r="E43" s="7">
+        <v>404.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>292.76</v>
+      </c>
+      <c r="D44" s="5">
+        <v>2.15</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-290.61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>369.95</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-44.95</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-414.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-4</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-2.59</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-28.52</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-27.51</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-33.55</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-30.76</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2.79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-22.97</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-21.82</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>8.56</v>
-      </c>
-      <c r="D21" s="6">
-        <v>13.26</v>
-      </c>
-      <c r="E21" s="8">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-2.26</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-0.77</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-7.51</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-10.91</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-2.13</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-1.33</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-11.93</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-9.84</v>
-      </c>
-      <c r="E25" s="8">
-        <v>2.09</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>7.12</v>
-      </c>
-      <c r="D26" s="6">
-        <v>10.62</v>
-      </c>
-      <c r="E26" s="8">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>16.24</v>
-      </c>
-      <c r="D27" s="6">
-        <v>18.31</v>
-      </c>
-      <c r="E27" s="8">
-        <v>2.07</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-33.84</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-34.47</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-32.33</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-31.11</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-28.14</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-26.02</v>
-      </c>
-      <c r="E30" s="8">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-12.87</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-11.43</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-13.16</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-12.6</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>607.85</v>
-      </c>
-      <c r="D33" s="6">
-        <v>602.05</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-5.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>552.25</v>
-      </c>
-      <c r="D34" s="6">
-        <v>562.2</v>
-      </c>
-      <c r="E34" s="8">
-        <v>9.949999999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>910</v>
-      </c>
-      <c r="D35" s="6">
-        <v>936.9</v>
-      </c>
-      <c r="E35" s="8">
-        <v>26.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1235.2</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1255.6</v>
-      </c>
-      <c r="E36" s="8">
-        <v>20.4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>2015</v>
-      </c>
-      <c r="D37" s="6">
-        <v>2028</v>
-      </c>
-      <c r="E37" s="8">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="6">
-        <v>40</v>
-      </c>
-      <c r="D38" s="6">
-        <v>21</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="6">
-        <v>21</v>
-      </c>
-      <c r="D39" s="6">
-        <v>40</v>
-      </c>
-      <c r="E39" s="8">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>29.88</v>
-      </c>
-      <c r="D40" s="6">
-        <v>28.46</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>45.07</v>
-      </c>
-      <c r="D41" s="6">
-        <v>50.6</v>
-      </c>
-      <c r="E41" s="8">
-        <v>5.53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>23.06</v>
-      </c>
-      <c r="D42" s="6">
-        <v>30.39</v>
-      </c>
-      <c r="E42" s="8">
-        <v>7.33</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>40.71</v>
-      </c>
-      <c r="D43" s="6">
-        <v>44.83</v>
-      </c>
-      <c r="E43" s="8">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>46.56</v>
-      </c>
-      <c r="D44" s="6">
-        <v>48.01</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="6">
-        <v>-42.84</v>
-      </c>
-      <c r="D45" s="6">
-        <v>32.28</v>
-      </c>
-      <c r="E45" s="8">
-        <v>75.12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-24.13</v>
-      </c>
-      <c r="D46" s="6">
-        <v>121.77</v>
-      </c>
-      <c r="E46" s="8">
-        <v>145.9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>3144.57</v>
-      </c>
-      <c r="D47" s="6">
-        <v>292.76</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-2851.81</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>9.73</v>
-      </c>
-      <c r="D48" s="6">
-        <v>369.95</v>
-      </c>
-      <c r="E48" s="8">
-        <v>360.22</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-35.25</v>
-      </c>
-      <c r="D49" s="6">
+      <c r="C46" s="5">
         <v>-55.54</v>
       </c>
-      <c r="E49" s="7">
-        <v>-20.29</v>
+      <c r="D46" s="5">
+        <v>-34.62</v>
+      </c>
+      <c r="E46" s="7">
+        <v>20.92</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2466,60 +2337,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
-        <v>49.92</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>40.5</v>
-      </c>
-      <c r="E2" s="11">
-        <v>40</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-7.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>1.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="10">
+        <v>40.8</v>
+      </c>
+      <c r="E2" s="10">
+        <v>60</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-7.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>40</v>
       </c>
     </row>
@@ -2621,37 +2492,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1743</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0557</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0005</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0177</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1448</v>
+      <c r="A2" s="13">
+        <v>0.1703</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0518</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0027</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1411</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>44.2 → 51.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>44.2</t>
+  </si>
+  <si>
+    <t>51.2</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +288,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +328,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,14 +404,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -893,7 +931,7 @@
         <v>593.95</v>
       </c>
       <c r="D2">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -908,40 +946,40 @@
         <v>13.82</v>
       </c>
       <c r="I2">
-        <v>-4.28</v>
+        <v>-4.3</v>
       </c>
       <c r="J2">
-        <v>-15.2</v>
+        <v>-14.01</v>
       </c>
       <c r="K2">
-        <v>-21.31</v>
+        <v>-19.6</v>
       </c>
       <c r="L2">
-        <v>-26.09</v>
+        <v>-24.47</v>
       </c>
       <c r="M2">
-        <v>-14.11</v>
+        <v>-14.66</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P2">
-        <v>607.9400000000001</v>
+        <v>602.6</v>
       </c>
       <c r="Q2">
-        <v>637.42</v>
+        <v>632.83</v>
       </c>
       <c r="R2">
-        <v>695.83</v>
+        <v>692.55</v>
       </c>
       <c r="S2">
-        <v>679.8099999999999</v>
+        <v>679.36</v>
       </c>
       <c r="T2">
-        <v>-12.63</v>
+        <v>-12.57</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -959,40 +997,40 @@
         <v>26.58</v>
       </c>
       <c r="Z2">
-        <v>-25.44</v>
+        <v>-25.64</v>
       </c>
       <c r="AA2">
-        <v>-24.15</v>
+        <v>-24.45</v>
       </c>
       <c r="AB2">
-        <v>-1.29</v>
+        <v>-1.19</v>
       </c>
       <c r="AC2">
-        <v>12.69</v>
+        <v>4.57</v>
       </c>
       <c r="AD2">
-        <v>25.11</v>
+        <v>14.24</v>
       </c>
       <c r="AE2">
-        <v>24.15</v>
+        <v>23.85</v>
       </c>
       <c r="AF2">
-        <v>-33.08</v>
+        <v>27.31</v>
       </c>
       <c r="AG2">
-        <v>691.71</v>
+        <v>685.39</v>
       </c>
       <c r="AH2">
-        <v>583.13</v>
+        <v>580.27</v>
       </c>
       <c r="AI2">
-        <v>672.71</v>
+        <v>671.8</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>47.96</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,55 +1044,55 @@
         <v>580.5</v>
       </c>
       <c r="D3">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>800.4</v>
+        <v>785.85</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-27.47</v>
+        <v>-26.13</v>
       </c>
       <c r="H3">
         <v>13.16</v>
       </c>
       <c r="I3">
-        <v>6.94</v>
+        <v>4.4</v>
       </c>
       <c r="J3">
-        <v>1.52</v>
+        <v>2.24</v>
       </c>
       <c r="K3">
-        <v>3.16</v>
+        <v>1.41</v>
       </c>
       <c r="L3">
-        <v>-28.86</v>
+        <v>-27.47</v>
       </c>
       <c r="M3">
-        <v>-0.96</v>
+        <v>-0.59</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P3">
-        <v>559.48</v>
+        <v>564.37</v>
       </c>
       <c r="Q3">
-        <v>563</v>
+        <v>563.4299999999999</v>
       </c>
       <c r="R3">
-        <v>564.6</v>
+        <v>564.61</v>
       </c>
       <c r="S3">
-        <v>579.35</v>
+        <v>578.95</v>
       </c>
       <c r="T3">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1072,31 +1110,31 @@
         <v>58.82</v>
       </c>
       <c r="Z3">
-        <v>-1.61</v>
+        <v>0.08</v>
       </c>
       <c r="AA3">
-        <v>-2.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AB3">
-        <v>1.18</v>
+        <v>2.3</v>
       </c>
       <c r="AC3">
-        <v>71.26000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="AD3">
-        <v>51.4</v>
+        <v>69.12</v>
       </c>
       <c r="AE3">
-        <v>13.94</v>
+        <v>14.97</v>
       </c>
       <c r="AF3">
-        <v>526.67</v>
+        <v>169.07</v>
       </c>
       <c r="AG3">
-        <v>584.77</v>
+        <v>586.25</v>
       </c>
       <c r="AH3">
-        <v>541.24</v>
+        <v>540.61</v>
       </c>
       <c r="AI3">
         <v>581</v>
@@ -1105,7 +1143,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>25.81</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,7 +1157,7 @@
         <v>934.3</v>
       </c>
       <c r="D4">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1134,19 +1172,19 @@
         <v>2.67</v>
       </c>
       <c r="I4">
-        <v>-11.02</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="J4">
-        <v>-11.67</v>
+        <v>-12.84</v>
       </c>
       <c r="K4">
-        <v>-7.9</v>
+        <v>-8.58</v>
       </c>
       <c r="L4">
-        <v>-19.81</v>
+        <v>-20.74</v>
       </c>
       <c r="M4">
-        <v>-0.27</v>
+        <v>-0.55</v>
       </c>
       <c r="N4">
         <v>40</v>
@@ -1155,22 +1193,22 @@
         <v>18</v>
       </c>
       <c r="P4">
-        <v>967.84</v>
+        <v>948.1</v>
       </c>
       <c r="Q4">
-        <v>1042.26</v>
+        <v>1035.73</v>
       </c>
       <c r="R4">
-        <v>1042.21</v>
+        <v>1040.94</v>
       </c>
       <c r="S4">
-        <v>1099.93</v>
+        <v>1099.1</v>
       </c>
       <c r="T4">
-        <v>-15.06</v>
+        <v>-14.99</v>
       </c>
       <c r="U4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V4" t="s">
         <v>43</v>
@@ -1179,37 +1217,37 @@
         <v>43</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
         <v>30.09</v>
       </c>
       <c r="Z4">
-        <v>-25.59</v>
+        <v>-29.39</v>
       </c>
       <c r="AA4">
-        <v>-8.289999999999999</v>
+        <v>-12.51</v>
       </c>
       <c r="AB4">
-        <v>-17.3</v>
+        <v>-16.89</v>
       </c>
       <c r="AC4">
+        <v>19.94</v>
+      </c>
+      <c r="AD4">
         <v>13.39</v>
       </c>
-      <c r="AD4">
-        <v>6.74</v>
-      </c>
       <c r="AE4">
-        <v>30.67</v>
+        <v>29.38</v>
       </c>
       <c r="AF4">
-        <v>2.15</v>
+        <v>-53.99</v>
       </c>
       <c r="AG4">
-        <v>1146.04</v>
+        <v>1149.48</v>
       </c>
       <c r="AH4">
-        <v>938.47</v>
+        <v>921.98</v>
       </c>
       <c r="AI4">
         <v>1018.82</v>
@@ -1218,7 +1256,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>40.58</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1267,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1252.5</v>
+        <v>1223</v>
       </c>
       <c r="D5">
-        <v>-0.25</v>
+        <v>-2.36</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,46 +1279,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-11.65</v>
+        <v>-13.73</v>
       </c>
       <c r="H5">
-        <v>67.22</v>
+        <v>63.28</v>
       </c>
       <c r="I5">
-        <v>-4.5</v>
+        <v>-5.36</v>
       </c>
       <c r="J5">
-        <v>-6.48</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="K5">
-        <v>8.32</v>
+        <v>7.84</v>
       </c>
       <c r="L5">
-        <v>13.8</v>
+        <v>11.83</v>
       </c>
       <c r="M5">
-        <v>17.03</v>
+        <v>16.57</v>
       </c>
       <c r="N5">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>1265.06</v>
+        <v>1251.22</v>
       </c>
       <c r="Q5">
-        <v>1312.42</v>
+        <v>1305.32</v>
       </c>
       <c r="R5">
-        <v>1228.3</v>
+        <v>1231.91</v>
       </c>
       <c r="S5">
-        <v>1059.19</v>
+        <v>1059.86</v>
       </c>
       <c r="T5">
-        <v>18.25</v>
+        <v>15.39</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1295,43 +1333,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>44.32</v>
+        <v>39.75</v>
       </c>
       <c r="Z5">
-        <v>2.34</v>
+        <v>-2.81</v>
       </c>
       <c r="AA5">
-        <v>17.8</v>
+        <v>13.68</v>
       </c>
       <c r="AB5">
-        <v>-15.46</v>
+        <v>-16.49</v>
       </c>
       <c r="AC5">
         <v>13.17</v>
       </c>
       <c r="AD5">
-        <v>6.69</v>
+        <v>11.08</v>
       </c>
       <c r="AE5">
-        <v>46.24</v>
+        <v>47.54</v>
       </c>
       <c r="AF5">
-        <v>-44.95</v>
+        <v>112.81</v>
       </c>
       <c r="AG5">
-        <v>1386.33</v>
+        <v>1385.06</v>
       </c>
       <c r="AH5">
-        <v>1238.5</v>
+        <v>1225.59</v>
       </c>
       <c r="AI5">
-        <v>1225.87</v>
+        <v>1373.81</v>
       </c>
       <c r="AJ5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK5">
-        <v>32.09</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1380,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1990</v>
+        <v>2054</v>
       </c>
       <c r="D6">
-        <v>-1.87</v>
+        <v>3.22</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1392,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-14.24</v>
+        <v>-11.48</v>
       </c>
       <c r="H6">
-        <v>35.25</v>
+        <v>39.6</v>
       </c>
       <c r="I6">
-        <v>-3.86</v>
+        <v>-2.58</v>
       </c>
       <c r="J6">
-        <v>-4.8</v>
+        <v>-2.29</v>
       </c>
       <c r="K6">
-        <v>18.01</v>
+        <v>19.74</v>
       </c>
       <c r="L6">
-        <v>0.92</v>
+        <v>3.17</v>
       </c>
       <c r="M6">
-        <v>5.18</v>
+        <v>6.17</v>
       </c>
       <c r="N6">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O6">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="P6">
-        <v>2035.86</v>
+        <v>2024.98</v>
       </c>
       <c r="Q6">
-        <v>2078.76</v>
+        <v>2075.53</v>
       </c>
       <c r="R6">
-        <v>1964.17</v>
+        <v>1971.08</v>
       </c>
       <c r="S6">
-        <v>1882.37</v>
+        <v>1881.16</v>
       </c>
       <c r="T6">
-        <v>5.72</v>
+        <v>9.19</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1408,34 +1446,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>44.24</v>
+        <v>51.2</v>
       </c>
       <c r="Z6">
-        <v>8.4</v>
+        <v>7.92</v>
       </c>
       <c r="AA6">
-        <v>28.53</v>
+        <v>24.41</v>
       </c>
       <c r="AB6">
-        <v>-20.13</v>
+        <v>-16.49</v>
       </c>
       <c r="AC6">
-        <v>2.72</v>
+        <v>14.27</v>
       </c>
       <c r="AD6">
-        <v>7</v>
+        <v>6.57</v>
       </c>
       <c r="AE6">
-        <v>62.26</v>
+        <v>63.96</v>
       </c>
       <c r="AF6">
-        <v>-34.62</v>
+        <v>11.08</v>
       </c>
       <c r="AG6">
-        <v>2174.62</v>
+        <v>2170.07</v>
       </c>
       <c r="AH6">
-        <v>1982.91</v>
+        <v>1980.99</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1444,7 +1482,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>25.64</v>
+        <v>24.33</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1605,719 +1643,672 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-11.81</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="7">
         <v>-15.2</v>
       </c>
-      <c r="E7" s="6">
-        <v>-3.39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="7">
+        <v>-14.01</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-2.46</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="7">
         <v>1.52</v>
       </c>
-      <c r="E8" s="7">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="7">
+        <v>2.24</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-11</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="7">
         <v>-11.67</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="7">
+        <v>-12.84</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-8.970000000000001</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="7">
         <v>-6.48</v>
       </c>
-      <c r="E10" s="7">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="7">
+        <v>-8.369999999999999</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-3.63</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="7">
         <v>-4.8</v>
       </c>
-      <c r="E11" s="6">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="7">
+        <v>-2.29</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-2.95</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="7">
         <v>-4.28</v>
       </c>
-      <c r="E12" s="6">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="7">
+        <v>-4.3</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>3.05</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="7">
         <v>6.94</v>
       </c>
-      <c r="E13" s="7">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="7">
+        <v>4.4</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-13.03</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="7">
         <v>-11.02</v>
       </c>
-      <c r="E14" s="7">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="7">
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-3.77</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="7">
         <v>-4.5</v>
       </c>
-      <c r="E15" s="6">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="7">
+        <v>-5.36</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-2.59</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="7">
         <v>-3.86</v>
       </c>
-      <c r="E16" s="6">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="7">
+        <v>-2.58</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>-27.51</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="7">
         <v>-26.09</v>
       </c>
-      <c r="E17" s="7">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="7">
+        <v>-24.47</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>-30.76</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="7">
         <v>-28.86</v>
       </c>
-      <c r="E18" s="7">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="7">
+        <v>-27.47</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-21.82</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="7">
         <v>-19.81</v>
       </c>
-      <c r="E19" s="7">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="7">
+        <v>-20.74</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>13.26</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="7">
         <v>13.8</v>
       </c>
-      <c r="E20" s="7">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="7">
+        <v>11.83</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-0.77</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="7">
         <v>0.92</v>
       </c>
-      <c r="E21" s="7">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="7">
+        <v>3.17</v>
+      </c>
+      <c r="E22" s="8">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>-10.91</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="7">
         <v>-21.31</v>
       </c>
-      <c r="E22" s="6">
-        <v>-10.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="7">
+        <v>-19.6</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>-1.33</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="7">
         <v>3.16</v>
       </c>
-      <c r="E23" s="7">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="7">
+        <v>1.41</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5">
-        <v>-9.84</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="7">
         <v>-7.9</v>
       </c>
-      <c r="E24" s="7">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="7">
+        <v>-8.58</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>10.62</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="7">
         <v>8.32</v>
       </c>
-      <c r="E25" s="6">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="7">
+        <v>7.84</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>18.31</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="7">
         <v>18.01</v>
       </c>
-      <c r="E26" s="6">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="7">
+        <v>19.74</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-27.47</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-26.13</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-11.65</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-13.73</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-2.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-14.24</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-11.48</v>
+      </c>
+      <c r="E30" s="8">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="7">
+        <v>1252.5</v>
+      </c>
+      <c r="D31" s="7">
+        <v>1223</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-29.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="7">
+        <v>1990</v>
+      </c>
+      <c r="D32" s="7">
+        <v>2054</v>
+      </c>
+      <c r="E32" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="7">
+        <v>99</v>
+      </c>
+      <c r="D33" s="7">
+        <v>79</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="7">
+        <v>79</v>
+      </c>
+      <c r="D34" s="7">
+        <v>99</v>
+      </c>
+      <c r="E34" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="7">
+        <v>44.32</v>
+      </c>
+      <c r="D35" s="7">
+        <v>39.75</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-4.57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="7">
+        <v>44.24</v>
+      </c>
+      <c r="D36" s="7">
+        <v>51.2</v>
+      </c>
+      <c r="E36" s="8">
+        <v>6.96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-34.47</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-35.35</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B37" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-33.08</v>
+      </c>
+      <c r="D37" s="7">
+        <v>27.31</v>
+      </c>
+      <c r="E37" s="8">
+        <v>60.39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-31.11</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-27.47</v>
-      </c>
-      <c r="E28" s="7">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B38" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="7">
+        <v>526.67</v>
+      </c>
+      <c r="D38" s="7">
+        <v>169.07</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-357.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-26.02</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-26.22</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B39" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="7">
+        <v>2.15</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-53.99</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-56.14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-11.43</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-11.65</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B40" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-44.95</v>
+      </c>
+      <c r="D40" s="7">
+        <v>112.81</v>
+      </c>
+      <c r="E40" s="8">
+        <v>157.76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-12.6</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-14.24</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>602.05</v>
-      </c>
-      <c r="D32" s="5">
-        <v>593.95</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-8.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>562.2</v>
-      </c>
-      <c r="D33" s="5">
-        <v>580.5</v>
-      </c>
-      <c r="E33" s="7">
-        <v>18.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>936.9</v>
-      </c>
-      <c r="D34" s="5">
-        <v>934.3</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>1255.6</v>
-      </c>
-      <c r="D35" s="5">
-        <v>1252.5</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2028</v>
-      </c>
-      <c r="D36" s="5">
-        <v>1990</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="5">
-        <v>28.46</v>
-      </c>
-      <c r="D37" s="5">
-        <v>26.58</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="5">
-        <v>50.6</v>
-      </c>
-      <c r="D38" s="5">
-        <v>58.82</v>
-      </c>
-      <c r="E38" s="7">
-        <v>8.220000000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>30.39</v>
-      </c>
-      <c r="D39" s="5">
-        <v>30.09</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>44.83</v>
-      </c>
-      <c r="D40" s="5">
-        <v>44.32</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>48.01</v>
-      </c>
-      <c r="D41" s="5">
-        <v>44.24</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-3.77</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="B41" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>32.28</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-33.08</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-65.36</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="5">
-        <v>121.77</v>
-      </c>
-      <c r="D43" s="5">
-        <v>526.67</v>
-      </c>
-      <c r="E43" s="7">
-        <v>404.9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="5">
-        <v>292.76</v>
-      </c>
-      <c r="D44" s="5">
-        <v>2.15</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-290.61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>369.95</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-44.95</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-414.9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-55.54</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C41" s="7">
         <v>-34.62</v>
       </c>
-      <c r="E46" s="7">
-        <v>20.92</v>
+      <c r="D41" s="7">
+        <v>11.08</v>
+      </c>
+      <c r="E41" s="8">
+        <v>45.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2337,60 +2328,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="12">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="13">
+        <v>5</v>
+      </c>
+      <c r="D2" s="12">
+        <v>41.3</v>
+      </c>
+      <c r="E2" s="12">
         <v>60</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="10">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="11">
-        <v>5</v>
-      </c>
-      <c r="D2" s="10">
-        <v>40.8</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-7.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="12">
+        <v>-7.1</v>
+      </c>
+      <c r="G2" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="12">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -2492,37 +2483,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1703</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0518</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0027</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.009599999999999999</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1411</v>
+      <c r="A2" s="15">
+        <v>0.1657</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.0617</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="D2" s="15">
+        <v>-0.0059</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.1466</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -179,21 +179,6 @@
   </si>
   <si>
     <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>44.2 → 51.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>44.2</t>
-  </si>
-  <si>
-    <t>51.2</t>
   </si>
   <si>
     <t>20 DMA &gt; 50 DMA</t>
@@ -288,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -328,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -412,11 +397,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -928,10 +912,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>593.95</v>
+        <v>585.55</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-1.41</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -940,46 +924,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-35.35</v>
+        <v>-36.27</v>
       </c>
       <c r="H2">
-        <v>13.82</v>
+        <v>12.21</v>
       </c>
       <c r="I2">
-        <v>-4.3</v>
+        <v>-4.82</v>
       </c>
       <c r="J2">
-        <v>-14.01</v>
+        <v>-14.62</v>
       </c>
       <c r="K2">
-        <v>-19.6</v>
+        <v>-22.09</v>
       </c>
       <c r="L2">
-        <v>-24.47</v>
+        <v>-28.88</v>
       </c>
       <c r="M2">
-        <v>-14.66</v>
+        <v>-14.95</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P2">
-        <v>602.6</v>
+        <v>596.67</v>
       </c>
       <c r="Q2">
-        <v>632.83</v>
+        <v>628.1799999999999</v>
       </c>
       <c r="R2">
-        <v>692.55</v>
+        <v>688.84</v>
       </c>
       <c r="S2">
-        <v>679.36</v>
+        <v>678.9299999999999</v>
       </c>
       <c r="T2">
-        <v>-12.57</v>
+        <v>-13.75</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -994,43 +978,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>26.58</v>
+        <v>24.61</v>
       </c>
       <c r="Z2">
-        <v>-25.64</v>
+        <v>-26.17</v>
       </c>
       <c r="AA2">
-        <v>-24.45</v>
+        <v>-24.79</v>
       </c>
       <c r="AB2">
-        <v>-1.19</v>
+        <v>-1.38</v>
       </c>
       <c r="AC2">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>14.24</v>
+        <v>5.75</v>
       </c>
       <c r="AE2">
-        <v>23.85</v>
+        <v>25.13</v>
       </c>
       <c r="AF2">
-        <v>27.31</v>
+        <v>97.42</v>
       </c>
       <c r="AG2">
-        <v>685.39</v>
+        <v>680.17</v>
       </c>
       <c r="AH2">
-        <v>580.27</v>
+        <v>576.1900000000001</v>
       </c>
       <c r="AI2">
-        <v>671.8</v>
+        <v>660.5599999999999</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>50.45</v>
+        <v>54.37</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1041,58 +1025,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>580.5</v>
+        <v>588.7</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="E3">
-        <v>785.85</v>
+        <v>776.75</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-26.13</v>
+        <v>-24.21</v>
       </c>
       <c r="H3">
-        <v>13.16</v>
+        <v>14.76</v>
       </c>
       <c r="I3">
-        <v>4.4</v>
+        <v>7.74</v>
       </c>
       <c r="J3">
-        <v>2.24</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
-        <v>1.41</v>
+        <v>2.53</v>
       </c>
       <c r="L3">
-        <v>-27.47</v>
+        <v>-25.09</v>
       </c>
       <c r="M3">
-        <v>-0.59</v>
+        <v>0.23</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P3">
-        <v>564.37</v>
+        <v>572.83</v>
       </c>
       <c r="Q3">
-        <v>563.4299999999999</v>
+        <v>564.09</v>
       </c>
       <c r="R3">
-        <v>564.61</v>
+        <v>565.04</v>
       </c>
       <c r="S3">
-        <v>578.95</v>
+        <v>578.5599999999999</v>
       </c>
       <c r="T3">
-        <v>0.27</v>
+        <v>1.75</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1107,43 +1091,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>58.82</v>
+        <v>62.09</v>
       </c>
       <c r="Z3">
-        <v>0.08</v>
+        <v>2.07</v>
       </c>
       <c r="AA3">
-        <v>-2.21</v>
+        <v>-1.36</v>
       </c>
       <c r="AB3">
-        <v>2.3</v>
+        <v>3.42</v>
       </c>
       <c r="AC3">
-        <v>90.59</v>
+        <v>100</v>
       </c>
       <c r="AD3">
-        <v>69.12</v>
+        <v>87.28</v>
       </c>
       <c r="AE3">
-        <v>14.97</v>
+        <v>15.22</v>
       </c>
       <c r="AF3">
-        <v>169.07</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AG3">
-        <v>586.25</v>
+        <v>589.04</v>
       </c>
       <c r="AH3">
-        <v>540.61</v>
+        <v>539.14</v>
       </c>
       <c r="AI3">
-        <v>581</v>
+        <v>546.4400000000001</v>
       </c>
       <c r="AJ3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK3">
-        <v>28.22</v>
+        <v>31.69</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1154,10 +1138,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>934.3</v>
+        <v>931</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1166,46 +1150,46 @@
         <v>910</v>
       </c>
       <c r="G4">
-        <v>-26.22</v>
+        <v>-26.48</v>
       </c>
       <c r="H4">
-        <v>2.67</v>
+        <v>2.31</v>
       </c>
       <c r="I4">
-        <v>-9.550000000000001</v>
+        <v>-9.17</v>
       </c>
       <c r="J4">
-        <v>-12.84</v>
+        <v>-12.57</v>
       </c>
       <c r="K4">
-        <v>-8.58</v>
+        <v>-8.98</v>
       </c>
       <c r="L4">
-        <v>-20.74</v>
+        <v>-21.05</v>
       </c>
       <c r="M4">
-        <v>-0.55</v>
+        <v>-0.61</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>948.1</v>
+        <v>929.3</v>
       </c>
       <c r="Q4">
-        <v>1035.73</v>
+        <v>1029.57</v>
       </c>
       <c r="R4">
-        <v>1040.94</v>
+        <v>1039.62</v>
       </c>
       <c r="S4">
-        <v>1099.1</v>
+        <v>1098.3</v>
       </c>
       <c r="T4">
-        <v>-14.99</v>
+        <v>-15.23</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1220,43 +1204,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>30.09</v>
+        <v>29.66</v>
       </c>
       <c r="Z4">
-        <v>-29.39</v>
+        <v>-32.3</v>
       </c>
       <c r="AA4">
-        <v>-12.51</v>
+        <v>-16.47</v>
       </c>
       <c r="AB4">
-        <v>-16.89</v>
+        <v>-15.84</v>
       </c>
       <c r="AC4">
-        <v>19.94</v>
+        <v>19.26</v>
       </c>
       <c r="AD4">
-        <v>13.39</v>
+        <v>17.53</v>
       </c>
       <c r="AE4">
-        <v>29.38</v>
+        <v>28.45</v>
       </c>
       <c r="AF4">
-        <v>-53.99</v>
+        <v>-32.16</v>
       </c>
       <c r="AG4">
-        <v>1149.48</v>
+        <v>1152.11</v>
       </c>
       <c r="AH4">
-        <v>921.98</v>
+        <v>907.03</v>
       </c>
       <c r="AI4">
-        <v>1018.82</v>
+        <v>1013.55</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>44.73</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1267,10 +1251,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1223</v>
+        <v>1229.9</v>
       </c>
       <c r="D5">
-        <v>-2.36</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1279,46 +1263,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-13.73</v>
+        <v>-13.25</v>
       </c>
       <c r="H5">
-        <v>63.28</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="I5">
-        <v>-5.36</v>
+        <v>-4.64</v>
       </c>
       <c r="J5">
-        <v>-8.369999999999999</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="K5">
-        <v>7.84</v>
+        <v>9.41</v>
       </c>
       <c r="L5">
-        <v>11.83</v>
+        <v>12.25</v>
       </c>
       <c r="M5">
-        <v>16.57</v>
+        <v>16.75</v>
       </c>
       <c r="N5">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="P5">
-        <v>1251.22</v>
+        <v>1239.24</v>
       </c>
       <c r="Q5">
-        <v>1305.32</v>
+        <v>1297.8</v>
       </c>
       <c r="R5">
-        <v>1231.91</v>
+        <v>1235.84</v>
       </c>
       <c r="S5">
-        <v>1059.86</v>
+        <v>1060.53</v>
       </c>
       <c r="T5">
-        <v>15.39</v>
+        <v>15.97</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1333,43 +1317,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>39.75</v>
+        <v>41.27</v>
       </c>
       <c r="Z5">
-        <v>-2.81</v>
+        <v>-6.26</v>
       </c>
       <c r="AA5">
-        <v>13.68</v>
+        <v>9.69</v>
       </c>
       <c r="AB5">
-        <v>-16.49</v>
+        <v>-15.95</v>
       </c>
       <c r="AC5">
-        <v>13.17</v>
+        <v>8.81</v>
       </c>
       <c r="AD5">
-        <v>11.08</v>
+        <v>11.72</v>
       </c>
       <c r="AE5">
-        <v>47.54</v>
+        <v>48.1</v>
       </c>
       <c r="AF5">
-        <v>112.81</v>
+        <v>74.47</v>
       </c>
       <c r="AG5">
-        <v>1385.06</v>
+        <v>1376.07</v>
       </c>
       <c r="AH5">
-        <v>1225.59</v>
+        <v>1219.52</v>
       </c>
       <c r="AI5">
-        <v>1373.81</v>
+        <v>1361.7</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>37.26</v>
+        <v>42.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1380,10 +1364,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2054</v>
+        <v>1997.4</v>
       </c>
       <c r="D6">
-        <v>3.22</v>
+        <v>-2.76</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1392,46 +1376,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-11.48</v>
+        <v>-13.92</v>
       </c>
       <c r="H6">
-        <v>39.6</v>
+        <v>35.76</v>
       </c>
       <c r="I6">
-        <v>-2.58</v>
+        <v>-1.99</v>
       </c>
       <c r="J6">
-        <v>-2.29</v>
+        <v>-5.73</v>
       </c>
       <c r="K6">
-        <v>19.74</v>
+        <v>16.17</v>
       </c>
       <c r="L6">
-        <v>3.17</v>
+        <v>2.49</v>
       </c>
       <c r="M6">
-        <v>6.17</v>
+        <v>5.8</v>
       </c>
       <c r="N6">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O6">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="P6">
-        <v>2024.98</v>
+        <v>2016.88</v>
       </c>
       <c r="Q6">
-        <v>2075.53</v>
+        <v>2067.18</v>
       </c>
       <c r="R6">
-        <v>1971.08</v>
+        <v>1977.94</v>
       </c>
       <c r="S6">
-        <v>1881.16</v>
+        <v>1879.59</v>
       </c>
       <c r="T6">
-        <v>9.19</v>
+        <v>6.27</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1446,34 +1430,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>51.2</v>
+        <v>45.76</v>
       </c>
       <c r="Z6">
-        <v>7.92</v>
+        <v>2.94</v>
       </c>
       <c r="AA6">
-        <v>24.41</v>
+        <v>20.11</v>
       </c>
       <c r="AB6">
-        <v>-16.49</v>
+        <v>-17.17</v>
       </c>
       <c r="AC6">
-        <v>14.27</v>
+        <v>15.05</v>
       </c>
       <c r="AD6">
-        <v>6.57</v>
+        <v>10.68</v>
       </c>
       <c r="AE6">
-        <v>63.96</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="AF6">
-        <v>11.08</v>
+        <v>0.67</v>
       </c>
       <c r="AG6">
-        <v>2170.07</v>
+        <v>2158.13</v>
       </c>
       <c r="AH6">
-        <v>1980.99</v>
+        <v>1976.24</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1482,7 +1466,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>24.33</v>
+        <v>23.2</v>
       </c>
     </row>
   </sheetData>
@@ -1623,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1663,7 +1647,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1675,640 +1659,722 @@
         <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-15.2</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-14.62</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="D8" s="6">
+        <v>2.94</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-11.67</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-12.57</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-6.48</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-9.880000000000001</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-4.8</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-5.73</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-15.2</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-14.01</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-4.28</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-4.82</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>6.94</v>
+      </c>
+      <c r="D13" s="6">
+        <v>7.74</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-11.02</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-9.17</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-4.5</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-4.64</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-3.86</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.99</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-26.09</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-28.88</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-28.86</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-25.09</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-19.81</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-21.05</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>13.8</v>
+      </c>
+      <c r="D20" s="6">
+        <v>12.25</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.92</v>
+      </c>
+      <c r="D21" s="6">
+        <v>2.49</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-21.31</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-22.09</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>3.16</v>
+      </c>
+      <c r="D23" s="6">
+        <v>2.53</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-7.9</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-8.98</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>8.32</v>
+      </c>
+      <c r="D25" s="6">
+        <v>9.41</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>18.01</v>
+      </c>
+      <c r="D26" s="6">
+        <v>16.17</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-35.35</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-36.27</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-27.47</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-24.21</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-26.22</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-26.48</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-11.65</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-13.25</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-14.24</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-13.92</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>593.95</v>
+      </c>
+      <c r="D32" s="6">
+        <v>585.55</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-8.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>580.5</v>
+      </c>
+      <c r="D33" s="6">
+        <v>588.7</v>
+      </c>
+      <c r="E33" s="7">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>934.3</v>
+      </c>
+      <c r="D34" s="6">
+        <v>931</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1252.5</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1229.9</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-22.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>1990</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1997.4</v>
+      </c>
+      <c r="E36" s="7">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="6">
+        <v>26.58</v>
+      </c>
+      <c r="D37" s="6">
+        <v>24.61</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="6">
+        <v>58.82</v>
+      </c>
+      <c r="D38" s="6">
+        <v>62.09</v>
+      </c>
+      <c r="E38" s="7">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>30.09</v>
+      </c>
+      <c r="D39" s="6">
+        <v>29.66</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>44.32</v>
+      </c>
+      <c r="D40" s="6">
+        <v>41.27</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-3.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>44.24</v>
+      </c>
+      <c r="D41" s="6">
+        <v>45.76</v>
+      </c>
+      <c r="E41" s="7">
         <v>1.52</v>
       </c>
-      <c r="D9" s="7">
-        <v>2.24</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-33.08</v>
+      </c>
+      <c r="D42" s="6">
+        <v>97.42</v>
+      </c>
+      <c r="E42" s="7">
+        <v>130.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="6">
+        <v>526.67</v>
+      </c>
+      <c r="D43" s="6">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-518.05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-11.67</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-12.84</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>2.15</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-32.16</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-34.31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-6.48</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-8.369999999999999</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-44.95</v>
+      </c>
+      <c r="D45" s="6">
+        <v>74.47</v>
+      </c>
+      <c r="E45" s="7">
+        <v>119.42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-4.8</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-2.29</v>
-      </c>
-      <c r="E12" s="8">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-4.28</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-4.3</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="7">
-        <v>6.94</v>
-      </c>
-      <c r="D14" s="7">
-        <v>4.4</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-11.02</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-9.550000000000001</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-4.5</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-5.36</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-3.86</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-2.58</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-26.09</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-24.47</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-28.86</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-27.47</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-19.81</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-20.74</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
-        <v>13.8</v>
-      </c>
-      <c r="D21" s="7">
-        <v>11.83</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>0.92</v>
-      </c>
-      <c r="D22" s="7">
-        <v>3.17</v>
-      </c>
-      <c r="E22" s="8">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-21.31</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-19.6</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7">
-        <v>3.16</v>
-      </c>
-      <c r="D24" s="7">
-        <v>1.41</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-7.9</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-8.58</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>8.32</v>
-      </c>
-      <c r="D26" s="7">
-        <v>7.84</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>18.01</v>
-      </c>
-      <c r="D27" s="7">
-        <v>19.74</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-27.47</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-26.13</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-11.65</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-13.73</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-2.08</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-14.24</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-11.48</v>
-      </c>
-      <c r="E30" s="8">
-        <v>2.76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="7">
-        <v>1252.5</v>
-      </c>
-      <c r="D31" s="7">
-        <v>1223</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-29.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="7">
-        <v>1990</v>
-      </c>
-      <c r="D32" s="7">
-        <v>2054</v>
-      </c>
-      <c r="E32" s="8">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="7">
-        <v>99</v>
-      </c>
-      <c r="D33" s="7">
-        <v>79</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="7">
-        <v>79</v>
-      </c>
-      <c r="D34" s="7">
-        <v>99</v>
-      </c>
-      <c r="E34" s="8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C35" s="7">
-        <v>44.32</v>
-      </c>
-      <c r="D35" s="7">
-        <v>39.75</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-4.57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="7">
-        <v>44.24</v>
-      </c>
-      <c r="D36" s="7">
-        <v>51.2</v>
-      </c>
-      <c r="E36" s="8">
-        <v>6.96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="7">
-        <v>-33.08</v>
-      </c>
-      <c r="D37" s="7">
-        <v>27.31</v>
-      </c>
-      <c r="E37" s="8">
-        <v>60.39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C38" s="7">
-        <v>526.67</v>
-      </c>
-      <c r="D38" s="7">
-        <v>169.07</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-357.6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="7">
-        <v>2.15</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-53.99</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-56.14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-44.95</v>
-      </c>
-      <c r="D40" s="7">
-        <v>112.81</v>
-      </c>
-      <c r="E40" s="8">
-        <v>157.76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41" s="7">
+      <c r="C46" s="6">
         <v>-34.62</v>
       </c>
-      <c r="D41" s="7">
-        <v>11.08</v>
-      </c>
-      <c r="E41" s="8">
-        <v>45.7</v>
+      <c r="D46" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="E46" s="7">
+        <v>35.29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2328,60 +2394,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>57.92</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="12">
-        <v>41.3</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>40.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
-        <v>-7.1</v>
-      </c>
-      <c r="G2" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-0.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -2483,37 +2549,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15">
-        <v>0.1657</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.0617</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.005500000000000001</v>
-      </c>
-      <c r="D2" s="15">
-        <v>-0.0059</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.1466</v>
+      <c r="A2" s="14">
+        <v>0.1675</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.058</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0023</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0061</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1495</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,13 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>24.6 → 35.7</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>24.6</t>
+  </si>
+  <si>
+    <t>35.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,8 +405,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -912,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>585.55</v>
+        <v>603.8</v>
       </c>
       <c r="D2">
-        <v>-1.41</v>
+        <v>3.12</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -924,46 +930,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-36.27</v>
+        <v>-34.28</v>
       </c>
       <c r="H2">
-        <v>12.21</v>
+        <v>15.7</v>
       </c>
       <c r="I2">
-        <v>-4.82</v>
+        <v>-0.67</v>
       </c>
       <c r="J2">
-        <v>-14.62</v>
+        <v>-11.01</v>
       </c>
       <c r="K2">
-        <v>-22.09</v>
+        <v>-18.03</v>
       </c>
       <c r="L2">
-        <v>-28.88</v>
+        <v>-24.56</v>
       </c>
       <c r="M2">
-        <v>-14.95</v>
+        <v>-14.12</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P2">
-        <v>596.67</v>
+        <v>595.86</v>
       </c>
       <c r="Q2">
-        <v>628.1799999999999</v>
+        <v>624.73</v>
       </c>
       <c r="R2">
-        <v>688.84</v>
+        <v>685.02</v>
       </c>
       <c r="S2">
-        <v>678.9299999999999</v>
+        <v>678.65</v>
       </c>
       <c r="T2">
-        <v>-13.75</v>
+        <v>-11.03</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -978,34 +984,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>24.61</v>
+        <v>35.73</v>
       </c>
       <c r="Z2">
-        <v>-26.17</v>
+        <v>-24.84</v>
       </c>
       <c r="AA2">
-        <v>-24.79</v>
+        <v>-24.8</v>
       </c>
       <c r="AB2">
-        <v>-1.38</v>
+        <v>-0.04</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>24.19</v>
       </c>
       <c r="AD2">
-        <v>5.75</v>
+        <v>9.59</v>
       </c>
       <c r="AE2">
-        <v>25.13</v>
+        <v>26.07</v>
       </c>
       <c r="AF2">
-        <v>97.42</v>
+        <v>364.09</v>
       </c>
       <c r="AG2">
-        <v>680.17</v>
+        <v>673.3099999999999</v>
       </c>
       <c r="AH2">
-        <v>576.1900000000001</v>
+        <v>576.15</v>
       </c>
       <c r="AI2">
         <v>660.5599999999999</v>
@@ -1014,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>54.37</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,58 +1031,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>588.7</v>
+        <v>573.35</v>
       </c>
       <c r="D3">
-        <v>1.41</v>
+        <v>-2.61</v>
       </c>
       <c r="E3">
-        <v>776.75</v>
+        <v>761.6</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-24.21</v>
+        <v>-24.72</v>
       </c>
       <c r="H3">
-        <v>14.76</v>
+        <v>11.76</v>
       </c>
       <c r="I3">
-        <v>7.74</v>
+        <v>3.82</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>-0.37</v>
       </c>
       <c r="K3">
-        <v>2.53</v>
+        <v>-2.47</v>
       </c>
       <c r="L3">
-        <v>-25.09</v>
+        <v>-26.19</v>
       </c>
       <c r="M3">
-        <v>0.23</v>
+        <v>-0.92</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P3">
-        <v>572.83</v>
+        <v>577.05</v>
       </c>
       <c r="Q3">
-        <v>564.09</v>
+        <v>564.29</v>
       </c>
       <c r="R3">
-        <v>565.04</v>
+        <v>565.14</v>
       </c>
       <c r="S3">
-        <v>578.5599999999999</v>
+        <v>578.1</v>
       </c>
       <c r="T3">
-        <v>1.75</v>
+        <v>-0.82</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1088,37 +1094,37 @@
         <v>43</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>62.09</v>
+        <v>53.51</v>
       </c>
       <c r="Z3">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="AA3">
-        <v>-1.36</v>
+        <v>-0.61</v>
       </c>
       <c r="AB3">
-        <v>3.42</v>
+        <v>2.98</v>
       </c>
       <c r="AC3">
-        <v>100</v>
+        <v>88.48</v>
       </c>
       <c r="AD3">
-        <v>87.28</v>
+        <v>93.02</v>
       </c>
       <c r="AE3">
-        <v>15.22</v>
+        <v>15.59</v>
       </c>
       <c r="AF3">
-        <v>8.619999999999999</v>
+        <v>13.85</v>
       </c>
       <c r="AG3">
-        <v>589.04</v>
+        <v>589.49</v>
       </c>
       <c r="AH3">
-        <v>539.14</v>
+        <v>539.1</v>
       </c>
       <c r="AI3">
         <v>546.4400000000001</v>
@@ -1127,7 +1133,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>31.69</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D4">
-        <v>-0.35</v>
+        <v>-0.11</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1150,46 +1156,46 @@
         <v>910</v>
       </c>
       <c r="G4">
-        <v>-26.48</v>
+        <v>-26.56</v>
       </c>
       <c r="H4">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="I4">
-        <v>-9.17</v>
+        <v>2.2</v>
       </c>
       <c r="J4">
-        <v>-12.57</v>
+        <v>-11.78</v>
       </c>
       <c r="K4">
-        <v>-8.98</v>
+        <v>-8.58</v>
       </c>
       <c r="L4">
-        <v>-21.05</v>
+        <v>-21.36</v>
       </c>
       <c r="M4">
-        <v>-0.61</v>
+        <v>-1.18</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P4">
-        <v>929.3</v>
+        <v>933.3</v>
       </c>
       <c r="Q4">
-        <v>1029.57</v>
+        <v>1022.63</v>
       </c>
       <c r="R4">
-        <v>1039.62</v>
+        <v>1037.95</v>
       </c>
       <c r="S4">
-        <v>1098.3</v>
+        <v>1097.46</v>
       </c>
       <c r="T4">
-        <v>-15.23</v>
+        <v>-15.26</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1204,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.66</v>
+        <v>29.53</v>
       </c>
       <c r="Z4">
-        <v>-32.3</v>
+        <v>-34.29</v>
       </c>
       <c r="AA4">
-        <v>-16.47</v>
+        <v>-20.03</v>
       </c>
       <c r="AB4">
-        <v>-15.84</v>
+        <v>-14.26</v>
       </c>
       <c r="AC4">
-        <v>19.26</v>
+        <v>18.74</v>
       </c>
       <c r="AD4">
-        <v>17.53</v>
+        <v>19.31</v>
       </c>
       <c r="AE4">
-        <v>28.45</v>
+        <v>27.23</v>
       </c>
       <c r="AF4">
-        <v>-32.16</v>
+        <v>-45.23</v>
       </c>
       <c r="AG4">
-        <v>1152.11</v>
+        <v>1151.38</v>
       </c>
       <c r="AH4">
-        <v>907.03</v>
+        <v>893.88</v>
       </c>
       <c r="AI4">
         <v>1013.55</v>
@@ -1240,7 +1246,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>48.65</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1251,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1229.9</v>
+        <v>1218</v>
       </c>
       <c r="D5">
-        <v>0.5600000000000001</v>
+        <v>-0.97</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1263,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-13.25</v>
+        <v>-14.09</v>
       </c>
       <c r="H5">
-        <v>64.20999999999999</v>
+        <v>62.62</v>
       </c>
       <c r="I5">
-        <v>-4.64</v>
+        <v>-1.39</v>
       </c>
       <c r="J5">
-        <v>-9.880000000000001</v>
+        <v>-11.77</v>
       </c>
       <c r="K5">
-        <v>9.41</v>
+        <v>9.59</v>
       </c>
       <c r="L5">
-        <v>12.25</v>
+        <v>3.63</v>
       </c>
       <c r="M5">
-        <v>16.75</v>
+        <v>17.06</v>
       </c>
       <c r="N5">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O5">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="P5">
-        <v>1239.24</v>
+        <v>1235.8</v>
       </c>
       <c r="Q5">
-        <v>1297.8</v>
+        <v>1290.95</v>
       </c>
       <c r="R5">
-        <v>1235.84</v>
+        <v>1239.27</v>
       </c>
       <c r="S5">
-        <v>1060.53</v>
+        <v>1061.14</v>
       </c>
       <c r="T5">
-        <v>15.97</v>
+        <v>14.78</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1317,43 +1323,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>41.27</v>
+        <v>39.42</v>
       </c>
       <c r="Z5">
-        <v>-6.26</v>
+        <v>-9.84</v>
       </c>
       <c r="AA5">
-        <v>9.69</v>
+        <v>5.79</v>
       </c>
       <c r="AB5">
-        <v>-15.95</v>
+        <v>-15.62</v>
       </c>
       <c r="AC5">
-        <v>8.81</v>
+        <v>2.53</v>
       </c>
       <c r="AD5">
-        <v>11.72</v>
+        <v>8.17</v>
       </c>
       <c r="AE5">
-        <v>48.1</v>
+        <v>46.38</v>
       </c>
       <c r="AF5">
-        <v>74.47</v>
+        <v>-56.89</v>
       </c>
       <c r="AG5">
-        <v>1376.07</v>
+        <v>1372.09</v>
       </c>
       <c r="AH5">
-        <v>1219.52</v>
+        <v>1209.81</v>
       </c>
       <c r="AI5">
-        <v>1361.7</v>
+        <v>1356.95</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>42.01</v>
+        <v>46.12</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1364,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1997.4</v>
+        <v>2007.3</v>
       </c>
       <c r="D6">
-        <v>-2.76</v>
+        <v>0.5</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1376,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-13.92</v>
+        <v>-13.49</v>
       </c>
       <c r="H6">
-        <v>35.76</v>
+        <v>36.43</v>
       </c>
       <c r="I6">
-        <v>-1.99</v>
+        <v>-0.38</v>
       </c>
       <c r="J6">
-        <v>-5.73</v>
+        <v>-7.25</v>
       </c>
       <c r="K6">
-        <v>16.17</v>
+        <v>15.57</v>
       </c>
       <c r="L6">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="M6">
-        <v>5.8</v>
+        <v>6.22</v>
       </c>
       <c r="N6">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O6">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P6">
-        <v>2016.88</v>
+        <v>2015.34</v>
       </c>
       <c r="Q6">
-        <v>2067.18</v>
+        <v>2063.49</v>
       </c>
       <c r="R6">
-        <v>1977.94</v>
+        <v>1984.4</v>
       </c>
       <c r="S6">
-        <v>1879.59</v>
+        <v>1878.13</v>
       </c>
       <c r="T6">
-        <v>6.27</v>
+        <v>6.88</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1430,34 +1436,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>45.76</v>
+        <v>46.82</v>
       </c>
       <c r="Z6">
-        <v>2.94</v>
+        <v>-0.2</v>
       </c>
       <c r="AA6">
-        <v>20.11</v>
+        <v>16.05</v>
       </c>
       <c r="AB6">
-        <v>-17.17</v>
+        <v>-16.26</v>
       </c>
       <c r="AC6">
-        <v>15.05</v>
+        <v>21.28</v>
       </c>
       <c r="AD6">
-        <v>10.68</v>
+        <v>16.87</v>
       </c>
       <c r="AE6">
-        <v>64.04000000000001</v>
+        <v>62.31</v>
       </c>
       <c r="AF6">
-        <v>0.67</v>
+        <v>-39.2</v>
       </c>
       <c r="AG6">
-        <v>2158.13</v>
+        <v>2157.98</v>
       </c>
       <c r="AH6">
-        <v>1976.24</v>
+        <v>1969.01</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1466,7 +1472,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>23.2</v>
+        <v>23.71</v>
       </c>
     </row>
   </sheetData>
@@ -1607,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1647,7 +1653,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1659,15 +1665,15 @@
         <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1679,16 +1685,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1699,13 +1705,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-15.2</v>
+        <v>-14.62</v>
       </c>
       <c r="D7" s="6">
-        <v>-14.62</v>
+        <v>-11.01</v>
       </c>
       <c r="E7" s="7">
-        <v>0.58</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1716,13 +1722,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>1.52</v>
+        <v>2.94</v>
       </c>
       <c r="D8" s="6">
-        <v>2.94</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.42</v>
+        <v>-0.37</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-3.31</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1733,13 +1739,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-11.67</v>
+        <v>-12.57</v>
       </c>
       <c r="D9" s="6">
-        <v>-12.57</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.9</v>
+        <v>-11.78</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.79</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1750,13 +1756,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-6.48</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="D10" s="6">
-        <v>-9.880000000000001</v>
+        <v>-11.77</v>
       </c>
       <c r="E10" s="8">
-        <v>-3.4</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1767,13 +1773,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.8</v>
+        <v>-5.73</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.73</v>
+        <v>-7.25</v>
       </c>
       <c r="E11" s="8">
-        <v>-0.93</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1784,13 +1790,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-4.28</v>
+        <v>-4.82</v>
       </c>
       <c r="D12" s="6">
-        <v>-4.82</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.54</v>
+        <v>-0.67</v>
+      </c>
+      <c r="E12" s="7">
+        <v>4.15</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1801,13 +1807,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>6.94</v>
+        <v>7.74</v>
       </c>
       <c r="D13" s="6">
-        <v>7.74</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.8</v>
+        <v>3.82</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-3.92</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1818,13 +1824,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-11.02</v>
+        <v>-9.17</v>
       </c>
       <c r="D14" s="6">
-        <v>-9.17</v>
+        <v>2.2</v>
       </c>
       <c r="E14" s="7">
-        <v>1.85</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1835,13 +1841,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.5</v>
+        <v>-4.64</v>
       </c>
       <c r="D15" s="6">
-        <v>-4.64</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.14</v>
+        <v>-1.39</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.25</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1852,13 +1858,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.86</v>
+        <v>-1.99</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.99</v>
+        <v>-0.38</v>
       </c>
       <c r="E16" s="7">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1869,13 +1875,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>-26.09</v>
+        <v>-28.88</v>
       </c>
       <c r="D17" s="6">
-        <v>-28.88</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-2.79</v>
+        <v>-24.56</v>
+      </c>
+      <c r="E17" s="7">
+        <v>4.32</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1886,13 +1892,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>-28.86</v>
+        <v>-25.09</v>
       </c>
       <c r="D18" s="6">
-        <v>-25.09</v>
-      </c>
-      <c r="E18" s="7">
-        <v>3.77</v>
+        <v>-26.19</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1903,13 +1909,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-19.81</v>
+        <v>-21.05</v>
       </c>
       <c r="D19" s="6">
-        <v>-21.05</v>
+        <v>-21.36</v>
       </c>
       <c r="E19" s="8">
-        <v>-1.24</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1920,13 +1926,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>13.8</v>
+        <v>12.25</v>
       </c>
       <c r="D20" s="6">
-        <v>12.25</v>
+        <v>3.63</v>
       </c>
       <c r="E20" s="8">
-        <v>-1.55</v>
+        <v>-8.619999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1937,13 +1943,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>0.92</v>
+        <v>2.49</v>
       </c>
       <c r="D21" s="6">
-        <v>2.49</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.57</v>
+        <v>2.41</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1954,13 +1960,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-21.31</v>
+        <v>-22.09</v>
       </c>
       <c r="D22" s="6">
-        <v>-22.09</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.78</v>
+        <v>-18.03</v>
+      </c>
+      <c r="E22" s="7">
+        <v>4.06</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1971,13 +1977,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>3.16</v>
+        <v>2.53</v>
       </c>
       <c r="D23" s="6">
-        <v>2.53</v>
+        <v>-2.47</v>
       </c>
       <c r="E23" s="8">
-        <v>-0.63</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1988,13 +1994,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-7.9</v>
+        <v>-8.98</v>
       </c>
       <c r="D24" s="6">
-        <v>-8.98</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.08</v>
+        <v>-8.58</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.4</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2005,13 +2011,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>8.32</v>
+        <v>9.41</v>
       </c>
       <c r="D25" s="6">
-        <v>9.41</v>
+        <v>9.59</v>
       </c>
       <c r="E25" s="7">
-        <v>1.09</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2022,13 +2028,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>18.01</v>
+        <v>16.17</v>
       </c>
       <c r="D26" s="6">
-        <v>16.17</v>
+        <v>15.57</v>
       </c>
       <c r="E26" s="8">
-        <v>-1.84</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2039,13 +2045,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-35.35</v>
+        <v>-36.27</v>
       </c>
       <c r="D27" s="6">
-        <v>-36.27</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.92</v>
+        <v>-34.28</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.99</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2056,13 +2062,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-27.47</v>
+        <v>-24.21</v>
       </c>
       <c r="D28" s="6">
-        <v>-24.21</v>
-      </c>
-      <c r="E28" s="7">
-        <v>3.26</v>
+        <v>-24.72</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2073,13 +2079,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-26.22</v>
+        <v>-26.48</v>
       </c>
       <c r="D29" s="6">
-        <v>-26.48</v>
+        <v>-26.56</v>
       </c>
       <c r="E29" s="8">
-        <v>-0.26</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2090,13 +2096,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-11.65</v>
+        <v>-13.25</v>
       </c>
       <c r="D30" s="6">
-        <v>-13.25</v>
+        <v>-14.09</v>
       </c>
       <c r="E30" s="8">
-        <v>-1.6</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2107,13 +2113,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-14.24</v>
+        <v>-13.92</v>
       </c>
       <c r="D31" s="6">
-        <v>-13.92</v>
+        <v>-13.49</v>
       </c>
       <c r="E31" s="7">
-        <v>0.32</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2124,13 +2130,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>593.95</v>
+        <v>585.55</v>
       </c>
       <c r="D32" s="6">
-        <v>585.55</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-8.4</v>
+        <v>603.8</v>
+      </c>
+      <c r="E32" s="7">
+        <v>18.25</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2141,13 +2147,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>580.5</v>
+        <v>588.7</v>
       </c>
       <c r="D33" s="6">
-        <v>588.7</v>
-      </c>
-      <c r="E33" s="7">
-        <v>8.199999999999999</v>
+        <v>573.35</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-15.35</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2158,13 +2164,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>934.3</v>
+        <v>931</v>
       </c>
       <c r="D34" s="6">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E34" s="8">
-        <v>-3.3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2175,13 +2181,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>1252.5</v>
+        <v>1229.9</v>
       </c>
       <c r="D35" s="6">
-        <v>1229.9</v>
+        <v>1218</v>
       </c>
       <c r="E35" s="8">
-        <v>-22.6</v>
+        <v>-11.9</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2192,183 +2198,217 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>1990</v>
+        <v>1997.4</v>
       </c>
       <c r="D36" s="6">
-        <v>1997.4</v>
+        <v>2007.3</v>
       </c>
       <c r="E36" s="7">
-        <v>7.4</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C37" s="6">
-        <v>26.58</v>
+        <v>99</v>
       </c>
       <c r="D37" s="6">
-        <v>24.61</v>
+        <v>79</v>
       </c>
       <c r="E37" s="8">
-        <v>-1.97</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C38" s="6">
-        <v>58.82</v>
+        <v>79</v>
       </c>
       <c r="D38" s="6">
-        <v>62.09</v>
+        <v>99</v>
       </c>
       <c r="E38" s="7">
-        <v>3.27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>30.09</v>
+        <v>24.61</v>
       </c>
       <c r="D39" s="6">
-        <v>29.66</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.43</v>
+        <v>35.73</v>
+      </c>
+      <c r="E39" s="7">
+        <v>11.12</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>44.32</v>
+        <v>62.09</v>
       </c>
       <c r="D40" s="6">
-        <v>41.27</v>
+        <v>53.51</v>
       </c>
       <c r="E40" s="8">
-        <v>-3.05</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>44.24</v>
+        <v>29.66</v>
       </c>
       <c r="D41" s="6">
-        <v>45.76</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.52</v>
+        <v>29.53</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C42" s="6">
-        <v>-33.08</v>
+        <v>41.27</v>
       </c>
       <c r="D42" s="6">
-        <v>97.42</v>
-      </c>
-      <c r="E42" s="7">
-        <v>130.5</v>
+        <v>39.42</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C43" s="6">
-        <v>526.67</v>
+        <v>45.76</v>
       </c>
       <c r="D43" s="6">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-518.05</v>
+        <v>46.82</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.06</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>2.15</v>
+        <v>97.42</v>
       </c>
       <c r="D44" s="6">
-        <v>-32.16</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-34.31</v>
+        <v>364.09</v>
+      </c>
+      <c r="E44" s="7">
+        <v>266.67</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>-44.95</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="D45" s="6">
-        <v>74.47</v>
+        <v>13.85</v>
       </c>
       <c r="E45" s="7">
-        <v>119.42</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>-34.62</v>
+        <v>-32.16</v>
       </c>
       <c r="D46" s="6">
+        <v>-45.23</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-13.07</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>74.47</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-56.89</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-131.36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="6">
         <v>0.67</v>
       </c>
-      <c r="E46" s="7">
-        <v>35.29</v>
+      <c r="D48" s="6">
+        <v>-39.2</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-39.87</v>
       </c>
     </row>
   </sheetData>
@@ -2398,28 +2438,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2427,22 +2467,22 @@
         <v>42</v>
       </c>
       <c r="B2" s="11">
-        <v>57.92</v>
+        <v>49.92</v>
       </c>
       <c r="C2" s="12">
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>40.7</v>
+        <v>41</v>
       </c>
       <c r="E2" s="11">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-8</v>
+        <v>-8.4</v>
       </c>
       <c r="G2" s="11">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2567,19 +2607,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.1675</v>
+        <v>0.1706</v>
       </c>
       <c r="B2" s="14">
-        <v>0.058</v>
+        <v>0.0622</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0023</v>
+        <v>-0.0092</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0061</v>
+        <v>-0.0118</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1495</v>
+        <v>-0.1412</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,16 +184,16 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>24.6 → 35.7</t>
+    <t>29.5 → 35.0</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>24.6</t>
-  </si>
-  <si>
-    <t>35.7</t>
+    <t>29.5</t>
+  </si>
+  <si>
+    <t>35.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -918,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>603.8</v>
+        <v>601.8</v>
       </c>
       <c r="D2">
-        <v>3.12</v>
+        <v>-0.33</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,46 +930,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-34.28</v>
+        <v>-34.5</v>
       </c>
       <c r="H2">
-        <v>15.7</v>
+        <v>15.32</v>
       </c>
       <c r="I2">
-        <v>-0.67</v>
+        <v>-0.04</v>
       </c>
       <c r="J2">
-        <v>-11.01</v>
+        <v>-10.55</v>
       </c>
       <c r="K2">
-        <v>-18.03</v>
+        <v>-22.03</v>
       </c>
       <c r="L2">
-        <v>-24.56</v>
+        <v>-25.72</v>
       </c>
       <c r="M2">
-        <v>-14.12</v>
+        <v>-14.17</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P2">
-        <v>595.86</v>
+        <v>595.8099999999999</v>
       </c>
       <c r="Q2">
-        <v>624.73</v>
+        <v>621.54</v>
       </c>
       <c r="R2">
-        <v>685.02</v>
+        <v>681.53</v>
       </c>
       <c r="S2">
-        <v>678.65</v>
+        <v>678.36</v>
       </c>
       <c r="T2">
-        <v>-11.03</v>
+        <v>-11.29</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -984,34 +984,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>35.73</v>
+        <v>35.11</v>
       </c>
       <c r="Z2">
-        <v>-24.84</v>
+        <v>-23.67</v>
       </c>
       <c r="AA2">
-        <v>-24.8</v>
+        <v>-24.58</v>
       </c>
       <c r="AB2">
-        <v>-0.04</v>
+        <v>0.91</v>
       </c>
       <c r="AC2">
-        <v>24.19</v>
+        <v>55.69</v>
       </c>
       <c r="AD2">
-        <v>9.59</v>
+        <v>26.63</v>
       </c>
       <c r="AE2">
-        <v>26.07</v>
+        <v>26.06</v>
       </c>
       <c r="AF2">
-        <v>364.09</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="AG2">
-        <v>673.3099999999999</v>
+        <v>667.12</v>
       </c>
       <c r="AH2">
-        <v>576.15</v>
+        <v>575.97</v>
       </c>
       <c r="AI2">
         <v>660.5599999999999</v>
@@ -1020,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>52.06</v>
+        <v>50.01</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1031,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>573.35</v>
+        <v>581.65</v>
       </c>
       <c r="D3">
-        <v>-2.61</v>
+        <v>1.45</v>
       </c>
       <c r="E3">
         <v>761.6</v>
@@ -1043,46 +1043,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-24.72</v>
+        <v>-23.63</v>
       </c>
       <c r="H3">
-        <v>11.76</v>
+        <v>13.38</v>
       </c>
       <c r="I3">
-        <v>3.82</v>
+        <v>3.46</v>
       </c>
       <c r="J3">
-        <v>-0.37</v>
+        <v>2.17</v>
       </c>
       <c r="K3">
-        <v>-2.47</v>
+        <v>0.46</v>
       </c>
       <c r="L3">
-        <v>-26.19</v>
+        <v>-22.71</v>
       </c>
       <c r="M3">
-        <v>-0.92</v>
+        <v>-0.63</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P3">
-        <v>577.05</v>
+        <v>580.9400000000001</v>
       </c>
       <c r="Q3">
-        <v>564.29</v>
+        <v>565.3200000000001</v>
       </c>
       <c r="R3">
-        <v>565.14</v>
+        <v>565.5599999999999</v>
       </c>
       <c r="S3">
-        <v>578.1</v>
+        <v>577.7</v>
       </c>
       <c r="T3">
-        <v>-0.82</v>
+        <v>0.68</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1094,37 +1094,37 @@
         <v>43</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>53.51</v>
+        <v>56.97</v>
       </c>
       <c r="Z3">
-        <v>2.37</v>
+        <v>3.24</v>
       </c>
       <c r="AA3">
-        <v>-0.61</v>
+        <v>0.16</v>
       </c>
       <c r="AB3">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="AC3">
-        <v>88.48</v>
+        <v>81.61</v>
       </c>
       <c r="AD3">
-        <v>93.02</v>
+        <v>90.03</v>
       </c>
       <c r="AE3">
-        <v>15.59</v>
+        <v>15.39</v>
       </c>
       <c r="AF3">
-        <v>13.85</v>
+        <v>-15.12</v>
       </c>
       <c r="AG3">
-        <v>589.49</v>
+        <v>591.62</v>
       </c>
       <c r="AH3">
-        <v>539.1</v>
+        <v>539.02</v>
       </c>
       <c r="AI3">
         <v>546.4400000000001</v>
@@ -1133,7 +1133,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>30.07</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>930</v>
+        <v>947</v>
       </c>
       <c r="D4">
-        <v>-0.11</v>
+        <v>1.83</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1156,46 +1156,46 @@
         <v>910</v>
       </c>
       <c r="G4">
-        <v>-26.56</v>
+        <v>-25.22</v>
       </c>
       <c r="H4">
-        <v>2.2</v>
+        <v>4.07</v>
       </c>
       <c r="I4">
-        <v>2.2</v>
+        <v>1.08</v>
       </c>
       <c r="J4">
-        <v>-11.78</v>
+        <v>-11.4</v>
       </c>
       <c r="K4">
-        <v>-8.58</v>
+        <v>-7.83</v>
       </c>
       <c r="L4">
-        <v>-21.36</v>
+        <v>-18.98</v>
       </c>
       <c r="M4">
-        <v>-1.18</v>
+        <v>-0.82</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P4">
-        <v>933.3</v>
+        <v>935.3200000000001</v>
       </c>
       <c r="Q4">
-        <v>1022.63</v>
+        <v>1017.05</v>
       </c>
       <c r="R4">
-        <v>1037.95</v>
+        <v>1036.34</v>
       </c>
       <c r="S4">
-        <v>1097.46</v>
+        <v>1096.68</v>
       </c>
       <c r="T4">
-        <v>-15.26</v>
+        <v>-13.65</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1210,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.53</v>
+        <v>35.04</v>
       </c>
       <c r="Z4">
-        <v>-34.29</v>
+        <v>-34.1</v>
       </c>
       <c r="AA4">
-        <v>-20.03</v>
+        <v>-22.85</v>
       </c>
       <c r="AB4">
-        <v>-14.26</v>
+        <v>-11.26</v>
       </c>
       <c r="AC4">
-        <v>18.74</v>
+        <v>23.34</v>
       </c>
       <c r="AD4">
-        <v>19.31</v>
+        <v>20.45</v>
       </c>
       <c r="AE4">
-        <v>27.23</v>
+        <v>26.57</v>
       </c>
       <c r="AF4">
-        <v>-45.23</v>
+        <v>-12.33</v>
       </c>
       <c r="AG4">
-        <v>1151.38</v>
+        <v>1148.87</v>
       </c>
       <c r="AH4">
-        <v>893.88</v>
+        <v>885.23</v>
       </c>
       <c r="AI4">
         <v>1013.55</v>
@@ -1246,7 +1246,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>51.38</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1218</v>
+        <v>1223.4</v>
       </c>
       <c r="D5">
-        <v>-0.97</v>
+        <v>0.44</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-14.09</v>
+        <v>-13.71</v>
       </c>
       <c r="H5">
-        <v>62.62</v>
+        <v>63.34</v>
       </c>
       <c r="I5">
-        <v>-1.39</v>
+        <v>-2.56</v>
       </c>
       <c r="J5">
-        <v>-11.77</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="K5">
-        <v>9.59</v>
+        <v>8.6</v>
       </c>
       <c r="L5">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="M5">
-        <v>17.06</v>
+        <v>17.16</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="P5">
-        <v>1235.8</v>
+        <v>1229.36</v>
       </c>
       <c r="Q5">
-        <v>1290.95</v>
+        <v>1284.84</v>
       </c>
       <c r="R5">
-        <v>1239.27</v>
+        <v>1243.08</v>
       </c>
       <c r="S5">
-        <v>1061.14</v>
+        <v>1061.73</v>
       </c>
       <c r="T5">
-        <v>14.78</v>
+        <v>15.23</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1323,34 +1323,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>39.42</v>
+        <v>40.72</v>
       </c>
       <c r="Z5">
-        <v>-9.84</v>
+        <v>-12.1</v>
       </c>
       <c r="AA5">
-        <v>5.79</v>
+        <v>2.21</v>
       </c>
       <c r="AB5">
-        <v>-15.62</v>
+        <v>-14.31</v>
       </c>
       <c r="AC5">
-        <v>2.53</v>
+        <v>4.65</v>
       </c>
       <c r="AD5">
-        <v>8.17</v>
+        <v>5.33</v>
       </c>
       <c r="AE5">
-        <v>46.38</v>
+        <v>45.89</v>
       </c>
       <c r="AF5">
-        <v>-56.89</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="AG5">
-        <v>1372.09</v>
+        <v>1367.05</v>
       </c>
       <c r="AH5">
-        <v>1209.81</v>
+        <v>1202.63</v>
       </c>
       <c r="AI5">
         <v>1356.95</v>
@@ -1359,7 +1359,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>46.12</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2007.3</v>
+        <v>2020</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1382,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-13.49</v>
+        <v>-12.94</v>
       </c>
       <c r="H6">
-        <v>36.43</v>
+        <v>37.29</v>
       </c>
       <c r="I6">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="J6">
-        <v>-7.25</v>
+        <v>-2.94</v>
       </c>
       <c r="K6">
-        <v>15.57</v>
+        <v>16.57</v>
       </c>
       <c r="L6">
-        <v>2.41</v>
+        <v>4.31</v>
       </c>
       <c r="M6">
-        <v>6.22</v>
+        <v>6.35</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P6">
-        <v>2015.34</v>
+        <v>2013.74</v>
       </c>
       <c r="Q6">
-        <v>2063.49</v>
+        <v>2062.44</v>
       </c>
       <c r="R6">
-        <v>1984.4</v>
+        <v>1991.97</v>
       </c>
       <c r="S6">
-        <v>1878.13</v>
+        <v>1876.79</v>
       </c>
       <c r="T6">
-        <v>6.88</v>
+        <v>7.63</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1436,34 +1436,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>46.82</v>
+        <v>48.23</v>
       </c>
       <c r="Z6">
-        <v>-0.2</v>
+        <v>-1.65</v>
       </c>
       <c r="AA6">
-        <v>16.05</v>
+        <v>12.51</v>
       </c>
       <c r="AB6">
-        <v>-16.26</v>
+        <v>-14.16</v>
       </c>
       <c r="AC6">
-        <v>21.28</v>
+        <v>20.57</v>
       </c>
       <c r="AD6">
-        <v>16.87</v>
+        <v>18.97</v>
       </c>
       <c r="AE6">
-        <v>62.31</v>
+        <v>60.76</v>
       </c>
       <c r="AF6">
-        <v>-39.2</v>
+        <v>-58.26</v>
       </c>
       <c r="AG6">
-        <v>2157.98</v>
+        <v>2158.44</v>
       </c>
       <c r="AH6">
-        <v>1969.01</v>
+        <v>1966.45</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1472,7 +1472,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>23.71</v>
+        <v>20.83</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1705,13 +1705,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-14.62</v>
+        <v>-11.01</v>
       </c>
       <c r="D7" s="6">
-        <v>-11.01</v>
+        <v>-10.55</v>
       </c>
       <c r="E7" s="7">
-        <v>3.61</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1722,13 +1722,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>2.94</v>
+        <v>-0.37</v>
       </c>
       <c r="D8" s="6">
-        <v>-0.37</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-3.31</v>
+        <v>2.17</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1739,13 +1739,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-12.57</v>
+        <v>-11.78</v>
       </c>
       <c r="D9" s="6">
-        <v>-11.78</v>
+        <v>-11.4</v>
       </c>
       <c r="E9" s="7">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1756,13 +1756,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-9.880000000000001</v>
+        <v>-11.77</v>
       </c>
       <c r="D10" s="6">
-        <v>-11.77</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.89</v>
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.06</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1773,13 +1773,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.73</v>
+        <v>-7.25</v>
       </c>
       <c r="D11" s="6">
-        <v>-7.25</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.52</v>
+        <v>-2.94</v>
+      </c>
+      <c r="E11" s="7">
+        <v>4.31</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1790,13 +1790,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-4.82</v>
+        <v>-0.67</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.67</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" s="7">
-        <v>4.15</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1807,13 +1807,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>7.74</v>
+        <v>3.82</v>
       </c>
       <c r="D13" s="6">
-        <v>3.82</v>
+        <v>3.46</v>
       </c>
       <c r="E13" s="8">
-        <v>-3.92</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1824,13 +1824,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-9.17</v>
+        <v>2.2</v>
       </c>
       <c r="D14" s="6">
-        <v>2.2</v>
-      </c>
-      <c r="E14" s="7">
-        <v>11.37</v>
+        <v>1.08</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1841,13 +1841,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.64</v>
+        <v>-1.39</v>
       </c>
       <c r="D15" s="6">
-        <v>-1.39</v>
-      </c>
-      <c r="E15" s="7">
-        <v>3.25</v>
+        <v>-2.56</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1858,13 +1858,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.99</v>
+        <v>-0.38</v>
       </c>
       <c r="D16" s="6">
-        <v>-0.38</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.61</v>
+        <v>-0.39</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1875,13 +1875,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>-28.88</v>
+        <v>-24.56</v>
       </c>
       <c r="D17" s="6">
-        <v>-24.56</v>
-      </c>
-      <c r="E17" s="7">
-        <v>4.32</v>
+        <v>-25.72</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1892,13 +1892,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>-25.09</v>
+        <v>-26.19</v>
       </c>
       <c r="D18" s="6">
-        <v>-26.19</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.1</v>
+        <v>-22.71</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3.48</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1909,13 +1909,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-21.05</v>
+        <v>-21.36</v>
       </c>
       <c r="D19" s="6">
-        <v>-21.36</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.31</v>
+        <v>-18.98</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.38</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1926,13 +1926,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>12.25</v>
+        <v>3.63</v>
       </c>
       <c r="D20" s="6">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="E20" s="8">
-        <v>-8.619999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1943,13 +1943,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="D21" s="6">
-        <v>2.41</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.08</v>
+        <v>4.31</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.9</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1960,13 +1960,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-22.09</v>
+        <v>-18.03</v>
       </c>
       <c r="D22" s="6">
-        <v>-18.03</v>
-      </c>
-      <c r="E22" s="7">
-        <v>4.06</v>
+        <v>-22.03</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1977,13 +1977,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>2.53</v>
+        <v>-2.47</v>
       </c>
       <c r="D23" s="6">
-        <v>-2.47</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-5</v>
+        <v>0.46</v>
+      </c>
+      <c r="E23" s="7">
+        <v>2.93</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1994,13 +1994,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-8.98</v>
+        <v>-8.58</v>
       </c>
       <c r="D24" s="6">
-        <v>-8.58</v>
+        <v>-7.83</v>
       </c>
       <c r="E24" s="7">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2011,13 +2011,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>9.41</v>
+        <v>9.59</v>
       </c>
       <c r="D25" s="6">
-        <v>9.59</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.18</v>
+        <v>8.6</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2028,13 +2028,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>16.17</v>
+        <v>15.57</v>
       </c>
       <c r="D26" s="6">
-        <v>15.57</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.6</v>
+        <v>16.57</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2045,13 +2045,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-36.27</v>
+        <v>-34.28</v>
       </c>
       <c r="D27" s="6">
-        <v>-34.28</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.99</v>
+        <v>-34.5</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2062,13 +2062,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-24.21</v>
+        <v>-24.72</v>
       </c>
       <c r="D28" s="6">
-        <v>-24.72</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.51</v>
+        <v>-23.63</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.09</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2079,13 +2079,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-26.48</v>
+        <v>-26.56</v>
       </c>
       <c r="D29" s="6">
-        <v>-26.56</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.08</v>
+        <v>-25.22</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.34</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2096,13 +2096,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-13.25</v>
+        <v>-14.09</v>
       </c>
       <c r="D30" s="6">
-        <v>-14.09</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.84</v>
+        <v>-13.71</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.38</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2113,13 +2113,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-13.92</v>
+        <v>-13.49</v>
       </c>
       <c r="D31" s="6">
-        <v>-13.49</v>
+        <v>-12.94</v>
       </c>
       <c r="E31" s="7">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2130,13 +2130,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>585.55</v>
+        <v>603.8</v>
       </c>
       <c r="D32" s="6">
-        <v>603.8</v>
-      </c>
-      <c r="E32" s="7">
-        <v>18.25</v>
+        <v>601.8</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2147,13 +2147,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>588.7</v>
+        <v>573.35</v>
       </c>
       <c r="D33" s="6">
-        <v>573.35</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-15.35</v>
+        <v>581.65</v>
+      </c>
+      <c r="E33" s="7">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2164,13 +2164,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D34" s="6">
-        <v>930</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1</v>
+        <v>947</v>
+      </c>
+      <c r="E34" s="7">
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2181,13 +2181,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>1229.9</v>
+        <v>1218</v>
       </c>
       <c r="D35" s="6">
-        <v>1218</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-11.9</v>
+        <v>1223.4</v>
+      </c>
+      <c r="E35" s="7">
+        <v>5.4</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2198,217 +2198,183 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>1997.4</v>
+        <v>2007.3</v>
       </c>
       <c r="D36" s="6">
-        <v>2007.3</v>
+        <v>2020</v>
       </c>
       <c r="E36" s="7">
-        <v>9.9</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C37" s="6">
-        <v>99</v>
+        <v>35.73</v>
       </c>
       <c r="D37" s="6">
-        <v>79</v>
+        <v>35.11</v>
       </c>
       <c r="E37" s="8">
-        <v>-20</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>79</v>
+        <v>53.51</v>
       </c>
       <c r="D38" s="6">
-        <v>99</v>
+        <v>56.97</v>
       </c>
       <c r="E38" s="7">
-        <v>20</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>24.61</v>
+        <v>29.53</v>
       </c>
       <c r="D39" s="6">
-        <v>35.73</v>
+        <v>35.04</v>
       </c>
       <c r="E39" s="7">
-        <v>11.12</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>62.09</v>
+        <v>39.42</v>
       </c>
       <c r="D40" s="6">
-        <v>53.51</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-8.58</v>
+        <v>40.72</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.3</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>29.66</v>
+        <v>46.82</v>
       </c>
       <c r="D41" s="6">
-        <v>29.53</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.13</v>
+        <v>48.23</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.41</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C42" s="6">
-        <v>41.27</v>
+        <v>364.09</v>
       </c>
       <c r="D42" s="6">
-        <v>39.42</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="E42" s="8">
-        <v>-1.85</v>
+        <v>-373.2</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>45.76</v>
+        <v>13.85</v>
       </c>
       <c r="D43" s="6">
-        <v>46.82</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.06</v>
+        <v>-15.12</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-28.97</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>97.42</v>
+        <v>-45.23</v>
       </c>
       <c r="D44" s="6">
-        <v>364.09</v>
+        <v>-12.33</v>
       </c>
       <c r="E44" s="7">
-        <v>266.67</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>8.619999999999999</v>
+        <v>-56.89</v>
       </c>
       <c r="D45" s="6">
-        <v>13.85</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="E45" s="7">
-        <v>5.23</v>
+        <v>124.15</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>-32.16</v>
+        <v>-39.2</v>
       </c>
       <c r="D46" s="6">
-        <v>-45.23</v>
+        <v>-58.26</v>
       </c>
       <c r="E46" s="8">
-        <v>-13.07</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>74.47</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-56.89</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-131.36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>0.67</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-39.2</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-39.87</v>
+        <v>-19.06</v>
       </c>
     </row>
   </sheetData>
@@ -2467,19 +2433,19 @@
         <v>42</v>
       </c>
       <c r="B2" s="11">
-        <v>49.92</v>
+        <v>57.92</v>
       </c>
       <c r="C2" s="12">
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>41</v>
+        <v>43.2</v>
       </c>
       <c r="E2" s="11">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-8.4</v>
+        <v>-6.5</v>
       </c>
       <c r="G2" s="11">
         <v>-0.8</v>
@@ -2607,19 +2573,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.1706</v>
+        <v>0.1716</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0622</v>
+        <v>0.0635</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0092</v>
+        <v>-0.0063</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0118</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1412</v>
+        <v>-0.1417</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,19 +181,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.5 → 35.0</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>49.9 → 50.5</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>29.5</t>
-  </si>
-  <si>
-    <t>35.0</t>
+    <t>49.9</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -395,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -403,10 +412,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -918,10 +928,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>601.8</v>
+        <v>592.7</v>
       </c>
       <c r="D2">
-        <v>-0.33</v>
+        <v>-1.52</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,88 +940,88 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-34.5</v>
+        <v>-35.49</v>
       </c>
       <c r="H2">
-        <v>15.32</v>
+        <v>13.58</v>
       </c>
       <c r="I2">
-        <v>-0.04</v>
+        <v>-0.21</v>
       </c>
       <c r="J2">
-        <v>-10.55</v>
+        <v>-10.07</v>
       </c>
       <c r="K2">
-        <v>-22.03</v>
+        <v>-20.65</v>
       </c>
       <c r="L2">
-        <v>-25.72</v>
+        <v>-28.43</v>
       </c>
       <c r="M2">
-        <v>-14.17</v>
+        <v>-14.46</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P2">
-        <v>595.8099999999999</v>
+        <v>597.14</v>
       </c>
       <c r="Q2">
-        <v>621.54</v>
+        <v>615.09</v>
       </c>
       <c r="R2">
-        <v>681.53</v>
+        <v>674.6</v>
       </c>
       <c r="S2">
-        <v>678.36</v>
+        <v>677.65</v>
       </c>
       <c r="T2">
-        <v>-11.29</v>
+        <v>-12.54</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
         <v>43</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.11</v>
+        <v>32.22</v>
       </c>
       <c r="Z2">
-        <v>-23.67</v>
+        <v>-22.02</v>
       </c>
       <c r="AA2">
-        <v>-24.58</v>
+        <v>-23.73</v>
       </c>
       <c r="AB2">
-        <v>0.91</v>
+        <v>1.71</v>
       </c>
       <c r="AC2">
-        <v>55.69</v>
+        <v>85.92</v>
       </c>
       <c r="AD2">
-        <v>26.63</v>
+        <v>76.3</v>
       </c>
       <c r="AE2">
-        <v>26.06</v>
+        <v>25.4</v>
       </c>
       <c r="AF2">
-        <v>-9.109999999999999</v>
+        <v>-41.57</v>
       </c>
       <c r="AG2">
-        <v>667.12</v>
+        <v>653.4400000000001</v>
       </c>
       <c r="AH2">
-        <v>575.97</v>
+        <v>576.73</v>
       </c>
       <c r="AI2">
         <v>660.5599999999999</v>
@@ -1020,7 +1030,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>50.01</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1041,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>581.65</v>
+        <v>572.75</v>
       </c>
       <c r="D3">
-        <v>1.45</v>
+        <v>-0.31</v>
       </c>
       <c r="E3">
         <v>761.6</v>
@@ -1043,46 +1053,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-23.63</v>
+        <v>-24.8</v>
       </c>
       <c r="H3">
-        <v>13.38</v>
+        <v>11.65</v>
       </c>
       <c r="I3">
-        <v>3.46</v>
+        <v>-1.34</v>
       </c>
       <c r="J3">
-        <v>2.17</v>
+        <v>-0.15</v>
       </c>
       <c r="K3">
-        <v>0.46</v>
+        <v>-1.98</v>
       </c>
       <c r="L3">
-        <v>-22.71</v>
+        <v>-24.74</v>
       </c>
       <c r="M3">
-        <v>-0.63</v>
+        <v>-0.18</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P3">
-        <v>580.9400000000001</v>
+        <v>578.2</v>
       </c>
       <c r="Q3">
-        <v>565.3200000000001</v>
+        <v>565.28</v>
       </c>
       <c r="R3">
-        <v>565.5599999999999</v>
+        <v>566.04</v>
       </c>
       <c r="S3">
-        <v>577.7</v>
+        <v>576.88</v>
       </c>
       <c r="T3">
-        <v>0.68</v>
+        <v>-0.72</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1094,34 +1104,34 @@
         <v>43</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>56.97</v>
+        <v>52.4</v>
       </c>
       <c r="Z3">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="AA3">
-        <v>0.16</v>
+        <v>1.28</v>
       </c>
       <c r="AB3">
-        <v>3.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC3">
-        <v>81.61</v>
+        <v>68.34</v>
       </c>
       <c r="AD3">
-        <v>90.03</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="AE3">
-        <v>15.39</v>
+        <v>15.02</v>
       </c>
       <c r="AF3">
-        <v>-15.12</v>
+        <v>32.04</v>
       </c>
       <c r="AG3">
-        <v>591.62</v>
+        <v>591.55</v>
       </c>
       <c r="AH3">
         <v>539.02</v>
@@ -1133,7 +1143,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>28.66</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1154,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>947</v>
+        <v>928.9</v>
       </c>
       <c r="D4">
-        <v>1.83</v>
+        <v>-0.44</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1156,22 +1166,22 @@
         <v>910</v>
       </c>
       <c r="G4">
-        <v>-25.22</v>
+        <v>-26.65</v>
       </c>
       <c r="H4">
-        <v>4.07</v>
+        <v>2.08</v>
       </c>
       <c r="I4">
-        <v>1.08</v>
+        <v>-0.58</v>
       </c>
       <c r="J4">
-        <v>-11.4</v>
+        <v>-12.33</v>
       </c>
       <c r="K4">
-        <v>-7.83</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="L4">
-        <v>-18.98</v>
+        <v>-22.73</v>
       </c>
       <c r="M4">
         <v>-0.82</v>
@@ -1180,22 +1190,22 @@
         <v>40</v>
       </c>
       <c r="O4">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="P4">
-        <v>935.3200000000001</v>
+        <v>933.98</v>
       </c>
       <c r="Q4">
-        <v>1017.05</v>
+        <v>1003.49</v>
       </c>
       <c r="R4">
-        <v>1036.34</v>
+        <v>1032.73</v>
       </c>
       <c r="S4">
-        <v>1096.68</v>
+        <v>1094.44</v>
       </c>
       <c r="T4">
-        <v>-13.65</v>
+        <v>-15.13</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1210,43 +1220,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.04</v>
+        <v>32.11</v>
       </c>
       <c r="Z4">
-        <v>-34.1</v>
+        <v>-35.07</v>
       </c>
       <c r="AA4">
-        <v>-22.85</v>
+        <v>-27.19</v>
       </c>
       <c r="AB4">
-        <v>-11.26</v>
+        <v>-7.89</v>
       </c>
       <c r="AC4">
-        <v>23.34</v>
+        <v>30.94</v>
       </c>
       <c r="AD4">
-        <v>20.45</v>
+        <v>27.23</v>
       </c>
       <c r="AE4">
-        <v>26.57</v>
+        <v>25.31</v>
       </c>
       <c r="AF4">
-        <v>-12.33</v>
+        <v>-15.08</v>
       </c>
       <c r="AG4">
-        <v>1148.87</v>
+        <v>1140.12</v>
       </c>
       <c r="AH4">
-        <v>885.23</v>
+        <v>866.85</v>
       </c>
       <c r="AI4">
-        <v>1013.55</v>
+        <v>1002.27</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>51.8</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1267,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1223.4</v>
+        <v>1184.5</v>
       </c>
       <c r="D5">
-        <v>0.44</v>
+        <v>-3.7</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,46 +1279,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-13.71</v>
+        <v>-16.45</v>
       </c>
       <c r="H5">
-        <v>63.34</v>
+        <v>58.14</v>
       </c>
       <c r="I5">
-        <v>-2.56</v>
+        <v>-3.15</v>
       </c>
       <c r="J5">
-        <v>-9.710000000000001</v>
+        <v>-11.09</v>
       </c>
       <c r="K5">
-        <v>8.6</v>
+        <v>3.86</v>
       </c>
       <c r="L5">
-        <v>3.56</v>
+        <v>-7.77</v>
       </c>
       <c r="M5">
-        <v>17.16</v>
+        <v>16.82</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="P5">
-        <v>1229.36</v>
+        <v>1217.16</v>
       </c>
       <c r="Q5">
-        <v>1284.84</v>
+        <v>1272.31</v>
       </c>
       <c r="R5">
-        <v>1243.08</v>
+        <v>1250.43</v>
       </c>
       <c r="S5">
-        <v>1061.73</v>
+        <v>1062.62</v>
       </c>
       <c r="T5">
-        <v>15.23</v>
+        <v>11.47</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1323,43 +1333,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>40.72</v>
+        <v>35.17</v>
       </c>
       <c r="Z5">
-        <v>-12.1</v>
+        <v>-17.55</v>
       </c>
       <c r="AA5">
-        <v>2.21</v>
+        <v>-4.21</v>
       </c>
       <c r="AB5">
-        <v>-14.31</v>
+        <v>-13.34</v>
       </c>
       <c r="AC5">
-        <v>4.65</v>
+        <v>7.98</v>
       </c>
       <c r="AD5">
-        <v>5.33</v>
+        <v>6.87</v>
       </c>
       <c r="AE5">
-        <v>45.89</v>
+        <v>46.14</v>
       </c>
       <c r="AF5">
-        <v>67.26000000000001</v>
+        <v>79.03</v>
       </c>
       <c r="AG5">
-        <v>1367.05</v>
+        <v>1361.14</v>
       </c>
       <c r="AH5">
-        <v>1202.63</v>
+        <v>1183.48</v>
       </c>
       <c r="AI5">
-        <v>1356.95</v>
+        <v>1348.98</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>46.8</v>
+        <v>50.28</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1380,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2020</v>
+        <v>2039.9</v>
       </c>
       <c r="D6">
-        <v>0.63</v>
+        <v>0.24</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1382,46 +1392,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-12.94</v>
+        <v>-12.08</v>
       </c>
       <c r="H6">
-        <v>37.29</v>
+        <v>38.65</v>
       </c>
       <c r="I6">
-        <v>-0.39</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J6">
-        <v>-2.94</v>
+        <v>0.55</v>
       </c>
       <c r="K6">
-        <v>16.57</v>
+        <v>15.89</v>
       </c>
       <c r="L6">
-        <v>4.31</v>
+        <v>1.49</v>
       </c>
       <c r="M6">
-        <v>6.35</v>
+        <v>6.93</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P6">
-        <v>2013.74</v>
+        <v>2019.92</v>
       </c>
       <c r="Q6">
-        <v>2062.44</v>
+        <v>2060.81</v>
       </c>
       <c r="R6">
-        <v>1991.97</v>
+        <v>2007.28</v>
       </c>
       <c r="S6">
-        <v>1876.79</v>
+        <v>1874.16</v>
       </c>
       <c r="T6">
-        <v>7.63</v>
+        <v>8.84</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1436,34 +1446,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>48.23</v>
+        <v>50.47</v>
       </c>
       <c r="Z6">
-        <v>-1.65</v>
+        <v>-1.1</v>
       </c>
       <c r="AA6">
-        <v>12.51</v>
+        <v>7.53</v>
       </c>
       <c r="AB6">
-        <v>-14.16</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="AC6">
-        <v>20.57</v>
+        <v>43.2</v>
       </c>
       <c r="AD6">
-        <v>18.97</v>
+        <v>32.08</v>
       </c>
       <c r="AE6">
-        <v>60.76</v>
+        <v>55.56</v>
       </c>
       <c r="AF6">
-        <v>-58.26</v>
+        <v>-57.56</v>
       </c>
       <c r="AG6">
-        <v>2158.44</v>
+        <v>2156.59</v>
       </c>
       <c r="AH6">
-        <v>1966.45</v>
+        <v>1965.04</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1472,7 +1482,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>20.83</v>
+        <v>16.45</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1653,7 +1663,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1671,716 +1681,736 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="C7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-11.01</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-10.55</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="C8" s="7">
+        <v>-9.57</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-10.07</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-0.37</v>
-      </c>
-      <c r="D8" s="6">
-        <v>2.17</v>
-      </c>
-      <c r="E8" s="7">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="C9" s="7">
+        <v>2.38</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-2.53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-11.78</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-11.4</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="C10" s="7">
+        <v>-11.86</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-12.33</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-11.77</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="C11" s="7">
+        <v>-8.59</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-11.09</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-7.25</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-2.94</v>
-      </c>
-      <c r="E11" s="7">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="C12" s="7">
+        <v>-0.29</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.55</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-0.67</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-0.04</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="C13" s="7">
+        <v>1.33</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-0.21</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>3.82</v>
-      </c>
-      <c r="D13" s="6">
-        <v>3.46</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="C14" s="7">
+        <v>-1.02</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-1.34</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>2.2</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1.08</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="C15" s="7">
+        <v>-0.14</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-0.58</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-1.39</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.56</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="C16" s="7">
+        <v>-1.8</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-3.15</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-0.38</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.39</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="C17" s="7">
+        <v>2.26</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C18" s="7">
+        <v>-24.53</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-28.43</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-23.46</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-24.74</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-21.76</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-22.73</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-3.45</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-7.77</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-4.32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>1.63</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1.49</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-20.06</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-20.65</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="7">
+        <v>0.42</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-1.98</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-8.57</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="7">
+        <v>5.98</v>
+      </c>
+      <c r="D26" s="7">
+        <v>3.86</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7">
+        <v>15.15</v>
+      </c>
+      <c r="D27" s="7">
+        <v>15.89</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-34.49</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-35.49</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="7">
         <v>-24.56</v>
       </c>
-      <c r="D17" s="6">
-        <v>-25.72</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="D29" s="7">
+        <v>-24.8</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-26.32</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-26.65</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-13.24</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-16.45</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-3.21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-12.3</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-12.08</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="7">
+        <v>601.85</v>
+      </c>
+      <c r="D33" s="7">
+        <v>592.7</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-9.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-26.19</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-22.71</v>
-      </c>
-      <c r="E18" s="7">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B34" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="7">
+        <v>574.55</v>
+      </c>
+      <c r="D34" s="7">
+        <v>572.75</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-21.36</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-18.98</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2.38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="7">
+        <v>933</v>
+      </c>
+      <c r="D35" s="7">
+        <v>928.9</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-4.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>3.63</v>
-      </c>
-      <c r="D20" s="6">
-        <v>3.56</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="7">
+        <v>1230</v>
+      </c>
+      <c r="D36" s="7">
+        <v>1184.5</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-45.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>2.41</v>
-      </c>
-      <c r="D21" s="6">
-        <v>4.31</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B37" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="7">
+        <v>2035</v>
+      </c>
+      <c r="D37" s="7">
+        <v>2039.9</v>
+      </c>
+      <c r="E37" s="9">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-18.03</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-22.03</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="7">
+        <v>35.14</v>
+      </c>
+      <c r="D38" s="7">
+        <v>32.22</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-2.92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-2.47</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="7">
+        <v>53.31</v>
+      </c>
+      <c r="D39" s="7">
+        <v>52.4</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-8.58</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-7.83</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="7">
+        <v>32.76</v>
+      </c>
+      <c r="D40" s="7">
+        <v>32.11</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>9.59</v>
-      </c>
-      <c r="D25" s="6">
-        <v>8.6</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="7">
+        <v>42.35</v>
+      </c>
+      <c r="D41" s="7">
+        <v>35.17</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-7.18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>15.57</v>
-      </c>
-      <c r="D26" s="6">
-        <v>16.57</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="7">
+        <v>49.91</v>
+      </c>
+      <c r="D42" s="7">
+        <v>50.47</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-34.28</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-34.5</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-43.59</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-41.57</v>
+      </c>
+      <c r="E43" s="9">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-24.72</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-23.63</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-46.8</v>
+      </c>
+      <c r="D44" s="7">
+        <v>32.04</v>
+      </c>
+      <c r="E44" s="9">
+        <v>78.84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-26.56</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-25.22</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-30.01</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-15.08</v>
+      </c>
+      <c r="E45" s="9">
+        <v>14.93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-14.09</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-13.71</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-71.45</v>
+      </c>
+      <c r="D46" s="7">
+        <v>79.03</v>
+      </c>
+      <c r="E46" s="9">
+        <v>150.48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-13.49</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-12.94</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>603.8</v>
-      </c>
-      <c r="D32" s="6">
-        <v>601.8</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>573.35</v>
-      </c>
-      <c r="D33" s="6">
-        <v>581.65</v>
-      </c>
-      <c r="E33" s="7">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>930</v>
-      </c>
-      <c r="D34" s="6">
-        <v>947</v>
-      </c>
-      <c r="E34" s="7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1218</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1223.4</v>
-      </c>
-      <c r="E35" s="7">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2007.3</v>
-      </c>
-      <c r="D36" s="6">
-        <v>2020</v>
-      </c>
-      <c r="E36" s="7">
-        <v>12.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>35.73</v>
-      </c>
-      <c r="D37" s="6">
-        <v>35.11</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>53.51</v>
-      </c>
-      <c r="D38" s="6">
-        <v>56.97</v>
-      </c>
-      <c r="E38" s="7">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>29.53</v>
-      </c>
-      <c r="D39" s="6">
-        <v>35.04</v>
-      </c>
-      <c r="E39" s="7">
-        <v>5.51</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>39.42</v>
-      </c>
-      <c r="D40" s="6">
-        <v>40.72</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>46.82</v>
-      </c>
-      <c r="D41" s="6">
-        <v>48.23</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="B47" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="6">
-        <v>364.09</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-9.109999999999999</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-373.2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>13.85</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-15.12</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-28.97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-45.23</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-12.33</v>
-      </c>
-      <c r="E44" s="7">
-        <v>32.9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-56.89</v>
-      </c>
-      <c r="D45" s="6">
-        <v>67.26000000000001</v>
-      </c>
-      <c r="E45" s="7">
-        <v>124.15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-39.2</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-58.26</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-19.06</v>
+      <c r="C47" s="7">
+        <v>-57.62</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-57.56</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2400,60 +2430,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>70</v>
       </c>
+      <c r="G1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>49.92</v>
+      </c>
+      <c r="C2" s="13">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>43.2</v>
-      </c>
-      <c r="E2" s="11">
-        <v>60</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-6.5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-0.8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="12">
+        <v>40.5</v>
+      </c>
+      <c r="E2" s="12">
+        <v>40</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-6.6</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-2.6</v>
+      </c>
+      <c r="H2" s="12">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -2555,37 +2585,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1716</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0635</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0063</v>
-      </c>
-      <c r="D2" s="14">
+      <c r="A2" s="15">
+        <v>0.1682</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.0693</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.0018</v>
+      </c>
+      <c r="D2" s="15">
         <v>-0.008199999999999999</v>
       </c>
-      <c r="E2" s="14">
-        <v>-0.1417</v>
+      <c r="E2" s="15">
+        <v>-0.1446</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,28 +181,13 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>49.9 → 50.5</t>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.9</t>
-  </si>
-  <si>
-    <t>50.5</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -404,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -412,7 +397,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -928,10 +912,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>592.7</v>
+        <v>597.25</v>
       </c>
       <c r="D2">
-        <v>-1.52</v>
+        <v>0.77</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -940,25 +924,25 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-35.49</v>
+        <v>-34.99</v>
       </c>
       <c r="H2">
-        <v>13.58</v>
+        <v>14.45</v>
       </c>
       <c r="I2">
-        <v>-0.21</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>-10.07</v>
+        <v>-10.13</v>
       </c>
       <c r="K2">
-        <v>-20.65</v>
+        <v>-21.54</v>
       </c>
       <c r="L2">
-        <v>-28.43</v>
+        <v>-27.84</v>
       </c>
       <c r="M2">
-        <v>-14.46</v>
+        <v>-14.23</v>
       </c>
       <c r="N2">
         <v>21</v>
@@ -967,19 +951,19 @@
         <v>9</v>
       </c>
       <c r="P2">
-        <v>597.14</v>
+        <v>599.48</v>
       </c>
       <c r="Q2">
-        <v>615.09</v>
+        <v>612.48</v>
       </c>
       <c r="R2">
-        <v>674.6</v>
+        <v>671.29</v>
       </c>
       <c r="S2">
-        <v>677.65</v>
+        <v>677.42</v>
       </c>
       <c r="T2">
-        <v>-12.54</v>
+        <v>-11.83</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -994,34 +978,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>32.22</v>
+        <v>35.11</v>
       </c>
       <c r="Z2">
-        <v>-22.02</v>
+        <v>-21.05</v>
       </c>
       <c r="AA2">
-        <v>-23.73</v>
+        <v>-23.19</v>
       </c>
       <c r="AB2">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="AC2">
-        <v>85.92</v>
+        <v>85.91</v>
       </c>
       <c r="AD2">
-        <v>76.3</v>
+        <v>86.37</v>
       </c>
       <c r="AE2">
-        <v>25.4</v>
+        <v>25.35</v>
       </c>
       <c r="AF2">
-        <v>-41.57</v>
+        <v>-44.57</v>
       </c>
       <c r="AG2">
-        <v>653.4400000000001</v>
+        <v>647.99</v>
       </c>
       <c r="AH2">
-        <v>576.73</v>
+        <v>576.97</v>
       </c>
       <c r="AI2">
         <v>660.5599999999999</v>
@@ -1030,7 +1014,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>48.66</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1041,61 +1025,61 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>572.75</v>
+        <v>610.1</v>
       </c>
       <c r="D3">
-        <v>-0.31</v>
+        <v>6.52</v>
       </c>
       <c r="E3">
-        <v>761.6</v>
+        <v>754</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-24.8</v>
+        <v>-19.08</v>
       </c>
       <c r="H3">
-        <v>11.65</v>
+        <v>18.93</v>
       </c>
       <c r="I3">
-        <v>-1.34</v>
+        <v>3.64</v>
       </c>
       <c r="J3">
-        <v>-0.15</v>
+        <v>6.22</v>
       </c>
       <c r="K3">
-        <v>-1.98</v>
+        <v>3.73</v>
       </c>
       <c r="L3">
-        <v>-24.74</v>
+        <v>-19.89</v>
       </c>
       <c r="M3">
-        <v>-0.18</v>
+        <v>0.74</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="P3">
-        <v>578.2</v>
+        <v>582.48</v>
       </c>
       <c r="Q3">
-        <v>565.28</v>
+        <v>566.9299999999999</v>
       </c>
       <c r="R3">
-        <v>566.04</v>
+        <v>566.83</v>
       </c>
       <c r="S3">
-        <v>576.88</v>
+        <v>576.84</v>
       </c>
       <c r="T3">
-        <v>-0.72</v>
+        <v>5.77</v>
       </c>
       <c r="U3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -1104,37 +1088,37 @@
         <v>43</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y3">
-        <v>52.4</v>
+        <v>65.63</v>
       </c>
       <c r="Z3">
-        <v>3.21</v>
+        <v>6.06</v>
       </c>
       <c r="AA3">
-        <v>1.28</v>
+        <v>2.23</v>
       </c>
       <c r="AB3">
-        <v>1.93</v>
+        <v>3.83</v>
       </c>
       <c r="AC3">
-        <v>68.34</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="AD3">
-        <v>73.26000000000001</v>
+        <v>71.13</v>
       </c>
       <c r="AE3">
-        <v>15.02</v>
+        <v>17.88</v>
       </c>
       <c r="AF3">
-        <v>32.04</v>
+        <v>1615.98</v>
       </c>
       <c r="AG3">
-        <v>591.55</v>
+        <v>599.67</v>
       </c>
       <c r="AH3">
-        <v>539.02</v>
+        <v>534.2</v>
       </c>
       <c r="AI3">
         <v>546.4400000000001</v>
@@ -1143,7 +1127,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>24.51</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1154,10 +1138,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>928.9</v>
+        <v>929.2</v>
       </c>
       <c r="D4">
-        <v>-0.44</v>
+        <v>0.03</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1166,46 +1150,46 @@
         <v>910</v>
       </c>
       <c r="G4">
-        <v>-26.65</v>
+        <v>-26.62</v>
       </c>
       <c r="H4">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="I4">
-        <v>-0.58</v>
+        <v>-0.19</v>
       </c>
       <c r="J4">
-        <v>-12.33</v>
+        <v>-13.46</v>
       </c>
       <c r="K4">
-        <v>-9.970000000000001</v>
+        <v>-11.03</v>
       </c>
       <c r="L4">
-        <v>-22.73</v>
+        <v>-24.45</v>
       </c>
       <c r="M4">
-        <v>-0.82</v>
+        <v>-1.34</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P4">
-        <v>933.98</v>
+        <v>933.62</v>
       </c>
       <c r="Q4">
-        <v>1003.49</v>
+        <v>996.6</v>
       </c>
       <c r="R4">
-        <v>1032.73</v>
+        <v>1030.58</v>
       </c>
       <c r="S4">
-        <v>1094.44</v>
+        <v>1093.43</v>
       </c>
       <c r="T4">
-        <v>-15.13</v>
+        <v>-15.02</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1220,43 +1204,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="Z4">
-        <v>-35.07</v>
+        <v>-34.95</v>
       </c>
       <c r="AA4">
-        <v>-27.19</v>
+        <v>-28.74</v>
       </c>
       <c r="AB4">
-        <v>-7.89</v>
+        <v>-6.21</v>
       </c>
       <c r="AC4">
-        <v>30.94</v>
+        <v>29.44</v>
       </c>
       <c r="AD4">
-        <v>27.23</v>
+        <v>29.26</v>
       </c>
       <c r="AE4">
-        <v>25.31</v>
+        <v>24.41</v>
       </c>
       <c r="AF4">
-        <v>-15.08</v>
+        <v>-72.23</v>
       </c>
       <c r="AG4">
-        <v>1140.12</v>
+        <v>1133.66</v>
       </c>
       <c r="AH4">
-        <v>866.85</v>
+        <v>859.54</v>
       </c>
       <c r="AI4">
-        <v>1002.27</v>
+        <v>997.77</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>53.83</v>
+        <v>54.94</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1267,10 +1251,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1184.5</v>
+        <v>1165.9</v>
       </c>
       <c r="D5">
-        <v>-3.7</v>
+        <v>-1.57</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1279,46 +1263,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-16.45</v>
+        <v>-17.76</v>
       </c>
       <c r="H5">
-        <v>58.14</v>
+        <v>55.66</v>
       </c>
       <c r="I5">
-        <v>-3.15</v>
+        <v>-5.2</v>
       </c>
       <c r="J5">
-        <v>-11.09</v>
+        <v>-12.53</v>
       </c>
       <c r="K5">
-        <v>3.86</v>
+        <v>2.8</v>
       </c>
       <c r="L5">
-        <v>-7.77</v>
+        <v>-9.49</v>
       </c>
       <c r="M5">
-        <v>16.82</v>
+        <v>16.51</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P5">
-        <v>1217.16</v>
+        <v>1204.36</v>
       </c>
       <c r="Q5">
-        <v>1272.31</v>
+        <v>1265.15</v>
       </c>
       <c r="R5">
-        <v>1250.43</v>
+        <v>1252.29</v>
       </c>
       <c r="S5">
-        <v>1062.62</v>
+        <v>1063.02</v>
       </c>
       <c r="T5">
-        <v>11.47</v>
+        <v>9.68</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1333,43 +1317,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>35.17</v>
+        <v>32.72</v>
       </c>
       <c r="Z5">
-        <v>-17.55</v>
+        <v>-22.24</v>
       </c>
       <c r="AA5">
-        <v>-4.21</v>
+        <v>-7.82</v>
       </c>
       <c r="AB5">
-        <v>-13.34</v>
+        <v>-14.43</v>
       </c>
       <c r="AC5">
-        <v>7.98</v>
+        <v>5.85</v>
       </c>
       <c r="AD5">
-        <v>6.87</v>
+        <v>7.27</v>
       </c>
       <c r="AE5">
-        <v>46.14</v>
+        <v>46.65</v>
       </c>
       <c r="AF5">
-        <v>79.03</v>
+        <v>165.33</v>
       </c>
       <c r="AG5">
-        <v>1361.14</v>
+        <v>1364</v>
       </c>
       <c r="AH5">
-        <v>1183.48</v>
+        <v>1166.29</v>
       </c>
       <c r="AI5">
-        <v>1348.98</v>
+        <v>1296.09</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>50.28</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1380,10 +1364,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2039.9</v>
+        <v>2049</v>
       </c>
       <c r="D6">
-        <v>0.24</v>
+        <v>0.45</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1392,25 +1376,25 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-12.08</v>
+        <v>-11.69</v>
       </c>
       <c r="H6">
-        <v>38.65</v>
+        <v>39.26</v>
       </c>
       <c r="I6">
-        <v>-0.6899999999999999</v>
+        <v>2.58</v>
       </c>
       <c r="J6">
-        <v>0.55</v>
+        <v>-1.43</v>
       </c>
       <c r="K6">
-        <v>15.89</v>
+        <v>14.56</v>
       </c>
       <c r="L6">
-        <v>1.49</v>
+        <v>0.35</v>
       </c>
       <c r="M6">
-        <v>6.93</v>
+        <v>7.3</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1419,19 +1403,19 @@
         <v>62</v>
       </c>
       <c r="P6">
-        <v>2019.92</v>
+        <v>2030.24</v>
       </c>
       <c r="Q6">
-        <v>2060.81</v>
+        <v>2056.43</v>
       </c>
       <c r="R6">
-        <v>2007.28</v>
+        <v>2012.93</v>
       </c>
       <c r="S6">
-        <v>1874.16</v>
+        <v>1873.44</v>
       </c>
       <c r="T6">
-        <v>8.84</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1446,34 +1430,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>50.47</v>
+        <v>51.57</v>
       </c>
       <c r="Z6">
-        <v>-1.1</v>
+        <v>0.01</v>
       </c>
       <c r="AA6">
-        <v>7.53</v>
+        <v>6.03</v>
       </c>
       <c r="AB6">
-        <v>-8.640000000000001</v>
+        <v>-6.02</v>
       </c>
       <c r="AC6">
-        <v>43.2</v>
+        <v>52.28</v>
       </c>
       <c r="AD6">
-        <v>32.08</v>
+        <v>42.65</v>
       </c>
       <c r="AE6">
-        <v>55.56</v>
+        <v>54.27</v>
       </c>
       <c r="AF6">
-        <v>-57.56</v>
+        <v>-36.25</v>
       </c>
       <c r="AG6">
-        <v>2156.59</v>
+        <v>2145.39</v>
       </c>
       <c r="AH6">
-        <v>1965.04</v>
+        <v>1967.48</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1482,7 +1466,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>16.45</v>
+        <v>15.48</v>
       </c>
     </row>
   </sheetData>
@@ -1623,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1663,7 +1647,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1675,742 +1659,722 @@
         <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-10.07</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-10.13</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-0.15</v>
+      </c>
+      <c r="D8" s="6">
+        <v>6.22</v>
+      </c>
+      <c r="E8" s="8">
+        <v>6.37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-12.33</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-13.46</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-11.09</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-12.53</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.55</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-1.43</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-9.57</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-10.07</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-0.21</v>
+      </c>
+      <c r="D12" s="6">
+        <v>2</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2.38</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-0.15</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-2.53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-1.34</v>
+      </c>
+      <c r="D13" s="6">
+        <v>3.64</v>
+      </c>
+      <c r="E13" s="8">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-11.86</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-12.33</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-0.58</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.19</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-8.59</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-11.09</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-3.15</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-5.2</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-0.29</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0.55</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="D16" s="6">
+        <v>2.58</v>
+      </c>
+      <c r="E16" s="8">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7">
-        <v>1.33</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-0.21</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-1.54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-28.43</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-27.84</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-1.02</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-1.34</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-24.74</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-19.89</v>
+      </c>
+      <c r="E18" s="8">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-0.14</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-0.58</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-22.73</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-24.45</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-1.8</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-3.15</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-7.77</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-9.49</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>2.26</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-2.95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1.49</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-24.53</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-28.43</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-3.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-20.65</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-21.54</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-23.46</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-24.74</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-1.98</v>
+      </c>
+      <c r="D23" s="6">
+        <v>3.73</v>
+      </c>
+      <c r="E23" s="8">
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-21.76</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-22.73</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-11.03</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-3.45</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-7.77</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-4.32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>3.86</v>
+      </c>
+      <c r="D25" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>1.63</v>
-      </c>
-      <c r="D22" s="7">
-        <v>1.49</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>15.89</v>
+      </c>
+      <c r="D26" s="6">
+        <v>14.56</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-20.06</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-20.65</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-35.49</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-34.99</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7">
-        <v>0.42</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-1.98</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-24.8</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-19.08</v>
+      </c>
+      <c r="E28" s="8">
+        <v>5.72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-8.57</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-26.65</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-26.62</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>5.98</v>
-      </c>
-      <c r="D26" s="7">
-        <v>3.86</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-2.12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-16.45</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-17.76</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>15.15</v>
-      </c>
-      <c r="D27" s="7">
-        <v>15.89</v>
-      </c>
-      <c r="E27" s="9">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-12.08</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-11.69</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-34.49</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-35.49</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>592.7</v>
+      </c>
+      <c r="D32" s="6">
+        <v>597.25</v>
+      </c>
+      <c r="E32" s="8">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-24.56</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-24.8</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>572.75</v>
+      </c>
+      <c r="D33" s="6">
+        <v>610.1</v>
+      </c>
+      <c r="E33" s="8">
+        <v>37.35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-26.32</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-26.65</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>928.9</v>
+      </c>
+      <c r="D34" s="6">
+        <v>929.2</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-13.24</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-16.45</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-3.21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1184.5</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1165.9</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-18.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-12.3</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-12.08</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2039.9</v>
+      </c>
+      <c r="D36" s="6">
+        <v>2049</v>
+      </c>
+      <c r="E36" s="8">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="7">
-        <v>601.85</v>
-      </c>
-      <c r="D33" s="7">
-        <v>592.7</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-9.15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="6">
+        <v>32.22</v>
+      </c>
+      <c r="D37" s="6">
+        <v>35.11</v>
+      </c>
+      <c r="E37" s="8">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="7">
-        <v>574.55</v>
-      </c>
-      <c r="D34" s="7">
-        <v>572.75</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="6">
+        <v>52.4</v>
+      </c>
+      <c r="D38" s="6">
+        <v>65.63</v>
+      </c>
+      <c r="E38" s="8">
+        <v>13.23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="7">
-        <v>933</v>
-      </c>
-      <c r="D35" s="7">
-        <v>928.9</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-4.1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>32.11</v>
+      </c>
+      <c r="D39" s="6">
+        <v>32.21</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="7">
-        <v>1230</v>
-      </c>
-      <c r="D36" s="7">
-        <v>1184.5</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-45.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>35.17</v>
+      </c>
+      <c r="D40" s="6">
+        <v>32.72</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="7">
-        <v>2035</v>
-      </c>
-      <c r="D37" s="7">
-        <v>2039.9</v>
-      </c>
-      <c r="E37" s="9">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>50.47</v>
+      </c>
+      <c r="D41" s="6">
+        <v>51.57</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="7">
-        <v>35.14</v>
-      </c>
-      <c r="D38" s="7">
-        <v>32.22</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-2.92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-41.57</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-44.57</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="7">
-        <v>53.31</v>
-      </c>
-      <c r="D39" s="7">
-        <v>52.4</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="6">
+        <v>32.04</v>
+      </c>
+      <c r="D43" s="6">
+        <v>1615.98</v>
+      </c>
+      <c r="E43" s="8">
+        <v>1583.94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="7">
-        <v>32.76</v>
-      </c>
-      <c r="D40" s="7">
-        <v>32.11</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-15.08</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-72.23</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-57.15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="7">
-        <v>42.35</v>
-      </c>
-      <c r="D41" s="7">
-        <v>35.17</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-7.18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>79.03</v>
+      </c>
+      <c r="D45" s="6">
+        <v>165.33</v>
+      </c>
+      <c r="E45" s="8">
+        <v>86.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="7">
-        <v>49.91</v>
-      </c>
-      <c r="D42" s="7">
-        <v>50.47</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="7">
-        <v>-43.59</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-41.57</v>
-      </c>
-      <c r="E43" s="9">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-46.8</v>
-      </c>
-      <c r="D44" s="7">
-        <v>32.04</v>
-      </c>
-      <c r="E44" s="9">
-        <v>78.84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-30.01</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-15.08</v>
-      </c>
-      <c r="E45" s="9">
-        <v>14.93</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-71.45</v>
-      </c>
-      <c r="D46" s="7">
-        <v>79.03</v>
-      </c>
-      <c r="E46" s="9">
-        <v>150.48</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-57.62</v>
-      </c>
-      <c r="D47" s="7">
+      <c r="C46" s="6">
         <v>-57.56</v>
       </c>
-      <c r="E47" s="9">
-        <v>0.06</v>
+      <c r="D46" s="6">
+        <v>-36.25</v>
+      </c>
+      <c r="E46" s="8">
+        <v>21.31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2430,60 +2394,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="12">
-        <v>49.92</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="12">
-        <v>40.5</v>
-      </c>
-      <c r="E2" s="12">
-        <v>40</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-6.6</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-2.6</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="11">
+        <v>43.4</v>
+      </c>
+      <c r="E2" s="11">
+        <v>60</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-6.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-2.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -2585,37 +2549,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15">
-        <v>0.1682</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.0693</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.0018</v>
-      </c>
-      <c r="D2" s="15">
-        <v>-0.008199999999999999</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.1446</v>
+      <c r="A2" s="14">
+        <v>0.1651</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.073</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0074</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0134</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1423</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,13 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.6 → 49.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.6</t>
+  </si>
+  <si>
+    <t>49.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -912,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>597.25</v>
+        <v>593.5</v>
       </c>
       <c r="D2">
-        <v>0.77</v>
+        <v>-0.63</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -924,25 +930,25 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-34.99</v>
+        <v>-35.4</v>
       </c>
       <c r="H2">
-        <v>14.45</v>
+        <v>13.73</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>-1.71</v>
       </c>
       <c r="J2">
-        <v>-10.13</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="K2">
-        <v>-21.54</v>
+        <v>-22.04</v>
       </c>
       <c r="L2">
-        <v>-27.84</v>
+        <v>-27.56</v>
       </c>
       <c r="M2">
-        <v>-14.23</v>
+        <v>-14.48</v>
       </c>
       <c r="N2">
         <v>21</v>
@@ -951,19 +957,19 @@
         <v>9</v>
       </c>
       <c r="P2">
-        <v>599.48</v>
+        <v>597.42</v>
       </c>
       <c r="Q2">
-        <v>612.48</v>
+        <v>610.02</v>
       </c>
       <c r="R2">
-        <v>671.29</v>
+        <v>667.36</v>
       </c>
       <c r="S2">
-        <v>677.42</v>
+        <v>677.22</v>
       </c>
       <c r="T2">
-        <v>-11.83</v>
+        <v>-12.36</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -978,34 +984,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.11</v>
+        <v>33.83</v>
       </c>
       <c r="Z2">
-        <v>-21.05</v>
+        <v>-20.35</v>
       </c>
       <c r="AA2">
-        <v>-23.19</v>
+        <v>-22.62</v>
       </c>
       <c r="AB2">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AC2">
-        <v>85.91</v>
+        <v>81.97</v>
       </c>
       <c r="AD2">
-        <v>86.37</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AE2">
-        <v>25.35</v>
+        <v>24.8</v>
       </c>
       <c r="AF2">
-        <v>-44.57</v>
+        <v>-55.49</v>
       </c>
       <c r="AG2">
-        <v>647.99</v>
+        <v>643.48</v>
       </c>
       <c r="AH2">
-        <v>576.97</v>
+        <v>576.5599999999999</v>
       </c>
       <c r="AI2">
         <v>660.5599999999999</v>
@@ -1014,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>49.24</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,58 +1031,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>610.1</v>
+        <v>625.75</v>
       </c>
       <c r="D3">
-        <v>6.52</v>
+        <v>2.57</v>
       </c>
       <c r="E3">
-        <v>754</v>
+        <v>749.1</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-19.08</v>
+        <v>-16.47</v>
       </c>
       <c r="H3">
-        <v>18.93</v>
+        <v>21.98</v>
       </c>
       <c r="I3">
-        <v>3.64</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="J3">
-        <v>6.22</v>
+        <v>8.43</v>
       </c>
       <c r="K3">
-        <v>3.73</v>
+        <v>6.39</v>
       </c>
       <c r="L3">
-        <v>-19.89</v>
+        <v>-17.01</v>
       </c>
       <c r="M3">
-        <v>0.74</v>
+        <v>1.28</v>
       </c>
       <c r="N3">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="O3">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P3">
-        <v>582.48</v>
+        <v>592.96</v>
       </c>
       <c r="Q3">
-        <v>566.9299999999999</v>
+        <v>570.2</v>
       </c>
       <c r="R3">
-        <v>566.83</v>
+        <v>567.83</v>
       </c>
       <c r="S3">
-        <v>576.84</v>
+        <v>577.02</v>
       </c>
       <c r="T3">
-        <v>5.77</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1091,43 +1097,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>65.63</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="Z3">
-        <v>6.06</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AA3">
-        <v>2.23</v>
+        <v>3.68</v>
       </c>
       <c r="AB3">
-        <v>3.83</v>
+        <v>5.79</v>
       </c>
       <c r="AC3">
-        <v>75.20999999999999</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="AD3">
-        <v>71.13</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="AE3">
-        <v>17.88</v>
+        <v>18.34</v>
       </c>
       <c r="AF3">
-        <v>1615.98</v>
+        <v>44.75</v>
       </c>
       <c r="AG3">
-        <v>599.67</v>
+        <v>611.99</v>
       </c>
       <c r="AH3">
-        <v>534.2</v>
+        <v>528.42</v>
       </c>
       <c r="AI3">
-        <v>546.4400000000001</v>
+        <v>567.6900000000001</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>28.57</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>929.2</v>
+        <v>922.8</v>
       </c>
       <c r="D4">
-        <v>0.03</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1150,46 +1156,46 @@
         <v>910</v>
       </c>
       <c r="G4">
-        <v>-26.62</v>
+        <v>-27.13</v>
       </c>
       <c r="H4">
-        <v>2.11</v>
+        <v>1.41</v>
       </c>
       <c r="I4">
-        <v>-0.19</v>
+        <v>-0.77</v>
       </c>
       <c r="J4">
-        <v>-13.46</v>
+        <v>-13.51</v>
       </c>
       <c r="K4">
-        <v>-11.03</v>
+        <v>-11.64</v>
       </c>
       <c r="L4">
-        <v>-24.45</v>
+        <v>-25</v>
       </c>
       <c r="M4">
-        <v>-1.34</v>
+        <v>-1.51</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P4">
-        <v>933.62</v>
+        <v>932.1799999999999</v>
       </c>
       <c r="Q4">
-        <v>996.6</v>
+        <v>988.92</v>
       </c>
       <c r="R4">
-        <v>1030.58</v>
+        <v>1028.35</v>
       </c>
       <c r="S4">
-        <v>1093.43</v>
+        <v>1092.49</v>
       </c>
       <c r="T4">
-        <v>-15.02</v>
+        <v>-15.53</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1204,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>32.21</v>
+        <v>31.09</v>
       </c>
       <c r="Z4">
-        <v>-34.95</v>
+        <v>-34.97</v>
       </c>
       <c r="AA4">
-        <v>-28.74</v>
+        <v>-29.99</v>
       </c>
       <c r="AB4">
-        <v>-6.21</v>
+        <v>-4.99</v>
       </c>
       <c r="AC4">
-        <v>29.44</v>
+        <v>30.87</v>
       </c>
       <c r="AD4">
-        <v>29.26</v>
+        <v>30.42</v>
       </c>
       <c r="AE4">
-        <v>24.41</v>
+        <v>23.46</v>
       </c>
       <c r="AF4">
-        <v>-72.23</v>
+        <v>-71.26000000000001</v>
       </c>
       <c r="AG4">
-        <v>1133.66</v>
+        <v>1124.34</v>
       </c>
       <c r="AH4">
-        <v>859.54</v>
+        <v>853.49</v>
       </c>
       <c r="AI4">
         <v>997.77</v>
@@ -1240,7 +1246,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>54.94</v>
+        <v>54.98</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1251,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1165.9</v>
+        <v>1138</v>
       </c>
       <c r="D5">
-        <v>-1.57</v>
+        <v>-2.39</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1263,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-17.76</v>
+        <v>-19.73</v>
       </c>
       <c r="H5">
-        <v>55.66</v>
+        <v>51.94</v>
       </c>
       <c r="I5">
-        <v>-5.2</v>
+        <v>-6.57</v>
       </c>
       <c r="J5">
-        <v>-12.53</v>
+        <v>-13.08</v>
       </c>
       <c r="K5">
-        <v>2.8</v>
+        <v>0.34</v>
       </c>
       <c r="L5">
-        <v>-9.49</v>
+        <v>-11.49</v>
       </c>
       <c r="M5">
-        <v>16.51</v>
+        <v>15.57</v>
       </c>
       <c r="N5">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="O5">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P5">
-        <v>1204.36</v>
+        <v>1188.36</v>
       </c>
       <c r="Q5">
-        <v>1265.15</v>
+        <v>1257.38</v>
       </c>
       <c r="R5">
-        <v>1252.29</v>
+        <v>1253.83</v>
       </c>
       <c r="S5">
-        <v>1063.02</v>
+        <v>1063.34</v>
       </c>
       <c r="T5">
-        <v>9.68</v>
+        <v>7.02</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1317,43 +1323,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>32.72</v>
+        <v>29.42</v>
       </c>
       <c r="Z5">
-        <v>-22.24</v>
+        <v>-27.89</v>
       </c>
       <c r="AA5">
-        <v>-7.82</v>
+        <v>-11.83</v>
       </c>
       <c r="AB5">
-        <v>-14.43</v>
+        <v>-16.06</v>
       </c>
       <c r="AC5">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>7.27</v>
+        <v>4.61</v>
       </c>
       <c r="AE5">
-        <v>46.65</v>
+        <v>46.27</v>
       </c>
       <c r="AF5">
-        <v>165.33</v>
+        <v>-21.28</v>
       </c>
       <c r="AG5">
-        <v>1364</v>
+        <v>1370.32</v>
       </c>
       <c r="AH5">
-        <v>1166.29</v>
+        <v>1144.44</v>
       </c>
       <c r="AI5">
-        <v>1296.09</v>
+        <v>1291.51</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>53.85</v>
+        <v>56.94</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1364,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2049</v>
+        <v>2035.1</v>
       </c>
       <c r="D6">
-        <v>0.45</v>
+        <v>-0.68</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1376,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-11.69</v>
+        <v>-12.29</v>
       </c>
       <c r="H6">
-        <v>39.26</v>
+        <v>38.32</v>
       </c>
       <c r="I6">
-        <v>2.58</v>
+        <v>1.38</v>
       </c>
       <c r="J6">
-        <v>-1.43</v>
+        <v>-4.75</v>
       </c>
       <c r="K6">
-        <v>14.56</v>
+        <v>13.78</v>
       </c>
       <c r="L6">
-        <v>0.35</v>
+        <v>-0.9</v>
       </c>
       <c r="M6">
-        <v>7.3</v>
+        <v>6.79</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P6">
-        <v>2030.24</v>
+        <v>2035.8</v>
       </c>
       <c r="Q6">
-        <v>2056.43</v>
+        <v>2050.39</v>
       </c>
       <c r="R6">
-        <v>2012.93</v>
+        <v>2017.75</v>
       </c>
       <c r="S6">
-        <v>1873.44</v>
+        <v>1872.9</v>
       </c>
       <c r="T6">
-        <v>9.369999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1430,34 +1436,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>51.57</v>
+        <v>49.76</v>
       </c>
       <c r="Z6">
-        <v>0.01</v>
+        <v>-0.23</v>
       </c>
       <c r="AA6">
-        <v>6.03</v>
+        <v>4.78</v>
       </c>
       <c r="AB6">
-        <v>-6.02</v>
+        <v>-5.01</v>
       </c>
       <c r="AC6">
-        <v>52.28</v>
+        <v>51.88</v>
       </c>
       <c r="AD6">
-        <v>42.65</v>
+        <v>49.12</v>
       </c>
       <c r="AE6">
-        <v>54.27</v>
+        <v>54.2</v>
       </c>
       <c r="AF6">
-        <v>-36.25</v>
+        <v>19.63</v>
       </c>
       <c r="AG6">
-        <v>2145.39</v>
+        <v>2126.33</v>
       </c>
       <c r="AH6">
-        <v>1967.48</v>
+        <v>1974.45</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1466,7 +1472,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>15.48</v>
+        <v>15.96</v>
       </c>
     </row>
   </sheetData>
@@ -1607,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1647,7 +1653,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1659,15 +1665,15 @@
         <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1679,16 +1685,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1699,13 +1705,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-10.07</v>
+        <v>-10.13</v>
       </c>
       <c r="D7" s="6">
-        <v>-10.13</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.06</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1716,13 +1722,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-0.15</v>
+        <v>6.22</v>
       </c>
       <c r="D8" s="6">
-        <v>6.22</v>
-      </c>
-      <c r="E8" s="8">
-        <v>6.37</v>
+        <v>8.43</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.21</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1733,13 +1739,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-12.33</v>
+        <v>-13.46</v>
       </c>
       <c r="D9" s="6">
-        <v>-13.46</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.13</v>
+        <v>-13.51</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1750,13 +1756,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-11.09</v>
+        <v>-12.53</v>
       </c>
       <c r="D10" s="6">
-        <v>-12.53</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.44</v>
+        <v>-13.08</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1767,13 +1773,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>0.55</v>
+        <v>-1.43</v>
       </c>
       <c r="D11" s="6">
-        <v>-1.43</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.98</v>
+        <v>-4.75</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-3.32</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1784,13 +1790,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-0.21</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6">
-        <v>2</v>
+        <v>-1.71</v>
       </c>
       <c r="E12" s="8">
-        <v>2.21</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1801,13 +1807,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.34</v>
+        <v>3.64</v>
       </c>
       <c r="D13" s="6">
-        <v>3.64</v>
-      </c>
-      <c r="E13" s="8">
-        <v>4.98</v>
+        <v>9.140000000000001</v>
+      </c>
+      <c r="E13" s="7">
+        <v>5.5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1818,13 +1824,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
+        <v>-0.19</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.77</v>
+      </c>
+      <c r="E14" s="8">
         <v>-0.58</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.19</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.39</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1835,13 +1841,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.15</v>
+        <v>-5.2</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.2</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.05</v>
+        <v>-6.57</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1852,13 +1858,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-0.6899999999999999</v>
+        <v>2.58</v>
       </c>
       <c r="D16" s="6">
-        <v>2.58</v>
+        <v>1.38</v>
       </c>
       <c r="E16" s="8">
-        <v>3.27</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1869,13 +1875,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>-28.43</v>
+        <v>-27.84</v>
       </c>
       <c r="D17" s="6">
-        <v>-27.84</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.59</v>
+        <v>-27.56</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.28</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1886,13 +1892,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>-24.74</v>
+        <v>-19.89</v>
       </c>
       <c r="D18" s="6">
-        <v>-19.89</v>
-      </c>
-      <c r="E18" s="8">
-        <v>4.85</v>
+        <v>-17.01</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.88</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1903,13 +1909,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-22.73</v>
+        <v>-24.45</v>
       </c>
       <c r="D19" s="6">
-        <v>-24.45</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.72</v>
+        <v>-25</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1920,13 +1926,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-7.77</v>
+        <v>-9.49</v>
       </c>
       <c r="D20" s="6">
-        <v>-9.49</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.72</v>
+        <v>-11.49</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1937,13 +1943,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>1.49</v>
+        <v>0.35</v>
       </c>
       <c r="D21" s="6">
-        <v>0.35</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.14</v>
+        <v>-0.9</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1954,13 +1960,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-20.65</v>
+        <v>-21.54</v>
       </c>
       <c r="D22" s="6">
-        <v>-21.54</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.89</v>
+        <v>-22.04</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1971,13 +1977,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-1.98</v>
+        <v>3.73</v>
       </c>
       <c r="D23" s="6">
-        <v>3.73</v>
-      </c>
-      <c r="E23" s="8">
-        <v>5.71</v>
+        <v>6.39</v>
+      </c>
+      <c r="E23" s="7">
+        <v>2.66</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1988,13 +1994,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-9.970000000000001</v>
+        <v>-11.03</v>
       </c>
       <c r="D24" s="6">
-        <v>-11.03</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.06</v>
+        <v>-11.64</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2005,13 +2011,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>3.86</v>
+        <v>2.8</v>
       </c>
       <c r="D25" s="6">
-        <v>2.8</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.06</v>
+        <v>0.34</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2022,13 +2028,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>15.89</v>
+        <v>14.56</v>
       </c>
       <c r="D26" s="6">
-        <v>14.56</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.33</v>
+        <v>13.78</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2039,13 +2045,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-35.49</v>
+        <v>-34.99</v>
       </c>
       <c r="D27" s="6">
-        <v>-34.99</v>
+        <v>-35.4</v>
       </c>
       <c r="E27" s="8">
-        <v>0.5</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2056,13 +2062,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-24.8</v>
+        <v>-19.08</v>
       </c>
       <c r="D28" s="6">
-        <v>-19.08</v>
-      </c>
-      <c r="E28" s="8">
-        <v>5.72</v>
+        <v>-16.47</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2073,13 +2079,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-26.65</v>
+        <v>-26.62</v>
       </c>
       <c r="D29" s="6">
-        <v>-26.62</v>
+        <v>-27.13</v>
       </c>
       <c r="E29" s="8">
-        <v>0.03</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2090,13 +2096,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-16.45</v>
+        <v>-17.76</v>
       </c>
       <c r="D30" s="6">
-        <v>-17.76</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.31</v>
+        <v>-19.73</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.97</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2107,13 +2113,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-12.08</v>
+        <v>-11.69</v>
       </c>
       <c r="D31" s="6">
-        <v>-11.69</v>
+        <v>-12.29</v>
       </c>
       <c r="E31" s="8">
-        <v>0.39</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2124,13 +2130,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>592.7</v>
+        <v>597.25</v>
       </c>
       <c r="D32" s="6">
-        <v>597.25</v>
+        <v>593.5</v>
       </c>
       <c r="E32" s="8">
-        <v>4.55</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2141,13 +2147,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>572.75</v>
+        <v>610.1</v>
       </c>
       <c r="D33" s="6">
-        <v>610.1</v>
-      </c>
-      <c r="E33" s="8">
-        <v>37.35</v>
+        <v>625.75</v>
+      </c>
+      <c r="E33" s="7">
+        <v>15.65</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2158,13 +2164,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>928.9</v>
+        <v>929.2</v>
       </c>
       <c r="D34" s="6">
-        <v>929.2</v>
+        <v>922.8</v>
       </c>
       <c r="E34" s="8">
-        <v>0.3</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2175,13 +2181,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>1184.5</v>
+        <v>1165.9</v>
       </c>
       <c r="D35" s="6">
-        <v>1165.9</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-18.6</v>
+        <v>1138</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-27.9</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2192,183 +2198,217 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>2039.9</v>
+        <v>2049</v>
       </c>
       <c r="D36" s="6">
-        <v>2049</v>
+        <v>2035.1</v>
       </c>
       <c r="E36" s="8">
-        <v>9.1</v>
+        <v>-13.9</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C37" s="6">
-        <v>32.22</v>
+        <v>60</v>
       </c>
       <c r="D37" s="6">
-        <v>35.11</v>
-      </c>
-      <c r="E37" s="8">
-        <v>2.89</v>
+        <v>79</v>
+      </c>
+      <c r="E37" s="7">
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C38" s="6">
-        <v>52.4</v>
+        <v>79</v>
       </c>
       <c r="D38" s="6">
-        <v>65.63</v>
+        <v>60</v>
       </c>
       <c r="E38" s="8">
-        <v>13.23</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>32.11</v>
+        <v>35.11</v>
       </c>
       <c r="D39" s="6">
-        <v>32.21</v>
+        <v>33.83</v>
       </c>
       <c r="E39" s="8">
-        <v>0.1</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>35.17</v>
+        <v>65.63</v>
       </c>
       <c r="D40" s="6">
-        <v>32.72</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="E40" s="7">
-        <v>-2.45</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>50.47</v>
+        <v>32.21</v>
       </c>
       <c r="D41" s="6">
-        <v>51.57</v>
+        <v>31.09</v>
       </c>
       <c r="E41" s="8">
-        <v>1.1</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C42" s="6">
-        <v>-41.57</v>
+        <v>32.72</v>
       </c>
       <c r="D42" s="6">
-        <v>-44.57</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-3</v>
+        <v>29.42</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-3.3</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C43" s="6">
-        <v>32.04</v>
+        <v>51.57</v>
       </c>
       <c r="D43" s="6">
-        <v>1615.98</v>
+        <v>49.76</v>
       </c>
       <c r="E43" s="8">
-        <v>1583.94</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-15.08</v>
+        <v>-44.57</v>
       </c>
       <c r="D44" s="6">
-        <v>-72.23</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-57.15</v>
+        <v>-55.49</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-10.92</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>79.03</v>
+        <v>1615.98</v>
       </c>
       <c r="D45" s="6">
-        <v>165.33</v>
+        <v>44.75</v>
       </c>
       <c r="E45" s="8">
-        <v>86.3</v>
+        <v>-1571.23</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>-57.56</v>
+        <v>-72.23</v>
       </c>
       <c r="D46" s="6">
+        <v>-71.26000000000001</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>165.33</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-21.28</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-186.61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="6">
         <v>-36.25</v>
       </c>
-      <c r="E46" s="8">
-        <v>21.31</v>
+      <c r="D48" s="6">
+        <v>19.63</v>
+      </c>
+      <c r="E48" s="7">
+        <v>55.88</v>
       </c>
     </row>
   </sheetData>
@@ -2398,28 +2438,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2433,7 +2473,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>43.4</v>
+        <v>42.7</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
@@ -2442,7 +2482,7 @@
         <v>-6.3</v>
       </c>
       <c r="G2" s="11">
-        <v>-2.3</v>
+        <v>-2.6</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2567,19 +2607,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.1651</v>
+        <v>0.1557</v>
       </c>
       <c r="B2" s="14">
-        <v>0.073</v>
+        <v>0.0679</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0074</v>
+        <v>0.0128</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0134</v>
+        <v>-0.0151</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1423</v>
+        <v>-0.1448</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,19 +181,40 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.4 → 32.7</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.4</t>
+  </si>
+  <si>
+    <t>32.7</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>51.6 → 49.8</t>
+    <t>49.8 → 54.0</t>
+  </si>
+  <si>
+    <t>49.8</t>
+  </si>
+  <si>
+    <t>54.0</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>51.6</t>
-  </si>
-  <si>
-    <t>49.8</t>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -279,14 +300,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -319,13 +340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -403,6 +424,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -918,10 +940,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>593.5</v>
+        <v>585.9</v>
       </c>
       <c r="D2">
-        <v>-0.63</v>
+        <v>-1.28</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,46 +952,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-35.4</v>
+        <v>-36.23</v>
       </c>
       <c r="H2">
-        <v>13.73</v>
+        <v>12.27</v>
       </c>
       <c r="I2">
-        <v>-1.71</v>
+        <v>-2.64</v>
       </c>
       <c r="J2">
-        <v>-8.609999999999999</v>
+        <v>-8.83</v>
       </c>
       <c r="K2">
-        <v>-22.04</v>
+        <v>-24</v>
       </c>
       <c r="L2">
-        <v>-27.56</v>
+        <v>-35.08</v>
       </c>
       <c r="M2">
-        <v>-14.48</v>
+        <v>-15.03</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P2">
-        <v>597.42</v>
+        <v>594.24</v>
       </c>
       <c r="Q2">
-        <v>610.02</v>
+        <v>607.96</v>
       </c>
       <c r="R2">
-        <v>667.36</v>
+        <v>663.29</v>
       </c>
       <c r="S2">
-        <v>677.22</v>
+        <v>677.0599999999999</v>
       </c>
       <c r="T2">
-        <v>-12.36</v>
+        <v>-13.46</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -984,34 +1006,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.83</v>
+        <v>31.34</v>
       </c>
       <c r="Z2">
-        <v>-20.35</v>
+        <v>-20.17</v>
       </c>
       <c r="AA2">
-        <v>-22.62</v>
+        <v>-22.13</v>
       </c>
       <c r="AB2">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="AC2">
-        <v>81.97</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="AD2">
-        <v>84.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AE2">
-        <v>24.8</v>
+        <v>23.95</v>
       </c>
       <c r="AF2">
-        <v>-55.49</v>
+        <v>-65.45999999999999</v>
       </c>
       <c r="AG2">
-        <v>643.48</v>
+        <v>642.08</v>
       </c>
       <c r="AH2">
-        <v>576.5599999999999</v>
+        <v>573.85</v>
       </c>
       <c r="AI2">
         <v>660.5599999999999</v>
@@ -1020,7 +1042,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>49.75</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1053,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>625.75</v>
+        <v>614.75</v>
       </c>
       <c r="D3">
-        <v>2.57</v>
+        <v>-1.76</v>
       </c>
       <c r="E3">
         <v>749.1</v>
@@ -1043,46 +1065,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-16.47</v>
+        <v>-17.93</v>
       </c>
       <c r="H3">
-        <v>21.98</v>
+        <v>19.83</v>
       </c>
       <c r="I3">
-        <v>9.140000000000001</v>
+        <v>5.69</v>
       </c>
       <c r="J3">
-        <v>8.43</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="K3">
-        <v>6.39</v>
+        <v>6.69</v>
       </c>
       <c r="L3">
-        <v>-17.01</v>
+        <v>-17.6</v>
       </c>
       <c r="M3">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
         <v>79</v>
       </c>
       <c r="O3">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P3">
-        <v>592.96</v>
+        <v>599.58</v>
       </c>
       <c r="Q3">
-        <v>570.2</v>
+        <v>572.97</v>
       </c>
       <c r="R3">
-        <v>567.83</v>
+        <v>568.65</v>
       </c>
       <c r="S3">
-        <v>577.02</v>
+        <v>577.15</v>
       </c>
       <c r="T3">
-        <v>8.449999999999999</v>
+        <v>6.52</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1097,34 +1119,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>69.45999999999999</v>
+        <v>64.06</v>
       </c>
       <c r="Z3">
-        <v>9.470000000000001</v>
+        <v>11.16</v>
       </c>
       <c r="AA3">
-        <v>3.68</v>
+        <v>5.18</v>
       </c>
       <c r="AB3">
-        <v>5.79</v>
+        <v>5.98</v>
       </c>
       <c r="AC3">
-        <v>86.98999999999999</v>
+        <v>93.56</v>
       </c>
       <c r="AD3">
-        <v>76.84999999999999</v>
+        <v>85.25</v>
       </c>
       <c r="AE3">
-        <v>18.34</v>
+        <v>18.17</v>
       </c>
       <c r="AF3">
-        <v>44.75</v>
+        <v>-52.8</v>
       </c>
       <c r="AG3">
-        <v>611.99</v>
+        <v>618.87</v>
       </c>
       <c r="AH3">
-        <v>528.42</v>
+        <v>527.0700000000001</v>
       </c>
       <c r="AI3">
         <v>567.6900000000001</v>
@@ -1133,7 +1155,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>32.76</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1166,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>922.8</v>
+        <v>923</v>
       </c>
       <c r="D4">
-        <v>-0.6899999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1156,46 +1178,46 @@
         <v>910</v>
       </c>
       <c r="G4">
-        <v>-27.13</v>
+        <v>-27.11</v>
       </c>
       <c r="H4">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="I4">
-        <v>-0.77</v>
+        <v>-2.53</v>
       </c>
       <c r="J4">
-        <v>-13.51</v>
+        <v>-14.26</v>
       </c>
       <c r="K4">
-        <v>-11.64</v>
+        <v>-10.33</v>
       </c>
       <c r="L4">
-        <v>-25</v>
+        <v>-25.57</v>
       </c>
       <c r="M4">
-        <v>-1.51</v>
+        <v>-1.72</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P4">
-        <v>932.1799999999999</v>
+        <v>927.38</v>
       </c>
       <c r="Q4">
-        <v>988.92</v>
+        <v>981.46</v>
       </c>
       <c r="R4">
-        <v>1028.35</v>
+        <v>1026.41</v>
       </c>
       <c r="S4">
-        <v>1092.49</v>
+        <v>1091.52</v>
       </c>
       <c r="T4">
-        <v>-15.53</v>
+        <v>-15.44</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1210,43 +1232,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.09</v>
+        <v>31.17</v>
       </c>
       <c r="Z4">
-        <v>-34.97</v>
+        <v>-34.57</v>
       </c>
       <c r="AA4">
-        <v>-29.99</v>
+        <v>-30.9</v>
       </c>
       <c r="AB4">
-        <v>-4.99</v>
+        <v>-3.67</v>
       </c>
       <c r="AC4">
-        <v>30.87</v>
+        <v>35.94</v>
       </c>
       <c r="AD4">
-        <v>30.42</v>
+        <v>32.08</v>
       </c>
       <c r="AE4">
-        <v>23.46</v>
+        <v>23.07</v>
       </c>
       <c r="AF4">
-        <v>-71.26000000000001</v>
+        <v>-46.95</v>
       </c>
       <c r="AG4">
-        <v>1124.34</v>
+        <v>1113.99</v>
       </c>
       <c r="AH4">
-        <v>853.49</v>
+        <v>848.9299999999999</v>
       </c>
       <c r="AI4">
-        <v>997.77</v>
+        <v>990.2</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>54.98</v>
+        <v>55.91</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1279,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1138</v>
+        <v>1150.5</v>
       </c>
       <c r="D5">
-        <v>-2.39</v>
+        <v>1.1</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,97 +1291,97 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-19.73</v>
+        <v>-18.85</v>
       </c>
       <c r="H5">
-        <v>51.94</v>
+        <v>53.6</v>
       </c>
       <c r="I5">
-        <v>-6.57</v>
+        <v>-5.96</v>
       </c>
       <c r="J5">
-        <v>-13.08</v>
+        <v>-11.04</v>
       </c>
       <c r="K5">
-        <v>0.34</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
-        <v>-11.49</v>
+        <v>-10.65</v>
       </c>
       <c r="M5">
-        <v>15.57</v>
+        <v>15.86</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P5">
-        <v>1188.36</v>
+        <v>1173.78</v>
       </c>
       <c r="Q5">
-        <v>1257.38</v>
+        <v>1249.44</v>
       </c>
       <c r="R5">
-        <v>1253.83</v>
+        <v>1255.8</v>
       </c>
       <c r="S5">
-        <v>1063.34</v>
+        <v>1063.78</v>
       </c>
       <c r="T5">
-        <v>7.02</v>
+        <v>8.15</v>
       </c>
       <c r="U5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V5" t="s">
         <v>44</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>29.42</v>
+        <v>32.7</v>
       </c>
       <c r="Z5">
-        <v>-27.89</v>
+        <v>-31</v>
       </c>
       <c r="AA5">
-        <v>-11.83</v>
+        <v>-15.66</v>
       </c>
       <c r="AB5">
-        <v>-16.06</v>
+        <v>-15.33</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD5">
-        <v>4.61</v>
+        <v>3.68</v>
       </c>
       <c r="AE5">
-        <v>46.27</v>
+        <v>45.93</v>
       </c>
       <c r="AF5">
-        <v>-21.28</v>
+        <v>-34.3</v>
       </c>
       <c r="AG5">
-        <v>1370.32</v>
+        <v>1369.12</v>
       </c>
       <c r="AH5">
-        <v>1144.44</v>
+        <v>1129.75</v>
       </c>
       <c r="AI5">
-        <v>1291.51</v>
+        <v>1283.64</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>56.94</v>
+        <v>59.79</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1392,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2035.1</v>
+        <v>2069.4</v>
       </c>
       <c r="D6">
-        <v>-0.68</v>
+        <v>1.69</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1382,46 +1404,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-12.29</v>
+        <v>-10.81</v>
       </c>
       <c r="H6">
-        <v>38.32</v>
+        <v>40.65</v>
       </c>
       <c r="I6">
-        <v>1.38</v>
+        <v>2.45</v>
       </c>
       <c r="J6">
-        <v>-4.75</v>
+        <v>-4.02</v>
       </c>
       <c r="K6">
-        <v>13.78</v>
+        <v>17.4</v>
       </c>
       <c r="L6">
-        <v>-0.9</v>
+        <v>0.8</v>
       </c>
       <c r="M6">
-        <v>6.79</v>
+        <v>7.03</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="P6">
-        <v>2035.8</v>
+        <v>2045.68</v>
       </c>
       <c r="Q6">
-        <v>2050.39</v>
+        <v>2048.31</v>
       </c>
       <c r="R6">
-        <v>2017.75</v>
+        <v>2023.37</v>
       </c>
       <c r="S6">
-        <v>1872.9</v>
+        <v>1872.41</v>
       </c>
       <c r="T6">
-        <v>8.66</v>
+        <v>10.52</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1436,34 +1458,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>49.76</v>
+        <v>54.04</v>
       </c>
       <c r="Z6">
-        <v>-0.23</v>
+        <v>2.32</v>
       </c>
       <c r="AA6">
-        <v>4.78</v>
+        <v>4.28</v>
       </c>
       <c r="AB6">
-        <v>-5.01</v>
+        <v>-1.97</v>
       </c>
       <c r="AC6">
-        <v>51.88</v>
+        <v>61.58</v>
       </c>
       <c r="AD6">
-        <v>49.12</v>
+        <v>55.24</v>
       </c>
       <c r="AE6">
-        <v>54.2</v>
+        <v>55.41</v>
       </c>
       <c r="AF6">
-        <v>19.63</v>
+        <v>98.81</v>
       </c>
       <c r="AG6">
-        <v>2126.33</v>
+        <v>2119.41</v>
       </c>
       <c r="AH6">
-        <v>1974.45</v>
+        <v>1977.22</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1472,7 +1494,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>15.96</v>
+        <v>15.13</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1635,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1653,7 +1675,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1671,750 +1693,776 @@
         <v>57</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-10.13</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C10" s="7">
         <v>-8.609999999999999</v>
       </c>
-      <c r="E7" s="7">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D10" s="7">
+        <v>-8.83</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>6.22</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C11" s="7">
         <v>8.43</v>
       </c>
-      <c r="E8" s="7">
-        <v>2.21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D11" s="7">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-13.46</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C12" s="7">
         <v>-13.51</v>
       </c>
-      <c r="E9" s="8">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D12" s="7">
+        <v>-14.26</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-12.53</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C13" s="7">
         <v>-13.08</v>
       </c>
-      <c r="E10" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D13" s="7">
+        <v>-11.04</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-1.43</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C14" s="7">
         <v>-4.75</v>
       </c>
-      <c r="E11" s="8">
-        <v>-3.32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D14" s="7">
+        <v>-4.02</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C15" s="7">
+        <v>-1.71</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-2.64</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="D16" s="7">
+        <v>5.69</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-0.77</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-2.53</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-6.57</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-5.96</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1.38</v>
+      </c>
+      <c r="D19" s="7">
+        <v>2.45</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-27.56</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-35.08</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-7.52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-17.01</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-17.6</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-25</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-25.57</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-11.49</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-10.65</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-0.9</v>
+      </c>
+      <c r="D24" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-22.04</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-24</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="7">
+        <v>6.39</v>
+      </c>
+      <c r="D26" s="7">
+        <v>6.69</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-11.64</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-10.33</v>
+      </c>
+      <c r="E27" s="9">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="7">
+        <v>0.34</v>
+      </c>
+      <c r="D28" s="7">
+        <v>3.9</v>
+      </c>
+      <c r="E28" s="9">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="7">
+        <v>13.78</v>
+      </c>
+      <c r="D29" s="7">
+        <v>17.4</v>
+      </c>
+      <c r="E29" s="9">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-35.4</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-36.23</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-16.47</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-17.93</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-27.13</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-27.11</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-19.73</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-18.85</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-12.29</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-10.81</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="6">
-        <v>-1.71</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-3.71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="C35" s="7">
+        <v>593.5</v>
+      </c>
+      <c r="D35" s="7">
+        <v>585.9</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-7.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>3.64</v>
-      </c>
-      <c r="D13" s="6">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="E13" s="7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="7">
+        <v>625.75</v>
+      </c>
+      <c r="D36" s="7">
+        <v>614.75</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-0.19</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.77</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B37" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="7">
+        <v>922.8</v>
+      </c>
+      <c r="D37" s="7">
+        <v>923</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-5.2</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-6.57</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B38" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="7">
+        <v>1138</v>
+      </c>
+      <c r="D38" s="7">
+        <v>1150.5</v>
+      </c>
+      <c r="E38" s="9">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>2.58</v>
-      </c>
-      <c r="D16" s="6">
-        <v>1.38</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="7">
+        <v>2035.1</v>
+      </c>
+      <c r="D39" s="7">
+        <v>2069.4</v>
+      </c>
+      <c r="E39" s="9">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-27.84</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-27.56</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="7">
+        <v>33.83</v>
+      </c>
+      <c r="D40" s="7">
+        <v>31.34</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-2.49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-19.89</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-17.01</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="7">
+        <v>69.45999999999999</v>
+      </c>
+      <c r="D41" s="7">
+        <v>64.06</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-24.45</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-25</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="7">
+        <v>31.09</v>
+      </c>
+      <c r="D42" s="7">
+        <v>31.17</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-9.49</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-11.49</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="7">
+        <v>29.42</v>
+      </c>
+      <c r="D43" s="7">
+        <v>32.7</v>
+      </c>
+      <c r="E43" s="9">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.35</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-0.9</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="7">
+        <v>49.76</v>
+      </c>
+      <c r="D44" s="7">
+        <v>54.04</v>
+      </c>
+      <c r="E44" s="9">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-21.54</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-22.04</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-55.49</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-65.45999999999999</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-9.970000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>3.73</v>
-      </c>
-      <c r="D23" s="6">
-        <v>6.39</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="7">
+        <v>44.75</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-52.8</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-97.55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-11.03</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-11.64</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-71.26000000000001</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-46.95</v>
+      </c>
+      <c r="E47" s="9">
+        <v>24.31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>2.8</v>
-      </c>
-      <c r="D25" s="6">
-        <v>0.34</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B48" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-21.28</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-34.3</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-13.02</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>14.56</v>
-      </c>
-      <c r="D26" s="6">
-        <v>13.78</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-34.99</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-35.4</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-19.08</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-16.47</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-26.62</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-27.13</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-17.76</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-19.73</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-11.69</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-12.29</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>597.25</v>
-      </c>
-      <c r="D32" s="6">
-        <v>593.5</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-3.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>610.1</v>
-      </c>
-      <c r="D33" s="6">
-        <v>625.75</v>
-      </c>
-      <c r="E33" s="7">
-        <v>15.65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>929.2</v>
-      </c>
-      <c r="D34" s="6">
-        <v>922.8</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-6.4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1165.9</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1138</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-27.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2049</v>
-      </c>
-      <c r="D36" s="6">
-        <v>2035.1</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-13.9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="6">
-        <v>60</v>
-      </c>
-      <c r="D37" s="6">
-        <v>79</v>
-      </c>
-      <c r="E37" s="7">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="6">
-        <v>79</v>
-      </c>
-      <c r="D38" s="6">
-        <v>60</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>35.11</v>
-      </c>
-      <c r="D39" s="6">
-        <v>33.83</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>65.63</v>
-      </c>
-      <c r="D40" s="6">
-        <v>69.45999999999999</v>
-      </c>
-      <c r="E40" s="7">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>32.21</v>
-      </c>
-      <c r="D41" s="6">
-        <v>31.09</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>32.72</v>
-      </c>
-      <c r="D42" s="6">
-        <v>29.42</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-3.3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>51.57</v>
-      </c>
-      <c r="D43" s="6">
-        <v>49.76</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-1.81</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="B49" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="6">
-        <v>-44.57</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-55.49</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-10.92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1615.98</v>
-      </c>
-      <c r="D45" s="6">
-        <v>44.75</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-1571.23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-72.23</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-71.26000000000001</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>165.33</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-21.28</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-186.61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-36.25</v>
-      </c>
-      <c r="D48" s="6">
+      <c r="C49" s="7">
         <v>19.63</v>
       </c>
-      <c r="E48" s="7">
-        <v>55.88</v>
+      <c r="D49" s="7">
+        <v>98.81</v>
+      </c>
+      <c r="E49" s="9">
+        <v>79.18000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2434,61 +2482,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>70</v>
       </c>
+      <c r="C1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>57.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="12">
         <v>42.7</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="12">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-2.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-5.7</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-1.3</v>
+      </c>
+      <c r="H2" s="12">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
-        <v>40</v>
+      <c r="I2" s="12">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2589,37 +2637,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1557</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0679</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0128</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0151</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1448</v>
+      <c r="A2" s="15">
+        <v>0.1586</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.0703</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.0105</v>
+      </c>
+      <c r="D2" s="15">
+        <v>-0.0172</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.1503</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,40 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.4 → 32.7</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.4</t>
-  </si>
-  <si>
-    <t>32.7</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.8 → 54.0</t>
-  </si>
-  <si>
-    <t>49.8</t>
+    <t>54.0 → 48.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>54.0</t>
   </si>
   <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>48.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -300,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -340,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -424,7 +403,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -940,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>585.9</v>
+        <v>581.45</v>
       </c>
       <c r="D2">
-        <v>-1.28</v>
+        <v>-0.76</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -952,46 +930,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-36.23</v>
+        <v>-36.71</v>
       </c>
       <c r="H2">
-        <v>12.27</v>
+        <v>11.42</v>
       </c>
       <c r="I2">
-        <v>-2.64</v>
+        <v>-3.39</v>
       </c>
       <c r="J2">
-        <v>-8.83</v>
+        <v>-7.26</v>
       </c>
       <c r="K2">
-        <v>-24</v>
+        <v>-21.24</v>
       </c>
       <c r="L2">
-        <v>-35.08</v>
+        <v>-33.02</v>
       </c>
       <c r="M2">
-        <v>-15.03</v>
+        <v>-15.09</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P2">
-        <v>594.24</v>
+        <v>590.16</v>
       </c>
       <c r="Q2">
-        <v>607.96</v>
+        <v>604.27</v>
       </c>
       <c r="R2">
-        <v>663.29</v>
+        <v>659.04</v>
       </c>
       <c r="S2">
-        <v>677.0599999999999</v>
+        <v>676.88</v>
       </c>
       <c r="T2">
-        <v>-13.46</v>
+        <v>-14.1</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -1006,43 +984,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>31.34</v>
+        <v>29.95</v>
       </c>
       <c r="Z2">
-        <v>-20.17</v>
+        <v>-20.16</v>
       </c>
       <c r="AA2">
-        <v>-22.13</v>
+        <v>-21.74</v>
       </c>
       <c r="AB2">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="AC2">
-        <v>79.31999999999999</v>
+        <v>63.82</v>
       </c>
       <c r="AD2">
-        <v>82.40000000000001</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AE2">
-        <v>23.95</v>
+        <v>23.81</v>
       </c>
       <c r="AF2">
-        <v>-65.45999999999999</v>
+        <v>-36.51</v>
       </c>
       <c r="AG2">
-        <v>642.08</v>
+        <v>632.22</v>
       </c>
       <c r="AH2">
-        <v>573.85</v>
+        <v>576.3200000000001</v>
       </c>
       <c r="AI2">
-        <v>660.5599999999999</v>
+        <v>654.41</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>50.87</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1053,58 +1031,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>614.75</v>
+        <v>609.3</v>
       </c>
       <c r="D3">
-        <v>-1.76</v>
+        <v>-0.89</v>
       </c>
       <c r="E3">
-        <v>749.1</v>
+        <v>748.6</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-17.93</v>
+        <v>-18.61</v>
       </c>
       <c r="H3">
-        <v>19.83</v>
+        <v>18.77</v>
       </c>
       <c r="I3">
-        <v>5.69</v>
+        <v>6.05</v>
       </c>
       <c r="J3">
-        <v>9.710000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="K3">
-        <v>6.69</v>
+        <v>5.55</v>
       </c>
       <c r="L3">
-        <v>-17.6</v>
+        <v>-18.66</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N3">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="O3">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="P3">
-        <v>599.58</v>
+        <v>606.53</v>
       </c>
       <c r="Q3">
-        <v>572.97</v>
+        <v>575.6</v>
       </c>
       <c r="R3">
-        <v>568.65</v>
+        <v>569.3099999999999</v>
       </c>
       <c r="S3">
-        <v>577.15</v>
+        <v>577.33</v>
       </c>
       <c r="T3">
-        <v>6.52</v>
+        <v>5.54</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1119,34 +1097,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>64.06</v>
+        <v>61.5</v>
       </c>
       <c r="Z3">
-        <v>11.16</v>
+        <v>11.92</v>
       </c>
       <c r="AA3">
-        <v>5.18</v>
+        <v>6.52</v>
       </c>
       <c r="AB3">
-        <v>5.98</v>
+        <v>5.4</v>
       </c>
       <c r="AC3">
-        <v>93.56</v>
+        <v>84.08</v>
       </c>
       <c r="AD3">
-        <v>85.25</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="AE3">
-        <v>18.17</v>
+        <v>17.77</v>
       </c>
       <c r="AF3">
-        <v>-52.8</v>
+        <v>-73.17</v>
       </c>
       <c r="AG3">
-        <v>618.87</v>
+        <v>623.5599999999999</v>
       </c>
       <c r="AH3">
-        <v>527.0700000000001</v>
+        <v>527.63</v>
       </c>
       <c r="AI3">
         <v>567.6900000000001</v>
@@ -1155,7 +1133,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>36.39</v>
+        <v>37.42</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1166,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="D4">
-        <v>0.02</v>
+        <v>-0.87</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1178,46 +1156,46 @@
         <v>910</v>
       </c>
       <c r="G4">
-        <v>-27.11</v>
+        <v>-27.75</v>
       </c>
       <c r="H4">
-        <v>1.43</v>
+        <v>0.55</v>
       </c>
       <c r="I4">
-        <v>-2.53</v>
+        <v>-1.93</v>
       </c>
       <c r="J4">
-        <v>-14.26</v>
+        <v>-14.65</v>
       </c>
       <c r="K4">
-        <v>-10.33</v>
+        <v>-9.32</v>
       </c>
       <c r="L4">
-        <v>-25.57</v>
+        <v>-26.48</v>
       </c>
       <c r="M4">
-        <v>-1.72</v>
+        <v>-2.51</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P4">
-        <v>927.38</v>
+        <v>923.78</v>
       </c>
       <c r="Q4">
-        <v>981.46</v>
+        <v>973.6900000000001</v>
       </c>
       <c r="R4">
-        <v>1026.41</v>
+        <v>1024.52</v>
       </c>
       <c r="S4">
-        <v>1091.52</v>
+        <v>1090.46</v>
       </c>
       <c r="T4">
-        <v>-15.44</v>
+        <v>-16.09</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1232,43 +1210,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.17</v>
+        <v>29.67</v>
       </c>
       <c r="Z4">
-        <v>-34.57</v>
+        <v>-34.5</v>
       </c>
       <c r="AA4">
-        <v>-30.9</v>
+        <v>-31.62</v>
       </c>
       <c r="AB4">
-        <v>-3.67</v>
+        <v>-2.88</v>
       </c>
       <c r="AC4">
-        <v>35.94</v>
+        <v>39.57</v>
       </c>
       <c r="AD4">
-        <v>32.08</v>
+        <v>35.46</v>
       </c>
       <c r="AE4">
-        <v>23.07</v>
+        <v>22.58</v>
       </c>
       <c r="AF4">
-        <v>-46.95</v>
+        <v>-62.89</v>
       </c>
       <c r="AG4">
-        <v>1113.99</v>
+        <v>1102.43</v>
       </c>
       <c r="AH4">
-        <v>848.9299999999999</v>
+        <v>844.95</v>
       </c>
       <c r="AI4">
-        <v>990.2</v>
+        <v>987.4299999999999</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>55.91</v>
+        <v>56.75</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1279,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1150.5</v>
+        <v>1167.5</v>
       </c>
       <c r="D5">
-        <v>1.1</v>
+        <v>1.48</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1291,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-18.85</v>
+        <v>-17.65</v>
       </c>
       <c r="H5">
-        <v>53.6</v>
+        <v>55.87</v>
       </c>
       <c r="I5">
-        <v>-5.96</v>
+        <v>-5.08</v>
       </c>
       <c r="J5">
-        <v>-11.04</v>
+        <v>-10.84</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>6.92</v>
       </c>
       <c r="L5">
-        <v>-10.65</v>
+        <v>-9.23</v>
       </c>
       <c r="M5">
         <v>15.86</v>
       </c>
       <c r="N5">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="O5">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="P5">
-        <v>1173.78</v>
+        <v>1161.28</v>
       </c>
       <c r="Q5">
-        <v>1249.44</v>
+        <v>1241.93</v>
       </c>
       <c r="R5">
-        <v>1255.8</v>
+        <v>1256.92</v>
       </c>
       <c r="S5">
-        <v>1063.78</v>
+        <v>1064.27</v>
       </c>
       <c r="T5">
-        <v>8.15</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1345,34 +1323,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>32.7</v>
+        <v>36.98</v>
       </c>
       <c r="Z5">
-        <v>-31</v>
+        <v>-31.72</v>
       </c>
       <c r="AA5">
-        <v>-15.66</v>
+        <v>-18.88</v>
       </c>
       <c r="AB5">
-        <v>-15.33</v>
+        <v>-12.85</v>
       </c>
       <c r="AC5">
-        <v>5.2</v>
+        <v>17.46</v>
       </c>
       <c r="AD5">
-        <v>3.68</v>
+        <v>7.55</v>
       </c>
       <c r="AE5">
-        <v>45.93</v>
+        <v>44.76</v>
       </c>
       <c r="AF5">
-        <v>-34.3</v>
+        <v>-43.5</v>
       </c>
       <c r="AG5">
-        <v>1369.12</v>
+        <v>1362.44</v>
       </c>
       <c r="AH5">
-        <v>1129.75</v>
+        <v>1121.42</v>
       </c>
       <c r="AI5">
         <v>1283.64</v>
@@ -1381,7 +1359,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>59.79</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1392,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2069.4</v>
+        <v>2029.1</v>
       </c>
       <c r="D6">
-        <v>1.69</v>
+        <v>-1.95</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1404,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-10.81</v>
+        <v>-12.55</v>
       </c>
       <c r="H6">
-        <v>40.65</v>
+        <v>37.91</v>
       </c>
       <c r="I6">
-        <v>2.45</v>
+        <v>-0.29</v>
       </c>
       <c r="J6">
-        <v>-4.02</v>
+        <v>-3.88</v>
       </c>
       <c r="K6">
-        <v>17.4</v>
+        <v>18.37</v>
       </c>
       <c r="L6">
-        <v>0.8</v>
+        <v>-1.92</v>
       </c>
       <c r="M6">
-        <v>7.03</v>
+        <v>6.32</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="P6">
-        <v>2045.68</v>
+        <v>2044.5</v>
       </c>
       <c r="Q6">
-        <v>2048.31</v>
+        <v>2044.48</v>
       </c>
       <c r="R6">
-        <v>2023.37</v>
+        <v>2027.75</v>
       </c>
       <c r="S6">
-        <v>1872.41</v>
+        <v>1871.76</v>
       </c>
       <c r="T6">
-        <v>10.52</v>
+        <v>8.41</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1458,34 +1436,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>54.04</v>
+        <v>48.78</v>
       </c>
       <c r="Z6">
-        <v>2.32</v>
+        <v>1.07</v>
       </c>
       <c r="AA6">
-        <v>4.28</v>
+        <v>3.64</v>
       </c>
       <c r="AB6">
-        <v>-1.97</v>
+        <v>-2.57</v>
       </c>
       <c r="AC6">
-        <v>61.58</v>
+        <v>57.1</v>
       </c>
       <c r="AD6">
-        <v>55.24</v>
+        <v>56.85</v>
       </c>
       <c r="AE6">
-        <v>55.41</v>
+        <v>55.65</v>
       </c>
       <c r="AF6">
-        <v>98.81</v>
+        <v>-44.45</v>
       </c>
       <c r="AG6">
-        <v>2119.41</v>
+        <v>2110.64</v>
       </c>
       <c r="AH6">
-        <v>1977.22</v>
+        <v>1978.33</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1494,7 +1472,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>15.13</v>
+        <v>14.41</v>
       </c>
     </row>
   </sheetData>
@@ -1635,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1675,7 +1653,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1693,776 +1671,750 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-8.83</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-7.26</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="D8" s="6">
+        <v>8.92</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-14.26</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-14.65</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-11.04</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-10.84</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-4.02</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-3.88</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-8.609999999999999</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-8.83</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>8.43</v>
-      </c>
-      <c r="D11" s="7">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="E11" s="9">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-13.51</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-14.26</v>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-2.64</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-3.39</v>
       </c>
       <c r="E12" s="8">
         <v>-0.75</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>5.69</v>
+      </c>
+      <c r="D13" s="6">
+        <v>6.05</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-2.53</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-1.93</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-13.08</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-11.04</v>
-      </c>
-      <c r="E13" s="9">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-5.96</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-5.08</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-4.75</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-4.02</v>
-      </c>
-      <c r="E14" s="9">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>2.45</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-0.29</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-2.74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-1.71</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-2.64</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-35.08</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-33.02</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="D16" s="7">
-        <v>5.69</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-17.6</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-18.66</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-0.77</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-2.53</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-25.57</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-26.48</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-6.57</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-5.96</v>
-      </c>
-      <c r="E18" s="9">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-10.65</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-9.23</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1.38</v>
-      </c>
-      <c r="D19" s="7">
-        <v>2.45</v>
-      </c>
-      <c r="E19" s="9">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-1.92</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-2.72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-27.56</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-35.08</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-7.52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-24</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-21.24</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-17.01</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-17.6</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>6.69</v>
+      </c>
+      <c r="D23" s="6">
+        <v>5.55</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-25</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-25.57</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-10.33</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-9.32</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-11.49</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-10.65</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="D25" s="6">
+        <v>6.92</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-0.9</v>
-      </c>
-      <c r="D24" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>17.4</v>
+      </c>
+      <c r="D26" s="6">
+        <v>18.37</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-22.04</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-24</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-36.23</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-36.71</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>6.39</v>
-      </c>
-      <c r="D26" s="7">
-        <v>6.69</v>
-      </c>
-      <c r="E26" s="9">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-17.93</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-18.61</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-11.64</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-10.33</v>
-      </c>
-      <c r="E27" s="9">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-27.11</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-27.75</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7">
-        <v>0.34</v>
-      </c>
-      <c r="D28" s="7">
-        <v>3.9</v>
-      </c>
-      <c r="E28" s="9">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-18.85</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-17.65</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>13.78</v>
-      </c>
-      <c r="D29" s="7">
-        <v>17.4</v>
-      </c>
-      <c r="E29" s="9">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-10.81</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-12.55</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-35.4</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-36.23</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>585.9</v>
+      </c>
+      <c r="D32" s="6">
+        <v>581.45</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-4.45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-16.47</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-17.93</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>614.75</v>
+      </c>
+      <c r="D33" s="6">
+        <v>609.3</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-5.45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-27.13</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-27.11</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>923</v>
+      </c>
+      <c r="D34" s="6">
+        <v>915</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-19.73</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-18.85</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1150.5</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1167.5</v>
+      </c>
+      <c r="E35" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-12.29</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-10.81</v>
-      </c>
-      <c r="E34" s="9">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2069.4</v>
+      </c>
+      <c r="D36" s="6">
+        <v>2029.1</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-40.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="6">
+        <v>79</v>
+      </c>
+      <c r="D37" s="6">
+        <v>60</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>60</v>
+      </c>
+      <c r="D38" s="6">
+        <v>79</v>
+      </c>
+      <c r="E38" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="7">
-        <v>593.5</v>
-      </c>
-      <c r="D35" s="7">
-        <v>585.9</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-7.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>31.34</v>
+      </c>
+      <c r="D39" s="6">
+        <v>29.95</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="7">
-        <v>625.75</v>
-      </c>
-      <c r="D36" s="7">
-        <v>614.75</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>64.06</v>
+      </c>
+      <c r="D40" s="6">
+        <v>61.5</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="7">
-        <v>922.8</v>
-      </c>
-      <c r="D37" s="7">
-        <v>923</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>31.17</v>
+      </c>
+      <c r="D41" s="6">
+        <v>29.67</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="7">
-        <v>1138</v>
-      </c>
-      <c r="D38" s="7">
-        <v>1150.5</v>
-      </c>
-      <c r="E38" s="9">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>32.7</v>
+      </c>
+      <c r="D42" s="6">
+        <v>36.98</v>
+      </c>
+      <c r="E42" s="7">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="7">
-        <v>2035.1</v>
-      </c>
-      <c r="D39" s="7">
-        <v>2069.4</v>
-      </c>
-      <c r="E39" s="9">
-        <v>34.3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>54.04</v>
+      </c>
+      <c r="D43" s="6">
+        <v>48.78</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-5.26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="7">
-        <v>33.83</v>
-      </c>
-      <c r="D40" s="7">
-        <v>31.34</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-65.45999999999999</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-36.51</v>
+      </c>
+      <c r="E44" s="7">
+        <v>28.95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="7">
-        <v>69.45999999999999</v>
-      </c>
-      <c r="D41" s="7">
-        <v>64.06</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-5.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-52.8</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-73.17</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-20.37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="7">
-        <v>31.09</v>
-      </c>
-      <c r="D42" s="7">
-        <v>31.17</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-46.95</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-62.89</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-15.94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="7">
-        <v>29.42</v>
-      </c>
-      <c r="D43" s="7">
-        <v>32.7</v>
-      </c>
-      <c r="E43" s="9">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-34.3</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-43.5</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-9.199999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="7">
-        <v>49.76</v>
-      </c>
-      <c r="D44" s="7">
-        <v>54.04</v>
-      </c>
-      <c r="E44" s="9">
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="6" t="s">
+      <c r="B48" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="7">
-        <v>-55.49</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-65.45999999999999</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-9.970000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="7">
-        <v>44.75</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-52.8</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-97.55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-71.26000000000001</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-46.95</v>
-      </c>
-      <c r="E47" s="9">
-        <v>24.31</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-21.28</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-34.3</v>
+      <c r="C48" s="6">
+        <v>98.81</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-44.45</v>
       </c>
       <c r="E48" s="8">
-        <v>-13.02</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="7">
-        <v>19.63</v>
-      </c>
-      <c r="D49" s="7">
-        <v>98.81</v>
-      </c>
-      <c r="E49" s="9">
-        <v>79.18000000000001</v>
+        <v>-143.26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2482,60 +2434,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>57.92</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="12">
-        <v>42.7</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>41.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
-        <v>-5.7</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-1.3</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-5.5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2637,37 +2589,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>0.1586</v>
       </c>
-      <c r="B2" s="15">
-        <v>0.0703</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.0105</v>
-      </c>
-      <c r="D2" s="15">
-        <v>-0.0172</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.1503</v>
+      <c r="B2" s="14">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0069</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0251</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1509</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,34 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>54.0 → 48.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>54.0</t>
-  </si>
-  <si>
-    <t>48.8</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -395,18 +368,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -918,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>581.45</v>
+        <v>560.7</v>
       </c>
       <c r="D2">
-        <v>-0.76</v>
+        <v>-3.57</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-36.71</v>
+        <v>-38.97</v>
       </c>
       <c r="H2">
-        <v>11.42</v>
+        <v>7.44</v>
       </c>
       <c r="I2">
-        <v>-3.39</v>
+        <v>-5.4</v>
       </c>
       <c r="J2">
-        <v>-7.26</v>
+        <v>-14.44</v>
       </c>
       <c r="K2">
-        <v>-21.24</v>
+        <v>-28.84</v>
       </c>
       <c r="L2">
-        <v>-33.02</v>
+        <v>-33.22</v>
       </c>
       <c r="M2">
-        <v>-15.09</v>
+        <v>-15.54</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>590.16</v>
+        <v>583.76</v>
       </c>
       <c r="Q2">
-        <v>604.27</v>
+        <v>600.89</v>
       </c>
       <c r="R2">
-        <v>659.04</v>
+        <v>654.3</v>
       </c>
       <c r="S2">
-        <v>676.88</v>
+        <v>676.62</v>
       </c>
       <c r="T2">
-        <v>-14.1</v>
+        <v>-17.13</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -984,43 +956,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>29.95</v>
+        <v>24.48</v>
       </c>
       <c r="Z2">
-        <v>-20.16</v>
+        <v>-21.57</v>
       </c>
       <c r="AA2">
-        <v>-21.74</v>
+        <v>-21.7</v>
       </c>
       <c r="AB2">
-        <v>1.58</v>
+        <v>0.13</v>
       </c>
       <c r="AC2">
-        <v>63.82</v>
+        <v>36.17</v>
       </c>
       <c r="AD2">
-        <v>75.04000000000001</v>
+        <v>59.77</v>
       </c>
       <c r="AE2">
-        <v>23.81</v>
+        <v>24.18</v>
       </c>
       <c r="AF2">
-        <v>-36.51</v>
+        <v>32.02</v>
       </c>
       <c r="AG2">
-        <v>632.22</v>
+        <v>632.6900000000001</v>
       </c>
       <c r="AH2">
-        <v>576.3200000000001</v>
+        <v>569.09</v>
       </c>
       <c r="AI2">
-        <v>654.41</v>
+        <v>643.05</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>53.07</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1003,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>609.3</v>
+        <v>615.3</v>
       </c>
       <c r="D3">
-        <v>-0.89</v>
+        <v>0.98</v>
       </c>
       <c r="E3">
         <v>748.6</v>
@@ -1043,46 +1015,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-18.61</v>
+        <v>-17.81</v>
       </c>
       <c r="H3">
-        <v>18.77</v>
+        <v>19.94</v>
       </c>
       <c r="I3">
-        <v>6.05</v>
+        <v>7.43</v>
       </c>
       <c r="J3">
-        <v>8.92</v>
+        <v>10.51</v>
       </c>
       <c r="K3">
-        <v>5.55</v>
+        <v>5.53</v>
       </c>
       <c r="L3">
-        <v>-18.66</v>
+        <v>-16.63</v>
       </c>
       <c r="M3">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="N3">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="O3">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P3">
-        <v>606.53</v>
+        <v>615.04</v>
       </c>
       <c r="Q3">
-        <v>575.6</v>
+        <v>578.11</v>
       </c>
       <c r="R3">
-        <v>569.3099999999999</v>
+        <v>570.12</v>
       </c>
       <c r="S3">
-        <v>577.33</v>
+        <v>577.53</v>
       </c>
       <c r="T3">
-        <v>5.54</v>
+        <v>6.54</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1097,34 +1069,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>61.5</v>
+        <v>63.24</v>
       </c>
       <c r="Z3">
-        <v>11.92</v>
+        <v>12.86</v>
       </c>
       <c r="AA3">
-        <v>6.52</v>
+        <v>7.79</v>
       </c>
       <c r="AB3">
-        <v>5.4</v>
+        <v>5.07</v>
       </c>
       <c r="AC3">
-        <v>84.08</v>
+        <v>75.58</v>
       </c>
       <c r="AD3">
-        <v>88.20999999999999</v>
+        <v>84.41</v>
       </c>
       <c r="AE3">
-        <v>17.77</v>
+        <v>17.62</v>
       </c>
       <c r="AF3">
-        <v>-73.17</v>
+        <v>-7.77</v>
       </c>
       <c r="AG3">
-        <v>623.5599999999999</v>
+        <v>628.9299999999999</v>
       </c>
       <c r="AH3">
-        <v>527.63</v>
+        <v>527.29</v>
       </c>
       <c r="AI3">
         <v>567.6900000000001</v>
@@ -1133,7 +1105,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>37.42</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,37 +1116,37 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>915</v>
+        <v>901.3</v>
       </c>
       <c r="D4">
-        <v>-0.87</v>
+        <v>-1.5</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
       </c>
       <c r="F4">
-        <v>910</v>
+        <v>901.3</v>
       </c>
       <c r="G4">
-        <v>-27.75</v>
+        <v>-28.83</v>
       </c>
       <c r="H4">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.93</v>
+        <v>-2.97</v>
       </c>
       <c r="J4">
-        <v>-14.65</v>
+        <v>-15.8</v>
       </c>
       <c r="K4">
-        <v>-9.32</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="L4">
-        <v>-26.48</v>
+        <v>-27.4</v>
       </c>
       <c r="M4">
-        <v>-2.51</v>
+        <v>-3.01</v>
       </c>
       <c r="N4">
         <v>40</v>
@@ -1183,19 +1155,19 @@
         <v>15</v>
       </c>
       <c r="P4">
-        <v>923.78</v>
+        <v>918.26</v>
       </c>
       <c r="Q4">
-        <v>973.6900000000001</v>
+        <v>964.46</v>
       </c>
       <c r="R4">
-        <v>1024.52</v>
+        <v>1022.54</v>
       </c>
       <c r="S4">
-        <v>1090.46</v>
+        <v>1089.34</v>
       </c>
       <c r="T4">
-        <v>-16.09</v>
+        <v>-17.26</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1210,43 +1182,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.67</v>
+        <v>27.25</v>
       </c>
       <c r="Z4">
-        <v>-34.5</v>
+        <v>-35.15</v>
       </c>
       <c r="AA4">
-        <v>-31.62</v>
+        <v>-32.33</v>
       </c>
       <c r="AB4">
-        <v>-2.88</v>
+        <v>-2.82</v>
       </c>
       <c r="AC4">
-        <v>39.57</v>
+        <v>39.56</v>
       </c>
       <c r="AD4">
-        <v>35.46</v>
+        <v>38.35</v>
       </c>
       <c r="AE4">
-        <v>22.58</v>
+        <v>21.94</v>
       </c>
       <c r="AF4">
-        <v>-62.89</v>
+        <v>-54.43</v>
       </c>
       <c r="AG4">
-        <v>1102.43</v>
+        <v>1085.57</v>
       </c>
       <c r="AH4">
-        <v>844.95</v>
+        <v>843.35</v>
       </c>
       <c r="AI4">
-        <v>987.4299999999999</v>
+        <v>973.13</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>56.75</v>
+        <v>58.28</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1167.5</v>
+        <v>1134.5</v>
       </c>
       <c r="D5">
-        <v>1.48</v>
+        <v>-2.83</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-17.65</v>
+        <v>-19.98</v>
       </c>
       <c r="H5">
-        <v>55.87</v>
+        <v>51.47</v>
       </c>
       <c r="I5">
-        <v>-5.08</v>
+        <v>-4.22</v>
       </c>
       <c r="J5">
-        <v>-10.84</v>
+        <v>-13.9</v>
       </c>
       <c r="K5">
-        <v>6.92</v>
+        <v>7.1</v>
       </c>
       <c r="L5">
-        <v>-9.23</v>
+        <v>-10.67</v>
       </c>
       <c r="M5">
-        <v>15.86</v>
+        <v>15.22</v>
       </c>
       <c r="N5">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="O5">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="P5">
-        <v>1161.28</v>
+        <v>1151.28</v>
       </c>
       <c r="Q5">
-        <v>1241.93</v>
+        <v>1231.8</v>
       </c>
       <c r="R5">
-        <v>1256.92</v>
+        <v>1257.37</v>
       </c>
       <c r="S5">
-        <v>1064.27</v>
+        <v>1064.61</v>
       </c>
       <c r="T5">
-        <v>9.699999999999999</v>
+        <v>6.57</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1323,43 +1295,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>36.98</v>
+        <v>32.64</v>
       </c>
       <c r="Z5">
-        <v>-31.72</v>
+        <v>-34.56</v>
       </c>
       <c r="AA5">
-        <v>-18.88</v>
+        <v>-22.01</v>
       </c>
       <c r="AB5">
-        <v>-12.85</v>
+        <v>-12.55</v>
       </c>
       <c r="AC5">
-        <v>17.46</v>
+        <v>24.43</v>
       </c>
       <c r="AD5">
-        <v>7.55</v>
+        <v>15.69</v>
       </c>
       <c r="AE5">
-        <v>44.76</v>
+        <v>44.25</v>
       </c>
       <c r="AF5">
-        <v>-43.5</v>
+        <v>-42.95</v>
       </c>
       <c r="AG5">
-        <v>1362.44</v>
+        <v>1352.69</v>
       </c>
       <c r="AH5">
-        <v>1121.42</v>
+        <v>1110.91</v>
       </c>
       <c r="AI5">
-        <v>1283.64</v>
+        <v>1281.46</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>60.4</v>
+        <v>61.58</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2029.1</v>
+        <v>2014.7</v>
       </c>
       <c r="D6">
-        <v>-1.95</v>
+        <v>-0.71</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1382,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-12.55</v>
+        <v>-13.17</v>
       </c>
       <c r="H6">
-        <v>37.91</v>
+        <v>36.93</v>
       </c>
       <c r="I6">
-        <v>-0.29</v>
+        <v>-1.24</v>
       </c>
       <c r="J6">
-        <v>-3.88</v>
+        <v>-4.32</v>
       </c>
       <c r="K6">
-        <v>18.37</v>
+        <v>17.1</v>
       </c>
       <c r="L6">
-        <v>-1.92</v>
+        <v>0.38</v>
       </c>
       <c r="M6">
-        <v>6.32</v>
+        <v>6.23</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P6">
-        <v>2044.5</v>
+        <v>2039.46</v>
       </c>
       <c r="Q6">
-        <v>2044.48</v>
+        <v>2040.73</v>
       </c>
       <c r="R6">
-        <v>2027.75</v>
+        <v>2032.12</v>
       </c>
       <c r="S6">
-        <v>1871.76</v>
+        <v>1870.86</v>
       </c>
       <c r="T6">
-        <v>8.41</v>
+        <v>7.69</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1436,34 +1408,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>48.78</v>
+        <v>47.02</v>
       </c>
       <c r="Z6">
-        <v>1.07</v>
+        <v>-1.06</v>
       </c>
       <c r="AA6">
-        <v>3.64</v>
+        <v>2.7</v>
       </c>
       <c r="AB6">
-        <v>-2.57</v>
+        <v>-3.76</v>
       </c>
       <c r="AC6">
-        <v>57.1</v>
+        <v>51.55</v>
       </c>
       <c r="AD6">
-        <v>56.85</v>
+        <v>56.74</v>
       </c>
       <c r="AE6">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="AF6">
-        <v>-44.45</v>
+        <v>21.24</v>
       </c>
       <c r="AG6">
-        <v>2110.64</v>
+        <v>2104.56</v>
       </c>
       <c r="AH6">
-        <v>1978.33</v>
+        <v>1976.91</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1472,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>14.41</v>
+        <v>16.53</v>
       </c>
     </row>
   </sheetData>
@@ -1633,47 +1605,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1681,734 +1618,734 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-7.26</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-14.44</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-7.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>8.92</v>
+      </c>
+      <c r="D8" s="5">
+        <v>10.51</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-14.65</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-15.8</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-10.84</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-13.9</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-3.06</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-3.88</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-4.32</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-3.39</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-5.4</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>6.05</v>
+      </c>
+      <c r="D13" s="5">
+        <v>7.43</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.93</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-2.97</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-5.08</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-4.22</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-0.29</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-1.24</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-33.02</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-33.22</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-18.66</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-16.63</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-26.48</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-27.4</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-9.23</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-10.67</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-1.92</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.38</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-21.24</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-28.84</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-7.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>5.55</v>
+      </c>
+      <c r="D23" s="5">
+        <v>5.53</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-9.32</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-9.789999999999999</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>6.92</v>
+      </c>
+      <c r="D25" s="5">
+        <v>7.1</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>18.37</v>
+      </c>
+      <c r="D26" s="5">
+        <v>17.1</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-36.71</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-38.97</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-18.61</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-17.81</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-27.75</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-28.83</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-17.65</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-19.98</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-12.55</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-13.17</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>581.45</v>
+      </c>
+      <c r="D32" s="5">
+        <v>560.7</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-20.75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>609.3</v>
+      </c>
+      <c r="D33" s="5">
+        <v>615.3</v>
+      </c>
+      <c r="E33" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>915</v>
+      </c>
+      <c r="D34" s="5">
+        <v>901.3</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-13.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1167.5</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1134.5</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2029.1</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2014.7</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-14.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="5">
         <v>60</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="D37" s="5">
+        <v>79</v>
+      </c>
+      <c r="E37" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="5">
+        <v>79</v>
+      </c>
+      <c r="D38" s="5">
+        <v>60</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-8.83</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-7.26</v>
-      </c>
-      <c r="E7" s="7">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>29.95</v>
+      </c>
+      <c r="D39" s="5">
+        <v>24.48</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-5.47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="D8" s="6">
-        <v>8.92</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>61.5</v>
+      </c>
+      <c r="D40" s="5">
+        <v>63.24</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-14.26</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-14.65</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>29.67</v>
+      </c>
+      <c r="D41" s="5">
+        <v>27.25</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-2.42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-11.04</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-10.84</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="5">
+        <v>36.98</v>
+      </c>
+      <c r="D42" s="5">
+        <v>32.64</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-4.34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-4.02</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-3.88</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>48.78</v>
+      </c>
+      <c r="D43" s="5">
+        <v>47.02</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-2.64</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-3.39</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-36.51</v>
+      </c>
+      <c r="D44" s="5">
+        <v>32.02</v>
+      </c>
+      <c r="E44" s="7">
+        <v>68.53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>5.69</v>
-      </c>
-      <c r="D13" s="6">
-        <v>6.05</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-73.17</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-7.77</v>
+      </c>
+      <c r="E45" s="7">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.53</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-1.93</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-62.89</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-54.43</v>
+      </c>
+      <c r="E46" s="7">
+        <v>8.460000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-5.96</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-5.08</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-43.5</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-42.95</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>2.45</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.29</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-35.08</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-33.02</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-17.6</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-18.66</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-25.57</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-26.48</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-10.65</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-9.23</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-1.92</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-2.72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-24</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-21.24</v>
-      </c>
-      <c r="E22" s="7">
-        <v>2.76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>6.69</v>
-      </c>
-      <c r="D23" s="6">
-        <v>5.55</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-10.33</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-9.32</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>3.9</v>
-      </c>
-      <c r="D25" s="6">
-        <v>6.92</v>
-      </c>
-      <c r="E25" s="7">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>17.4</v>
-      </c>
-      <c r="D26" s="6">
-        <v>18.37</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-36.23</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-36.71</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-17.93</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-18.61</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-27.11</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-27.75</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-18.85</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-17.65</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-10.81</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-12.55</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>585.9</v>
-      </c>
-      <c r="D32" s="6">
-        <v>581.45</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-4.45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>614.75</v>
-      </c>
-      <c r="D33" s="6">
-        <v>609.3</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-5.45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>923</v>
-      </c>
-      <c r="D34" s="6">
-        <v>915</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1150.5</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1167.5</v>
-      </c>
-      <c r="E35" s="7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2069.4</v>
-      </c>
-      <c r="D36" s="6">
-        <v>2029.1</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-40.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="6">
-        <v>79</v>
-      </c>
-      <c r="D37" s="6">
-        <v>60</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="6">
-        <v>60</v>
-      </c>
-      <c r="D38" s="6">
-        <v>79</v>
-      </c>
-      <c r="E38" s="7">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>31.34</v>
-      </c>
-      <c r="D39" s="6">
-        <v>29.95</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>64.06</v>
-      </c>
-      <c r="D40" s="6">
-        <v>61.5</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2.56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>31.17</v>
-      </c>
-      <c r="D41" s="6">
-        <v>29.67</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>32.7</v>
-      </c>
-      <c r="D42" s="6">
-        <v>36.98</v>
-      </c>
-      <c r="E42" s="7">
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>54.04</v>
-      </c>
-      <c r="D43" s="6">
-        <v>48.78</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-5.26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="B48" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="6">
-        <v>-65.45999999999999</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-36.51</v>
-      </c>
-      <c r="E44" s="7">
-        <v>28.95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-52.8</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-73.17</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-20.37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-46.95</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-62.89</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-15.94</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-34.3</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-43.5</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-9.199999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>98.81</v>
-      </c>
-      <c r="D48" s="6">
+      <c r="C48" s="5">
         <v>-44.45</v>
       </c>
-      <c r="E48" s="8">
-        <v>-143.26</v>
+      <c r="D48" s="5">
+        <v>21.24</v>
+      </c>
+      <c r="E48" s="7">
+        <v>65.69</v>
       </c>
     </row>
   </sheetData>
@@ -2434,60 +2371,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>57.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>41.4</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-5.5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-7.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-1.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2589,37 +2526,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1586</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.06320000000000001</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0069</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0251</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1509</v>
+      <c r="A2" s="13">
+        <v>0.1522</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0623</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0073</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0301</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1554</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>63.2 → 72.1</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>63.2</t>
+  </si>
+  <si>
+    <t>72.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -218,7 +245,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,7 +279,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -264,8 +291,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,13 +326,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,21 +408,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -391,7 +432,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -890,10 +931,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>560.7</v>
+        <v>562.4</v>
       </c>
       <c r="D2">
-        <v>-3.57</v>
+        <v>0.3</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +943,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-38.97</v>
+        <v>-38.79</v>
       </c>
       <c r="H2">
-        <v>7.44</v>
+        <v>7.77</v>
       </c>
       <c r="I2">
-        <v>-5.4</v>
+        <v>-5.84</v>
       </c>
       <c r="J2">
-        <v>-14.44</v>
+        <v>-10.49</v>
       </c>
       <c r="K2">
-        <v>-28.84</v>
+        <v>-28.16</v>
       </c>
       <c r="L2">
-        <v>-33.22</v>
+        <v>-34.4</v>
       </c>
       <c r="M2">
-        <v>-15.54</v>
+        <v>-15.6</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>583.76</v>
+        <v>576.79</v>
       </c>
       <c r="Q2">
-        <v>600.89</v>
+        <v>597.9</v>
       </c>
       <c r="R2">
-        <v>654.3</v>
+        <v>650</v>
       </c>
       <c r="S2">
-        <v>676.62</v>
+        <v>676.29</v>
       </c>
       <c r="T2">
-        <v>-17.13</v>
+        <v>-16.84</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,43 +997,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>24.48</v>
+        <v>25.68</v>
       </c>
       <c r="Z2">
-        <v>-21.57</v>
+        <v>-22.3</v>
       </c>
       <c r="AA2">
-        <v>-21.7</v>
+        <v>-21.82</v>
       </c>
       <c r="AB2">
-        <v>0.13</v>
+        <v>-0.48</v>
       </c>
       <c r="AC2">
-        <v>36.17</v>
+        <v>19.54</v>
       </c>
       <c r="AD2">
-        <v>59.77</v>
+        <v>39.85</v>
       </c>
       <c r="AE2">
-        <v>24.18</v>
+        <v>23.98</v>
       </c>
       <c r="AF2">
-        <v>32.02</v>
+        <v>-39.8</v>
       </c>
       <c r="AG2">
-        <v>632.6900000000001</v>
+        <v>632.39</v>
       </c>
       <c r="AH2">
-        <v>569.09</v>
+        <v>563.41</v>
       </c>
       <c r="AI2">
-        <v>643.05</v>
+        <v>637.88</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>56.1</v>
+        <v>58.77</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1044,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>615.3</v>
+        <v>654.4</v>
       </c>
       <c r="D3">
-        <v>0.98</v>
+        <v>6.35</v>
       </c>
       <c r="E3">
         <v>748.6</v>
@@ -1015,46 +1056,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-17.81</v>
+        <v>-12.58</v>
       </c>
       <c r="H3">
-        <v>19.94</v>
+        <v>27.56</v>
       </c>
       <c r="I3">
-        <v>7.43</v>
+        <v>7.26</v>
       </c>
       <c r="J3">
-        <v>10.51</v>
+        <v>15.81</v>
       </c>
       <c r="K3">
-        <v>5.53</v>
+        <v>13.5</v>
       </c>
       <c r="L3">
-        <v>-16.63</v>
+        <v>-11.1</v>
       </c>
       <c r="M3">
-        <v>0.73</v>
+        <v>1.88</v>
       </c>
       <c r="N3">
         <v>79</v>
       </c>
       <c r="O3">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="P3">
-        <v>615.04</v>
+        <v>623.9</v>
       </c>
       <c r="Q3">
-        <v>578.11</v>
+        <v>582.67</v>
       </c>
       <c r="R3">
-        <v>570.12</v>
+        <v>571.67</v>
       </c>
       <c r="S3">
-        <v>577.53</v>
+        <v>577.88</v>
       </c>
       <c r="T3">
-        <v>6.54</v>
+        <v>13.24</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1069,43 +1110,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>63.24</v>
+        <v>72.08</v>
       </c>
       <c r="Z3">
-        <v>12.86</v>
+        <v>16.57</v>
       </c>
       <c r="AA3">
-        <v>7.79</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AB3">
-        <v>5.07</v>
+        <v>7.02</v>
       </c>
       <c r="AC3">
-        <v>75.58</v>
+        <v>82.02</v>
       </c>
       <c r="AD3">
-        <v>84.41</v>
+        <v>80.56</v>
       </c>
       <c r="AE3">
-        <v>17.62</v>
+        <v>22.1</v>
       </c>
       <c r="AF3">
-        <v>-7.77</v>
+        <v>2639.22</v>
       </c>
       <c r="AG3">
-        <v>628.9299999999999</v>
+        <v>643.28</v>
       </c>
       <c r="AH3">
-        <v>527.29</v>
+        <v>522.0599999999999</v>
       </c>
       <c r="AI3">
-        <v>567.6900000000001</v>
+        <v>598.35</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>39.08</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1157,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>901.3</v>
+        <v>905</v>
       </c>
       <c r="D4">
-        <v>-1.5</v>
+        <v>0.41</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1128,25 +1169,25 @@
         <v>901.3</v>
       </c>
       <c r="G4">
-        <v>-28.83</v>
+        <v>-28.54</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="I4">
-        <v>-2.97</v>
+        <v>-2.6</v>
       </c>
       <c r="J4">
-        <v>-15.8</v>
+        <v>-16.66</v>
       </c>
       <c r="K4">
-        <v>-9.789999999999999</v>
+        <v>-8.26</v>
       </c>
       <c r="L4">
-        <v>-27.4</v>
+        <v>-26.64</v>
       </c>
       <c r="M4">
-        <v>-3.01</v>
+        <v>-2.9</v>
       </c>
       <c r="N4">
         <v>40</v>
@@ -1155,19 +1196,19 @@
         <v>15</v>
       </c>
       <c r="P4">
-        <v>918.26</v>
+        <v>913.42</v>
       </c>
       <c r="Q4">
-        <v>964.46</v>
+        <v>956.8</v>
       </c>
       <c r="R4">
-        <v>1022.54</v>
+        <v>1020.25</v>
       </c>
       <c r="S4">
-        <v>1089.34</v>
+        <v>1088.25</v>
       </c>
       <c r="T4">
-        <v>-17.26</v>
+        <v>-16.84</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1182,43 +1223,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>27.25</v>
+        <v>28.93</v>
       </c>
       <c r="Z4">
-        <v>-35.15</v>
+        <v>-34.96</v>
       </c>
       <c r="AA4">
-        <v>-32.33</v>
+        <v>-32.85</v>
       </c>
       <c r="AB4">
-        <v>-2.82</v>
+        <v>-2.1</v>
       </c>
       <c r="AC4">
-        <v>39.56</v>
+        <v>32.17</v>
       </c>
       <c r="AD4">
-        <v>38.35</v>
+        <v>37.1</v>
       </c>
       <c r="AE4">
-        <v>21.94</v>
+        <v>21.41</v>
       </c>
       <c r="AF4">
-        <v>-54.43</v>
+        <v>-72.88</v>
       </c>
       <c r="AG4">
-        <v>1085.57</v>
+        <v>1072.19</v>
       </c>
       <c r="AH4">
-        <v>843.35</v>
+        <v>841.41</v>
       </c>
       <c r="AI4">
-        <v>973.13</v>
+        <v>962.62</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>58.28</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1270,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1134.5</v>
+        <v>1152.9</v>
       </c>
       <c r="D5">
-        <v>-2.83</v>
+        <v>1.62</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,46 +1282,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-19.98</v>
+        <v>-18.68</v>
       </c>
       <c r="H5">
-        <v>51.47</v>
+        <v>53.93</v>
       </c>
       <c r="I5">
-        <v>-4.22</v>
+        <v>-1.12</v>
       </c>
       <c r="J5">
-        <v>-13.9</v>
+        <v>-13.78</v>
       </c>
       <c r="K5">
-        <v>7.1</v>
+        <v>9.32</v>
       </c>
       <c r="L5">
-        <v>-10.67</v>
+        <v>-7.8</v>
       </c>
       <c r="M5">
-        <v>15.22</v>
+        <v>15.57</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="P5">
-        <v>1151.28</v>
+        <v>1148.68</v>
       </c>
       <c r="Q5">
-        <v>1231.8</v>
+        <v>1224.01</v>
       </c>
       <c r="R5">
-        <v>1257.37</v>
+        <v>1258.12</v>
       </c>
       <c r="S5">
-        <v>1064.61</v>
+        <v>1065.05</v>
       </c>
       <c r="T5">
-        <v>6.57</v>
+        <v>8.25</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1295,34 +1336,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>32.64</v>
+        <v>37.08</v>
       </c>
       <c r="Z5">
-        <v>-34.56</v>
+        <v>-34.93</v>
       </c>
       <c r="AA5">
-        <v>-22.01</v>
+        <v>-24.6</v>
       </c>
       <c r="AB5">
-        <v>-12.55</v>
+        <v>-10.33</v>
       </c>
       <c r="AC5">
-        <v>24.43</v>
+        <v>35.8</v>
       </c>
       <c r="AD5">
-        <v>15.69</v>
+        <v>25.89</v>
       </c>
       <c r="AE5">
-        <v>44.25</v>
+        <v>47.33</v>
       </c>
       <c r="AF5">
-        <v>-42.95</v>
+        <v>267.91</v>
       </c>
       <c r="AG5">
-        <v>1352.69</v>
+        <v>1344.09</v>
       </c>
       <c r="AH5">
-        <v>1110.91</v>
+        <v>1103.92</v>
       </c>
       <c r="AI5">
         <v>1281.46</v>
@@ -1331,7 +1372,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>61.58</v>
+        <v>55.31</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1383,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2014.7</v>
+        <v>1978</v>
       </c>
       <c r="D6">
-        <v>-0.71</v>
+        <v>-1.82</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,25 +1395,25 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-13.17</v>
+        <v>-14.75</v>
       </c>
       <c r="H6">
-        <v>36.93</v>
+        <v>34.44</v>
       </c>
       <c r="I6">
-        <v>-1.24</v>
+        <v>-3.47</v>
       </c>
       <c r="J6">
-        <v>-4.32</v>
+        <v>-5.35</v>
       </c>
       <c r="K6">
-        <v>17.1</v>
+        <v>16.03</v>
       </c>
       <c r="L6">
-        <v>0.38</v>
+        <v>-0.33</v>
       </c>
       <c r="M6">
-        <v>6.23</v>
+        <v>4.86</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1381,19 +1422,19 @@
         <v>63</v>
       </c>
       <c r="P6">
-        <v>2039.46</v>
+        <v>2025.26</v>
       </c>
       <c r="Q6">
-        <v>2040.73</v>
+        <v>2037.95</v>
       </c>
       <c r="R6">
-        <v>2032.12</v>
+        <v>2035.7</v>
       </c>
       <c r="S6">
-        <v>1870.86</v>
+        <v>1869.72</v>
       </c>
       <c r="T6">
-        <v>7.69</v>
+        <v>5.79</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1408,34 +1449,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>47.02</v>
+        <v>42.78</v>
       </c>
       <c r="Z6">
-        <v>-1.06</v>
+        <v>-5.65</v>
       </c>
       <c r="AA6">
-        <v>2.7</v>
+        <v>1.03</v>
       </c>
       <c r="AB6">
-        <v>-3.76</v>
+        <v>-6.68</v>
       </c>
       <c r="AC6">
-        <v>51.55</v>
+        <v>24.9</v>
       </c>
       <c r="AD6">
-        <v>56.74</v>
+        <v>44.52</v>
       </c>
       <c r="AE6">
-        <v>56.43</v>
+        <v>56.55</v>
       </c>
       <c r="AF6">
-        <v>21.24</v>
+        <v>-44.1</v>
       </c>
       <c r="AG6">
-        <v>2104.56</v>
+        <v>2107.66</v>
       </c>
       <c r="AH6">
-        <v>1976.91</v>
+        <v>1968.25</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1444,7 +1485,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>16.53</v>
+        <v>18.36</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1605,12 +1646,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1618,734 +1694,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-7.26</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-14.44</v>
       </c>
-      <c r="E7" s="6">
-        <v>-7.18</v>
+      <c r="D7" s="6">
+        <v>-10.49</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3.95</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>8.92</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>10.51</v>
       </c>
+      <c r="D8" s="6">
+        <v>15.81</v>
+      </c>
       <c r="E8" s="7">
-        <v>1.59</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-14.65</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-15.8</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.15</v>
+      <c r="D9" s="6">
+        <v>-16.66</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-10.84</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-13.9</v>
       </c>
-      <c r="E10" s="6">
-        <v>-3.06</v>
+      <c r="D10" s="6">
+        <v>-13.78</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-3.88</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-4.32</v>
       </c>
-      <c r="E11" s="6">
+      <c r="D11" s="6">
+        <v>-5.35</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-5.4</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-5.84</v>
+      </c>
+      <c r="E12" s="8">
         <v>-0.44</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>7.43</v>
+      </c>
+      <c r="D13" s="6">
+        <v>7.26</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-2.97</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-2.6</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-4.22</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-1.12</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-1.24</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.47</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-3.39</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-5.4</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-33.22</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-34.4</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>6.05</v>
-      </c>
-      <c r="D13" s="5">
-        <v>7.43</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-16.63</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-11.1</v>
+      </c>
+      <c r="E18" s="7">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-1.93</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-2.97</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-27.4</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-26.64</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-5.08</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-4.22</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-10.67</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-7.8</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-0.29</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-1.24</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-0.33</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-33.02</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-33.22</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-28.84</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-28.16</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-18.66</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-16.63</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.03</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>5.53</v>
+      </c>
+      <c r="D23" s="6">
+        <v>13.5</v>
+      </c>
+      <c r="E23" s="7">
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-26.48</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-27.4</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-9.789999999999999</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-8.26</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-9.23</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-10.67</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>7.1</v>
+      </c>
+      <c r="D25" s="6">
+        <v>9.32</v>
+      </c>
+      <c r="E25" s="7">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-1.92</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>17.1</v>
+      </c>
+      <c r="D26" s="6">
+        <v>16.03</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-21.24</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-28.84</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-7.6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-38.97</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-38.79</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5">
-        <v>5.55</v>
-      </c>
-      <c r="D23" s="5">
-        <v>5.53</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-17.81</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-12.58</v>
+      </c>
+      <c r="E28" s="7">
+        <v>5.23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-9.32</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-9.789999999999999</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-28.83</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-28.54</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>6.92</v>
-      </c>
-      <c r="D25" s="5">
-        <v>7.1</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-19.98</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-18.68</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>18.37</v>
-      </c>
-      <c r="D26" s="5">
-        <v>17.1</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-13.17</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-14.75</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-36.71</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-38.97</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>560.7</v>
+      </c>
+      <c r="D32" s="6">
+        <v>562.4</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-18.61</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-17.81</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>615.3</v>
+      </c>
+      <c r="D33" s="6">
+        <v>654.4</v>
+      </c>
+      <c r="E33" s="7">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-27.75</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-28.83</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>901.3</v>
+      </c>
+      <c r="D34" s="6">
+        <v>905</v>
+      </c>
+      <c r="E34" s="7">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-17.65</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-19.98</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-2.33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1134.5</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1152.9</v>
+      </c>
+      <c r="E35" s="7">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-12.55</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-13.17</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2014.7</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1978</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-36.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>581.45</v>
-      </c>
-      <c r="D32" s="5">
-        <v>560.7</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-20.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="6">
+        <v>24.48</v>
+      </c>
+      <c r="D37" s="6">
+        <v>25.68</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>609.3</v>
-      </c>
-      <c r="D33" s="5">
-        <v>615.3</v>
-      </c>
-      <c r="E33" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="6">
+        <v>63.24</v>
+      </c>
+      <c r="D38" s="6">
+        <v>72.08</v>
+      </c>
+      <c r="E38" s="7">
+        <v>8.84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>915</v>
-      </c>
-      <c r="D34" s="5">
-        <v>901.3</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-13.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>27.25</v>
+      </c>
+      <c r="D39" s="6">
+        <v>28.93</v>
+      </c>
+      <c r="E39" s="7">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>1167.5</v>
-      </c>
-      <c r="D35" s="5">
-        <v>1134.5</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>32.64</v>
+      </c>
+      <c r="D40" s="6">
+        <v>37.08</v>
+      </c>
+      <c r="E40" s="7">
+        <v>4.44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2029.1</v>
-      </c>
-      <c r="D36" s="5">
-        <v>2014.7</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-14.4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>47.02</v>
+      </c>
+      <c r="D41" s="6">
+        <v>42.78</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-4.24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="6">
+        <v>32.02</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-39.8</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-71.81999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="5">
-        <v>60</v>
-      </c>
-      <c r="D37" s="5">
-        <v>79</v>
-      </c>
-      <c r="E37" s="7">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-7.77</v>
+      </c>
+      <c r="D43" s="6">
+        <v>2639.22</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2646.99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-54.43</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-72.88</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-18.45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="5">
-        <v>79</v>
-      </c>
-      <c r="D38" s="5">
-        <v>60</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>29.95</v>
-      </c>
-      <c r="D39" s="5">
-        <v>24.48</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-5.47</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>61.5</v>
-      </c>
-      <c r="D40" s="5">
-        <v>63.24</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>29.67</v>
-      </c>
-      <c r="D41" s="5">
-        <v>27.25</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-2.42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="5">
-        <v>36.98</v>
-      </c>
-      <c r="D42" s="5">
-        <v>32.64</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-4.34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-42.95</v>
+      </c>
+      <c r="D45" s="6">
+        <v>267.91</v>
+      </c>
+      <c r="E45" s="7">
+        <v>310.86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>48.78</v>
-      </c>
-      <c r="D43" s="5">
-        <v>47.02</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="5">
-        <v>-36.51</v>
-      </c>
-      <c r="D44" s="5">
-        <v>32.02</v>
-      </c>
-      <c r="E44" s="7">
-        <v>68.53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-73.17</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-7.77</v>
-      </c>
-      <c r="E45" s="7">
-        <v>65.40000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-62.89</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-54.43</v>
-      </c>
-      <c r="E46" s="7">
-        <v>8.460000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-43.5</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-42.95</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-44.45</v>
-      </c>
-      <c r="D48" s="5">
+      <c r="C46" s="6">
         <v>21.24</v>
       </c>
-      <c r="E48" s="7">
-        <v>65.69</v>
+      <c r="D46" s="6">
+        <v>-44.1</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-65.34</v>
       </c>
     </row>
   </sheetData>
@@ -2371,60 +2413,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="11">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="12">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>41.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="10">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="11">
-        <v>5</v>
-      </c>
-      <c r="D2" s="10">
-        <v>38.9</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-7.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-1.8</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-6.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2526,37 +2568,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1522</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0623</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.0073</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0301</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1554</v>
+      <c r="A2" s="14">
+        <v>0.1557</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0486</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0188</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.029</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.156</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,19 +181,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>63.2 → 72.1</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>63.2</t>
-  </si>
-  <si>
-    <t>72.1</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>25.7 → 32.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>25.7</t>
+  </si>
+  <si>
+    <t>32.5</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -245,7 +254,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,13 +288,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -299,7 +301,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,12 +323,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -416,14 +412,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -432,7 +429,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -931,10 +928,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>562.4</v>
+        <v>572.55</v>
       </c>
       <c r="D2">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -943,46 +940,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-38.79</v>
+        <v>-37.68</v>
       </c>
       <c r="H2">
-        <v>7.77</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I2">
-        <v>-5.84</v>
+        <v>-3.53</v>
       </c>
       <c r="J2">
-        <v>-10.49</v>
+        <v>-7.99</v>
       </c>
       <c r="K2">
-        <v>-28.16</v>
+        <v>-26.34</v>
       </c>
       <c r="L2">
-        <v>-34.4</v>
+        <v>-34.39</v>
       </c>
       <c r="M2">
-        <v>-15.6</v>
+        <v>-15.16</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P2">
-        <v>576.79</v>
+        <v>572.6</v>
       </c>
       <c r="Q2">
-        <v>597.9</v>
+        <v>595.7</v>
       </c>
       <c r="R2">
-        <v>650</v>
+        <v>646.08</v>
       </c>
       <c r="S2">
-        <v>676.29</v>
+        <v>675.99</v>
       </c>
       <c r="T2">
-        <v>-16.84</v>
+        <v>-15.3</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -997,34 +994,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>25.68</v>
+        <v>32.55</v>
       </c>
       <c r="Z2">
-        <v>-22.3</v>
+        <v>-21.8</v>
       </c>
       <c r="AA2">
         <v>-21.82</v>
       </c>
       <c r="AB2">
-        <v>-0.48</v>
+        <v>0.01</v>
       </c>
       <c r="AC2">
-        <v>19.54</v>
+        <v>27.46</v>
       </c>
       <c r="AD2">
-        <v>39.85</v>
+        <v>27.72</v>
       </c>
       <c r="AE2">
-        <v>23.98</v>
+        <v>24.54</v>
       </c>
       <c r="AF2">
-        <v>-39.8</v>
+        <v>6.61</v>
       </c>
       <c r="AG2">
-        <v>632.39</v>
+        <v>630.79</v>
       </c>
       <c r="AH2">
-        <v>563.41</v>
+        <v>560.61</v>
       </c>
       <c r="AI2">
         <v>637.88</v>
@@ -1033,7 +1030,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>58.77</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1044,10 +1041,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>654.4</v>
+        <v>670.25</v>
       </c>
       <c r="D3">
-        <v>6.35</v>
+        <v>2.42</v>
       </c>
       <c r="E3">
         <v>748.6</v>
@@ -1056,46 +1053,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-12.58</v>
+        <v>-10.47</v>
       </c>
       <c r="H3">
-        <v>27.56</v>
+        <v>30.65</v>
       </c>
       <c r="I3">
-        <v>7.26</v>
+        <v>7.11</v>
       </c>
       <c r="J3">
-        <v>15.81</v>
+        <v>19</v>
       </c>
       <c r="K3">
-        <v>13.5</v>
+        <v>16.23</v>
       </c>
       <c r="L3">
-        <v>-11.1</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="M3">
-        <v>1.88</v>
+        <v>2.33</v>
       </c>
       <c r="N3">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="P3">
-        <v>623.9</v>
+        <v>632.8</v>
       </c>
       <c r="Q3">
-        <v>582.67</v>
+        <v>587.86</v>
       </c>
       <c r="R3">
-        <v>571.67</v>
+        <v>573.75</v>
       </c>
       <c r="S3">
-        <v>577.88</v>
+        <v>578.39</v>
       </c>
       <c r="T3">
-        <v>13.24</v>
+        <v>15.88</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1110,34 +1107,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>72.08</v>
+        <v>74.73</v>
       </c>
       <c r="Z3">
-        <v>16.57</v>
+        <v>20.55</v>
       </c>
       <c r="AA3">
-        <v>9.550000000000001</v>
+        <v>11.75</v>
       </c>
       <c r="AB3">
-        <v>7.02</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
-        <v>82.02</v>
+        <v>91.5</v>
       </c>
       <c r="AD3">
-        <v>80.56</v>
+        <v>83.03</v>
       </c>
       <c r="AE3">
-        <v>22.1</v>
+        <v>22.64</v>
       </c>
       <c r="AF3">
-        <v>2639.22</v>
+        <v>145.53</v>
       </c>
       <c r="AG3">
-        <v>643.28</v>
+        <v>659.41</v>
       </c>
       <c r="AH3">
-        <v>522.0599999999999</v>
+        <v>516.3099999999999</v>
       </c>
       <c r="AI3">
         <v>598.35</v>
@@ -1146,7 +1143,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>44.19</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1160,7 +1157,7 @@
         <v>905</v>
       </c>
       <c r="D4">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
@@ -1175,40 +1172,40 @@
         <v>0.41</v>
       </c>
       <c r="I4">
-        <v>-2.6</v>
+        <v>-1.93</v>
       </c>
       <c r="J4">
-        <v>-16.66</v>
+        <v>-14.48</v>
       </c>
       <c r="K4">
-        <v>-8.26</v>
+        <v>-9.08</v>
       </c>
       <c r="L4">
-        <v>-26.64</v>
+        <v>-26.17</v>
       </c>
       <c r="M4">
-        <v>-2.9</v>
+        <v>-3.39</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P4">
-        <v>913.42</v>
+        <v>909.86</v>
       </c>
       <c r="Q4">
-        <v>956.8</v>
+        <v>948.6</v>
       </c>
       <c r="R4">
-        <v>1020.25</v>
+        <v>1017.93</v>
       </c>
       <c r="S4">
-        <v>1088.25</v>
+        <v>1087.09</v>
       </c>
       <c r="T4">
-        <v>-16.84</v>
+        <v>-16.75</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1226,40 +1223,40 @@
         <v>28.93</v>
       </c>
       <c r="Z4">
-        <v>-34.96</v>
+        <v>-34.41</v>
       </c>
       <c r="AA4">
-        <v>-32.85</v>
+        <v>-33.16</v>
       </c>
       <c r="AB4">
-        <v>-2.1</v>
+        <v>-1.24</v>
       </c>
       <c r="AC4">
-        <v>32.17</v>
+        <v>26.1</v>
       </c>
       <c r="AD4">
-        <v>37.1</v>
+        <v>32.61</v>
       </c>
       <c r="AE4">
-        <v>21.41</v>
+        <v>20.85</v>
       </c>
       <c r="AF4">
-        <v>-72.88</v>
+        <v>-56.11</v>
       </c>
       <c r="AG4">
-        <v>1072.19</v>
+        <v>1053.23</v>
       </c>
       <c r="AH4">
-        <v>841.41</v>
+        <v>843.97</v>
       </c>
       <c r="AI4">
-        <v>962.62</v>
+        <v>960.8</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>60.26</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1270,10 +1267,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1152.9</v>
+        <v>1138.8</v>
       </c>
       <c r="D5">
-        <v>1.62</v>
+        <v>-1.22</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1282,25 +1279,25 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-18.68</v>
+        <v>-19.67</v>
       </c>
       <c r="H5">
-        <v>53.93</v>
+        <v>52.04</v>
       </c>
       <c r="I5">
-        <v>-1.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J5">
-        <v>-13.78</v>
+        <v>-12.99</v>
       </c>
       <c r="K5">
-        <v>9.32</v>
+        <v>8.74</v>
       </c>
       <c r="L5">
-        <v>-7.8</v>
+        <v>-7.43</v>
       </c>
       <c r="M5">
-        <v>15.57</v>
+        <v>15.22</v>
       </c>
       <c r="N5">
         <v>60</v>
@@ -1309,19 +1306,19 @@
         <v>49</v>
       </c>
       <c r="P5">
-        <v>1148.68</v>
+        <v>1148.84</v>
       </c>
       <c r="Q5">
-        <v>1224.01</v>
+        <v>1214.93</v>
       </c>
       <c r="R5">
-        <v>1258.12</v>
+        <v>1258.27</v>
       </c>
       <c r="S5">
-        <v>1065.05</v>
+        <v>1065.43</v>
       </c>
       <c r="T5">
-        <v>8.25</v>
+        <v>6.89</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1336,43 +1333,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>37.08</v>
+        <v>35.17</v>
       </c>
       <c r="Z5">
-        <v>-34.93</v>
+        <v>-35.94</v>
       </c>
       <c r="AA5">
-        <v>-24.6</v>
+        <v>-26.86</v>
       </c>
       <c r="AB5">
-        <v>-10.33</v>
+        <v>-9.07</v>
       </c>
       <c r="AC5">
-        <v>35.8</v>
+        <v>36.38</v>
       </c>
       <c r="AD5">
-        <v>25.89</v>
+        <v>32.2</v>
       </c>
       <c r="AE5">
-        <v>47.33</v>
+        <v>45.23</v>
       </c>
       <c r="AF5">
-        <v>267.91</v>
+        <v>-68.72</v>
       </c>
       <c r="AG5">
-        <v>1344.09</v>
+        <v>1331.74</v>
       </c>
       <c r="AH5">
-        <v>1103.92</v>
+        <v>1098.11</v>
       </c>
       <c r="AI5">
-        <v>1281.46</v>
+        <v>1279.65</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>55.31</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1383,10 +1380,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1978</v>
+        <v>1970.7</v>
       </c>
       <c r="D6">
-        <v>-1.82</v>
+        <v>-0.37</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1395,88 +1392,88 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-14.75</v>
+        <v>-15.07</v>
       </c>
       <c r="H6">
-        <v>34.44</v>
+        <v>33.94</v>
       </c>
       <c r="I6">
-        <v>-3.47</v>
+        <v>-3.16</v>
       </c>
       <c r="J6">
-        <v>-5.35</v>
+        <v>-3.09</v>
       </c>
       <c r="K6">
-        <v>16.03</v>
+        <v>16.31</v>
       </c>
       <c r="L6">
-        <v>-0.33</v>
+        <v>1.18</v>
       </c>
       <c r="M6">
-        <v>4.86</v>
+        <v>4.32</v>
       </c>
       <c r="N6">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O6">
         <v>63</v>
       </c>
       <c r="P6">
-        <v>2025.26</v>
+        <v>2012.38</v>
       </c>
       <c r="Q6">
-        <v>2037.95</v>
+        <v>2031.54</v>
       </c>
       <c r="R6">
-        <v>2035.7</v>
+        <v>2039.32</v>
       </c>
       <c r="S6">
-        <v>1869.72</v>
+        <v>1868.6</v>
       </c>
       <c r="T6">
-        <v>5.79</v>
+        <v>5.46</v>
       </c>
       <c r="U6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V6" t="s">
         <v>44</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>42.78</v>
+        <v>41.97</v>
       </c>
       <c r="Z6">
-        <v>-5.65</v>
+        <v>-9.76</v>
       </c>
       <c r="AA6">
-        <v>1.03</v>
+        <v>-1.13</v>
       </c>
       <c r="AB6">
-        <v>-6.68</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="AC6">
-        <v>24.9</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AD6">
-        <v>44.52</v>
+        <v>28.64</v>
       </c>
       <c r="AE6">
-        <v>56.55</v>
+        <v>57.45</v>
       </c>
       <c r="AF6">
-        <v>-44.1</v>
+        <v>31.11</v>
       </c>
       <c r="AG6">
-        <v>2107.66</v>
+        <v>2101.21</v>
       </c>
       <c r="AH6">
-        <v>1968.25</v>
+        <v>1961.87</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1485,7 +1482,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>18.36</v>
+        <v>22.79</v>
       </c>
     </row>
   </sheetData>
@@ -1626,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1666,7 +1663,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1684,716 +1681,739 @@
         <v>57</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="D5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="C8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-14.44</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C9" s="7">
         <v>-10.49</v>
       </c>
-      <c r="E7" s="7">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D9" s="7">
+        <v>-7.99</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>10.51</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C10" s="7">
         <v>15.81</v>
       </c>
-      <c r="E8" s="7">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D10" s="7">
+        <v>19</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-15.8</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C11" s="7">
         <v>-16.66</v>
       </c>
-      <c r="E9" s="8">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D11" s="7">
+        <v>-14.48</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-13.9</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C12" s="7">
         <v>-13.78</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D12" s="7">
+        <v>-12.99</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-4.32</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C13" s="7">
         <v>-5.35</v>
       </c>
-      <c r="E11" s="8">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D13" s="7">
+        <v>-3.09</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-5.4</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C14" s="7">
         <v>-5.84</v>
       </c>
-      <c r="E12" s="8">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D14" s="7">
+        <v>-3.53</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>7.43</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C15" s="7">
         <v>7.26</v>
       </c>
-      <c r="E13" s="8">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D15" s="7">
+        <v>7.11</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-2.97</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C16" s="7">
         <v>-2.6</v>
       </c>
-      <c r="E14" s="7">
+      <c r="D16" s="7">
+        <v>-1.93</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1.12</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-3.47</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-3.16</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-34.4</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-34.39</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-11.1</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-26.64</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-26.17</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-7.8</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-7.43</v>
+      </c>
+      <c r="E22" s="8">
         <v>0.37</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-0.33</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1.18</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-28.16</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-26.34</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="D25" s="7">
+        <v>16.23</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-8.26</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-9.08</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-4.22</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-1.12</v>
-      </c>
-      <c r="E15" s="7">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7">
+        <v>9.32</v>
+      </c>
+      <c r="D27" s="7">
+        <v>8.74</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-1.24</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.47</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="7">
+        <v>16.03</v>
+      </c>
+      <c r="D28" s="7">
+        <v>16.31</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-33.22</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-34.4</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B29" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-38.79</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-37.68</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-16.63</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-11.1</v>
-      </c>
-      <c r="E18" s="7">
-        <v>5.53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B30" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-12.58</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-10.47</v>
+      </c>
+      <c r="E30" s="8">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-18.68</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-19.67</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-14.75</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-15.07</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="7">
+        <v>562.4</v>
+      </c>
+      <c r="D33" s="7">
+        <v>572.55</v>
+      </c>
+      <c r="E33" s="8">
+        <v>10.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="7">
+        <v>654.4</v>
+      </c>
+      <c r="D34" s="7">
+        <v>670.25</v>
+      </c>
+      <c r="E34" s="8">
+        <v>15.85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="7">
+        <v>1152.9</v>
+      </c>
+      <c r="D35" s="7">
+        <v>1138.8</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-14.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="7">
+        <v>1978</v>
+      </c>
+      <c r="D36" s="7">
+        <v>1970.7</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-7.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="7">
+        <v>79</v>
+      </c>
+      <c r="D37" s="7">
+        <v>99</v>
+      </c>
+      <c r="E37" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="7">
+        <v>99</v>
+      </c>
+      <c r="D38" s="7">
+        <v>79</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="7">
+        <v>25.68</v>
+      </c>
+      <c r="D39" s="7">
+        <v>32.55</v>
+      </c>
+      <c r="E39" s="8">
+        <v>6.87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="7">
+        <v>72.08</v>
+      </c>
+      <c r="D40" s="7">
+        <v>74.73</v>
+      </c>
+      <c r="E40" s="8">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="7">
+        <v>37.08</v>
+      </c>
+      <c r="D41" s="7">
+        <v>35.17</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="7">
+        <v>42.78</v>
+      </c>
+      <c r="D42" s="7">
+        <v>41.97</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-39.8</v>
+      </c>
+      <c r="D43" s="7">
+        <v>6.61</v>
+      </c>
+      <c r="E43" s="8">
+        <v>46.41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="7">
+        <v>2639.22</v>
+      </c>
+      <c r="D44" s="7">
+        <v>145.53</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-2493.69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-27.4</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-26.64</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-72.88</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-56.11</v>
+      </c>
+      <c r="E45" s="8">
+        <v>16.77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-10.67</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-7.8</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="7">
+        <v>267.91</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-68.72</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-336.63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.38</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-0.33</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-28.84</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-28.16</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>5.53</v>
-      </c>
-      <c r="D23" s="6">
-        <v>13.5</v>
-      </c>
-      <c r="E23" s="7">
-        <v>7.97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-9.789999999999999</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-8.26</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>7.1</v>
-      </c>
-      <c r="D25" s="6">
-        <v>9.32</v>
-      </c>
-      <c r="E25" s="7">
-        <v>2.22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>17.1</v>
-      </c>
-      <c r="D26" s="6">
-        <v>16.03</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-38.97</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-38.79</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-17.81</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-12.58</v>
-      </c>
-      <c r="E28" s="7">
-        <v>5.23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-28.83</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-28.54</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-19.98</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-18.68</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-13.17</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-14.75</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>560.7</v>
-      </c>
-      <c r="D32" s="6">
-        <v>562.4</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>615.3</v>
-      </c>
-      <c r="D33" s="6">
-        <v>654.4</v>
-      </c>
-      <c r="E33" s="7">
-        <v>39.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>901.3</v>
-      </c>
-      <c r="D34" s="6">
-        <v>905</v>
-      </c>
-      <c r="E34" s="7">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1134.5</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1152.9</v>
-      </c>
-      <c r="E35" s="7">
-        <v>18.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2014.7</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1978</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-36.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>24.48</v>
-      </c>
-      <c r="D37" s="6">
-        <v>25.68</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>63.24</v>
-      </c>
-      <c r="D38" s="6">
-        <v>72.08</v>
-      </c>
-      <c r="E38" s="7">
-        <v>8.84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>27.25</v>
-      </c>
-      <c r="D39" s="6">
-        <v>28.93</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>32.64</v>
-      </c>
-      <c r="D40" s="6">
-        <v>37.08</v>
-      </c>
-      <c r="E40" s="7">
-        <v>4.44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>47.02</v>
-      </c>
-      <c r="D41" s="6">
-        <v>42.78</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-4.24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="B47" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="6">
-        <v>32.02</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-39.8</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-71.81999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-7.77</v>
-      </c>
-      <c r="D43" s="6">
-        <v>2639.22</v>
-      </c>
-      <c r="E43" s="7">
-        <v>2646.99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-54.43</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-72.88</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-18.45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-42.95</v>
-      </c>
-      <c r="D45" s="6">
-        <v>267.91</v>
-      </c>
-      <c r="E45" s="7">
-        <v>310.86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>21.24</v>
-      </c>
-      <c r="D46" s="6">
+      <c r="C47" s="7">
         <v>-44.1</v>
       </c>
-      <c r="E46" s="8">
-        <v>-65.34</v>
+      <c r="D47" s="7">
+        <v>31.11</v>
+      </c>
+      <c r="E47" s="8">
+        <v>75.20999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2413,61 +2433,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>70</v>
       </c>
+      <c r="G1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>57.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>41.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>42.7</v>
+      </c>
+      <c r="E2" s="12">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-3.9</v>
+      </c>
+      <c r="G2" s="12">
+        <v>1.2</v>
+      </c>
+      <c r="H2" s="12">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
-        <v>20</v>
+      <c r="I2" s="12">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2568,37 +2588,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1557</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0486</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0188</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.029</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.156</v>
+      <c r="A2" s="15">
+        <v>0.1522</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.0432</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.0233</v>
+      </c>
+      <c r="D2" s="15">
+        <v>-0.0339</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.1516</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,28 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>25.7 → 32.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>25.7</t>
-  </si>
-  <si>
-    <t>32.5</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>74.7 → 69.7</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>74.7</t>
+  </si>
+  <si>
+    <t>69.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -254,7 +245,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,6 +279,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -301,7 +299,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -323,6 +321,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +408,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -412,15 +416,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -429,7 +432,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -788,7 +791,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -928,10 +932,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>572.55</v>
+        <v>573.25</v>
       </c>
       <c r="D2">
-        <v>1.8</v>
+        <v>0.12</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -940,46 +944,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-37.68</v>
+        <v>-37.61</v>
       </c>
       <c r="H2">
-        <v>9.720000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="I2">
-        <v>-3.53</v>
+        <v>-2.16</v>
       </c>
       <c r="J2">
-        <v>-7.99</v>
+        <v>-7.02</v>
       </c>
       <c r="K2">
-        <v>-26.34</v>
+        <v>-24.37</v>
       </c>
       <c r="L2">
-        <v>-34.39</v>
+        <v>-34.25</v>
       </c>
       <c r="M2">
-        <v>-15.16</v>
+        <v>-15.01</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P2">
-        <v>572.6</v>
+        <v>570.0700000000001</v>
       </c>
       <c r="Q2">
-        <v>595.7</v>
+        <v>593.34</v>
       </c>
       <c r="R2">
-        <v>646.08</v>
+        <v>642.51</v>
       </c>
       <c r="S2">
-        <v>675.99</v>
+        <v>675.67</v>
       </c>
       <c r="T2">
-        <v>-15.3</v>
+        <v>-15.16</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -994,34 +998,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>32.55</v>
+        <v>33.01</v>
       </c>
       <c r="Z2">
-        <v>-21.8</v>
+        <v>-21.11</v>
       </c>
       <c r="AA2">
-        <v>-21.82</v>
+        <v>-21.68</v>
       </c>
       <c r="AB2">
-        <v>0.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC2">
-        <v>27.46</v>
+        <v>52.73</v>
       </c>
       <c r="AD2">
-        <v>27.72</v>
+        <v>33.24</v>
       </c>
       <c r="AE2">
-        <v>24.54</v>
+        <v>23.56</v>
       </c>
       <c r="AF2">
-        <v>6.61</v>
+        <v>-70.23999999999999</v>
       </c>
       <c r="AG2">
-        <v>630.79</v>
+        <v>627.78</v>
       </c>
       <c r="AH2">
-        <v>560.61</v>
+        <v>558.9</v>
       </c>
       <c r="AI2">
         <v>637.88</v>
@@ -1030,7 +1034,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>57.57</v>
+        <v>56.54</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1041,10 +1045,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>670.25</v>
+        <v>658.95</v>
       </c>
       <c r="D3">
-        <v>2.42</v>
+        <v>-1.69</v>
       </c>
       <c r="E3">
         <v>748.6</v>
@@ -1053,46 +1057,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-10.47</v>
+        <v>-11.98</v>
       </c>
       <c r="H3">
-        <v>30.65</v>
+        <v>28.45</v>
       </c>
       <c r="I3">
-        <v>7.11</v>
+        <v>7.19</v>
       </c>
       <c r="J3">
-        <v>19</v>
+        <v>16.33</v>
       </c>
       <c r="K3">
-        <v>16.23</v>
+        <v>13.65</v>
       </c>
       <c r="L3">
-        <v>-9.460000000000001</v>
+        <v>-11.22</v>
       </c>
       <c r="M3">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P3">
-        <v>632.8</v>
+        <v>641.64</v>
       </c>
       <c r="Q3">
-        <v>587.86</v>
+        <v>593.53</v>
       </c>
       <c r="R3">
-        <v>573.75</v>
+        <v>575.62</v>
       </c>
       <c r="S3">
-        <v>578.39</v>
+        <v>578.77</v>
       </c>
       <c r="T3">
-        <v>15.88</v>
+        <v>13.85</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1107,34 +1111,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>74.73</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="Z3">
-        <v>20.55</v>
+        <v>22.53</v>
       </c>
       <c r="AA3">
-        <v>11.75</v>
+        <v>13.9</v>
       </c>
       <c r="AB3">
-        <v>8.800000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AC3">
-        <v>91.5</v>
+        <v>92.42</v>
       </c>
       <c r="AD3">
-        <v>83.03</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="AE3">
-        <v>22.64</v>
+        <v>22.37</v>
       </c>
       <c r="AF3">
-        <v>145.53</v>
+        <v>-66.38</v>
       </c>
       <c r="AG3">
-        <v>659.41</v>
+        <v>668.84</v>
       </c>
       <c r="AH3">
-        <v>516.3099999999999</v>
+        <v>518.22</v>
       </c>
       <c r="AI3">
         <v>598.35</v>
@@ -1143,7 +1147,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>48.62</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1154,58 +1158,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-2.76</v>
       </c>
       <c r="E4">
         <v>1266.37</v>
       </c>
       <c r="F4">
-        <v>901.3</v>
+        <v>880</v>
       </c>
       <c r="G4">
-        <v>-28.54</v>
+        <v>-30.51</v>
       </c>
       <c r="H4">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.93</v>
+        <v>-4.66</v>
       </c>
       <c r="J4">
-        <v>-14.48</v>
+        <v>-17.68</v>
       </c>
       <c r="K4">
-        <v>-9.08</v>
+        <v>-11.82</v>
       </c>
       <c r="L4">
-        <v>-26.17</v>
+        <v>-29.02</v>
       </c>
       <c r="M4">
-        <v>-3.39</v>
+        <v>-3.82</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P4">
-        <v>909.86</v>
+        <v>901.26</v>
       </c>
       <c r="Q4">
-        <v>948.6</v>
+        <v>938.74</v>
       </c>
       <c r="R4">
-        <v>1017.93</v>
+        <v>1015.12</v>
       </c>
       <c r="S4">
-        <v>1087.09</v>
+        <v>1085.78</v>
       </c>
       <c r="T4">
-        <v>-16.75</v>
+        <v>-18.95</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1220,43 +1224,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.93</v>
+        <v>24.49</v>
       </c>
       <c r="Z4">
-        <v>-34.41</v>
+        <v>-35.58</v>
       </c>
       <c r="AA4">
-        <v>-33.16</v>
+        <v>-33.65</v>
       </c>
       <c r="AB4">
-        <v>-1.24</v>
+        <v>-1.93</v>
       </c>
       <c r="AC4">
-        <v>26.1</v>
+        <v>14.44</v>
       </c>
       <c r="AD4">
-        <v>32.61</v>
+        <v>24.24</v>
       </c>
       <c r="AE4">
-        <v>20.85</v>
+        <v>22.61</v>
       </c>
       <c r="AF4">
-        <v>-56.11</v>
+        <v>182.88</v>
       </c>
       <c r="AG4">
-        <v>1053.23</v>
+        <v>1028.4</v>
       </c>
       <c r="AH4">
-        <v>843.97</v>
+        <v>849.0700000000001</v>
       </c>
       <c r="AI4">
-        <v>960.8</v>
+        <v>944.09</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>61.97</v>
+        <v>64.86</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1267,10 +1271,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1138.8</v>
+        <v>1154.3</v>
       </c>
       <c r="D5">
-        <v>-1.22</v>
+        <v>1.36</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1279,46 +1283,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-19.67</v>
+        <v>-18.58</v>
       </c>
       <c r="H5">
-        <v>52.04</v>
+        <v>54.11</v>
       </c>
       <c r="I5">
-        <v>0.07000000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="J5">
-        <v>-12.99</v>
+        <v>-12.58</v>
       </c>
       <c r="K5">
-        <v>8.74</v>
+        <v>10.71</v>
       </c>
       <c r="L5">
-        <v>-7.43</v>
+        <v>-5.7</v>
       </c>
       <c r="M5">
-        <v>15.22</v>
+        <v>15.11</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="P5">
-        <v>1148.84</v>
+        <v>1149.6</v>
       </c>
       <c r="Q5">
-        <v>1214.93</v>
+        <v>1207.4</v>
       </c>
       <c r="R5">
-        <v>1258.27</v>
+        <v>1258.3</v>
       </c>
       <c r="S5">
-        <v>1065.43</v>
+        <v>1065.83</v>
       </c>
       <c r="T5">
-        <v>6.89</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1333,34 +1337,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>35.17</v>
+        <v>38.9</v>
       </c>
       <c r="Z5">
-        <v>-35.94</v>
+        <v>-35.08</v>
       </c>
       <c r="AA5">
-        <v>-26.86</v>
+        <v>-28.51</v>
       </c>
       <c r="AB5">
-        <v>-9.07</v>
+        <v>-6.58</v>
       </c>
       <c r="AC5">
-        <v>36.38</v>
+        <v>53.85</v>
       </c>
       <c r="AD5">
-        <v>32.2</v>
+        <v>42.01</v>
       </c>
       <c r="AE5">
-        <v>45.23</v>
+        <v>43.62</v>
       </c>
       <c r="AF5">
-        <v>-68.72</v>
+        <v>-64.98999999999999</v>
       </c>
       <c r="AG5">
-        <v>1331.74</v>
+        <v>1319.11</v>
       </c>
       <c r="AH5">
-        <v>1098.11</v>
+        <v>1095.69</v>
       </c>
       <c r="AI5">
         <v>1279.65</v>
@@ -1369,7 +1373,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>49.88</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1380,10 +1384,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1970.7</v>
+        <v>2001.5</v>
       </c>
       <c r="D6">
-        <v>-0.37</v>
+        <v>1.56</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1392,46 +1396,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-15.07</v>
+        <v>-13.74</v>
       </c>
       <c r="H6">
-        <v>33.94</v>
+        <v>36.04</v>
       </c>
       <c r="I6">
-        <v>-3.16</v>
+        <v>-3.28</v>
       </c>
       <c r="J6">
-        <v>-3.09</v>
+        <v>-4.65</v>
       </c>
       <c r="K6">
-        <v>16.31</v>
+        <v>17.16</v>
       </c>
       <c r="L6">
-        <v>1.18</v>
+        <v>2.53</v>
       </c>
       <c r="M6">
-        <v>4.32</v>
+        <v>4.84</v>
       </c>
       <c r="N6">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O6">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P6">
-        <v>2012.38</v>
+        <v>1998.8</v>
       </c>
       <c r="Q6">
-        <v>2031.54</v>
+        <v>2027.52</v>
       </c>
       <c r="R6">
-        <v>2039.32</v>
+        <v>2042.94</v>
       </c>
       <c r="S6">
-        <v>1868.6</v>
+        <v>1867.68</v>
       </c>
       <c r="T6">
-        <v>5.46</v>
+        <v>7.16</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1446,34 +1450,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>41.97</v>
+        <v>46.57</v>
       </c>
       <c r="Z6">
-        <v>-9.76</v>
+        <v>-10.42</v>
       </c>
       <c r="AA6">
-        <v>-1.13</v>
+        <v>-2.99</v>
       </c>
       <c r="AB6">
-        <v>-8.630000000000001</v>
+        <v>-7.43</v>
       </c>
       <c r="AC6">
-        <v>9.460000000000001</v>
+        <v>12.7</v>
       </c>
       <c r="AD6">
-        <v>28.64</v>
+        <v>15.69</v>
       </c>
       <c r="AE6">
-        <v>57.45</v>
+        <v>60.25</v>
       </c>
       <c r="AF6">
-        <v>31.11</v>
+        <v>133.63</v>
       </c>
       <c r="AG6">
-        <v>2101.21</v>
+        <v>2094.17</v>
       </c>
       <c r="AH6">
-        <v>1961.87</v>
+        <v>1960.87</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1482,7 +1486,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>22.79</v>
+        <v>19.97</v>
       </c>
     </row>
   </sheetData>
@@ -1623,7 +1627,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1663,7 +1667,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1681,739 +1685,750 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-7.99</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-7.02</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>19</v>
+      </c>
+      <c r="D8" s="6">
+        <v>16.33</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-2.67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-14.48</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-17.68</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-12.99</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-12.58</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-3.09</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-4.65</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-3.53</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-2.16</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>7.11</v>
+      </c>
+      <c r="D13" s="6">
+        <v>7.19</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-1.93</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-4.66</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-2.73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.33</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-3.16</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.28</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-10.49</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-7.99</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-34.39</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-34.25</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>15.81</v>
-      </c>
-      <c r="D10" s="7">
-        <v>19</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-11.22</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-16.66</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-14.48</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-26.17</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-29.02</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-13.78</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-12.99</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-7.43</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-5.7</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-5.35</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-3.09</v>
-      </c>
-      <c r="E13" s="8">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1.18</v>
+      </c>
+      <c r="D21" s="6">
+        <v>2.53</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-5.84</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-3.53</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-26.34</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-24.37</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>7.26</v>
-      </c>
-      <c r="D15" s="7">
-        <v>7.11</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>16.23</v>
+      </c>
+      <c r="D23" s="6">
+        <v>13.65</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-2.6</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-1.93</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-9.08</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-11.82</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-2.74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1.12</v>
-      </c>
-      <c r="D17" s="7">
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>8.74</v>
+      </c>
+      <c r="D25" s="6">
+        <v>10.71</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>16.31</v>
+      </c>
+      <c r="D26" s="6">
+        <v>17.16</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-37.68</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-37.61</v>
+      </c>
+      <c r="E27" s="7">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E17" s="8">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-10.47</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-11.98</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-28.54</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-30.51</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-19.67</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-18.58</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-3.47</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-3.16</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-15.07</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-13.74</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-34.4</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-34.39</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>572.55</v>
+      </c>
+      <c r="D32" s="6">
+        <v>573.25</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-11.1</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-9.460000000000001</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>670.25</v>
+      </c>
+      <c r="D33" s="6">
+        <v>658.95</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-11.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-26.64</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-26.17</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>905</v>
+      </c>
+      <c r="D34" s="6">
+        <v>880</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-7.8</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-7.43</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1138.8</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1154.3</v>
+      </c>
+      <c r="E35" s="7">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-0.33</v>
-      </c>
-      <c r="D23" s="7">
-        <v>1.18</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>1970.7</v>
+      </c>
+      <c r="D36" s="6">
+        <v>2001.5</v>
+      </c>
+      <c r="E36" s="7">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="6">
+        <v>99</v>
+      </c>
+      <c r="D37" s="6">
+        <v>79</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>79</v>
+      </c>
+      <c r="D38" s="6">
+        <v>99</v>
+      </c>
+      <c r="E38" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-28.16</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-26.34</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>32.55</v>
+      </c>
+      <c r="D39" s="6">
+        <v>33.01</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="7">
-        <v>13.5</v>
-      </c>
-      <c r="D25" s="7">
-        <v>16.23</v>
-      </c>
-      <c r="E25" s="8">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>74.73</v>
+      </c>
+      <c r="D40" s="6">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-5.08</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-8.26</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-9.08</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>28.93</v>
+      </c>
+      <c r="D41" s="6">
+        <v>24.49</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-4.44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>9.32</v>
-      </c>
-      <c r="D27" s="7">
-        <v>8.74</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>35.17</v>
+      </c>
+      <c r="D42" s="6">
+        <v>38.9</v>
+      </c>
+      <c r="E42" s="7">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7">
-        <v>16.03</v>
-      </c>
-      <c r="D28" s="7">
-        <v>16.31</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>41.97</v>
+      </c>
+      <c r="D43" s="6">
+        <v>46.57</v>
+      </c>
+      <c r="E43" s="7">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-38.79</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-37.68</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>6.61</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-70.23999999999999</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-76.84999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-12.58</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-10.47</v>
-      </c>
-      <c r="E30" s="8">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>145.53</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-66.38</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-211.91</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-56.11</v>
+      </c>
+      <c r="D46" s="6">
+        <v>182.88</v>
+      </c>
+      <c r="E46" s="7">
+        <v>238.99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-18.68</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-19.67</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-68.72</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-64.98999999999999</v>
+      </c>
+      <c r="E47" s="7">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-14.75</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-15.07</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="7">
-        <v>562.4</v>
-      </c>
-      <c r="D33" s="7">
-        <v>572.55</v>
-      </c>
-      <c r="E33" s="8">
-        <v>10.15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="7">
-        <v>654.4</v>
-      </c>
-      <c r="D34" s="7">
-        <v>670.25</v>
-      </c>
-      <c r="E34" s="8">
-        <v>15.85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="7">
-        <v>1152.9</v>
-      </c>
-      <c r="D35" s="7">
-        <v>1138.8</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-14.1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="7">
-        <v>1978</v>
-      </c>
-      <c r="D36" s="7">
-        <v>1970.7</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-7.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="7">
-        <v>79</v>
-      </c>
-      <c r="D37" s="7">
-        <v>99</v>
-      </c>
-      <c r="E37" s="8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="7">
-        <v>99</v>
-      </c>
-      <c r="D38" s="7">
-        <v>79</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="7">
-        <v>25.68</v>
-      </c>
-      <c r="D39" s="7">
-        <v>32.55</v>
-      </c>
-      <c r="E39" s="8">
-        <v>6.87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="7">
-        <v>72.08</v>
-      </c>
-      <c r="D40" s="7">
-        <v>74.73</v>
-      </c>
-      <c r="E40" s="8">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="7">
-        <v>37.08</v>
-      </c>
-      <c r="D41" s="7">
-        <v>35.17</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="7">
-        <v>42.78</v>
-      </c>
-      <c r="D42" s="7">
-        <v>41.97</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
+      <c r="B48" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="7">
-        <v>-39.8</v>
-      </c>
-      <c r="D43" s="7">
-        <v>6.61</v>
-      </c>
-      <c r="E43" s="8">
-        <v>46.41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="7">
-        <v>2639.22</v>
-      </c>
-      <c r="D44" s="7">
-        <v>145.53</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-2493.69</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-72.88</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-56.11</v>
-      </c>
-      <c r="E45" s="8">
-        <v>16.77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="7">
-        <v>267.91</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-68.72</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-336.63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-44.1</v>
-      </c>
-      <c r="D47" s="7">
+      <c r="C48" s="6">
         <v>31.11</v>
       </c>
-      <c r="E47" s="8">
-        <v>75.20999999999999</v>
+      <c r="D48" s="6">
+        <v>133.63</v>
+      </c>
+      <c r="E48" s="7">
+        <v>102.52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2433,60 +2448,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>57.92</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="12">
-        <v>42.7</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>42.5</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
-        <v>-3.9</v>
-      </c>
-      <c r="G2" s="12">
-        <v>1.2</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-5.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2588,37 +2603,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15">
-        <v>0.1522</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.0432</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.0233</v>
-      </c>
-      <c r="D2" s="15">
-        <v>-0.0339</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.1516</v>
+      <c r="A2" s="14">
+        <v>0.1511</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0484</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0382</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1501</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,34 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>74.7 → 69.7</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>74.7</t>
-  </si>
-  <si>
-    <t>69.7</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -245,7 +218,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,7 +252,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -291,15 +264,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -326,19 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,22 +368,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -432,7 +391,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -791,8 +750,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -932,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>573.25</v>
+        <v>554.45</v>
       </c>
       <c r="D2">
-        <v>0.12</v>
+        <v>-3.28</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -944,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-37.61</v>
+        <v>-39.65</v>
       </c>
       <c r="H2">
-        <v>9.85</v>
+        <v>6.25</v>
       </c>
       <c r="I2">
-        <v>-2.16</v>
+        <v>-4.64</v>
       </c>
       <c r="J2">
-        <v>-7.02</v>
+        <v>-10.62</v>
       </c>
       <c r="K2">
-        <v>-24.37</v>
+        <v>-28.11</v>
       </c>
       <c r="L2">
-        <v>-34.25</v>
+        <v>-35.43</v>
       </c>
       <c r="M2">
-        <v>-15.01</v>
+        <v>-15.53</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>570.0700000000001</v>
+        <v>564.67</v>
       </c>
       <c r="Q2">
-        <v>593.34</v>
+        <v>590.04</v>
       </c>
       <c r="R2">
-        <v>642.51</v>
+        <v>639.09</v>
       </c>
       <c r="S2">
-        <v>675.67</v>
+        <v>675.2</v>
       </c>
       <c r="T2">
-        <v>-15.16</v>
+        <v>-17.88</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -998,34 +956,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.01</v>
+        <v>27.57</v>
       </c>
       <c r="Z2">
-        <v>-21.11</v>
+        <v>-21.83</v>
       </c>
       <c r="AA2">
-        <v>-21.68</v>
+        <v>-21.71</v>
       </c>
       <c r="AB2">
-        <v>0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AC2">
-        <v>52.73</v>
+        <v>58.34</v>
       </c>
       <c r="AD2">
-        <v>33.24</v>
+        <v>46.18</v>
       </c>
       <c r="AE2">
-        <v>23.56</v>
+        <v>24</v>
       </c>
       <c r="AF2">
-        <v>-70.23999999999999</v>
+        <v>29.87</v>
       </c>
       <c r="AG2">
-        <v>627.78</v>
+        <v>626.14</v>
       </c>
       <c r="AH2">
-        <v>558.9</v>
+        <v>553.9400000000001</v>
       </c>
       <c r="AI2">
         <v>637.88</v>
@@ -1034,7 +992,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>56.54</v>
+        <v>57.66</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1045,10 +1003,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>658.95</v>
+        <v>644.85</v>
       </c>
       <c r="D3">
-        <v>-1.69</v>
+        <v>-2.14</v>
       </c>
       <c r="E3">
         <v>748.6</v>
@@ -1057,46 +1015,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-11.98</v>
+        <v>-13.86</v>
       </c>
       <c r="H3">
-        <v>28.45</v>
+        <v>25.7</v>
       </c>
       <c r="I3">
-        <v>7.19</v>
+        <v>5.83</v>
       </c>
       <c r="J3">
-        <v>16.33</v>
+        <v>18.2</v>
       </c>
       <c r="K3">
-        <v>13.65</v>
+        <v>13.67</v>
       </c>
       <c r="L3">
-        <v>-11.22</v>
+        <v>-13.71</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>0.51</v>
       </c>
       <c r="N3">
         <v>79</v>
       </c>
       <c r="O3">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P3">
-        <v>641.64</v>
+        <v>648.75</v>
       </c>
       <c r="Q3">
-        <v>593.53</v>
+        <v>598.63</v>
       </c>
       <c r="R3">
-        <v>575.62</v>
+        <v>577.27</v>
       </c>
       <c r="S3">
-        <v>578.77</v>
+        <v>579.11</v>
       </c>
       <c r="T3">
-        <v>13.85</v>
+        <v>11.35</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1111,34 +1069,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>69.65000000000001</v>
+        <v>63.82</v>
       </c>
       <c r="Z3">
-        <v>22.53</v>
+        <v>22.7</v>
       </c>
       <c r="AA3">
-        <v>13.9</v>
+        <v>15.66</v>
       </c>
       <c r="AB3">
-        <v>8.630000000000001</v>
+        <v>7.04</v>
       </c>
       <c r="AC3">
-        <v>92.42</v>
+        <v>76.13</v>
       </c>
       <c r="AD3">
-        <v>88.65000000000001</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="AE3">
-        <v>22.37</v>
+        <v>22.68</v>
       </c>
       <c r="AF3">
-        <v>-66.38</v>
+        <v>-70.11</v>
       </c>
       <c r="AG3">
-        <v>668.84</v>
+        <v>673.3</v>
       </c>
       <c r="AH3">
-        <v>518.22</v>
+        <v>523.96</v>
       </c>
       <c r="AI3">
         <v>598.35</v>
@@ -1147,7 +1105,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>52.46</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1158,58 +1116,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D4">
-        <v>-2.76</v>
+        <v>-0.23</v>
       </c>
       <c r="E4">
-        <v>1266.37</v>
+        <v>1258.18</v>
       </c>
       <c r="F4">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="G4">
-        <v>-30.51</v>
+        <v>-30.22</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-4.66</v>
+        <v>-4.04</v>
       </c>
       <c r="J4">
-        <v>-17.68</v>
+        <v>-18.5</v>
       </c>
       <c r="K4">
-        <v>-11.82</v>
+        <v>-11.94</v>
       </c>
       <c r="L4">
-        <v>-29.02</v>
+        <v>-30.67</v>
       </c>
       <c r="M4">
-        <v>-3.82</v>
+        <v>-3.76</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>901.26</v>
+        <v>893.86</v>
       </c>
       <c r="Q4">
-        <v>938.74</v>
+        <v>930.14</v>
       </c>
       <c r="R4">
-        <v>1015.12</v>
+        <v>1011.99</v>
       </c>
       <c r="S4">
-        <v>1085.78</v>
+        <v>1084.52</v>
       </c>
       <c r="T4">
-        <v>-18.95</v>
+        <v>-19.04</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1224,43 +1182,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>24.49</v>
+        <v>24.17</v>
       </c>
       <c r="Z4">
-        <v>-35.58</v>
+        <v>-36.26</v>
       </c>
       <c r="AA4">
-        <v>-33.65</v>
+        <v>-34.17</v>
       </c>
       <c r="AB4">
-        <v>-1.93</v>
+        <v>-2.09</v>
       </c>
       <c r="AC4">
-        <v>14.44</v>
+        <v>7.22</v>
       </c>
       <c r="AD4">
-        <v>24.24</v>
+        <v>15.92</v>
       </c>
       <c r="AE4">
-        <v>22.61</v>
+        <v>21.98</v>
       </c>
       <c r="AF4">
-        <v>182.88</v>
+        <v>-54.34</v>
       </c>
       <c r="AG4">
-        <v>1028.4</v>
+        <v>1006.94</v>
       </c>
       <c r="AH4">
-        <v>849.0700000000001</v>
+        <v>853.33</v>
       </c>
       <c r="AI4">
-        <v>944.09</v>
+        <v>939</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>64.86</v>
+        <v>67.36</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1271,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1154.3</v>
+        <v>1163.5</v>
       </c>
       <c r="D5">
-        <v>1.36</v>
+        <v>0.8</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1283,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-18.58</v>
+        <v>-17.93</v>
       </c>
       <c r="H5">
-        <v>54.11</v>
+        <v>55.34</v>
       </c>
       <c r="I5">
-        <v>0.33</v>
+        <v>-0.34</v>
       </c>
       <c r="J5">
-        <v>-12.58</v>
+        <v>-10.83</v>
       </c>
       <c r="K5">
-        <v>10.71</v>
+        <v>12.59</v>
       </c>
       <c r="L5">
-        <v>-5.7</v>
+        <v>-3.19</v>
       </c>
       <c r="M5">
-        <v>15.11</v>
+        <v>15.18</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P5">
-        <v>1149.6</v>
+        <v>1148.8</v>
       </c>
       <c r="Q5">
-        <v>1207.4</v>
+        <v>1200</v>
       </c>
       <c r="R5">
-        <v>1258.3</v>
+        <v>1258.36</v>
       </c>
       <c r="S5">
-        <v>1065.83</v>
+        <v>1066.36</v>
       </c>
       <c r="T5">
-        <v>8.300000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1337,34 +1295,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>38.9</v>
+        <v>41.06</v>
       </c>
       <c r="Z5">
-        <v>-35.08</v>
+        <v>-33.28</v>
       </c>
       <c r="AA5">
-        <v>-28.51</v>
+        <v>-29.46</v>
       </c>
       <c r="AB5">
-        <v>-6.58</v>
+        <v>-3.82</v>
       </c>
       <c r="AC5">
-        <v>53.85</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="AD5">
-        <v>42.01</v>
+        <v>52.51</v>
       </c>
       <c r="AE5">
-        <v>43.62</v>
+        <v>43.01</v>
       </c>
       <c r="AF5">
-        <v>-64.98999999999999</v>
+        <v>-55.91</v>
       </c>
       <c r="AG5">
-        <v>1319.11</v>
+        <v>1301.85</v>
       </c>
       <c r="AH5">
-        <v>1095.69</v>
+        <v>1098.15</v>
       </c>
       <c r="AI5">
         <v>1279.65</v>
@@ -1373,7 +1331,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>44.1</v>
+        <v>40.15</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1384,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2001.5</v>
+        <v>1982</v>
       </c>
       <c r="D6">
-        <v>1.56</v>
+        <v>-0.97</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1396,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-13.74</v>
+        <v>-14.58</v>
       </c>
       <c r="H6">
-        <v>36.04</v>
+        <v>34.71</v>
       </c>
       <c r="I6">
-        <v>-3.28</v>
+        <v>-2.32</v>
       </c>
       <c r="J6">
-        <v>-4.65</v>
+        <v>-4.8</v>
       </c>
       <c r="K6">
-        <v>17.16</v>
+        <v>19.79</v>
       </c>
       <c r="L6">
-        <v>2.53</v>
+        <v>0.19</v>
       </c>
       <c r="M6">
-        <v>4.84</v>
+        <v>4.31</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="P6">
-        <v>1998.8</v>
+        <v>1989.38</v>
       </c>
       <c r="Q6">
-        <v>2027.52</v>
+        <v>2023.12</v>
       </c>
       <c r="R6">
-        <v>2042.94</v>
+        <v>2045.57</v>
       </c>
       <c r="S6">
-        <v>1867.68</v>
+        <v>1866.84</v>
       </c>
       <c r="T6">
-        <v>7.16</v>
+        <v>6.17</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1450,34 +1408,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>46.57</v>
+        <v>44.18</v>
       </c>
       <c r="Z6">
-        <v>-10.42</v>
+        <v>-12.37</v>
       </c>
       <c r="AA6">
-        <v>-2.99</v>
+        <v>-4.86</v>
       </c>
       <c r="AB6">
-        <v>-7.43</v>
+        <v>-7.5</v>
       </c>
       <c r="AC6">
-        <v>12.7</v>
+        <v>18.81</v>
       </c>
       <c r="AD6">
-        <v>15.69</v>
+        <v>13.66</v>
       </c>
       <c r="AE6">
-        <v>60.25</v>
+        <v>59.57</v>
       </c>
       <c r="AF6">
-        <v>133.63</v>
+        <v>-43.02</v>
       </c>
       <c r="AG6">
-        <v>2094.17</v>
+        <v>2089.58</v>
       </c>
       <c r="AH6">
-        <v>1960.87</v>
+        <v>1956.66</v>
       </c>
       <c r="AI6">
         <v>1961.92</v>
@@ -1486,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>19.97</v>
+        <v>17.52</v>
       </c>
     </row>
   </sheetData>
@@ -1627,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1647,47 +1605,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1695,734 +1618,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-7.99</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-7.02</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.97</v>
+      <c r="D7" s="5">
+        <v>-10.62</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-3.6</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>19</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>16.33</v>
       </c>
-      <c r="E8" s="8">
-        <v>-2.67</v>
+      <c r="D8" s="5">
+        <v>18.2</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.87</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-14.48</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-17.68</v>
       </c>
-      <c r="E9" s="8">
-        <v>-3.2</v>
+      <c r="D9" s="5">
+        <v>-18.5</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-12.99</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-12.58</v>
       </c>
+      <c r="D10" s="5">
+        <v>-10.83</v>
+      </c>
       <c r="E10" s="7">
-        <v>0.41</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-3.09</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-4.65</v>
       </c>
-      <c r="E11" s="8">
-        <v>-1.56</v>
+      <c r="D11" s="5">
+        <v>-4.8</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-3.53</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-2.16</v>
       </c>
-      <c r="E12" s="7">
-        <v>1.37</v>
+      <c r="D12" s="5">
+        <v>-4.64</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-2.48</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>7.11</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>7.19</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.08</v>
+      <c r="D13" s="5">
+        <v>5.83</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-1.93</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-4.66</v>
       </c>
-      <c r="E14" s="8">
-        <v>-2.73</v>
+      <c r="D14" s="5">
+        <v>-4.04</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>0.33</v>
       </c>
-      <c r="E15" s="7">
-        <v>0.26</v>
+      <c r="D15" s="5">
+        <v>-0.34</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-3.16</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-3.28</v>
       </c>
-      <c r="E16" s="8">
+      <c r="D16" s="5">
+        <v>-2.32</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-34.25</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-35.43</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-11.22</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-13.71</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-2.49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-29.02</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-30.67</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-5.7</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-3.19</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>2.53</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-24.37</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-28.11</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-3.74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>13.65</v>
+      </c>
+      <c r="D23" s="5">
+        <v>13.67</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-11.82</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-11.94</v>
+      </c>
+      <c r="E24" s="6">
         <v>-0.12</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>10.71</v>
+      </c>
+      <c r="D25" s="5">
+        <v>12.59</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>17.16</v>
+      </c>
+      <c r="D26" s="5">
+        <v>19.79</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-34.39</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-34.25</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-37.61</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-39.65</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-2.04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-9.460000000000001</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-11.22</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-11.98</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-13.86</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-26.17</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-29.02</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-30.51</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-30.22</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-7.43</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-5.7</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-18.58</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-17.93</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>1.18</v>
-      </c>
-      <c r="D21" s="6">
-        <v>2.53</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-13.74</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-14.58</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-26.34</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-24.37</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>573.25</v>
+      </c>
+      <c r="D32" s="5">
+        <v>554.45</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-18.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>16.23</v>
-      </c>
-      <c r="D23" s="6">
-        <v>13.65</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>658.95</v>
+      </c>
+      <c r="D33" s="5">
+        <v>644.85</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-14.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-9.08</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-11.82</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>880</v>
+      </c>
+      <c r="D34" s="5">
+        <v>878</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>8.74</v>
-      </c>
-      <c r="D25" s="6">
-        <v>10.71</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1154.3</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1163.5</v>
+      </c>
+      <c r="E35" s="7">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>16.31</v>
-      </c>
-      <c r="D26" s="6">
-        <v>17.16</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2001.5</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1982</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-19.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-37.68</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-37.61</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>33.01</v>
+      </c>
+      <c r="D37" s="5">
+        <v>27.57</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-5.44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-10.47</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-11.98</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="D38" s="5">
+        <v>63.82</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-5.83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-28.54</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-30.51</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>24.49</v>
+      </c>
+      <c r="D39" s="5">
+        <v>24.17</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-19.67</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-18.58</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>38.9</v>
+      </c>
+      <c r="D40" s="5">
+        <v>41.06</v>
+      </c>
+      <c r="E40" s="7">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-15.07</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-13.74</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>46.57</v>
+      </c>
+      <c r="D41" s="5">
+        <v>44.18</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-2.39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>572.55</v>
-      </c>
-      <c r="D32" s="6">
-        <v>573.25</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-70.23999999999999</v>
+      </c>
+      <c r="D42" s="5">
+        <v>29.87</v>
+      </c>
+      <c r="E42" s="7">
+        <v>100.11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>670.25</v>
-      </c>
-      <c r="D33" s="6">
-        <v>658.95</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-11.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-66.38</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-70.11</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-3.73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>905</v>
-      </c>
-      <c r="D34" s="6">
-        <v>880</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>182.88</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-54.34</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-237.22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1138.8</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1154.3</v>
-      </c>
-      <c r="E35" s="7">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-64.98999999999999</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-55.91</v>
+      </c>
+      <c r="E45" s="7">
+        <v>9.08</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1970.7</v>
-      </c>
-      <c r="D36" s="6">
-        <v>2001.5</v>
-      </c>
-      <c r="E36" s="7">
-        <v>30.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="6">
-        <v>99</v>
-      </c>
-      <c r="D37" s="6">
-        <v>79</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="6">
-        <v>79</v>
-      </c>
-      <c r="D38" s="6">
-        <v>99</v>
-      </c>
-      <c r="E38" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>32.55</v>
-      </c>
-      <c r="D39" s="6">
-        <v>33.01</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>74.73</v>
-      </c>
-      <c r="D40" s="6">
-        <v>69.65000000000001</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-5.08</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>28.93</v>
-      </c>
-      <c r="D41" s="6">
-        <v>24.49</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-4.44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>35.17</v>
-      </c>
-      <c r="D42" s="6">
-        <v>38.9</v>
-      </c>
-      <c r="E42" s="7">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>41.97</v>
-      </c>
-      <c r="D43" s="6">
-        <v>46.57</v>
-      </c>
-      <c r="E43" s="7">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="6">
-        <v>6.61</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-70.23999999999999</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-76.84999999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>145.53</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-66.38</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-211.91</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-56.11</v>
-      </c>
-      <c r="D46" s="6">
-        <v>182.88</v>
-      </c>
-      <c r="E46" s="7">
-        <v>238.99</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-68.72</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-64.98999999999999</v>
-      </c>
-      <c r="E47" s="7">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>31.11</v>
-      </c>
-      <c r="D48" s="6">
+      <c r="C46" s="5">
         <v>133.63</v>
       </c>
-      <c r="E48" s="7">
-        <v>102.52</v>
+      <c r="D46" s="5">
+        <v>-43.02</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-176.65</v>
       </c>
     </row>
   </sheetData>
@@ -2448,60 +2337,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>57.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>42.5</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>40.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-5.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>1.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-5.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2603,37 +2492,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1511</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0484</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.02</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0382</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1501</v>
+      <c r="A2" s="13">
+        <v>0.1518</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0431</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0051</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.03759999999999999</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1553</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -890,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>554.45</v>
+        <v>552.35</v>
       </c>
       <c r="D2">
-        <v>-3.28</v>
+        <v>-0.38</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-39.65</v>
+        <v>-39.88</v>
       </c>
       <c r="H2">
-        <v>6.25</v>
+        <v>5.84</v>
       </c>
       <c r="I2">
-        <v>-4.64</v>
+        <v>-1.49</v>
       </c>
       <c r="J2">
-        <v>-10.62</v>
+        <v>-10.98</v>
       </c>
       <c r="K2">
-        <v>-28.11</v>
+        <v>-30.5</v>
       </c>
       <c r="L2">
-        <v>-35.43</v>
+        <v>-35.28</v>
       </c>
       <c r="M2">
-        <v>-15.53</v>
+        <v>-15.62</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
       <c r="O2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>564.67</v>
+        <v>563</v>
       </c>
       <c r="Q2">
-        <v>590.04</v>
+        <v>586.62</v>
       </c>
       <c r="R2">
-        <v>639.09</v>
+        <v>635.88</v>
       </c>
       <c r="S2">
-        <v>675.2</v>
+        <v>674.83</v>
       </c>
       <c r="T2">
-        <v>-17.88</v>
+        <v>-18.15</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,43 +956,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>27.57</v>
+        <v>27.04</v>
       </c>
       <c r="Z2">
+        <v>-22.31</v>
+      </c>
+      <c r="AA2">
         <v>-21.83</v>
       </c>
-      <c r="AA2">
-        <v>-21.71</v>
-      </c>
       <c r="AB2">
-        <v>-0.12</v>
+        <v>-0.48</v>
       </c>
       <c r="AC2">
-        <v>58.34</v>
+        <v>42</v>
       </c>
       <c r="AD2">
-        <v>46.18</v>
+        <v>51.02</v>
       </c>
       <c r="AE2">
-        <v>24</v>
+        <v>23.67</v>
       </c>
       <c r="AF2">
-        <v>29.87</v>
+        <v>16.47</v>
       </c>
       <c r="AG2">
-        <v>626.14</v>
+        <v>623.45</v>
       </c>
       <c r="AH2">
-        <v>553.9400000000001</v>
+        <v>549.8</v>
       </c>
       <c r="AI2">
-        <v>637.88</v>
+        <v>620.65</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>57.66</v>
+        <v>59.51</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1003,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>644.85</v>
+        <v>665.5</v>
       </c>
       <c r="D3">
-        <v>-2.14</v>
+        <v>3.2</v>
       </c>
       <c r="E3">
         <v>748.6</v>
@@ -1015,46 +1015,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-13.86</v>
+        <v>-11.1</v>
       </c>
       <c r="H3">
-        <v>25.7</v>
+        <v>29.73</v>
       </c>
       <c r="I3">
-        <v>5.83</v>
+        <v>8.16</v>
       </c>
       <c r="J3">
-        <v>18.2</v>
+        <v>22.59</v>
       </c>
       <c r="K3">
-        <v>13.67</v>
+        <v>17.06</v>
       </c>
       <c r="L3">
-        <v>-13.71</v>
+        <v>-9.69</v>
       </c>
       <c r="M3">
-        <v>0.51</v>
+        <v>1.32</v>
       </c>
       <c r="N3">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="P3">
-        <v>648.75</v>
+        <v>658.79</v>
       </c>
       <c r="Q3">
-        <v>598.63</v>
+        <v>604.1</v>
       </c>
       <c r="R3">
-        <v>577.27</v>
+        <v>579.4299999999999</v>
       </c>
       <c r="S3">
-        <v>579.11</v>
+        <v>579.59</v>
       </c>
       <c r="T3">
-        <v>11.35</v>
+        <v>14.82</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1069,34 +1069,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>63.82</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="Z3">
-        <v>22.7</v>
+        <v>24.23</v>
       </c>
       <c r="AA3">
-        <v>15.66</v>
+        <v>17.38</v>
       </c>
       <c r="AB3">
-        <v>7.04</v>
+        <v>6.85</v>
       </c>
       <c r="AC3">
-        <v>76.13</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="AD3">
-        <v>86.68000000000001</v>
+        <v>78.23</v>
       </c>
       <c r="AE3">
-        <v>22.68</v>
+        <v>23.12</v>
       </c>
       <c r="AF3">
-        <v>-70.11</v>
+        <v>-66.75</v>
       </c>
       <c r="AG3">
-        <v>673.3</v>
+        <v>681.62</v>
       </c>
       <c r="AH3">
-        <v>523.96</v>
+        <v>526.58</v>
       </c>
       <c r="AI3">
         <v>598.35</v>
@@ -1105,7 +1105,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>52.7</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,58 +1116,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>878</v>
+        <v>861.9</v>
       </c>
       <c r="D4">
-        <v>-0.23</v>
+        <v>-1.83</v>
       </c>
       <c r="E4">
-        <v>1258.18</v>
+        <v>1249.31</v>
       </c>
       <c r="F4">
-        <v>878</v>
+        <v>861.9</v>
       </c>
       <c r="G4">
-        <v>-30.22</v>
+        <v>-31.01</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-4.04</v>
+        <v>-4.37</v>
       </c>
       <c r="J4">
-        <v>-18.5</v>
+        <v>-17.91</v>
       </c>
       <c r="K4">
-        <v>-11.94</v>
+        <v>-14.93</v>
       </c>
       <c r="L4">
-        <v>-30.67</v>
+        <v>-31.5</v>
       </c>
       <c r="M4">
-        <v>-3.76</v>
+        <v>-4.1</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>893.86</v>
+        <v>885.98</v>
       </c>
       <c r="Q4">
-        <v>930.14</v>
+        <v>921.58</v>
       </c>
       <c r="R4">
-        <v>1011.99</v>
+        <v>1008.79</v>
       </c>
       <c r="S4">
-        <v>1084.52</v>
+        <v>1083.18</v>
       </c>
       <c r="T4">
-        <v>-19.04</v>
+        <v>-20.43</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1182,43 +1182,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>24.17</v>
+        <v>21.71</v>
       </c>
       <c r="Z4">
-        <v>-36.26</v>
+        <v>-37.65</v>
       </c>
       <c r="AA4">
-        <v>-34.17</v>
+        <v>-34.87</v>
       </c>
       <c r="AB4">
-        <v>-2.09</v>
+        <v>-2.79</v>
       </c>
       <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
         <v>7.22</v>
-      </c>
-      <c r="AD4">
-        <v>15.92</v>
       </c>
       <c r="AE4">
         <v>21.98</v>
       </c>
       <c r="AF4">
-        <v>-54.34</v>
+        <v>-8.69</v>
       </c>
       <c r="AG4">
-        <v>1006.94</v>
+        <v>987.49</v>
       </c>
       <c r="AH4">
-        <v>853.33</v>
+        <v>855.67</v>
       </c>
       <c r="AI4">
-        <v>939</v>
+        <v>934.02</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>67.36</v>
+        <v>69.81</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1163.5</v>
+        <v>1159.8</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>-0.32</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-17.93</v>
+        <v>-18.19</v>
       </c>
       <c r="H5">
-        <v>55.34</v>
+        <v>54.85</v>
       </c>
       <c r="I5">
-        <v>-0.34</v>
+        <v>2.23</v>
       </c>
       <c r="J5">
-        <v>-10.83</v>
+        <v>-11.57</v>
       </c>
       <c r="K5">
-        <v>12.59</v>
+        <v>10.86</v>
       </c>
       <c r="L5">
-        <v>-3.19</v>
+        <v>-3.43</v>
       </c>
       <c r="M5">
-        <v>15.18</v>
+        <v>15.45</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P5">
-        <v>1148.8</v>
+        <v>1153.86</v>
       </c>
       <c r="Q5">
-        <v>1200</v>
+        <v>1193.38</v>
       </c>
       <c r="R5">
-        <v>1258.36</v>
+        <v>1258.48</v>
       </c>
       <c r="S5">
-        <v>1066.36</v>
+        <v>1066.86</v>
       </c>
       <c r="T5">
-        <v>9.109999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1295,34 +1295,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>41.06</v>
+        <v>40.44</v>
       </c>
       <c r="Z5">
-        <v>-33.28</v>
+        <v>-31.79</v>
       </c>
       <c r="AA5">
-        <v>-29.46</v>
+        <v>-29.93</v>
       </c>
       <c r="AB5">
-        <v>-3.82</v>
+        <v>-1.86</v>
       </c>
       <c r="AC5">
-        <v>67.29000000000001</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="AD5">
-        <v>52.51</v>
+        <v>68</v>
       </c>
       <c r="AE5">
-        <v>43.01</v>
+        <v>42.52</v>
       </c>
       <c r="AF5">
-        <v>-55.91</v>
+        <v>-53.91</v>
       </c>
       <c r="AG5">
-        <v>1301.85</v>
+        <v>1286.87</v>
       </c>
       <c r="AH5">
-        <v>1098.15</v>
+        <v>1099.89</v>
       </c>
       <c r="AI5">
         <v>1279.65</v>
@@ -1331,7 +1331,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>40.15</v>
+        <v>36.32</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1982</v>
+        <v>1922.2</v>
       </c>
       <c r="D6">
-        <v>-0.97</v>
+        <v>-3.02</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-14.58</v>
+        <v>-17.16</v>
       </c>
       <c r="H6">
-        <v>34.71</v>
+        <v>30.65</v>
       </c>
       <c r="I6">
-        <v>-2.32</v>
+        <v>-4.59</v>
       </c>
       <c r="J6">
-        <v>-4.8</v>
+        <v>-7.14</v>
       </c>
       <c r="K6">
-        <v>19.79</v>
+        <v>14.12</v>
       </c>
       <c r="L6">
-        <v>0.19</v>
+        <v>-4.46</v>
       </c>
       <c r="M6">
-        <v>4.31</v>
+        <v>4.03</v>
       </c>
       <c r="N6">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O6">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P6">
-        <v>1989.38</v>
+        <v>1970.88</v>
       </c>
       <c r="Q6">
-        <v>2023.12</v>
+        <v>2013.81</v>
       </c>
       <c r="R6">
-        <v>2045.57</v>
+        <v>2047.41</v>
       </c>
       <c r="S6">
-        <v>1866.84</v>
+        <v>1865.8</v>
       </c>
       <c r="T6">
-        <v>6.17</v>
+        <v>3.02</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1408,43 +1408,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>44.18</v>
+        <v>37.78</v>
       </c>
       <c r="Z6">
-        <v>-12.37</v>
+        <v>-18.52</v>
       </c>
       <c r="AA6">
-        <v>-4.86</v>
+        <v>-7.59</v>
       </c>
       <c r="AB6">
-        <v>-7.5</v>
+        <v>-10.93</v>
       </c>
       <c r="AC6">
         <v>18.81</v>
       </c>
       <c r="AD6">
-        <v>13.66</v>
+        <v>16.77</v>
       </c>
       <c r="AE6">
-        <v>59.57</v>
+        <v>61.95</v>
       </c>
       <c r="AF6">
-        <v>-43.02</v>
+        <v>39.43</v>
       </c>
       <c r="AG6">
-        <v>2089.58</v>
+        <v>2082.11</v>
       </c>
       <c r="AH6">
-        <v>1956.66</v>
+        <v>1945.51</v>
       </c>
       <c r="AI6">
-        <v>1961.92</v>
+        <v>2112.15</v>
       </c>
       <c r="AJ6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK6">
-        <v>17.52</v>
+        <v>19.07</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1642,13 +1642,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.02</v>
+        <v>-10.62</v>
       </c>
       <c r="D7" s="5">
-        <v>-10.62</v>
+        <v>-10.98</v>
       </c>
       <c r="E7" s="6">
-        <v>-3.6</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1659,13 +1659,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>16.33</v>
+        <v>18.2</v>
       </c>
       <c r="D8" s="5">
-        <v>18.2</v>
+        <v>22.59</v>
       </c>
       <c r="E8" s="7">
-        <v>1.87</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1676,13 +1676,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-17.68</v>
+        <v>-18.5</v>
       </c>
       <c r="D9" s="5">
-        <v>-18.5</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.82</v>
+        <v>-17.91</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1693,13 +1693,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-12.58</v>
+        <v>-10.83</v>
       </c>
       <c r="D10" s="5">
-        <v>-10.83</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.75</v>
+        <v>-11.57</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1710,13 +1710,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-4.65</v>
+        <v>-4.8</v>
       </c>
       <c r="D11" s="5">
-        <v>-4.8</v>
+        <v>-7.14</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.15</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1727,13 +1727,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-2.16</v>
+        <v>-4.64</v>
       </c>
       <c r="D12" s="5">
-        <v>-4.64</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-2.48</v>
+        <v>-1.49</v>
+      </c>
+      <c r="E12" s="7">
+        <v>3.15</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1744,13 +1744,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>7.19</v>
+        <v>5.83</v>
       </c>
       <c r="D13" s="5">
-        <v>5.83</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-1.36</v>
+        <v>8.16</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.33</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1761,13 +1761,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-4.66</v>
+        <v>-4.04</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.04</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.62</v>
+        <v>-4.37</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1778,13 +1778,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>0.33</v>
+        <v>-0.34</v>
       </c>
       <c r="D15" s="5">
-        <v>-0.34</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.67</v>
+        <v>2.23</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1795,13 +1795,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-3.28</v>
+        <v>-2.32</v>
       </c>
       <c r="D16" s="5">
-        <v>-2.32</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.96</v>
+        <v>-4.59</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1812,13 +1812,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>-34.25</v>
+        <v>-35.43</v>
       </c>
       <c r="D17" s="5">
-        <v>-35.43</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.18</v>
+        <v>-35.28</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.15</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1829,13 +1829,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-11.22</v>
+        <v>-13.71</v>
       </c>
       <c r="D18" s="5">
-        <v>-13.71</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-2.49</v>
+        <v>-9.69</v>
+      </c>
+      <c r="E18" s="7">
+        <v>4.02</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1846,13 +1846,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-29.02</v>
+        <v>-30.67</v>
       </c>
       <c r="D19" s="5">
-        <v>-30.67</v>
+        <v>-31.5</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.65</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1863,13 +1863,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-5.7</v>
+        <v>-3.19</v>
       </c>
       <c r="D20" s="5">
-        <v>-3.19</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.51</v>
+        <v>-3.43</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1880,13 +1880,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>2.53</v>
+        <v>0.19</v>
       </c>
       <c r="D21" s="5">
-        <v>0.19</v>
+        <v>-4.46</v>
       </c>
       <c r="E21" s="6">
-        <v>-2.34</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1897,13 +1897,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-24.37</v>
+        <v>-28.11</v>
       </c>
       <c r="D22" s="5">
-        <v>-28.11</v>
+        <v>-30.5</v>
       </c>
       <c r="E22" s="6">
-        <v>-3.74</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1914,13 +1914,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>13.65</v>
+        <v>13.67</v>
       </c>
       <c r="D23" s="5">
-        <v>13.67</v>
+        <v>17.06</v>
       </c>
       <c r="E23" s="7">
-        <v>0.02</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1931,13 +1931,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-11.82</v>
+        <v>-11.94</v>
       </c>
       <c r="D24" s="5">
-        <v>-11.94</v>
+        <v>-14.93</v>
       </c>
       <c r="E24" s="6">
-        <v>-0.12</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1948,13 +1948,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>10.71</v>
+        <v>12.59</v>
       </c>
       <c r="D25" s="5">
-        <v>12.59</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.88</v>
+        <v>10.86</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1965,13 +1965,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>17.16</v>
+        <v>19.79</v>
       </c>
       <c r="D26" s="5">
-        <v>19.79</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.63</v>
+        <v>14.12</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-5.67</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1982,13 +1982,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-37.61</v>
+        <v>-39.65</v>
       </c>
       <c r="D27" s="5">
-        <v>-39.65</v>
+        <v>-39.88</v>
       </c>
       <c r="E27" s="6">
-        <v>-2.04</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1999,13 +1999,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-11.98</v>
+        <v>-13.86</v>
       </c>
       <c r="D28" s="5">
-        <v>-13.86</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-1.88</v>
+        <v>-11.1</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.76</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2016,13 +2016,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-30.51</v>
+        <v>-30.22</v>
       </c>
       <c r="D29" s="5">
-        <v>-30.22</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.29</v>
+        <v>-31.01</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2033,13 +2033,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-18.58</v>
+        <v>-17.93</v>
       </c>
       <c r="D30" s="5">
-        <v>-17.93</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.65</v>
+        <v>-18.19</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2050,13 +2050,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-13.74</v>
+        <v>-14.58</v>
       </c>
       <c r="D31" s="5">
-        <v>-14.58</v>
+        <v>-17.16</v>
       </c>
       <c r="E31" s="6">
-        <v>-0.84</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2067,13 +2067,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>573.25</v>
+        <v>554.45</v>
       </c>
       <c r="D32" s="5">
-        <v>554.45</v>
+        <v>552.35</v>
       </c>
       <c r="E32" s="6">
-        <v>-18.8</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2084,13 +2084,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>658.95</v>
+        <v>644.85</v>
       </c>
       <c r="D33" s="5">
-        <v>644.85</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-14.1</v>
+        <v>665.5</v>
+      </c>
+      <c r="E33" s="7">
+        <v>20.65</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2101,13 +2101,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D34" s="5">
-        <v>878</v>
+        <v>861.9</v>
       </c>
       <c r="E34" s="6">
-        <v>-2</v>
+        <v>-16.1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2118,13 +2118,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>1154.3</v>
+        <v>1163.5</v>
       </c>
       <c r="D35" s="5">
-        <v>1163.5</v>
-      </c>
-      <c r="E35" s="7">
-        <v>9.199999999999999</v>
+        <v>1159.8</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-3.7</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2135,183 +2135,217 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>2001.5</v>
+        <v>1982</v>
       </c>
       <c r="D36" s="5">
-        <v>1982</v>
+        <v>1922.2</v>
       </c>
       <c r="E36" s="6">
-        <v>-19.5</v>
+        <v>-59.8</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C37" s="5">
-        <v>33.01</v>
+        <v>79</v>
       </c>
       <c r="D37" s="5">
-        <v>27.57</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-5.44</v>
+        <v>99</v>
+      </c>
+      <c r="E37" s="7">
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C38" s="5">
-        <v>69.65000000000001</v>
+        <v>99</v>
       </c>
       <c r="D38" s="5">
-        <v>63.82</v>
+        <v>79</v>
       </c>
       <c r="E38" s="6">
-        <v>-5.83</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>24.49</v>
+        <v>27.57</v>
       </c>
       <c r="D39" s="5">
-        <v>24.17</v>
+        <v>27.04</v>
       </c>
       <c r="E39" s="6">
-        <v>-0.32</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>38.9</v>
+        <v>63.82</v>
       </c>
       <c r="D40" s="5">
-        <v>41.06</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="E40" s="7">
-        <v>2.16</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>46.57</v>
+        <v>24.17</v>
       </c>
       <c r="D41" s="5">
-        <v>44.18</v>
+        <v>21.71</v>
       </c>
       <c r="E41" s="6">
-        <v>-2.39</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C42" s="5">
-        <v>-70.23999999999999</v>
+        <v>41.06</v>
       </c>
       <c r="D42" s="5">
-        <v>29.87</v>
-      </c>
-      <c r="E42" s="7">
-        <v>100.11</v>
+        <v>40.44</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C43" s="5">
-        <v>-66.38</v>
+        <v>44.18</v>
       </c>
       <c r="D43" s="5">
-        <v>-70.11</v>
+        <v>37.78</v>
       </c>
       <c r="E43" s="6">
-        <v>-3.73</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>182.88</v>
+        <v>29.87</v>
       </c>
       <c r="D44" s="5">
-        <v>-54.34</v>
+        <v>16.47</v>
       </c>
       <c r="E44" s="6">
-        <v>-237.22</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-64.98999999999999</v>
+        <v>-70.11</v>
       </c>
       <c r="D45" s="5">
-        <v>-55.91</v>
+        <v>-66.75</v>
       </c>
       <c r="E45" s="7">
-        <v>9.08</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>133.63</v>
+        <v>-54.34</v>
       </c>
       <c r="D46" s="5">
+        <v>-8.69</v>
+      </c>
+      <c r="E46" s="7">
+        <v>45.65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-55.91</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-53.91</v>
+      </c>
+      <c r="E47" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="5">
         <v>-43.02</v>
       </c>
-      <c r="E46" s="6">
-        <v>-176.65</v>
+      <c r="D48" s="5">
+        <v>39.43</v>
+      </c>
+      <c r="E48" s="7">
+        <v>82.45</v>
       </c>
     </row>
   </sheetData>
@@ -2376,16 +2410,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>40.2</v>
+        <v>39</v>
       </c>
       <c r="E2" s="10">
         <v>60</v>
       </c>
       <c r="F2" s="10">
-        <v>-5.3</v>
+        <v>-5</v>
       </c>
       <c r="G2" s="10">
-        <v>1.2</v>
+        <v>-0.7</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2510,19 +2544,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1518</v>
+        <v>0.1545</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0431</v>
+        <v>0.0403</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0051</v>
+        <v>0.0132</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.03759999999999999</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1553</v>
+        <v>-0.1562</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,16 +157,55 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 GOLDEN CROSS</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>27.0 → 65.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>27.0</t>
+  </si>
+  <si>
+    <t>65.3</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,14 +407,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -890,10 +930,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>552.35</v>
+        <v>662.8</v>
       </c>
       <c r="D2">
-        <v>-0.38</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +942,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-39.88</v>
+        <v>-27.86</v>
       </c>
       <c r="H2">
-        <v>5.84</v>
+        <v>27.01</v>
       </c>
       <c r="I2">
-        <v>-1.49</v>
+        <v>17.85</v>
       </c>
       <c r="J2">
-        <v>-10.98</v>
+        <v>6.79</v>
       </c>
       <c r="K2">
-        <v>-30.5</v>
+        <v>-14.58</v>
       </c>
       <c r="L2">
-        <v>-35.28</v>
+        <v>-22.31</v>
       </c>
       <c r="M2">
-        <v>-15.62</v>
+        <v>-12.43</v>
       </c>
       <c r="N2">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P2">
-        <v>563</v>
+        <v>583.08</v>
       </c>
       <c r="Q2">
-        <v>586.62</v>
+        <v>589</v>
       </c>
       <c r="R2">
-        <v>635.88</v>
+        <v>634.92</v>
       </c>
       <c r="S2">
-        <v>674.83</v>
+        <v>674.47</v>
       </c>
       <c r="T2">
-        <v>-18.15</v>
+        <v>-1.73</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,43 +996,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>27.04</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="Z2">
-        <v>-22.31</v>
+        <v>-13.62</v>
       </c>
       <c r="AA2">
-        <v>-21.83</v>
+        <v>-20.19</v>
       </c>
       <c r="AB2">
-        <v>-0.48</v>
+        <v>6.56</v>
       </c>
       <c r="AC2">
-        <v>42</v>
+        <v>50.06</v>
       </c>
       <c r="AD2">
-        <v>51.02</v>
+        <v>50.13</v>
       </c>
       <c r="AE2">
-        <v>23.67</v>
+        <v>29.95</v>
       </c>
       <c r="AF2">
-        <v>16.47</v>
+        <v>3360.88</v>
       </c>
       <c r="AG2">
-        <v>623.45</v>
+        <v>637.8099999999999</v>
       </c>
       <c r="AH2">
-        <v>549.8</v>
+        <v>540.2</v>
       </c>
       <c r="AI2">
-        <v>620.65</v>
+        <v>533.65</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>59.51</v>
+        <v>56.94</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1043,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>665.5</v>
+        <v>673.6</v>
       </c>
       <c r="D3">
-        <v>3.2</v>
+        <v>1.22</v>
       </c>
       <c r="E3">
         <v>748.6</v>
@@ -1015,25 +1055,25 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-11.1</v>
+        <v>-10.02</v>
       </c>
       <c r="H3">
-        <v>29.73</v>
+        <v>31.31</v>
       </c>
       <c r="I3">
-        <v>8.16</v>
+        <v>2.93</v>
       </c>
       <c r="J3">
-        <v>22.59</v>
+        <v>21.14</v>
       </c>
       <c r="K3">
-        <v>17.06</v>
+        <v>20.15</v>
       </c>
       <c r="L3">
-        <v>-9.69</v>
+        <v>-7.78</v>
       </c>
       <c r="M3">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1042,70 +1082,70 @@
         <v>66</v>
       </c>
       <c r="P3">
-        <v>658.79</v>
+        <v>662.63</v>
       </c>
       <c r="Q3">
-        <v>604.1</v>
+        <v>610.46</v>
       </c>
       <c r="R3">
-        <v>579.4299999999999</v>
+        <v>581.77</v>
       </c>
       <c r="S3">
-        <v>579.59</v>
+        <v>580.1</v>
       </c>
       <c r="T3">
-        <v>14.82</v>
+        <v>16.12</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y3">
-        <v>68.04000000000001</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="Z3">
-        <v>24.23</v>
+        <v>25.79</v>
       </c>
       <c r="AA3">
-        <v>17.38</v>
+        <v>19.06</v>
       </c>
       <c r="AB3">
-        <v>6.85</v>
+        <v>6.73</v>
       </c>
       <c r="AC3">
-        <v>66.15000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="AD3">
-        <v>78.23</v>
+        <v>69.42</v>
       </c>
       <c r="AE3">
-        <v>23.12</v>
+        <v>22.87</v>
       </c>
       <c r="AF3">
-        <v>-66.75</v>
+        <v>-58.92</v>
       </c>
       <c r="AG3">
-        <v>681.62</v>
+        <v>688.92</v>
       </c>
       <c r="AH3">
-        <v>526.58</v>
+        <v>532</v>
       </c>
       <c r="AI3">
         <v>598.35</v>
       </c>
       <c r="AJ3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK3">
-        <v>53.28</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1156,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>861.9</v>
+        <v>865</v>
       </c>
       <c r="D4">
-        <v>-1.83</v>
+        <v>0.36</v>
       </c>
       <c r="E4">
         <v>1249.31</v>
@@ -1128,46 +1168,46 @@
         <v>861.9</v>
       </c>
       <c r="G4">
-        <v>-31.01</v>
+        <v>-30.76</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="I4">
-        <v>-4.37</v>
+        <v>-4.42</v>
       </c>
       <c r="J4">
-        <v>-17.91</v>
+        <v>-16.26</v>
       </c>
       <c r="K4">
-        <v>-14.93</v>
+        <v>-15.82</v>
       </c>
       <c r="L4">
-        <v>-31.5</v>
+        <v>-29.58</v>
       </c>
       <c r="M4">
-        <v>-4.1</v>
+        <v>-3.97</v>
       </c>
       <c r="N4">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="O4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>885.98</v>
+        <v>877.98</v>
       </c>
       <c r="Q4">
-        <v>921.58</v>
+        <v>913.58</v>
       </c>
       <c r="R4">
-        <v>1008.79</v>
+        <v>1005.89</v>
       </c>
       <c r="S4">
-        <v>1083.18</v>
+        <v>1081.92</v>
       </c>
       <c r="T4">
-        <v>-20.43</v>
+        <v>-20.05</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1182,43 +1222,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>21.71</v>
+        <v>23.32</v>
       </c>
       <c r="Z4">
-        <v>-37.65</v>
+        <v>-38.07</v>
       </c>
       <c r="AA4">
-        <v>-34.87</v>
+        <v>-35.51</v>
       </c>
       <c r="AB4">
-        <v>-2.79</v>
+        <v>-2.57</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD4">
-        <v>7.22</v>
+        <v>3.75</v>
       </c>
       <c r="AE4">
-        <v>21.98</v>
+        <v>21.54</v>
       </c>
       <c r="AF4">
-        <v>-8.69</v>
+        <v>-50.43</v>
       </c>
       <c r="AG4">
-        <v>987.49</v>
+        <v>963.55</v>
       </c>
       <c r="AH4">
-        <v>855.67</v>
+        <v>863.61</v>
       </c>
       <c r="AI4">
-        <v>934.02</v>
+        <v>927.67</v>
       </c>
       <c r="AJ4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK4">
-        <v>69.81</v>
+        <v>71.98999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1269,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1159.8</v>
+        <v>1144</v>
       </c>
       <c r="D5">
-        <v>-0.32</v>
+        <v>-1.36</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,46 +1281,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-18.19</v>
+        <v>-19.31</v>
       </c>
       <c r="H5">
-        <v>54.85</v>
+        <v>52.74</v>
       </c>
       <c r="I5">
-        <v>2.23</v>
+        <v>-0.77</v>
       </c>
       <c r="J5">
-        <v>-11.57</v>
+        <v>-11.47</v>
       </c>
       <c r="K5">
-        <v>10.86</v>
+        <v>10.75</v>
       </c>
       <c r="L5">
-        <v>-3.43</v>
+        <v>-4.39</v>
       </c>
       <c r="M5">
-        <v>15.45</v>
+        <v>15.27</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P5">
-        <v>1153.86</v>
+        <v>1152.08</v>
       </c>
       <c r="Q5">
-        <v>1193.38</v>
+        <v>1186.09</v>
       </c>
       <c r="R5">
-        <v>1258.48</v>
+        <v>1257.87</v>
       </c>
       <c r="S5">
-        <v>1066.86</v>
+        <v>1067.34</v>
       </c>
       <c r="T5">
-        <v>8.710000000000001</v>
+        <v>7.18</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1295,43 +1335,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>40.44</v>
+        <v>37.81</v>
       </c>
       <c r="Z5">
-        <v>-31.79</v>
+        <v>-31.51</v>
       </c>
       <c r="AA5">
-        <v>-29.93</v>
+        <v>-30.24</v>
       </c>
       <c r="AB5">
-        <v>-1.86</v>
+        <v>-1.27</v>
       </c>
       <c r="AC5">
-        <v>82.84999999999999</v>
+        <v>80.06</v>
       </c>
       <c r="AD5">
-        <v>68</v>
+        <v>76.73</v>
       </c>
       <c r="AE5">
-        <v>42.52</v>
+        <v>41.6</v>
       </c>
       <c r="AF5">
-        <v>-53.91</v>
+        <v>-54.38</v>
       </c>
       <c r="AG5">
-        <v>1286.87</v>
+        <v>1270.19</v>
       </c>
       <c r="AH5">
-        <v>1099.89</v>
+        <v>1101.99</v>
       </c>
       <c r="AI5">
-        <v>1279.65</v>
+        <v>1267.39</v>
       </c>
       <c r="AJ5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK5">
-        <v>36.32</v>
+        <v>32.27</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1382,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1922.2</v>
+        <v>1906.6</v>
       </c>
       <c r="D6">
-        <v>-3.02</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1394,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-17.16</v>
+        <v>-17.83</v>
       </c>
       <c r="H6">
-        <v>30.65</v>
+        <v>29.59</v>
       </c>
       <c r="I6">
-        <v>-4.59</v>
+        <v>-3.61</v>
       </c>
       <c r="J6">
-        <v>-7.14</v>
+        <v>-9.57</v>
       </c>
       <c r="K6">
-        <v>14.12</v>
+        <v>16.15</v>
       </c>
       <c r="L6">
-        <v>-4.46</v>
+        <v>-4.8</v>
       </c>
       <c r="M6">
-        <v>4.03</v>
+        <v>3.79</v>
       </c>
       <c r="N6">
         <v>79</v>
       </c>
       <c r="O6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P6">
-        <v>1970.88</v>
+        <v>1956.6</v>
       </c>
       <c r="Q6">
-        <v>2013.81</v>
+        <v>2007.24</v>
       </c>
       <c r="R6">
-        <v>2047.41</v>
+        <v>2048.21</v>
       </c>
       <c r="S6">
-        <v>1865.8</v>
+        <v>1864.71</v>
       </c>
       <c r="T6">
-        <v>3.02</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1408,43 +1448,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>37.78</v>
+        <v>36.3</v>
       </c>
       <c r="Z6">
-        <v>-18.52</v>
+        <v>-24.38</v>
       </c>
       <c r="AA6">
-        <v>-7.59</v>
+        <v>-10.95</v>
       </c>
       <c r="AB6">
-        <v>-10.93</v>
+        <v>-13.43</v>
       </c>
       <c r="AC6">
-        <v>18.81</v>
+        <v>6.11</v>
       </c>
       <c r="AD6">
-        <v>16.77</v>
+        <v>14.58</v>
       </c>
       <c r="AE6">
-        <v>61.95</v>
+        <v>60.47</v>
       </c>
       <c r="AF6">
-        <v>39.43</v>
+        <v>-8.15</v>
       </c>
       <c r="AG6">
-        <v>2082.11</v>
+        <v>2089.59</v>
       </c>
       <c r="AH6">
-        <v>1945.51</v>
+        <v>1924.9</v>
       </c>
       <c r="AI6">
-        <v>2112.15</v>
+        <v>2087.11</v>
       </c>
       <c r="AJ6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK6">
-        <v>19.07</v>
+        <v>20.65</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1625,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1605,753 +1645,848 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-10.62</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-10.98</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-0.36</v>
+        <v>43</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>18.2</v>
-      </c>
-      <c r="D8" s="5">
-        <v>22.59</v>
-      </c>
-      <c r="E8" s="7">
-        <v>4.39</v>
-      </c>
+      <c r="A8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-10.98</v>
+      </c>
+      <c r="D10" s="6">
+        <v>6.79</v>
+      </c>
+      <c r="E10" s="7">
+        <v>17.77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>22.59</v>
+      </c>
+      <c r="D11" s="6">
+        <v>21.14</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-18.5</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C12" s="6">
         <v>-17.91</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-16.26</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-10.83</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C13" s="6">
         <v>-11.57</v>
       </c>
-      <c r="E10" s="6">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-11.47</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C14" s="6">
+        <v>-7.14</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-9.57</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-1.49</v>
+      </c>
+      <c r="D15" s="6">
+        <v>17.85</v>
+      </c>
+      <c r="E15" s="7">
+        <v>19.34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>8.16</v>
+      </c>
+      <c r="D16" s="6">
+        <v>2.93</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-5.23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-4.37</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-4.42</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2.23</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.77</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-4.59</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-3.61</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-35.28</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-22.31</v>
+      </c>
+      <c r="E20" s="7">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-9.69</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-7.78</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-31.5</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-29.58</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-3.43</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-4.39</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-4.46</v>
+      </c>
+      <c r="D24" s="6">
         <v>-4.8</v>
       </c>
-      <c r="D11" s="5">
-        <v>-7.14</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="E24" s="8">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-4.64</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-1.49</v>
-      </c>
-      <c r="E12" s="7">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-30.5</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-14.58</v>
+      </c>
+      <c r="E25" s="7">
+        <v>15.92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>5.83</v>
-      </c>
-      <c r="D13" s="5">
-        <v>8.16</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>17.06</v>
+      </c>
+      <c r="D26" s="6">
+        <v>20.15</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-4.04</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-4.37</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-14.93</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-15.82</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-0.34</v>
-      </c>
-      <c r="D15" s="5">
-        <v>2.23</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>10.86</v>
+      </c>
+      <c r="D28" s="6">
+        <v>10.75</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-2.32</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-4.59</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>14.12</v>
+      </c>
+      <c r="D29" s="6">
+        <v>16.15</v>
+      </c>
+      <c r="E29" s="7">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-35.43</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-35.28</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-39.88</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-27.86</v>
+      </c>
+      <c r="E30" s="7">
+        <v>12.02</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-13.71</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-9.69</v>
-      </c>
-      <c r="E18" s="7">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-11.1</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-10.02</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-30.67</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-31.5</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-31.01</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-30.76</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-3.19</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-3.43</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-18.19</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-19.31</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>0.19</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-4.46</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-4.65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-17.16</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-17.83</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-28.11</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-30.5</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-2.39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>552.35</v>
+      </c>
+      <c r="D35" s="6">
+        <v>662.8</v>
+      </c>
+      <c r="E35" s="7">
+        <v>110.45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5">
-        <v>13.67</v>
-      </c>
-      <c r="D23" s="5">
-        <v>17.06</v>
-      </c>
-      <c r="E23" s="7">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>665.5</v>
+      </c>
+      <c r="D36" s="6">
+        <v>673.6</v>
+      </c>
+      <c r="E36" s="7">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-11.94</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-14.93</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-2.99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>861.9</v>
+      </c>
+      <c r="D37" s="6">
+        <v>865</v>
+      </c>
+      <c r="E37" s="7">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>12.59</v>
-      </c>
-      <c r="D25" s="5">
-        <v>10.86</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>1159.8</v>
+      </c>
+      <c r="D38" s="6">
+        <v>1144</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-15.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>19.79</v>
-      </c>
-      <c r="D26" s="5">
-        <v>14.12</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-5.67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>1922.2</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1906.6</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-15.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-39.65</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-39.88</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="6">
+        <v>21</v>
+      </c>
+      <c r="D40" s="6">
+        <v>40</v>
+      </c>
+      <c r="E40" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="6">
+        <v>40</v>
+      </c>
+      <c r="D41" s="6">
+        <v>21</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>27.04</v>
+      </c>
+      <c r="D42" s="6">
+        <v>65.26000000000001</v>
+      </c>
+      <c r="E42" s="7">
+        <v>38.22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-13.86</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-11.1</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>68.04000000000001</v>
+      </c>
+      <c r="D43" s="6">
+        <v>69.54000000000001</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-30.22</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-31.01</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>21.71</v>
+      </c>
+      <c r="D44" s="6">
+        <v>23.32</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-17.93</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-18.19</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6">
+        <v>40.44</v>
+      </c>
+      <c r="D45" s="6">
+        <v>37.81</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-2.63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-14.58</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-17.16</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>37.78</v>
+      </c>
+      <c r="D46" s="6">
+        <v>36.3</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>554.45</v>
-      </c>
-      <c r="D32" s="5">
-        <v>552.35</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>16.47</v>
+      </c>
+      <c r="D47" s="6">
+        <v>3360.88</v>
+      </c>
+      <c r="E47" s="7">
+        <v>3344.41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>644.85</v>
-      </c>
-      <c r="D33" s="5">
-        <v>665.5</v>
-      </c>
-      <c r="E33" s="7">
-        <v>20.65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-66.75</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-58.92</v>
+      </c>
+      <c r="E48" s="7">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>878</v>
-      </c>
-      <c r="D34" s="5">
-        <v>861.9</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-16.1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-8.69</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-50.43</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-41.74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>1163.5</v>
-      </c>
-      <c r="D35" s="5">
-        <v>1159.8</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-53.91</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-54.38</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>1982</v>
-      </c>
-      <c r="D36" s="5">
-        <v>1922.2</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-59.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="5">
-        <v>79</v>
-      </c>
-      <c r="D37" s="5">
-        <v>99</v>
-      </c>
-      <c r="E37" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="5">
-        <v>99</v>
-      </c>
-      <c r="D38" s="5">
-        <v>79</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>27.57</v>
-      </c>
-      <c r="D39" s="5">
-        <v>27.04</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>63.82</v>
-      </c>
-      <c r="D40" s="5">
-        <v>68.04000000000001</v>
-      </c>
-      <c r="E40" s="7">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>24.17</v>
-      </c>
-      <c r="D41" s="5">
-        <v>21.71</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="5">
-        <v>41.06</v>
-      </c>
-      <c r="D42" s="5">
-        <v>40.44</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>44.18</v>
-      </c>
-      <c r="D43" s="5">
-        <v>37.78</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-6.4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="B51" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="5">
-        <v>29.87</v>
-      </c>
-      <c r="D44" s="5">
-        <v>16.47</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-13.4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-70.11</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-66.75</v>
-      </c>
-      <c r="E45" s="7">
-        <v>3.36</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-54.34</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-8.69</v>
-      </c>
-      <c r="E46" s="7">
-        <v>45.65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-55.91</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-53.91</v>
-      </c>
-      <c r="E47" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-43.02</v>
-      </c>
-      <c r="D48" s="5">
+      <c r="C51" s="6">
         <v>39.43</v>
       </c>
-      <c r="E48" s="7">
-        <v>82.45</v>
+      <c r="D51" s="6">
+        <v>-8.15</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-47.58</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2371,61 +2506,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="11">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="12">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>46.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="10">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="11">
-        <v>5</v>
-      </c>
-      <c r="D2" s="10">
-        <v>39</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-0.7</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-1.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
-        <v>0</v>
+      <c r="I2" s="11">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2526,37 +2661,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1545</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0403</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.0132</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.04099999999999999</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1562</v>
+      <c r="A2" s="14">
+        <v>0.1527</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0379</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0168</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0397</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1243</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,31 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 GOLDEN CROSS</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>27.0 → 65.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>27.0</t>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>65.3 → 76.9</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
   </si>
   <si>
     <t>65.3</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
+    <t>76.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -257,7 +245,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,6 +279,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -304,7 +299,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -326,6 +321,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,12 +418,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -431,7 +432,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -930,10 +931,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>662.8</v>
+        <v>761</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>14.82</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -942,46 +943,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-27.86</v>
+        <v>-17.17</v>
       </c>
       <c r="H2">
-        <v>27.01</v>
+        <v>45.83</v>
       </c>
       <c r="I2">
-        <v>17.85</v>
+        <v>32.91</v>
       </c>
       <c r="J2">
-        <v>6.79</v>
+        <v>23.7</v>
       </c>
       <c r="K2">
-        <v>-14.58</v>
+        <v>-1.36</v>
       </c>
       <c r="L2">
-        <v>-22.31</v>
+        <v>-10.52</v>
       </c>
       <c r="M2">
-        <v>-12.43</v>
+        <v>-10.79</v>
       </c>
       <c r="N2">
         <v>40</v>
       </c>
       <c r="O2">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="P2">
-        <v>583.08</v>
+        <v>620.77</v>
       </c>
       <c r="Q2">
-        <v>589</v>
+        <v>596.66</v>
       </c>
       <c r="R2">
-        <v>634.92</v>
+        <v>635.86</v>
       </c>
       <c r="S2">
-        <v>674.47</v>
+        <v>674.13</v>
       </c>
       <c r="T2">
-        <v>-1.73</v>
+        <v>12.89</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -993,46 +994,46 @@
         <v>43</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>65.26000000000001</v>
+        <v>76.87</v>
       </c>
       <c r="Z2">
-        <v>-13.62</v>
+        <v>1.17</v>
       </c>
       <c r="AA2">
-        <v>-20.19</v>
+        <v>-15.92</v>
       </c>
       <c r="AB2">
-        <v>6.56</v>
+        <v>17.09</v>
       </c>
       <c r="AC2">
-        <v>50.06</v>
+        <v>74.23</v>
       </c>
       <c r="AD2">
-        <v>50.13</v>
+        <v>55.43</v>
       </c>
       <c r="AE2">
-        <v>29.95</v>
+        <v>36.13</v>
       </c>
       <c r="AF2">
-        <v>3360.88</v>
+        <v>5429.86</v>
       </c>
       <c r="AG2">
-        <v>637.8099999999999</v>
+        <v>687.7</v>
       </c>
       <c r="AH2">
-        <v>540.2</v>
+        <v>505.62</v>
       </c>
       <c r="AI2">
-        <v>533.65</v>
+        <v>626.27</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>56.94</v>
+        <v>58.36</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,58 +1044,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>673.6</v>
+        <v>674.65</v>
       </c>
       <c r="D3">
-        <v>1.22</v>
+        <v>0.16</v>
       </c>
       <c r="E3">
-        <v>748.6</v>
+        <v>740.6</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-10.02</v>
+        <v>-8.9</v>
       </c>
       <c r="H3">
-        <v>31.31</v>
+        <v>31.51</v>
       </c>
       <c r="I3">
-        <v>2.93</v>
+        <v>0.66</v>
       </c>
       <c r="J3">
-        <v>21.14</v>
+        <v>23.47</v>
       </c>
       <c r="K3">
-        <v>20.15</v>
+        <v>20.93</v>
       </c>
       <c r="L3">
-        <v>-7.78</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="M3">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P3">
-        <v>662.63</v>
+        <v>663.51</v>
       </c>
       <c r="Q3">
-        <v>610.46</v>
+        <v>616.58</v>
       </c>
       <c r="R3">
-        <v>581.77</v>
+        <v>584.24</v>
       </c>
       <c r="S3">
-        <v>580.1</v>
+        <v>580.6</v>
       </c>
       <c r="T3">
-        <v>16.12</v>
+        <v>16.2</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1109,43 +1110,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>69.54000000000001</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="Z3">
-        <v>25.79</v>
+        <v>26.81</v>
       </c>
       <c r="AA3">
-        <v>19.06</v>
+        <v>20.61</v>
       </c>
       <c r="AB3">
-        <v>6.73</v>
+        <v>6.2</v>
       </c>
       <c r="AC3">
-        <v>65.98</v>
+        <v>74.81</v>
       </c>
       <c r="AD3">
-        <v>69.42</v>
+        <v>68.98</v>
       </c>
       <c r="AE3">
-        <v>22.87</v>
+        <v>22.77</v>
       </c>
       <c r="AF3">
-        <v>-58.92</v>
+        <v>-68.92</v>
       </c>
       <c r="AG3">
-        <v>688.92</v>
+        <v>695.01</v>
       </c>
       <c r="AH3">
-        <v>532</v>
+        <v>538.15</v>
       </c>
       <c r="AI3">
-        <v>598.35</v>
+        <v>600.28</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>54.06</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1157,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>865</v>
+        <v>863.8</v>
       </c>
       <c r="D4">
-        <v>0.36</v>
+        <v>-0.14</v>
       </c>
       <c r="E4">
         <v>1249.31</v>
@@ -1168,25 +1169,25 @@
         <v>861.9</v>
       </c>
       <c r="G4">
-        <v>-30.76</v>
+        <v>-30.86</v>
       </c>
       <c r="H4">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="I4">
-        <v>-4.42</v>
+        <v>-4.55</v>
       </c>
       <c r="J4">
-        <v>-16.26</v>
+        <v>-15.73</v>
       </c>
       <c r="K4">
-        <v>-15.82</v>
+        <v>-14.38</v>
       </c>
       <c r="L4">
-        <v>-29.58</v>
+        <v>-28.89</v>
       </c>
       <c r="M4">
-        <v>-3.97</v>
+        <v>-4</v>
       </c>
       <c r="N4">
         <v>21</v>
@@ -1195,19 +1196,19 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>877.98</v>
+        <v>869.74</v>
       </c>
       <c r="Q4">
-        <v>913.58</v>
+        <v>911.27</v>
       </c>
       <c r="R4">
-        <v>1005.89</v>
+        <v>1002.3</v>
       </c>
       <c r="S4">
-        <v>1081.92</v>
+        <v>1080.66</v>
       </c>
       <c r="T4">
-        <v>-20.05</v>
+        <v>-20.07</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1222,43 +1223,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>23.32</v>
+        <v>23.13</v>
       </c>
       <c r="Z4">
-        <v>-38.07</v>
+        <v>-38.06</v>
       </c>
       <c r="AA4">
-        <v>-35.51</v>
+        <v>-36.02</v>
       </c>
       <c r="AB4">
-        <v>-2.57</v>
+        <v>-2.05</v>
       </c>
       <c r="AC4">
-        <v>4.05</v>
+        <v>8.32</v>
       </c>
       <c r="AD4">
-        <v>3.75</v>
+        <v>4.12</v>
       </c>
       <c r="AE4">
-        <v>21.54</v>
+        <v>20.85</v>
       </c>
       <c r="AF4">
-        <v>-50.43</v>
+        <v>-50.25</v>
       </c>
       <c r="AG4">
-        <v>963.55</v>
+        <v>965.98</v>
       </c>
       <c r="AH4">
-        <v>863.61</v>
+        <v>856.5599999999999</v>
       </c>
       <c r="AI4">
-        <v>927.67</v>
+        <v>924.5700000000001</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>71.98999999999999</v>
+        <v>73.88</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1270,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1144</v>
+        <v>1133.4</v>
       </c>
       <c r="D5">
-        <v>-1.36</v>
+        <v>-0.93</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1281,46 +1282,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-19.31</v>
+        <v>-20.05</v>
       </c>
       <c r="H5">
-        <v>52.74</v>
+        <v>51.32</v>
       </c>
       <c r="I5">
-        <v>-0.77</v>
+        <v>-0.47</v>
       </c>
       <c r="J5">
-        <v>-11.47</v>
+        <v>-12.13</v>
       </c>
       <c r="K5">
-        <v>10.75</v>
+        <v>12.31</v>
       </c>
       <c r="L5">
-        <v>-4.39</v>
+        <v>-5.7</v>
       </c>
       <c r="M5">
-        <v>15.27</v>
+        <v>15.16</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="P5">
-        <v>1152.08</v>
+        <v>1151</v>
       </c>
       <c r="Q5">
-        <v>1186.09</v>
+        <v>1181</v>
       </c>
       <c r="R5">
-        <v>1257.87</v>
+        <v>1256.59</v>
       </c>
       <c r="S5">
-        <v>1067.34</v>
+        <v>1067.76</v>
       </c>
       <c r="T5">
-        <v>7.18</v>
+        <v>6.15</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1335,43 +1336,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>37.81</v>
+        <v>36.11</v>
       </c>
       <c r="Z5">
-        <v>-31.51</v>
+        <v>-31.78</v>
       </c>
       <c r="AA5">
-        <v>-30.24</v>
+        <v>-30.55</v>
       </c>
       <c r="AB5">
-        <v>-1.27</v>
+        <v>-1.23</v>
       </c>
       <c r="AC5">
-        <v>80.06</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="AD5">
         <v>76.73</v>
       </c>
       <c r="AE5">
-        <v>41.6</v>
+        <v>40.03</v>
       </c>
       <c r="AF5">
-        <v>-54.38</v>
+        <v>-67.84999999999999</v>
       </c>
       <c r="AG5">
-        <v>1270.19</v>
+        <v>1264.9</v>
       </c>
       <c r="AH5">
-        <v>1101.99</v>
+        <v>1097.1</v>
       </c>
       <c r="AI5">
-        <v>1267.39</v>
+        <v>1253.78</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>32.27</v>
+        <v>29.43</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1383,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1906.6</v>
+        <v>1857.1</v>
       </c>
       <c r="D6">
-        <v>-0.8100000000000001</v>
+        <v>-2.6</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1394,46 +1395,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-17.83</v>
+        <v>-19.96</v>
       </c>
       <c r="H6">
-        <v>29.59</v>
+        <v>26.22</v>
       </c>
       <c r="I6">
-        <v>-3.61</v>
+        <v>-5.76</v>
       </c>
       <c r="J6">
-        <v>-9.57</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="K6">
-        <v>16.15</v>
+        <v>14.78</v>
       </c>
       <c r="L6">
-        <v>-4.8</v>
+        <v>-5.34</v>
       </c>
       <c r="M6">
-        <v>3.79</v>
+        <v>3.26</v>
       </c>
       <c r="N6">
         <v>79</v>
       </c>
       <c r="O6">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="P6">
-        <v>1956.6</v>
+        <v>1933.88</v>
       </c>
       <c r="Q6">
-        <v>2007.24</v>
+        <v>1999.35</v>
       </c>
       <c r="R6">
-        <v>2048.21</v>
+        <v>2046.16</v>
       </c>
       <c r="S6">
-        <v>1864.71</v>
+        <v>1863.54</v>
       </c>
       <c r="T6">
-        <v>2.25</v>
+        <v>-0.35</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1445,46 +1446,46 @@
         <v>43</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>36.3</v>
+        <v>32.02</v>
       </c>
       <c r="Z6">
-        <v>-24.38</v>
+        <v>-32.64</v>
       </c>
       <c r="AA6">
-        <v>-10.95</v>
+        <v>-15.29</v>
       </c>
       <c r="AB6">
-        <v>-13.43</v>
+        <v>-17.35</v>
       </c>
       <c r="AC6">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>14.58</v>
+        <v>8.31</v>
       </c>
       <c r="AE6">
-        <v>60.47</v>
+        <v>59.95</v>
       </c>
       <c r="AF6">
-        <v>-8.15</v>
+        <v>-3.75</v>
       </c>
       <c r="AG6">
-        <v>2089.59</v>
+        <v>2105.42</v>
       </c>
       <c r="AH6">
-        <v>1924.9</v>
+        <v>1893.28</v>
       </c>
       <c r="AI6">
-        <v>2087.11</v>
+        <v>2061.45</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>20.65</v>
+        <v>23.21</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1665,7 +1666,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1677,640 +1678,631 @@
         <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>6.79</v>
+      </c>
+      <c r="D7" s="6">
+        <v>23.7</v>
+      </c>
+      <c r="E7" s="7">
+        <v>16.91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>21.14</v>
+      </c>
+      <c r="D8" s="6">
+        <v>23.47</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.33</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>66</v>
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-16.26</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-15.73</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-10.98</v>
+        <v>-11.47</v>
       </c>
       <c r="D10" s="6">
-        <v>6.79</v>
-      </c>
-      <c r="E10" s="7">
-        <v>17.77</v>
+        <v>-12.13</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>22.59</v>
+        <v>-9.57</v>
       </c>
       <c r="D11" s="6">
-        <v>21.14</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.45</v>
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-17.91</v>
+        <v>17.85</v>
       </c>
       <c r="D12" s="6">
-        <v>-16.26</v>
+        <v>32.91</v>
       </c>
       <c r="E12" s="7">
-        <v>1.65</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-11.57</v>
+        <v>2.93</v>
       </c>
       <c r="D13" s="6">
-        <v>-11.47</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.1</v>
+        <v>0.66</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-7.14</v>
+        <v>-4.42</v>
       </c>
       <c r="D14" s="6">
-        <v>-9.57</v>
+        <v>-4.55</v>
       </c>
       <c r="E14" s="8">
-        <v>-2.43</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-1.49</v>
+        <v>-0.77</v>
       </c>
       <c r="D15" s="6">
-        <v>17.85</v>
+        <v>-0.47</v>
       </c>
       <c r="E15" s="7">
-        <v>19.34</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>8.16</v>
+        <v>-3.61</v>
       </c>
       <c r="D16" s="6">
-        <v>2.93</v>
+        <v>-5.76</v>
       </c>
       <c r="E16" s="8">
-        <v>-5.23</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.37</v>
+        <v>-22.31</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.42</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.05</v>
+        <v>-10.52</v>
+      </c>
+      <c r="E17" s="7">
+        <v>11.79</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>2.23</v>
+        <v>-7.78</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.77</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="E18" s="8">
-        <v>-3</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-4.59</v>
+        <v>-29.58</v>
       </c>
       <c r="D19" s="6">
-        <v>-3.61</v>
+        <v>-28.89</v>
       </c>
       <c r="E19" s="7">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-35.28</v>
+        <v>-4.39</v>
       </c>
       <c r="D20" s="6">
-        <v>-22.31</v>
-      </c>
-      <c r="E20" s="7">
-        <v>12.97</v>
+        <v>-5.7</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-9.69</v>
+        <v>-4.8</v>
       </c>
       <c r="D21" s="6">
-        <v>-7.78</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.91</v>
+        <v>-5.34</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-31.5</v>
+        <v>-14.58</v>
       </c>
       <c r="D22" s="6">
-        <v>-29.58</v>
+        <v>-1.36</v>
       </c>
       <c r="E22" s="7">
-        <v>1.92</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-3.43</v>
+        <v>20.15</v>
       </c>
       <c r="D23" s="6">
-        <v>-4.39</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.96</v>
+        <v>20.93</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.78</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.46</v>
+        <v>-15.82</v>
       </c>
       <c r="D24" s="6">
-        <v>-4.8</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.34</v>
+        <v>-14.38</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.44</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-30.5</v>
+        <v>10.75</v>
       </c>
       <c r="D25" s="6">
-        <v>-14.58</v>
+        <v>12.31</v>
       </c>
       <c r="E25" s="7">
-        <v>15.92</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>17.06</v>
+        <v>16.15</v>
       </c>
       <c r="D26" s="6">
-        <v>20.15</v>
-      </c>
-      <c r="E26" s="7">
-        <v>3.09</v>
+        <v>14.78</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-14.93</v>
+        <v>-27.86</v>
       </c>
       <c r="D27" s="6">
-        <v>-15.82</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.89</v>
+        <v>-17.17</v>
+      </c>
+      <c r="E27" s="7">
+        <v>10.69</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>10.86</v>
+        <v>-10.02</v>
       </c>
       <c r="D28" s="6">
-        <v>10.75</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.11</v>
+        <v>-8.9</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.12</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>14.12</v>
+        <v>-30.76</v>
       </c>
       <c r="D29" s="6">
-        <v>16.15</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.03</v>
+        <v>-30.86</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-39.88</v>
+        <v>-19.31</v>
       </c>
       <c r="D30" s="6">
-        <v>-27.86</v>
-      </c>
-      <c r="E30" s="7">
-        <v>12.02</v>
+        <v>-20.05</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-11.1</v>
+        <v>-17.83</v>
       </c>
       <c r="D31" s="6">
-        <v>-10.02</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.08</v>
+        <v>-19.96</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>-31.01</v>
+        <v>662.8</v>
       </c>
       <c r="D32" s="6">
-        <v>-30.76</v>
+        <v>761</v>
       </c>
       <c r="E32" s="7">
-        <v>0.25</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>-18.19</v>
+        <v>673.6</v>
       </c>
       <c r="D33" s="6">
-        <v>-19.31</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-1.12</v>
+        <v>674.65</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.05</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>-17.16</v>
+        <v>865</v>
       </c>
       <c r="D34" s="6">
-        <v>-17.83</v>
+        <v>863.8</v>
       </c>
       <c r="E34" s="8">
-        <v>-0.67</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>552.35</v>
+        <v>1144</v>
       </c>
       <c r="D35" s="6">
-        <v>662.8</v>
-      </c>
-      <c r="E35" s="7">
-        <v>110.45</v>
+        <v>1133.4</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-10.6</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>665.5</v>
+        <v>1906.6</v>
       </c>
       <c r="D36" s="6">
-        <v>673.6</v>
-      </c>
-      <c r="E36" s="7">
-        <v>8.1</v>
+        <v>1857.1</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-49.5</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C37" s="6">
-        <v>861.9</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="D37" s="6">
-        <v>865</v>
+        <v>76.87</v>
       </c>
       <c r="E37" s="7">
-        <v>3.1</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>1159.8</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="D38" s="6">
-        <v>1144</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-15.8</v>
+        <v>69.73999999999999</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.2</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>1922.2</v>
+        <v>23.32</v>
       </c>
       <c r="D39" s="6">
-        <v>1906.6</v>
+        <v>23.13</v>
       </c>
       <c r="E39" s="8">
-        <v>-15.6</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>21</v>
+        <v>37.81</v>
       </c>
       <c r="D40" s="6">
-        <v>40</v>
-      </c>
-      <c r="E40" s="7">
-        <v>19</v>
+        <v>36.11</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>40</v>
+        <v>36.3</v>
       </c>
       <c r="D41" s="6">
-        <v>21</v>
+        <v>32.02</v>
       </c>
       <c r="E41" s="8">
-        <v>-19</v>
+        <v>-4.28</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2318,16 +2310,16 @@
         <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C42" s="6">
-        <v>27.04</v>
+        <v>3360.88</v>
       </c>
       <c r="D42" s="6">
-        <v>65.26000000000001</v>
+        <v>5429.86</v>
       </c>
       <c r="E42" s="7">
-        <v>38.22</v>
+        <v>2068.98</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2335,16 +2327,16 @@
         <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>68.04000000000001</v>
+        <v>-58.92</v>
       </c>
       <c r="D43" s="6">
-        <v>69.54000000000001</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.5</v>
+        <v>-68.92</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-10</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2352,16 +2344,16 @@
         <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>21.71</v>
+        <v>-50.43</v>
       </c>
       <c r="D44" s="6">
-        <v>23.32</v>
+        <v>-50.25</v>
       </c>
       <c r="E44" s="7">
-        <v>1.61</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2369,16 +2361,16 @@
         <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>40.44</v>
+        <v>-54.38</v>
       </c>
       <c r="D45" s="6">
-        <v>37.81</v>
+        <v>-67.84999999999999</v>
       </c>
       <c r="E45" s="8">
-        <v>-2.63</v>
+        <v>-13.47</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2386,107 +2378,22 @@
         <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>37.78</v>
+        <v>-8.15</v>
       </c>
       <c r="D46" s="6">
-        <v>36.3</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>16.47</v>
-      </c>
-      <c r="D47" s="6">
-        <v>3360.88</v>
-      </c>
-      <c r="E47" s="7">
-        <v>3344.41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-66.75</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-58.92</v>
-      </c>
-      <c r="E48" s="7">
-        <v>7.83</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-8.69</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-50.43</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-41.74</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-53.91</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-54.38</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="6">
-        <v>39.43</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-8.15</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-47.58</v>
+        <v>-3.75</v>
+      </c>
+      <c r="E46" s="7">
+        <v>4.4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2510,28 +2417,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2545,16 +2452,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>46.4</v>
+        <v>47.6</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-1.9</v>
+        <v>2.1</v>
       </c>
       <c r="G2" s="11">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2679,19 +2586,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.1527</v>
+        <v>0.1516</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0379</v>
+        <v>0.0326</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0168</v>
+        <v>0.0169</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0397</v>
+        <v>-0.04</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1243</v>
+        <v>-0.1079</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -181,19 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>65.3 → 76.9</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>65.3</t>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>76.9 → 66.0</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
   </si>
   <si>
     <t>76.9</t>
+  </si>
+  <si>
+    <t>66.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -279,7 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -287,13 +294,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -326,19 +326,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -931,10 +931,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>761</v>
+        <v>715.8</v>
       </c>
       <c r="D2">
-        <v>14.82</v>
+        <v>-5.94</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -943,46 +943,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-17.17</v>
+        <v>-22.09</v>
       </c>
       <c r="H2">
-        <v>45.83</v>
+        <v>37.17</v>
       </c>
       <c r="I2">
-        <v>32.91</v>
+        <v>24.87</v>
       </c>
       <c r="J2">
-        <v>23.7</v>
+        <v>17.76</v>
       </c>
       <c r="K2">
-        <v>-1.36</v>
+        <v>-6.99</v>
       </c>
       <c r="L2">
-        <v>-10.52</v>
+        <v>-15.41</v>
       </c>
       <c r="M2">
-        <v>-10.79</v>
+        <v>-11.71</v>
       </c>
       <c r="N2">
         <v>40</v>
       </c>
       <c r="O2">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="P2">
-        <v>620.77</v>
+        <v>649.28</v>
       </c>
       <c r="Q2">
-        <v>596.66</v>
+        <v>602.35</v>
       </c>
       <c r="R2">
-        <v>635.86</v>
+        <v>635.74</v>
       </c>
       <c r="S2">
-        <v>674.13</v>
+        <v>673.26</v>
       </c>
       <c r="T2">
-        <v>12.89</v>
+        <v>6.32</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -997,34 +997,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>76.87</v>
+        <v>65.95</v>
       </c>
       <c r="Z2">
-        <v>1.17</v>
+        <v>9.15</v>
       </c>
       <c r="AA2">
-        <v>-15.92</v>
+        <v>-10.9</v>
       </c>
       <c r="AB2">
-        <v>17.09</v>
+        <v>20.05</v>
       </c>
       <c r="AC2">
-        <v>74.23</v>
+        <v>93.05</v>
       </c>
       <c r="AD2">
-        <v>55.43</v>
+        <v>72.45</v>
       </c>
       <c r="AE2">
-        <v>36.13</v>
+        <v>38.38</v>
       </c>
       <c r="AF2">
-        <v>5429.86</v>
+        <v>49.71</v>
       </c>
       <c r="AG2">
-        <v>687.7</v>
+        <v>707.87</v>
       </c>
       <c r="AH2">
-        <v>505.62</v>
+        <v>496.83</v>
       </c>
       <c r="AI2">
         <v>626.27</v>
@@ -1033,7 +1033,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>58.36</v>
+        <v>59.59</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1044,10 +1044,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>674.65</v>
+        <v>673.05</v>
       </c>
       <c r="D3">
-        <v>0.16</v>
+        <v>-0.24</v>
       </c>
       <c r="E3">
         <v>740.6</v>
@@ -1056,25 +1056,25 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-8.9</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="H3">
-        <v>31.51</v>
+        <v>31.2</v>
       </c>
       <c r="I3">
-        <v>0.66</v>
+        <v>2.14</v>
       </c>
       <c r="J3">
-        <v>23.47</v>
+        <v>21.87</v>
       </c>
       <c r="K3">
-        <v>20.93</v>
+        <v>19.13</v>
       </c>
       <c r="L3">
-        <v>-9.880000000000001</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="M3">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1083,19 +1083,19 @@
         <v>67</v>
       </c>
       <c r="P3">
-        <v>663.51</v>
+        <v>666.33</v>
       </c>
       <c r="Q3">
-        <v>616.58</v>
+        <v>622.12</v>
       </c>
       <c r="R3">
-        <v>584.24</v>
+        <v>586.61</v>
       </c>
       <c r="S3">
-        <v>580.6</v>
+        <v>581.14</v>
       </c>
       <c r="T3">
-        <v>16.2</v>
+        <v>15.81</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1110,43 +1110,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>69.73999999999999</v>
+        <v>69</v>
       </c>
       <c r="Z3">
-        <v>26.81</v>
+        <v>27.17</v>
       </c>
       <c r="AA3">
-        <v>20.61</v>
+        <v>21.92</v>
       </c>
       <c r="AB3">
-        <v>6.2</v>
+        <v>5.25</v>
       </c>
       <c r="AC3">
-        <v>74.81</v>
+        <v>76.25</v>
       </c>
       <c r="AD3">
-        <v>68.98</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="AE3">
-        <v>22.77</v>
+        <v>22.55</v>
       </c>
       <c r="AF3">
-        <v>-68.92</v>
+        <v>-59.56</v>
       </c>
       <c r="AG3">
-        <v>695.01</v>
+        <v>700.04</v>
       </c>
       <c r="AH3">
-        <v>538.15</v>
+        <v>544.21</v>
       </c>
       <c r="AI3">
-        <v>600.28</v>
+        <v>606.01</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>55.04</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1157,10 +1157,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>863.8</v>
+        <v>869.9</v>
       </c>
       <c r="D4">
-        <v>-0.14</v>
+        <v>0.71</v>
       </c>
       <c r="E4">
         <v>1249.31</v>
@@ -1169,46 +1169,46 @@
         <v>861.9</v>
       </c>
       <c r="G4">
-        <v>-30.86</v>
+        <v>-30.37</v>
       </c>
       <c r="H4">
-        <v>0.22</v>
+        <v>0.93</v>
       </c>
       <c r="I4">
-        <v>-4.55</v>
+        <v>-1.15</v>
       </c>
       <c r="J4">
-        <v>-15.73</v>
+        <v>-4.41</v>
       </c>
       <c r="K4">
-        <v>-14.38</v>
+        <v>-15.81</v>
       </c>
       <c r="L4">
-        <v>-28.89</v>
+        <v>-28.3</v>
       </c>
       <c r="M4">
-        <v>-4</v>
+        <v>-4.08</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P4">
-        <v>869.74</v>
+        <v>867.72</v>
       </c>
       <c r="Q4">
-        <v>911.27</v>
+        <v>907.92</v>
       </c>
       <c r="R4">
-        <v>1002.3</v>
+        <v>998.15</v>
       </c>
       <c r="S4">
-        <v>1080.66</v>
+        <v>1079.51</v>
       </c>
       <c r="T4">
-        <v>-20.07</v>
+        <v>-19.42</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1223,34 +1223,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>23.13</v>
+        <v>26.56</v>
       </c>
       <c r="Z4">
-        <v>-38.06</v>
+        <v>-37.14</v>
       </c>
       <c r="AA4">
-        <v>-36.02</v>
+        <v>-36.24</v>
       </c>
       <c r="AB4">
-        <v>-2.05</v>
+        <v>-0.89</v>
       </c>
       <c r="AC4">
-        <v>8.32</v>
+        <v>23.72</v>
       </c>
       <c r="AD4">
-        <v>4.12</v>
+        <v>12.03</v>
       </c>
       <c r="AE4">
-        <v>20.85</v>
+        <v>20.34</v>
       </c>
       <c r="AF4">
-        <v>-50.25</v>
+        <v>-76.14</v>
       </c>
       <c r="AG4">
-        <v>965.98</v>
+        <v>964.2</v>
       </c>
       <c r="AH4">
-        <v>856.5599999999999</v>
+        <v>851.64</v>
       </c>
       <c r="AI4">
         <v>924.5700000000001</v>
@@ -1259,7 +1259,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>73.88</v>
+        <v>73.20999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1270,10 +1270,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1133.4</v>
+        <v>1122.3</v>
       </c>
       <c r="D5">
-        <v>-0.93</v>
+        <v>-0.98</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1282,46 +1282,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-20.05</v>
+        <v>-20.84</v>
       </c>
       <c r="H5">
-        <v>51.32</v>
+        <v>49.84</v>
       </c>
       <c r="I5">
-        <v>-0.47</v>
+        <v>-2.77</v>
       </c>
       <c r="J5">
-        <v>-12.13</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="K5">
-        <v>12.31</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L5">
-        <v>-5.7</v>
+        <v>-6.95</v>
       </c>
       <c r="M5">
-        <v>15.16</v>
+        <v>15.21</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P5">
-        <v>1151</v>
+        <v>1144.6</v>
       </c>
       <c r="Q5">
-        <v>1181</v>
+        <v>1174.34</v>
       </c>
       <c r="R5">
-        <v>1256.59</v>
+        <v>1254.8</v>
       </c>
       <c r="S5">
-        <v>1067.76</v>
+        <v>1068.28</v>
       </c>
       <c r="T5">
-        <v>6.15</v>
+        <v>5.06</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1336,43 +1336,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>36.11</v>
+        <v>34.37</v>
       </c>
       <c r="Z5">
-        <v>-31.78</v>
+        <v>-32.52</v>
       </c>
       <c r="AA5">
-        <v>-30.55</v>
+        <v>-30.95</v>
       </c>
       <c r="AB5">
-        <v>-1.23</v>
+        <v>-1.57</v>
       </c>
       <c r="AC5">
-        <v>67.29000000000001</v>
+        <v>53.06</v>
       </c>
       <c r="AD5">
-        <v>76.73</v>
+        <v>66.8</v>
       </c>
       <c r="AE5">
-        <v>40.03</v>
+        <v>38.27</v>
       </c>
       <c r="AF5">
-        <v>-67.84999999999999</v>
+        <v>-35.81</v>
       </c>
       <c r="AG5">
-        <v>1264.9</v>
+        <v>1254.37</v>
       </c>
       <c r="AH5">
-        <v>1097.1</v>
+        <v>1094.3</v>
       </c>
       <c r="AI5">
-        <v>1253.78</v>
+        <v>1242.5</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>29.43</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1383,10 +1383,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1857.1</v>
+        <v>1872</v>
       </c>
       <c r="D6">
-        <v>-2.6</v>
+        <v>0.8</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1395,46 +1395,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-19.96</v>
+        <v>-19.32</v>
       </c>
       <c r="H6">
-        <v>26.22</v>
+        <v>27.23</v>
       </c>
       <c r="I6">
-        <v>-5.76</v>
+        <v>-6.47</v>
       </c>
       <c r="J6">
-        <v>-8.869999999999999</v>
+        <v>-7.1</v>
       </c>
       <c r="K6">
-        <v>14.78</v>
+        <v>10.68</v>
       </c>
       <c r="L6">
-        <v>-5.34</v>
+        <v>-4.7</v>
       </c>
       <c r="M6">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="N6">
         <v>79</v>
       </c>
       <c r="O6">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P6">
-        <v>1933.88</v>
+        <v>1907.98</v>
       </c>
       <c r="Q6">
-        <v>1999.35</v>
+        <v>1991.55</v>
       </c>
       <c r="R6">
-        <v>2046.16</v>
+        <v>2044.23</v>
       </c>
       <c r="S6">
-        <v>1863.54</v>
+        <v>1862.67</v>
       </c>
       <c r="T6">
-        <v>-0.35</v>
+        <v>0.5</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1446,46 +1446,46 @@
         <v>43</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>32.02</v>
+        <v>34.53</v>
       </c>
       <c r="Z6">
-        <v>-32.64</v>
+        <v>-37.55</v>
       </c>
       <c r="AA6">
-        <v>-15.29</v>
+        <v>-19.74</v>
       </c>
       <c r="AB6">
-        <v>-17.35</v>
+        <v>-17.81</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AD6">
-        <v>8.31</v>
+        <v>3.3</v>
       </c>
       <c r="AE6">
-        <v>59.95</v>
+        <v>58.44</v>
       </c>
       <c r="AF6">
-        <v>-3.75</v>
+        <v>22.97</v>
       </c>
       <c r="AG6">
-        <v>2105.42</v>
+        <v>2110.87</v>
       </c>
       <c r="AH6">
-        <v>1893.28</v>
+        <v>1872.23</v>
       </c>
       <c r="AI6">
-        <v>2061.45</v>
+        <v>2030.72</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>23.21</v>
+        <v>26.12</v>
       </c>
     </row>
   </sheetData>
@@ -1718,13 +1718,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>6.79</v>
+        <v>23.7</v>
       </c>
       <c r="D7" s="6">
-        <v>23.7</v>
+        <v>17.76</v>
       </c>
       <c r="E7" s="7">
-        <v>16.91</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1735,13 +1735,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>21.14</v>
+        <v>23.47</v>
       </c>
       <c r="D8" s="6">
-        <v>23.47</v>
+        <v>21.87</v>
       </c>
       <c r="E8" s="7">
-        <v>2.33</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1752,13 +1752,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-16.26</v>
+        <v>-15.73</v>
       </c>
       <c r="D9" s="6">
-        <v>-15.73</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.53</v>
+        <v>-4.41</v>
+      </c>
+      <c r="E9" s="8">
+        <v>11.32</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1769,13 +1769,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-11.47</v>
+        <v>-12.13</v>
       </c>
       <c r="D10" s="6">
-        <v>-12.13</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="E10" s="8">
-        <v>-0.66</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1786,13 +1786,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-9.57</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="D11" s="6">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.7</v>
+        <v>-7.1</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.77</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1803,13 +1803,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>17.85</v>
+        <v>32.91</v>
       </c>
       <c r="D12" s="6">
-        <v>32.91</v>
+        <v>24.87</v>
       </c>
       <c r="E12" s="7">
-        <v>15.06</v>
+        <v>-8.039999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1820,13 +1820,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>2.93</v>
+        <v>0.66</v>
       </c>
       <c r="D13" s="6">
-        <v>0.66</v>
+        <v>2.14</v>
       </c>
       <c r="E13" s="8">
-        <v>-2.27</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1837,13 +1837,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.42</v>
+        <v>-4.55</v>
       </c>
       <c r="D14" s="6">
-        <v>-4.55</v>
+        <v>-1.15</v>
       </c>
       <c r="E14" s="8">
-        <v>-0.13</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1854,13 +1854,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-0.77</v>
+        <v>-0.47</v>
       </c>
       <c r="D15" s="6">
-        <v>-0.47</v>
+        <v>-2.77</v>
       </c>
       <c r="E15" s="7">
-        <v>0.3</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1871,13 +1871,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.61</v>
+        <v>-5.76</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.76</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-2.15</v>
+        <v>-6.47</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1888,13 +1888,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>-22.31</v>
+        <v>-10.52</v>
       </c>
       <c r="D17" s="6">
-        <v>-10.52</v>
+        <v>-15.41</v>
       </c>
       <c r="E17" s="7">
-        <v>11.79</v>
+        <v>-4.89</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1905,13 +1905,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>-7.78</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="D18" s="6">
-        <v>-9.880000000000001</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="E18" s="8">
-        <v>-2.1</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1922,13 +1922,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-29.58</v>
+        <v>-28.89</v>
       </c>
       <c r="D19" s="6">
-        <v>-28.89</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.6899999999999999</v>
+        <v>-28.3</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.59</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1939,13 +1939,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-4.39</v>
+        <v>-5.7</v>
       </c>
       <c r="D20" s="6">
-        <v>-5.7</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-1.31</v>
+        <v>-6.95</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1956,13 +1956,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-4.8</v>
+        <v>-5.34</v>
       </c>
       <c r="D21" s="6">
-        <v>-5.34</v>
+        <v>-4.7</v>
       </c>
       <c r="E21" s="8">
-        <v>-0.54</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1973,13 +1973,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-14.58</v>
+        <v>-1.36</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.36</v>
+        <v>-6.99</v>
       </c>
       <c r="E22" s="7">
-        <v>13.22</v>
+        <v>-5.63</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1990,13 +1990,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>20.15</v>
+        <v>20.93</v>
       </c>
       <c r="D23" s="6">
-        <v>20.93</v>
+        <v>19.13</v>
       </c>
       <c r="E23" s="7">
-        <v>0.78</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2007,13 +2007,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-15.82</v>
+        <v>-14.38</v>
       </c>
       <c r="D24" s="6">
-        <v>-14.38</v>
+        <v>-15.81</v>
       </c>
       <c r="E24" s="7">
-        <v>1.44</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2024,13 +2024,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>10.75</v>
+        <v>12.31</v>
       </c>
       <c r="D25" s="6">
-        <v>12.31</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="E25" s="7">
-        <v>1.56</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2041,13 +2041,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>16.15</v>
+        <v>14.78</v>
       </c>
       <c r="D26" s="6">
-        <v>14.78</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-1.37</v>
+        <v>10.68</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-4.1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2058,13 +2058,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-27.86</v>
+        <v>-17.17</v>
       </c>
       <c r="D27" s="6">
-        <v>-17.17</v>
+        <v>-22.09</v>
       </c>
       <c r="E27" s="7">
-        <v>10.69</v>
+        <v>-4.92</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2075,13 +2075,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-10.02</v>
+        <v>-8.9</v>
       </c>
       <c r="D28" s="6">
-        <v>-8.9</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="E28" s="7">
-        <v>1.12</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2092,13 +2092,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-30.76</v>
+        <v>-30.86</v>
       </c>
       <c r="D29" s="6">
-        <v>-30.86</v>
+        <v>-30.37</v>
       </c>
       <c r="E29" s="8">
-        <v>-0.1</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2109,13 +2109,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-19.31</v>
+        <v>-20.05</v>
       </c>
       <c r="D30" s="6">
-        <v>-20.05</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.74</v>
+        <v>-20.84</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2126,13 +2126,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-17.83</v>
+        <v>-19.96</v>
       </c>
       <c r="D31" s="6">
-        <v>-19.96</v>
+        <v>-19.32</v>
       </c>
       <c r="E31" s="8">
-        <v>-2.13</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2143,13 +2143,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>662.8</v>
+        <v>761</v>
       </c>
       <c r="D32" s="6">
-        <v>761</v>
+        <v>715.8</v>
       </c>
       <c r="E32" s="7">
-        <v>98.2</v>
+        <v>-45.2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2160,13 +2160,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>673.6</v>
+        <v>674.65</v>
       </c>
       <c r="D33" s="6">
-        <v>674.65</v>
+        <v>673.05</v>
       </c>
       <c r="E33" s="7">
-        <v>1.05</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2177,13 +2177,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>865</v>
+        <v>863.8</v>
       </c>
       <c r="D34" s="6">
-        <v>863.8</v>
+        <v>869.9</v>
       </c>
       <c r="E34" s="8">
-        <v>-1.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2194,13 +2194,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>1144</v>
+        <v>1133.4</v>
       </c>
       <c r="D35" s="6">
-        <v>1133.4</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-10.6</v>
+        <v>1122.3</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-11.1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2211,13 +2211,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>1906.6</v>
+        <v>1857.1</v>
       </c>
       <c r="D36" s="6">
-        <v>1857.1</v>
+        <v>1872</v>
       </c>
       <c r="E36" s="8">
-        <v>-49.5</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2228,13 +2228,13 @@
         <v>24</v>
       </c>
       <c r="C37" s="6">
-        <v>65.26000000000001</v>
+        <v>76.87</v>
       </c>
       <c r="D37" s="6">
-        <v>76.87</v>
+        <v>65.95</v>
       </c>
       <c r="E37" s="7">
-        <v>11.61</v>
+        <v>-10.92</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2245,13 +2245,13 @@
         <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>69.54000000000001</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="D38" s="6">
-        <v>69.73999999999999</v>
+        <v>69</v>
       </c>
       <c r="E38" s="7">
-        <v>0.2</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2262,13 +2262,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>23.32</v>
+        <v>23.13</v>
       </c>
       <c r="D39" s="6">
-        <v>23.13</v>
+        <v>26.56</v>
       </c>
       <c r="E39" s="8">
-        <v>-0.19</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2279,13 +2279,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>37.81</v>
+        <v>36.11</v>
       </c>
       <c r="D40" s="6">
-        <v>36.11</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.7</v>
+        <v>34.37</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2296,13 +2296,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>36.3</v>
+        <v>32.02</v>
       </c>
       <c r="D41" s="6">
-        <v>32.02</v>
+        <v>34.53</v>
       </c>
       <c r="E41" s="8">
-        <v>-4.28</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2313,13 +2313,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="6">
-        <v>3360.88</v>
+        <v>5429.86</v>
       </c>
       <c r="D42" s="6">
-        <v>5429.86</v>
+        <v>49.71</v>
       </c>
       <c r="E42" s="7">
-        <v>2068.98</v>
+        <v>-5380.15</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2330,13 +2330,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>-58.92</v>
+        <v>-68.92</v>
       </c>
       <c r="D43" s="6">
-        <v>-68.92</v>
+        <v>-59.56</v>
       </c>
       <c r="E43" s="8">
-        <v>-10</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2347,13 +2347,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-50.43</v>
+        <v>-50.25</v>
       </c>
       <c r="D44" s="6">
-        <v>-50.25</v>
+        <v>-76.14</v>
       </c>
       <c r="E44" s="7">
-        <v>0.18</v>
+        <v>-25.89</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2364,13 +2364,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>-54.38</v>
+        <v>-67.84999999999999</v>
       </c>
       <c r="D45" s="6">
-        <v>-67.84999999999999</v>
+        <v>-35.81</v>
       </c>
       <c r="E45" s="8">
-        <v>-13.47</v>
+        <v>32.04</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2381,13 +2381,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>-8.15</v>
+        <v>-3.75</v>
       </c>
       <c r="D46" s="6">
-        <v>-3.75</v>
-      </c>
-      <c r="E46" s="7">
-        <v>4.4</v>
+        <v>22.97</v>
+      </c>
+      <c r="E46" s="8">
+        <v>26.72</v>
       </c>
     </row>
   </sheetData>
@@ -2446,22 +2446,22 @@
         <v>42</v>
       </c>
       <c r="B2" s="11">
-        <v>57.92</v>
+        <v>65.92</v>
       </c>
       <c r="C2" s="12">
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>47.6</v>
+        <v>46.1</v>
       </c>
       <c r="E2" s="11">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F2" s="11">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="G2" s="11">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2586,19 +2586,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.1516</v>
+        <v>0.1521</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0326</v>
+        <v>0.0312</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0169</v>
+        <v>0.0185</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.04</v>
+        <v>-0.0408</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1079</v>
+        <v>-0.1171</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,34 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>76.9 → 66.0</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>76.9</t>
-  </si>
-  <si>
-    <t>66.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -245,7 +218,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,13 +252,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -299,7 +265,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,12 +287,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,22 +368,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -432,7 +391,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -931,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>715.8</v>
+        <v>699.8</v>
       </c>
       <c r="D2">
-        <v>-5.94</v>
+        <v>-2.24</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -943,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-22.09</v>
+        <v>-23.83</v>
       </c>
       <c r="H2">
-        <v>37.17</v>
+        <v>34.1</v>
       </c>
       <c r="I2">
-        <v>24.87</v>
+        <v>26.22</v>
       </c>
       <c r="J2">
-        <v>17.76</v>
+        <v>16.24</v>
       </c>
       <c r="K2">
-        <v>-6.99</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L2">
-        <v>-15.41</v>
+        <v>-19.24</v>
       </c>
       <c r="M2">
-        <v>-11.71</v>
+        <v>-12.1</v>
       </c>
       <c r="N2">
         <v>40</v>
       </c>
       <c r="O2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="P2">
-        <v>649.28</v>
+        <v>678.35</v>
       </c>
       <c r="Q2">
-        <v>602.35</v>
+        <v>607.64</v>
       </c>
       <c r="R2">
-        <v>635.74</v>
+        <v>635.54</v>
       </c>
       <c r="S2">
-        <v>673.26</v>
+        <v>672.17</v>
       </c>
       <c r="T2">
-        <v>6.32</v>
+        <v>4.11</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -997,34 +956,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>65.95</v>
+        <v>62.56</v>
       </c>
       <c r="Z2">
-        <v>9.15</v>
+        <v>14.01</v>
       </c>
       <c r="AA2">
-        <v>-10.9</v>
+        <v>-5.92</v>
       </c>
       <c r="AB2">
-        <v>20.05</v>
+        <v>19.93</v>
       </c>
       <c r="AC2">
-        <v>93.05</v>
+        <v>83.95</v>
       </c>
       <c r="AD2">
-        <v>72.45</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="AE2">
-        <v>38.38</v>
+        <v>37.67</v>
       </c>
       <c r="AF2">
-        <v>49.71</v>
+        <v>-77.78</v>
       </c>
       <c r="AG2">
-        <v>707.87</v>
+        <v>721.66</v>
       </c>
       <c r="AH2">
-        <v>496.83</v>
+        <v>493.62</v>
       </c>
       <c r="AI2">
         <v>626.27</v>
@@ -1033,7 +992,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>59.59</v>
+        <v>60.66</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1044,10 +1003,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>673.05</v>
+        <v>675.85</v>
       </c>
       <c r="D3">
-        <v>-0.24</v>
+        <v>0.42</v>
       </c>
       <c r="E3">
         <v>740.6</v>
@@ -1056,46 +1015,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-9.119999999999999</v>
+        <v>-8.74</v>
       </c>
       <c r="H3">
-        <v>31.2</v>
+        <v>31.74</v>
       </c>
       <c r="I3">
-        <v>2.14</v>
+        <v>4.81</v>
       </c>
       <c r="J3">
-        <v>21.87</v>
+        <v>20.22</v>
       </c>
       <c r="K3">
-        <v>19.13</v>
+        <v>18.39</v>
       </c>
       <c r="L3">
-        <v>-8.359999999999999</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="M3">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>666.33</v>
+        <v>672.53</v>
       </c>
       <c r="Q3">
-        <v>622.12</v>
+        <v>626.89</v>
       </c>
       <c r="R3">
-        <v>586.61</v>
+        <v>588.9400000000001</v>
       </c>
       <c r="S3">
-        <v>581.14</v>
+        <v>581.67</v>
       </c>
       <c r="T3">
-        <v>15.81</v>
+        <v>16.19</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1110,34 +1069,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>69</v>
+        <v>69.61</v>
       </c>
       <c r="Z3">
-        <v>27.17</v>
+        <v>27.37</v>
       </c>
       <c r="AA3">
-        <v>21.92</v>
+        <v>23.01</v>
       </c>
       <c r="AB3">
-        <v>5.25</v>
+        <v>4.36</v>
       </c>
       <c r="AC3">
-        <v>76.25</v>
+        <v>71.08</v>
       </c>
       <c r="AD3">
-        <v>72.34999999999999</v>
+        <v>74.05</v>
       </c>
       <c r="AE3">
-        <v>22.55</v>
+        <v>22.42</v>
       </c>
       <c r="AF3">
-        <v>-59.56</v>
+        <v>-79.56</v>
       </c>
       <c r="AG3">
-        <v>700.04</v>
+        <v>705.75</v>
       </c>
       <c r="AH3">
-        <v>544.21</v>
+        <v>548.03</v>
       </c>
       <c r="AI3">
         <v>606.01</v>
@@ -1146,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>56.2</v>
+        <v>55.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1157,10 +1116,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>869.9</v>
+        <v>865</v>
       </c>
       <c r="D4">
-        <v>0.71</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E4">
         <v>1249.31</v>
@@ -1169,46 +1128,46 @@
         <v>861.9</v>
       </c>
       <c r="G4">
-        <v>-30.37</v>
+        <v>-30.76</v>
       </c>
       <c r="H4">
-        <v>0.93</v>
+        <v>0.36</v>
       </c>
       <c r="I4">
-        <v>-1.15</v>
+        <v>-1.48</v>
       </c>
       <c r="J4">
-        <v>-4.41</v>
+        <v>-7.67</v>
       </c>
       <c r="K4">
-        <v>-15.81</v>
+        <v>-16.57</v>
       </c>
       <c r="L4">
-        <v>-28.3</v>
+        <v>-29.56</v>
       </c>
       <c r="M4">
-        <v>-4.08</v>
+        <v>-4.19</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P4">
-        <v>867.72</v>
+        <v>865.12</v>
       </c>
       <c r="Q4">
-        <v>907.92</v>
+        <v>904.46</v>
       </c>
       <c r="R4">
-        <v>998.15</v>
+        <v>993.91</v>
       </c>
       <c r="S4">
-        <v>1079.51</v>
+        <v>1078.16</v>
       </c>
       <c r="T4">
-        <v>-19.42</v>
+        <v>-19.77</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1223,34 +1182,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>26.56</v>
+        <v>25.57</v>
       </c>
       <c r="Z4">
-        <v>-37.14</v>
+        <v>-36.38</v>
       </c>
       <c r="AA4">
-        <v>-36.24</v>
+        <v>-36.27</v>
       </c>
       <c r="AB4">
-        <v>-0.89</v>
+        <v>-0.11</v>
       </c>
       <c r="AC4">
-        <v>23.72</v>
+        <v>31.93</v>
       </c>
       <c r="AD4">
-        <v>12.03</v>
+        <v>21.33</v>
       </c>
       <c r="AE4">
-        <v>20.34</v>
+        <v>19.86</v>
       </c>
       <c r="AF4">
-        <v>-76.14</v>
+        <v>-58.9</v>
       </c>
       <c r="AG4">
-        <v>964.2</v>
+        <v>962.41</v>
       </c>
       <c r="AH4">
-        <v>851.64</v>
+        <v>846.5</v>
       </c>
       <c r="AI4">
         <v>924.5700000000001</v>
@@ -1259,7 +1218,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>73.20999999999999</v>
+        <v>72.62</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1270,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1122.3</v>
+        <v>1126.8</v>
       </c>
       <c r="D5">
-        <v>-0.98</v>
+        <v>0.4</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1282,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-20.84</v>
+        <v>-20.52</v>
       </c>
       <c r="H5">
-        <v>49.84</v>
+        <v>50.44</v>
       </c>
       <c r="I5">
-        <v>-2.77</v>
+        <v>-3.15</v>
       </c>
       <c r="J5">
-        <v>-9.140000000000001</v>
+        <v>-10.26</v>
       </c>
       <c r="K5">
-        <v>8.130000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="L5">
-        <v>-6.95</v>
+        <v>-7.37</v>
       </c>
       <c r="M5">
-        <v>15.21</v>
+        <v>15.29</v>
       </c>
       <c r="N5">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="O5">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="P5">
-        <v>1144.6</v>
+        <v>1137.26</v>
       </c>
       <c r="Q5">
-        <v>1174.34</v>
+        <v>1168.05</v>
       </c>
       <c r="R5">
-        <v>1254.8</v>
+        <v>1253.14</v>
       </c>
       <c r="S5">
-        <v>1068.28</v>
+        <v>1068.8</v>
       </c>
       <c r="T5">
-        <v>5.06</v>
+        <v>5.43</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1336,43 +1295,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>34.37</v>
+        <v>35.73</v>
       </c>
       <c r="Z5">
-        <v>-32.52</v>
+        <v>-32.37</v>
       </c>
       <c r="AA5">
-        <v>-30.95</v>
+        <v>-31.23</v>
       </c>
       <c r="AB5">
-        <v>-1.57</v>
+        <v>-1.14</v>
       </c>
       <c r="AC5">
-        <v>53.06</v>
+        <v>49.48</v>
       </c>
       <c r="AD5">
-        <v>66.8</v>
+        <v>56.61</v>
       </c>
       <c r="AE5">
-        <v>38.27</v>
+        <v>37.6</v>
       </c>
       <c r="AF5">
-        <v>-35.81</v>
+        <v>-66.93000000000001</v>
       </c>
       <c r="AG5">
-        <v>1254.37</v>
+        <v>1241.74</v>
       </c>
       <c r="AH5">
-        <v>1094.3</v>
+        <v>1094.36</v>
       </c>
       <c r="AI5">
-        <v>1242.5</v>
+        <v>1228.34</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>27.49</v>
+        <v>27.86</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1383,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1872</v>
+        <v>1748</v>
       </c>
       <c r="D6">
-        <v>0.8</v>
+        <v>-6.62</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1395,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-19.32</v>
+        <v>-24.66</v>
       </c>
       <c r="H6">
-        <v>27.23</v>
+        <v>18.81</v>
       </c>
       <c r="I6">
-        <v>-6.47</v>
+        <v>-11.81</v>
       </c>
       <c r="J6">
-        <v>-7.1</v>
+        <v>-13.81</v>
       </c>
       <c r="K6">
-        <v>10.68</v>
+        <v>-1.03</v>
       </c>
       <c r="L6">
-        <v>-4.7</v>
+        <v>-10.35</v>
       </c>
       <c r="M6">
-        <v>3.12</v>
+        <v>1.71</v>
       </c>
       <c r="N6">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="O6">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="P6">
-        <v>1907.98</v>
+        <v>1861.18</v>
       </c>
       <c r="Q6">
-        <v>1991.55</v>
+        <v>1979.45</v>
       </c>
       <c r="R6">
-        <v>2044.23</v>
+        <v>2039.26</v>
       </c>
       <c r="S6">
-        <v>1862.67</v>
+        <v>1860.94</v>
       </c>
       <c r="T6">
-        <v>0.5</v>
+        <v>-6.07</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1446,46 +1405,46 @@
         <v>43</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>34.53</v>
+        <v>25.96</v>
       </c>
       <c r="Z6">
-        <v>-37.55</v>
+        <v>-50.86</v>
       </c>
       <c r="AA6">
-        <v>-19.74</v>
+        <v>-25.96</v>
       </c>
       <c r="AB6">
-        <v>-17.81</v>
+        <v>-24.9</v>
       </c>
       <c r="AC6">
         <v>3.79</v>
       </c>
       <c r="AD6">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AE6">
-        <v>58.44</v>
+        <v>65.19</v>
       </c>
       <c r="AF6">
-        <v>22.97</v>
+        <v>372.1</v>
       </c>
       <c r="AG6">
-        <v>2110.87</v>
+        <v>2141.03</v>
       </c>
       <c r="AH6">
-        <v>1872.23</v>
+        <v>1817.87</v>
       </c>
       <c r="AI6">
-        <v>2030.72</v>
+        <v>1982.58</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>26.12</v>
+        <v>31.42</v>
       </c>
     </row>
   </sheetData>
@@ -1626,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1646,47 +1605,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1694,700 +1618,734 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>17.76</v>
+      </c>
+      <c r="D7" s="5">
+        <v>16.24</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>21.87</v>
+      </c>
+      <c r="D8" s="5">
+        <v>20.22</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-4.41</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-7.67</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-10.26</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-7.1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-13.81</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-6.71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>24.87</v>
+      </c>
+      <c r="D12" s="5">
+        <v>26.22</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2.14</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4.81</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.15</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-1.48</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-2.77</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-3.15</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-6.47</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-11.81</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-5.34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-15.41</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-19.24</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-3.83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-28.3</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-29.56</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-6.95</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-7.37</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-4.7</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-10.35</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-5.65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-6.99</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>19.13</v>
+      </c>
+      <c r="D23" s="5">
+        <v>18.39</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-15.81</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-16.57</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="D25" s="5">
+        <v>5.05</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-3.08</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>10.68</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-1.03</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-11.71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-22.09</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-23.83</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-8.74</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-30.37</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-30.76</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-20.84</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-20.52</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-19.32</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-24.66</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-5.34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>715.8</v>
+      </c>
+      <c r="D32" s="5">
+        <v>699.8</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>673.05</v>
+      </c>
+      <c r="D33" s="5">
+        <v>675.85</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>869.9</v>
+      </c>
+      <c r="D34" s="5">
+        <v>865</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1122.3</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1126.8</v>
+      </c>
+      <c r="E35" s="7">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1872</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1748</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="5">
         <v>60</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="D37" s="5">
+        <v>79</v>
+      </c>
+      <c r="E37" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="5">
+        <v>79</v>
+      </c>
+      <c r="D38" s="5">
+        <v>60</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>23.7</v>
-      </c>
-      <c r="D7" s="6">
-        <v>17.76</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-5.94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>65.95</v>
+      </c>
+      <c r="D39" s="5">
+        <v>62.56</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-3.39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>23.47</v>
-      </c>
-      <c r="D8" s="6">
-        <v>21.87</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>69</v>
+      </c>
+      <c r="D40" s="5">
+        <v>69.61</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-15.73</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-4.41</v>
-      </c>
-      <c r="E9" s="8">
-        <v>11.32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>26.56</v>
+      </c>
+      <c r="D41" s="5">
+        <v>25.57</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-12.13</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-9.140000000000001</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="5">
+        <v>34.37</v>
+      </c>
+      <c r="D42" s="5">
+        <v>35.73</v>
+      </c>
+      <c r="E42" s="7">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-7.1</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>34.53</v>
+      </c>
+      <c r="D43" s="5">
+        <v>25.96</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-8.57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>32.91</v>
-      </c>
-      <c r="D12" s="6">
-        <v>24.87</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-8.039999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>49.71</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-77.78</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-127.49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.66</v>
-      </c>
-      <c r="D13" s="6">
-        <v>2.14</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-59.56</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-79.56</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-4.55</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-1.15</v>
-      </c>
-      <c r="E14" s="8">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-76.14</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-58.9</v>
+      </c>
+      <c r="E46" s="7">
+        <v>17.24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.47</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.77</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-35.81</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-66.93000000000001</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-31.12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-5.76</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-6.47</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-10.52</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-15.41</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-4.89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-9.880000000000001</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-28.89</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-28.3</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-5.7</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-6.95</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-4.7</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-1.36</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-6.99</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-5.63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>20.93</v>
-      </c>
-      <c r="D23" s="6">
-        <v>19.13</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-14.38</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-15.81</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>12.31</v>
-      </c>
-      <c r="D25" s="6">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-4.18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>14.78</v>
-      </c>
-      <c r="D26" s="6">
-        <v>10.68</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-4.1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-17.17</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-22.09</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-4.92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-8.9</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-9.119999999999999</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-30.86</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-30.37</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-20.05</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-20.84</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-19.96</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-19.32</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>761</v>
-      </c>
-      <c r="D32" s="6">
-        <v>715.8</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-45.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>674.65</v>
-      </c>
-      <c r="D33" s="6">
-        <v>673.05</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>863.8</v>
-      </c>
-      <c r="D34" s="6">
-        <v>869.9</v>
-      </c>
-      <c r="E34" s="8">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1133.4</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1122.3</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-11.1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1857.1</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1872</v>
-      </c>
-      <c r="E36" s="8">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>76.87</v>
-      </c>
-      <c r="D37" s="6">
-        <v>65.95</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-10.92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>69.73999999999999</v>
-      </c>
-      <c r="D38" s="6">
-        <v>69</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>23.13</v>
-      </c>
-      <c r="D39" s="6">
-        <v>26.56</v>
-      </c>
-      <c r="E39" s="8">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>36.11</v>
-      </c>
-      <c r="D40" s="6">
-        <v>34.37</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>32.02</v>
-      </c>
-      <c r="D41" s="6">
-        <v>34.53</v>
-      </c>
-      <c r="E41" s="8">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="B48" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="6">
-        <v>5429.86</v>
-      </c>
-      <c r="D42" s="6">
-        <v>49.71</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-5380.15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-68.92</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-59.56</v>
-      </c>
-      <c r="E43" s="8">
-        <v>9.359999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-50.25</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-76.14</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-25.89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-67.84999999999999</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-35.81</v>
-      </c>
-      <c r="E45" s="8">
-        <v>32.04</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-3.75</v>
-      </c>
-      <c r="D46" s="6">
+      <c r="C48" s="5">
         <v>22.97</v>
       </c>
-      <c r="E46" s="8">
-        <v>26.72</v>
+      <c r="D48" s="5">
+        <v>372.1</v>
+      </c>
+      <c r="E48" s="7">
+        <v>349.13</v>
       </c>
     </row>
   </sheetData>
@@ -2413,60 +2371,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
-        <v>65.92</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>46.1</v>
-      </c>
-      <c r="E2" s="11">
-        <v>80</v>
-      </c>
-      <c r="F2" s="11">
-        <v>3.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>3</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="10">
+        <v>43.9</v>
+      </c>
+      <c r="E2" s="10">
+        <v>60</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-0.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2568,37 +2526,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1521</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0312</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0185</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0408</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1171</v>
+      <c r="A2" s="13">
+        <v>0.1529</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0193</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0171</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.04190000000000001</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.121</v>
       </c>
     </row>
   </sheetData>
